--- a/المواد.xlsx
+++ b/المواد.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="1312">
   <si>
     <t/>
   </si>
@@ -654,12 +654,6 @@
     <t>PT kit 80T Agappe</t>
   </si>
   <si>
-    <t>32410089</t>
-  </si>
-  <si>
-    <t>03/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
     <t>32411054</t>
   </si>
   <si>
@@ -714,13 +708,13 @@
     <t>22/08/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>2025082952</t>
+    <t>2025082953</t>
   </si>
   <si>
     <t>28/08/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>2025082953</t>
+    <t>2025082954</t>
   </si>
   <si>
     <t>M-30R Rinse Reagent 3-part 20L Hematology Mindray</t>
@@ -954,186 +948,183 @@
     <t>HBA1c (R) kit Chemistry Mindray</t>
   </si>
   <si>
-    <t>044625001</t>
+    <t>044625009</t>
+  </si>
+  <si>
+    <t>044625010</t>
+  </si>
+  <si>
+    <t>07/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Specific Protein Calibrator Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>150725010</t>
+  </si>
+  <si>
+    <t>Semi-cuvettes (steel ball included)/350 كيوفيت</t>
+  </si>
+  <si>
+    <t>Mispa i2 Instrument agappe</t>
+  </si>
+  <si>
+    <t>CYBOW 3</t>
+  </si>
+  <si>
+    <t>EVA 251027</t>
+  </si>
+  <si>
+    <t>26/10/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CYBOW 10</t>
+  </si>
+  <si>
+    <t>241118</t>
+  </si>
+  <si>
+    <t>17/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>ichamber</t>
+  </si>
+  <si>
+    <t>IgM kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>144225003</t>
+  </si>
+  <si>
+    <t>17/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Lipids Calibrator Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>150425013</t>
+  </si>
+  <si>
+    <t>Aqappe 30ml Nano Detergent</t>
+  </si>
+  <si>
+    <t>32410142</t>
+  </si>
+  <si>
+    <t>31/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Afias-6 paper + i chroma 11</t>
+  </si>
+  <si>
+    <t>RF II cal - Mindray</t>
+  </si>
+  <si>
+    <t>158925010</t>
+  </si>
+  <si>
+    <t>13/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Capillary tube 15ul  25/tube</t>
+  </si>
+  <si>
+    <t>BC-10-3part Instrument Auto Hematology Mindray</t>
+  </si>
+  <si>
+    <t>Semi-auto BA-88A used</t>
+  </si>
+  <si>
+    <t>Creatinine kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>141125018</t>
+  </si>
+  <si>
+    <t>M-62 FN Dye Reagent 7-part 12mL Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025061351</t>
+  </si>
+  <si>
+    <t>12/06/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 FD Dye Reagent 7-part 12mL Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025073051</t>
+  </si>
+  <si>
+    <t>29/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 FR Dye Reagent 7-part 12mL Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025080652</t>
+  </si>
+  <si>
+    <t>05/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 LD Lyse Reagent 7-part 1L Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025050651</t>
+  </si>
+  <si>
+    <t>05/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 LH Lyse Reagent 7-part 1L Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025050951</t>
+  </si>
+  <si>
+    <t>08/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 DS Diluent Reagent 7-part 20L Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025051651</t>
+  </si>
+  <si>
+    <t>15/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HbA1c 5ul micro capillary tube</t>
+  </si>
+  <si>
+    <t>CP05TAA01</t>
+  </si>
+  <si>
+    <t>12/01/2028 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>حديدة فيتامين دي</t>
+  </si>
+  <si>
+    <t>FT4 kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025070111</t>
+  </si>
+  <si>
+    <t>14/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>T3 kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2024100113</t>
   </si>
   <si>
     <t>08/07/2026 12:00:00 ص</t>
   </si>
   <si>
-    <t>044625009</t>
-  </si>
-  <si>
-    <t>044625010</t>
-  </si>
-  <si>
-    <t>07/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Specific Protein Calibrator Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>150725010</t>
-  </si>
-  <si>
-    <t>Semi-cuvettes (steel ball included)/350 كيوفيت</t>
-  </si>
-  <si>
-    <t>Mispa i2 Instrument agappe</t>
-  </si>
-  <si>
-    <t>CYBOW 3</t>
-  </si>
-  <si>
-    <t>EVA 251027</t>
-  </si>
-  <si>
-    <t>26/10/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CYBOW 10</t>
-  </si>
-  <si>
-    <t>241118</t>
-  </si>
-  <si>
-    <t>17/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>ichamber</t>
-  </si>
-  <si>
-    <t>IgM kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>144225003</t>
-  </si>
-  <si>
-    <t>17/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Lipids Calibrator Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>150425013</t>
-  </si>
-  <si>
-    <t>Aqappe 30ml Nano Detergent</t>
-  </si>
-  <si>
-    <t>32410142</t>
-  </si>
-  <si>
-    <t>31/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Afias-6 paper + i chroma 11</t>
-  </si>
-  <si>
-    <t>RF II cal - Mindray</t>
-  </si>
-  <si>
-    <t>158925010</t>
-  </si>
-  <si>
-    <t>13/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Capillary tube 15ul  25/tube</t>
-  </si>
-  <si>
-    <t>BC-10-3part Instrument Auto Hematology Mindray</t>
-  </si>
-  <si>
-    <t>Semi-auto BA-88A used</t>
-  </si>
-  <si>
-    <t>Creatinine kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>141125018</t>
-  </si>
-  <si>
-    <t>M-62 FN Dye Reagent 7-part 12mL Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025061351</t>
-  </si>
-  <si>
-    <t>12/06/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 FD Dye Reagent 7-part 12mL Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025073051</t>
-  </si>
-  <si>
-    <t>29/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 FR Dye Reagent 7-part 12mL Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025080652</t>
-  </si>
-  <si>
-    <t>05/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 LD Lyse Reagent 7-part 1L Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025050651</t>
-  </si>
-  <si>
-    <t>05/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 LH Lyse Reagent 7-part 1L Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025050951</t>
-  </si>
-  <si>
-    <t>08/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 DS Diluent Reagent 7-part 20L Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025051651</t>
-  </si>
-  <si>
-    <t>15/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HbA1c 5ul micro capillary tube</t>
-  </si>
-  <si>
-    <t>CP05TAA01</t>
-  </si>
-  <si>
-    <t>12/01/2028 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>حديدة فيتامين دي</t>
-  </si>
-  <si>
-    <t>FT4 kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025070111</t>
-  </si>
-  <si>
-    <t>14/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>T3 kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2024100113</t>
-  </si>
-  <si>
     <t>T4 kit 2×50T Cl900i Mindray</t>
   </si>
   <si>
@@ -1530,9 +1521,6 @@
     <t>Substrate Solution Consumables Cl900i Mindray</t>
   </si>
   <si>
-    <t>02/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>2025060432</t>
   </si>
   <si>
@@ -1584,9 +1572,6 @@
     <t>Wash Buffer Consumables 1X10L Cl-900i Mindray</t>
   </si>
   <si>
-    <t>2025082151</t>
-  </si>
-  <si>
     <t>Immunoassay Cuvette Consumables 2*88 Cl900i Mindray</t>
   </si>
   <si>
@@ -1851,93 +1836,90 @@
     <t>14/02/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>Rubella Virus IgM kit 2×50T  with cal.Cl900i  Mindray</t>
+    <t>TOXO IgG kit 2×50T with cal.Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>13/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TOXO IgM kit 2×50T with cal.Cl900i Mindray</t>
   </si>
   <si>
     <t>2025050131</t>
   </si>
   <si>
+    <t>CMV IgM kit 2×50T with cal.Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>26/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CMV IgG kit  2×50T with cal.Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>07/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>ESR solution  Reagent 7-part 1L Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025082551</t>
+  </si>
+  <si>
+    <t>24/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>ZINC kit 20T Agappe</t>
+  </si>
+  <si>
+    <t>32412054</t>
+  </si>
+  <si>
+    <t>Iron kit 100T Agappe</t>
+  </si>
+  <si>
+    <t>32411254</t>
+  </si>
+  <si>
+    <t>32411296</t>
+  </si>
+  <si>
+    <t>IGRA -TB  Kit 8T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA TBVYA30G</t>
+  </si>
+  <si>
+    <t>free T4  Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA  F4VFA37G</t>
+  </si>
+  <si>
+    <t>Free T4 Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA F4VBD05</t>
+  </si>
+  <si>
+    <t>CA19-9 Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  CXVHB05EX</t>
+  </si>
+  <si>
+    <t>25/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Vitamin D  Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  VEVDB07E</t>
+  </si>
+  <si>
     <t>09/12/2026 12:00:00 ص</t>
   </si>
   <si>
-    <t>TOXO IgG kit 2×50T with cal.Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>13/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TOXO IgM kit 2×50T with cal.Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>CMV IgM kit 2×50T with cal.Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>26/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CMV IgG kit  2×50T with cal.Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>07/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>ESR solution  Reagent 7-part 1L Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025082551</t>
-  </si>
-  <si>
-    <t>24/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>ZINC kit 20T Agappe</t>
-  </si>
-  <si>
-    <t>32412054</t>
-  </si>
-  <si>
-    <t>Iron kit 100T Agappe</t>
-  </si>
-  <si>
-    <t>32411254</t>
-  </si>
-  <si>
-    <t>32411296</t>
-  </si>
-  <si>
-    <t>IGRA -TB  Kit 8T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA TBVYA30G</t>
-  </si>
-  <si>
-    <t>free T4  Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA  F4VFA37G</t>
-  </si>
-  <si>
-    <t>Free T4 Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA F4VBD05</t>
-  </si>
-  <si>
-    <t>CA19-9 Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  CXVHB05EX</t>
-  </si>
-  <si>
-    <t>25/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Vitamin D  Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  VEVDB07E</t>
-  </si>
-  <si>
     <t>EVA VEVCB01E</t>
   </si>
   <si>
@@ -2481,12 +2463,6 @@
     <t>12/04/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>Insulin Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA INVHB06</t>
-  </si>
-  <si>
     <t>CD-80 Detergent 2L</t>
   </si>
   <si>
@@ -3979,9 +3955,6 @@
   </si>
   <si>
     <t>EVA KMVHA06X</t>
-  </si>
-  <si>
-    <t>ح</t>
   </si>
 </sst>
 </file>
@@ -4021,7 +3994,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4044,29 +4017,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4347,7 +4308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C690"/>
+  <dimension ref="A1:C683"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="30" customWidth="1"/>
@@ -5378,13 +5339,13 @@
     </row>
     <row r="94" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5395,45 +5356,45 @@
         <v>216</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B96" s="1" t="s">
-        <v>218</v>
-      </c>
       <c r="C96" s="4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>224</v>
@@ -5444,18 +5405,18 @@
     </row>
     <row r="100" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>229</v>
@@ -5466,35 +5427,35 @@
     </row>
     <row r="102" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>231</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>233</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5505,89 +5466,89 @@
         <v>238</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B109" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B109" s="3" t="s">
-        <v>246</v>
-      </c>
       <c r="C109" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B111" s="3" t="s">
-        <v>246</v>
-      </c>
       <c r="C111" s="5" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>255</v>
+        <v>0</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>0</v>
@@ -5598,7 +5559,7 @@
     </row>
     <row r="114" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>0</v>
@@ -5609,40 +5570,40 @@
     </row>
     <row r="115" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B115" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>0</v>
+      <c r="C115" s="5" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>266</v>
@@ -5653,51 +5614,51 @@
     </row>
     <row r="119" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>272</v>
+        <v>155</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="C121" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>278</v>
@@ -5708,18 +5669,18 @@
     </row>
     <row r="124" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>283</v>
@@ -5730,57 +5691,57 @@
     </row>
     <row r="126" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>298</v>
+        <v>53</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5791,56 +5752,56 @@
         <v>300</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>53</v>
+        <v>301</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>309</v>
+        <v>84</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B135" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="C135" s="5" t="s">
         <v>311</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>313</v>
@@ -5851,35 +5812,35 @@
     </row>
     <row r="137" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>315</v>
+        <v>0</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>84</v>
+        <v>0</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C139" s="5" t="s">
         <v>318</v>
-      </c>
-      <c r="B139" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5887,21 +5848,21 @@
         <v>319</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>0</v>
+        <v>320</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>322</v>
+        <v>0</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5920,32 +5881,32 @@
         <v>326</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>0</v>
+        <v>327</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5975,15 +5936,15 @@
         <v>336</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>338</v>
+        <v>0</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>0</v>
@@ -5994,101 +5955,101 @@
     </row>
     <row r="150" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>0</v>
+        <v>339</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B151" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B151" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>0</v>
+      <c r="C151" s="5" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>138</v>
+        <v>345</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>361</v>
+        <v>0</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6107,62 +6068,62 @@
         <v>365</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>0</v>
+        <v>366</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>312</v>
+        <v>373</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>376</v>
+        <v>84</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B165" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>367</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>378</v>
@@ -6173,98 +6134,98 @@
         <v>379</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>84</v>
+        <v>380</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>395</v>
+        <v>363</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>399</v>
+        <v>48</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6272,7 +6233,7 @@
         <v>400</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C175" s="5" t="s">
         <v>401</v>
@@ -6280,13 +6241,13 @@
     </row>
     <row r="176" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B176" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="C176" s="4" t="s">
-        <v>48</v>
+        <v>401</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6294,32 +6255,32 @@
         <v>403</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>367</v>
+        <v>404</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>408</v>
+        <v>13</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6327,7 +6288,7 @@
         <v>409</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>411</v>
@@ -6338,29 +6299,29 @@
         <v>412</v>
       </c>
       <c r="B181" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C181" s="5" t="s">
         <v>413</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C183" s="5" t="s">
         <v>416</v>
@@ -6371,7 +6332,7 @@
         <v>417</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>418</v>
@@ -6379,46 +6340,46 @@
     </row>
     <row r="185" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>367</v>
+        <v>424</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>423</v>
+        <v>274</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>425</v>
+        <v>375</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6429,92 +6390,92 @@
         <v>427</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>276</v>
+        <v>428</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>378</v>
+        <v>431</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>434</v>
+        <v>253</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B193" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="B193" s="3" t="s">
-        <v>436</v>
-      </c>
       <c r="C193" s="5" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>255</v>
+        <v>321</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>325</v>
+        <v>445</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>444</v>
+        <v>387</v>
       </c>
       <c r="C197" s="5" t="s">
         <v>445</v>
@@ -6522,10 +6483,10 @@
     </row>
     <row r="198" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>447</v>
+        <v>387</v>
       </c>
       <c r="C198" s="4" t="s">
         <v>448</v>
@@ -6536,65 +6497,65 @@
         <v>449</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>453</v>
+        <v>363</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>398</v>
+        <v>457</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>460</v>
+        <v>433</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>461</v>
+        <v>334</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6602,7 +6563,7 @@
         <v>462</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="C205" s="5" t="s">
         <v>463</v>
@@ -6613,76 +6574,76 @@
         <v>464</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>338</v>
+        <v>465</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>390</v>
+        <v>424</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>436</v>
+        <v>392</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>427</v>
+        <v>471</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B210" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="C210" s="4" t="s">
-        <v>472</v>
+        <v>148</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>474</v>
+        <v>424</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>475</v>
+        <v>28</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C212" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6690,65 +6651,65 @@
         <v>477</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>427</v>
+        <v>387</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>28</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>398</v>
+        <v>480</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>390</v>
+        <v>483</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>481</v>
+        <v>287</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>483</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>486</v>
+        <v>433</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>289</v>
+        <v>487</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>486</v>
+        <v>395</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>488</v>
+        <v>103</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6756,7 +6717,7 @@
         <v>489</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="C219" s="5" t="s">
         <v>490</v>
@@ -6767,18 +6728,18 @@
         <v>491</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>398</v>
+        <v>480</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>103</v>
+        <v>492</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C221" s="5" t="s">
         <v>493</v>
@@ -6789,7 +6750,7 @@
         <v>494</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>495</v>
@@ -6797,24 +6758,24 @@
     </row>
     <row r="223" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>398</v>
+        <v>450</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>474</v>
+        <v>387</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>498</v>
+        <v>79</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6822,373 +6783,373 @@
         <v>499</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>453</v>
+        <v>500</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>395</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>398</v>
+        <v>507</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>133</v>
+        <v>508</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>398</v>
+        <v>510</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>508</v>
+        <v>79</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>510</v>
+        <v>79</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B233" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="B233" s="3" t="s">
+      <c r="C233" s="5" t="s">
         <v>514</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>514</v>
+        <v>236</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>79</v>
+        <v>138</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>238</v>
+        <v>524</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>138</v>
+        <v>31</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>524</v>
+        <v>40</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>526</v>
+        <v>259</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>92</v>
+        <v>531</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>31</v>
+        <v>533</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>261</v>
+        <v>537</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>537</v>
+        <v>424</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>20</v>
+        <v>545</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>541</v>
+        <v>369</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>544</v>
+        <v>471</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>427</v>
+        <v>550</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>550</v>
+        <v>98</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C252" s="4" t="s">
-        <v>551</v>
+        <v>0</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>474</v>
+        <v>392</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>555</v>
+        <v>424</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>556</v>
+        <v>155</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>557</v>
+        <v>392</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>98</v>
+        <v>558</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>0</v>
+        <v>363</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>560</v>
+        <v>82</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>427</v>
+        <v>563</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>155</v>
+        <v>458</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7196,21 +7157,21 @@
         <v>562</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>395</v>
+        <v>564</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>563</v>
+        <v>138</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="C260" s="4" t="s">
-        <v>565</v>
+        <v>138</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7218,10 +7179,10 @@
         <v>566</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>82</v>
+        <v>0</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7232,84 +7193,84 @@
         <v>568</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>461</v>
+        <v>20</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>138</v>
+        <v>571</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C265" s="3" t="s">
-        <v>0</v>
+        <v>575</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>575</v>
+        <v>392</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>576</v>
+        <v>101</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>578</v>
+        <v>433</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>92</v>
+        <v>581</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7317,175 +7278,175 @@
         <v>582</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>13</v>
+        <v>586</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>395</v>
+        <v>588</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>101</v>
+        <v>589</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>436</v>
+        <v>591</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>586</v>
+        <v>212</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>590</v>
-      </c>
-      <c r="C274" s="4" t="s">
-        <v>591</v>
+        <v>0</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>594</v>
+        <v>31</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>214</v>
+        <v>465</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C278" s="1" t="s">
-        <v>0</v>
+        <v>601</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>31</v>
+        <v>604</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>603</v>
+        <v>363</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>468</v>
+        <v>606</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>604</v>
+        <v>384</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>468</v>
+        <v>98</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>608</v>
+        <v>471</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>609</v>
+        <v>428</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C284" s="4" t="s">
         <v>610</v>
-      </c>
-      <c r="B284" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="C284" s="4" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>367</v>
+        <v>471</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7493,153 +7454,153 @@
         <v>613</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>387</v>
+        <v>614</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>98</v>
+        <v>177</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>474</v>
+        <v>619</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>431</v>
+        <v>197</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>398</v>
+        <v>620</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>617</v>
+        <v>171</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>474</v>
+        <v>622</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>619</v>
+        <v>267</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>398</v>
+        <v>624</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>617</v>
+        <v>17</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>622</v>
+        <v>111</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>177</v>
+        <v>629</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>197</v>
+        <v>632</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>171</v>
+        <v>274</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>269</v>
+        <v>636</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>17</v>
+        <v>405</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>111</v>
+        <v>265</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7647,1715 +7608,1715 @@
         <v>637</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>612</v>
+        <v>458</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>276</v>
+        <v>645</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>642</v>
+        <v>174</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>408</v>
+        <v>177</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>267</v>
+        <v>652</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>647</v>
+        <v>301</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>643</v>
+        <v>653</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>461</v>
+        <v>270</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>651</v>
+        <v>354</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>174</v>
+        <v>659</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>177</v>
+        <v>662</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>303</v>
+        <v>665</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>272</v>
+        <v>667</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>358</v>
+        <v>25</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>665</v>
+        <v>334</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>25</v>
+        <v>685</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>677</v>
+        <v>686</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>680</v>
+        <v>416</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>685</v>
+        <v>495</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>419</v>
+        <v>645</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>696</v>
+        <v>401</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>498</v>
+        <v>171</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>123</v>
+        <v>279</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>651</v>
+        <v>109</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>404</v>
+        <v>714</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>171</v>
+        <v>716</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>713</v>
+        <v>723</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>281</v>
+        <v>405</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>720</v>
+        <v>729</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>717</v>
+        <v>727</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>721</v>
+        <v>730</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>722</v>
+        <v>731</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>408</v>
+        <v>458</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>22</v>
+        <v>208</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>737</v>
+        <v>208</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>735</v>
+        <v>208</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>461</v>
+        <v>208</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>208</v>
+        <v>13</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>208</v>
+        <v>70</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>208</v>
+        <v>685</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>735</v>
+        <v>760</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>208</v>
+        <v>763</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>13</v>
+        <v>766</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>758</v>
+        <v>767</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>759</v>
+        <v>768</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>760</v>
+        <v>769</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>761</v>
+        <v>770</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>762</v>
+        <v>771</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>70</v>
+        <v>772</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>763</v>
+        <v>774</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>691</v>
+        <v>775</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>769</v>
+        <v>422</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>771</v>
+        <v>782</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>772</v>
+        <v>783</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>773</v>
+        <v>784</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>774</v>
+        <v>785</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>777</v>
+        <v>788</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>778</v>
+        <v>789</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>779</v>
+        <v>790</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>780</v>
+        <v>791</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>781</v>
+        <v>43</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>784</v>
+        <v>652</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>425</v>
+        <v>795</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>787</v>
+        <v>796</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>788</v>
+        <v>797</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>789</v>
+        <v>798</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>790</v>
+        <v>796</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="C371" s="5" t="s">
-        <v>795</v>
+        <v>0</v>
+      </c>
+      <c r="C371" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>796</v>
+        <v>802</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="C372" s="4" t="s">
-        <v>43</v>
+        <v>0</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="C373" s="5" t="s">
-        <v>658</v>
+        <v>0</v>
+      </c>
+      <c r="C373" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="C374" s="4" t="s">
-        <v>801</v>
+        <v>0</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C377" s="3" t="s">
-        <v>0</v>
+        <v>812</v>
+      </c>
+      <c r="C377" s="5" t="s">
+        <v>813</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>808</v>
+        <v>814</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C378" s="1" t="s">
-        <v>0</v>
+        <v>815</v>
+      </c>
+      <c r="C378" s="4" t="s">
+        <v>816</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C379" s="3" t="s">
-        <v>0</v>
+        <v>818</v>
+      </c>
+      <c r="C379" s="5" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C380" s="1" t="s">
-        <v>0</v>
+        <v>819</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>811</v>
+        <v>820</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>812</v>
+        <v>821</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>813</v>
+        <v>822</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>814</v>
+        <v>823</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>815</v>
+        <v>824</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>816</v>
+        <v>388</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>819</v>
+        <v>388</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="C384" s="4" t="s">
-        <v>556</v>
+        <v>0</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>822</v>
+        <v>827</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="C385" s="5" t="s">
-        <v>824</v>
+        <v>0</v>
+      </c>
+      <c r="C385" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>826</v>
-      </c>
-      <c r="C386" s="4" t="s">
-        <v>722</v>
+        <v>0</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>505</v>
+        <v>831</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="B389" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="C389" s="5" t="s">
         <v>831</v>
-      </c>
-      <c r="B389" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="C389" s="5" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="C390" s="4" t="s">
-        <v>391</v>
+        <v>0</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C391" s="3" t="s">
-        <v>0</v>
+        <v>836</v>
+      </c>
+      <c r="C391" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C392" s="1" t="s">
-        <v>0</v>
+        <v>838</v>
+      </c>
+      <c r="C392" s="4" t="s">
+        <v>839</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C393" s="3" t="s">
-        <v>0</v>
+        <v>841</v>
+      </c>
+      <c r="C393" s="5" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>839</v>
+        <v>600</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>840</v>
+        <v>845</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>839</v>
+        <v>25</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>839</v>
+        <v>20</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C397" s="3" t="s">
-        <v>0</v>
+        <v>848</v>
+      </c>
+      <c r="C397" s="5" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>38</v>
+        <v>849</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="B400" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="C400" s="4" t="s">
         <v>849</v>
-      </c>
-      <c r="C400" s="4" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>605</v>
+        <v>849</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>25</v>
+        <v>849</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>852</v>
+        <v>861</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>20</v>
+        <v>849</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>869</v>
+        <v>875</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>874</v>
+        <v>879</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>877</v>
+        <v>882</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>857</v>
+        <v>887</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>862</v>
+        <v>849</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>895</v>
+        <v>849</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>857</v>
+        <v>904</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>857</v>
+        <v>907</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>857</v>
+        <v>910</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>902</v>
+        <v>911</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>903</v>
+        <v>912</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>857</v>
+        <v>162</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>904</v>
+        <v>913</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>905</v>
+        <v>914</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>857</v>
+        <v>915</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>906</v>
+        <v>916</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>907</v>
+        <v>917</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>857</v>
+        <v>148</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>908</v>
+        <v>918</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>909</v>
+        <v>919</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>857</v>
+        <v>920</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>913</v>
+        <v>924</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>915</v>
+        <v>345</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>916</v>
+        <v>926</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>917</v>
+        <v>927</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>918</v>
+        <v>928</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>919</v>
+        <v>929</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>920</v>
+        <v>930</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>922</v>
+        <v>932</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>923</v>
+        <v>116</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>924</v>
+        <v>933</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>925</v>
+        <v>934</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>148</v>
+        <v>370</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
-        <v>926</v>
+        <v>935</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>927</v>
+        <v>936</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>928</v>
+        <v>937</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>929</v>
+        <v>938</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>930</v>
+        <v>939</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>931</v>
+        <v>940</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
-        <v>932</v>
+        <v>941</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>349</v>
+        <v>937</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>127</v>
+        <v>947</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>939</v>
+        <v>948</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>940</v>
+        <v>949</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>116</v>
+        <v>636</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>941</v>
+        <v>950</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>942</v>
+        <v>951</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>373</v>
+        <v>952</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>943</v>
+        <v>953</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>945</v>
+        <v>492</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>946</v>
+        <v>955</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>947</v>
+        <v>956</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>948</v>
+        <v>957</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>949</v>
+        <v>958</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>944</v>
+        <v>959</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>945</v>
+        <v>960</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>952</v>
+        <v>963</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>954</v>
+        <v>965</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>955</v>
+        <v>966</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>957</v>
+        <v>968</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>642</v>
+        <v>293</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>958</v>
+        <v>969</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>959</v>
-      </c>
-      <c r="C450" s="4" t="s">
-        <v>960</v>
+        <v>0</v>
+      </c>
+      <c r="C450" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>961</v>
+        <v>970</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>962</v>
-      </c>
-      <c r="C451" s="5" t="s">
-        <v>495</v>
+        <v>0</v>
+      </c>
+      <c r="C451" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="C452" s="4" t="s">
-        <v>965</v>
+        <v>0</v>
+      </c>
+      <c r="C452" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>967</v>
-      </c>
-      <c r="C453" s="5" t="s">
-        <v>968</v>
+        <v>0</v>
+      </c>
+      <c r="C453" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>970</v>
+        <v>912</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>971</v>
+        <v>162</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>973</v>
+        <v>912</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>974</v>
+        <v>162</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9363,114 +9324,114 @@
         <v>975</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>976</v>
+        <v>912</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>295</v>
+        <v>162</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C457" s="3" t="s">
-        <v>0</v>
+        <v>914</v>
+      </c>
+      <c r="C457" s="5" t="s">
+        <v>915</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C458" s="1" t="s">
-        <v>0</v>
+        <v>914</v>
+      </c>
+      <c r="C458" s="4" t="s">
+        <v>915</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C459" s="3" t="s">
-        <v>0</v>
+        <v>914</v>
+      </c>
+      <c r="C459" s="5" t="s">
+        <v>915</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C460" s="1" t="s">
-        <v>0</v>
+        <v>917</v>
+      </c>
+      <c r="C460" s="4" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B463" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="C463" s="5" t="s">
         <v>920</v>
-      </c>
-      <c r="C463" s="5" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>922</v>
@@ -9481,46 +9442,46 @@
     </row>
     <row r="467" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>148</v>
+        <v>923</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>148</v>
+        <v>923</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B469" s="3" t="s">
         <v>925</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>148</v>
+        <v>345</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="B470" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="B470" s="1" t="s">
-        <v>927</v>
-      </c>
       <c r="C470" s="4" t="s">
-        <v>928</v>
+        <v>604</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9550,10 +9511,10 @@
         <v>993</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9564,7 +9525,7 @@
         <v>930</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>931</v>
+        <v>127</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9575,7 +9536,7 @@
         <v>930</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>931</v>
+        <v>127</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9583,10 +9544,10 @@
         <v>996</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>349</v>
+        <v>127</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9594,252 +9555,252 @@
         <v>997</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>998</v>
+        <v>932</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>609</v>
+        <v>116</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>936</v>
+        <v>116</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>936</v>
+        <v>116</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>936</v>
+        <v>370</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>127</v>
+        <v>370</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>127</v>
+        <v>370</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>127</v>
+        <v>940</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B484" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="C484" s="4" t="s">
         <v>940</v>
-      </c>
-      <c r="C484" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B485" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="C485" s="5" t="s">
         <v>940</v>
-      </c>
-      <c r="C485" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>116</v>
+        <v>944</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>373</v>
+        <v>944</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>373</v>
+        <v>944</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>373</v>
+        <v>947</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B490" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="C490" s="4" t="s">
         <v>947</v>
-      </c>
-      <c r="C490" s="4" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B491" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="C491" s="5" t="s">
         <v>947</v>
-      </c>
-      <c r="C491" s="5" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>947</v>
+        <v>936</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>948</v>
+        <v>937</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>951</v>
+        <v>936</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>954</v>
+        <v>936</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>955</v>
+        <v>937</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>954</v>
+        <v>936</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>955</v>
+        <v>937</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B498" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="B498" s="1" t="s">
-        <v>954</v>
-      </c>
       <c r="C498" s="4" t="s">
-        <v>955</v>
+        <v>636</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B499" s="3" t="s">
         <v>1020</v>
       </c>
-      <c r="B499" s="3" t="s">
-        <v>944</v>
-      </c>
       <c r="C499" s="5" t="s">
-        <v>945</v>
+        <v>636</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9847,10 +9808,10 @@
         <v>1021</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>945</v>
+        <v>636</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9858,10 +9819,10 @@
         <v>1022</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>945</v>
+        <v>636</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9869,21 +9830,21 @@
         <v>1023</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>944</v>
+        <v>1024</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9891,10 +9852,10 @@
         <v>1025</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>944</v>
+        <v>949</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>945</v>
+        <v>636</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9902,54 +9863,54 @@
         <v>1026</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>1027</v>
+        <v>959</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>642</v>
+        <v>960</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1028</v>
+        <v>959</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>642</v>
+        <v>960</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>642</v>
+        <v>960</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B508" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="C508" s="4" t="s">
         <v>957</v>
-      </c>
-      <c r="C508" s="4" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>1032</v>
+        <v>956</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9957,98 +9918,98 @@
         <v>1031</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="C510" s="4" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B511" s="3" t="s">
         <v>1033</v>
       </c>
-      <c r="B511" s="3" t="s">
-        <v>957</v>
-      </c>
       <c r="C511" s="5" t="s">
-        <v>642</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B512" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C512" s="4" t="s">
         <v>1034</v>
-      </c>
-      <c r="B512" s="1" t="s">
-        <v>967</v>
-      </c>
-      <c r="C512" s="4" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>967</v>
+        <v>1033</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>968</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>967</v>
+        <v>954</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>968</v>
+        <v>492</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>964</v>
+        <v>954</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>965</v>
+        <v>492</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>964</v>
+        <v>954</v>
       </c>
       <c r="C516" s="4" t="s">
-        <v>965</v>
+        <v>492</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>964</v>
+        <v>1041</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>965</v>
+        <v>741</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B518" s="1" t="s">
         <v>1041</v>
       </c>
       <c r="C518" s="4" t="s">
-        <v>1042</v>
+        <v>741</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10059,7 +10020,7 @@
         <v>1041</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>1042</v>
+        <v>741</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10067,92 +10028,92 @@
         <v>1044</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>962</v>
-      </c>
-      <c r="C521" s="5" t="s">
-        <v>495</v>
+        <v>0</v>
+      </c>
+      <c r="C521" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>962</v>
+        <v>1049</v>
       </c>
       <c r="C522" s="4" t="s">
-        <v>495</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>962</v>
+        <v>1052</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>495</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>1048</v>
+        <v>1054</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1049</v>
+        <v>603</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>747</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>1050</v>
+        <v>1056</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>1049</v>
+        <v>603</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>747</v>
+        <v>334</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1049</v>
+        <v>1058</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>747</v>
+        <v>731</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="B528" s="1" t="s">
         <v>0</v>
@@ -10163,167 +10124,167 @@
     </row>
     <row r="529" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>1058</v>
+        <v>915</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1060</v>
+        <v>404</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>1061</v>
+        <v>155</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>608</v>
+        <v>1066</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>1063</v>
+        <v>287</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>608</v>
+        <v>1068</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>737</v>
+        <v>652</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="C534" s="4" t="s">
-        <v>1068</v>
+        <v>652</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C535" s="3" t="s">
-        <v>0</v>
+        <v>1073</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>1074</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>923</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>407</v>
+        <v>1078</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>155</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="C538" s="4" t="s">
-        <v>289</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="B539" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C539" s="5" t="s">
         <v>1076</v>
-      </c>
-      <c r="C539" s="5" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1078</v>
+        <v>1041</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>658</v>
+        <v>741</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
-        <v>1077</v>
+        <v>1082</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>1079</v>
+        <v>946</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>658</v>
+        <v>947</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1081</v>
+        <v>946</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>1082</v>
+        <v>947</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>1083</v>
+        <v>946</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>1084</v>
+        <v>947</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10331,142 +10292,142 @@
         <v>1085</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1086</v>
+        <v>946</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>1084</v>
+        <v>947</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B545" s="3" t="s">
         <v>1087</v>
       </c>
-      <c r="B545" s="3" t="s">
-        <v>1086</v>
-      </c>
       <c r="C545" s="5" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B546" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C546" s="4" t="s">
         <v>1088</v>
-      </c>
-      <c r="B546" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C546" s="4" t="s">
-        <v>1084</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>1049</v>
+        <v>1090</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>747</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B548" s="1" t="s">
         <v>1090</v>
       </c>
-      <c r="B548" s="1" t="s">
-        <v>954</v>
-      </c>
       <c r="C548" s="4" t="s">
-        <v>955</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>954</v>
+        <v>1094</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>955</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>954</v>
+        <v>1094</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>955</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>954</v>
+        <v>1094</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>955</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B552" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="B552" s="1" t="s">
+      <c r="C552" s="4" t="s">
         <v>1095</v>
-      </c>
-      <c r="C552" s="4" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>1096</v>
+        <v>581</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="C554" s="4" t="s">
-        <v>1096</v>
+        <v>581</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B555" s="3" t="s">
         <v>1100</v>
       </c>
-      <c r="B555" s="3" t="s">
-        <v>1098</v>
-      </c>
       <c r="C555" s="5" t="s">
-        <v>1096</v>
+        <v>581</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="C556" s="4" t="s">
-        <v>1103</v>
+        <v>581</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10474,87 +10435,87 @@
         <v>1104</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B558" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="B558" s="1" t="s">
-        <v>1102</v>
-      </c>
       <c r="C558" s="4" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B559" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C559" s="5" t="s">
         <v>1106</v>
-      </c>
-      <c r="B559" s="3" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C559" s="5" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>586</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="C562" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B563" s="3" t="s">
         <v>1111</v>
       </c>
-      <c r="B563" s="3" t="s">
-        <v>1108</v>
-      </c>
       <c r="C563" s="5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>1114</v>
+        <v>584</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10562,142 +10523,142 @@
         <v>1115</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B566" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="B566" s="1" t="s">
-        <v>1113</v>
-      </c>
       <c r="C566" s="4" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B567" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C567" s="5" t="s">
         <v>1117</v>
-      </c>
-      <c r="B567" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C567" s="5" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="C568" s="4" t="s">
-        <v>589</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="C569" s="5" t="s">
-        <v>589</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="C570" s="4" t="s">
-        <v>589</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B571" s="3" t="s">
         <v>1122</v>
       </c>
-      <c r="B571" s="3" t="s">
-        <v>1119</v>
-      </c>
       <c r="C571" s="5" t="s">
-        <v>589</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C572" s="4" t="s">
         <v>1123</v>
-      </c>
-      <c r="B572" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C572" s="4" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>1124</v>
+        <v>1033</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>1125</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1124</v>
+        <v>1033</v>
       </c>
       <c r="C574" s="4" t="s">
-        <v>1125</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>1124</v>
+        <v>1033</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>1125</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="576" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>1130</v>
+        <v>1033</v>
       </c>
       <c r="C576" s="4" t="s">
-        <v>1131</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="577" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B577" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="B577" s="3" t="s">
-        <v>1130</v>
-      </c>
       <c r="C577" s="5" t="s">
-        <v>1131</v>
+        <v>481</v>
       </c>
     </row>
     <row r="578" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10705,10 +10666,10 @@
         <v>1133</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C578" s="4" t="s">
-        <v>1131</v>
+        <v>481</v>
       </c>
     </row>
     <row r="579" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10716,10 +10677,10 @@
         <v>1134</v>
       </c>
       <c r="B579" s="3" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>1131</v>
+        <v>481</v>
       </c>
     </row>
     <row r="580" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10727,10 +10688,10 @@
         <v>1135</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>1041</v>
+        <v>1132</v>
       </c>
       <c r="C580" s="4" t="s">
-        <v>1042</v>
+        <v>481</v>
       </c>
     </row>
     <row r="581" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10738,10 +10699,10 @@
         <v>1136</v>
       </c>
       <c r="B581" s="3" t="s">
-        <v>1041</v>
+        <v>919</v>
       </c>
       <c r="C581" s="5" t="s">
-        <v>1042</v>
+        <v>920</v>
       </c>
     </row>
     <row r="582" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10749,10 +10710,10 @@
         <v>1137</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1041</v>
+        <v>919</v>
       </c>
       <c r="C582" s="4" t="s">
-        <v>1042</v>
+        <v>920</v>
       </c>
     </row>
     <row r="583" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10760,10 +10721,10 @@
         <v>1138</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>1041</v>
+        <v>919</v>
       </c>
       <c r="C583" s="5" t="s">
-        <v>1042</v>
+        <v>920</v>
       </c>
     </row>
     <row r="584" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10771,351 +10732,351 @@
         <v>1139</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>1140</v>
+        <v>919</v>
       </c>
       <c r="C584" s="4" t="s">
-        <v>484</v>
+        <v>920</v>
       </c>
     </row>
     <row r="585" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>1140</v>
+        <v>922</v>
       </c>
       <c r="C585" s="5" t="s">
-        <v>484</v>
+        <v>923</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>1140</v>
+        <v>922</v>
       </c>
       <c r="C586" s="4" t="s">
-        <v>484</v>
+        <v>923</v>
       </c>
     </row>
     <row r="587" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A587" s="3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>1140</v>
+        <v>922</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>484</v>
+        <v>923</v>
       </c>
     </row>
     <row r="588" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="C588" s="4" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
     </row>
     <row r="589" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>927</v>
+        <v>1105</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>928</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="590" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>927</v>
+        <v>1105</v>
       </c>
       <c r="C590" s="4" t="s">
-        <v>928</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="591" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>927</v>
+        <v>1105</v>
       </c>
       <c r="C591" s="5" t="s">
-        <v>928</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="C592" s="4" t="s">
-        <v>931</v>
+        <v>148</v>
       </c>
     </row>
     <row r="593" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>931</v>
+        <v>148</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="C594" s="4" t="s">
-        <v>931</v>
+        <v>148</v>
       </c>
     </row>
     <row r="595" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A595" s="3" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>930</v>
+        <v>917</v>
       </c>
       <c r="C595" s="5" t="s">
-        <v>931</v>
+        <v>148</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B596" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="B596" s="1" t="s">
-        <v>1113</v>
-      </c>
       <c r="C596" s="4" t="s">
-        <v>1114</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="597" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A597" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B597" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C597" s="5" t="s">
         <v>1153</v>
-      </c>
-      <c r="B597" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C597" s="5" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>1113</v>
+        <v>1152</v>
       </c>
       <c r="C598" s="4" t="s">
-        <v>1114</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A599" s="3" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B599" s="3" t="s">
-        <v>925</v>
+        <v>1152</v>
       </c>
       <c r="C599" s="5" t="s">
-        <v>148</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="600" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>925</v>
+        <v>1100</v>
       </c>
       <c r="C600" s="4" t="s">
-        <v>148</v>
+        <v>581</v>
       </c>
     </row>
     <row r="601" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A601" s="3" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>925</v>
+        <v>1100</v>
       </c>
       <c r="C601" s="5" t="s">
-        <v>148</v>
+        <v>581</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>925</v>
+        <v>1100</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>148</v>
+        <v>581</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A603" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="604" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C604" s="4" t="s">
         <v>1162</v>
-      </c>
-      <c r="B604" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C604" s="4" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="605" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A605" s="3" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C605" s="5" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="606" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B606" s="1" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C606" s="4" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="607" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A607" s="3" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>1108</v>
+        <v>1132</v>
       </c>
       <c r="C607" s="5" t="s">
-        <v>586</v>
+        <v>481</v>
       </c>
     </row>
     <row r="608" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>1108</v>
+        <v>1132</v>
       </c>
       <c r="C608" s="4" t="s">
-        <v>586</v>
+        <v>481</v>
       </c>
     </row>
     <row r="609" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A609" s="3" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>1108</v>
+        <v>1132</v>
       </c>
       <c r="C609" s="5" t="s">
-        <v>586</v>
+        <v>481</v>
       </c>
     </row>
     <row r="610" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B610" s="1" t="s">
-        <v>1169</v>
+        <v>1132</v>
       </c>
       <c r="C610" s="4" t="s">
-        <v>1170</v>
+        <v>481</v>
       </c>
     </row>
     <row r="611" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A611" s="3" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>1169</v>
+        <v>1132</v>
       </c>
       <c r="C611" s="5" t="s">
-        <v>1170</v>
+        <v>481</v>
       </c>
     </row>
     <row r="612" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>1169</v>
+        <v>1132</v>
       </c>
       <c r="C612" s="4" t="s">
-        <v>1170</v>
+        <v>481</v>
       </c>
     </row>
     <row r="613" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A613" s="3" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>1169</v>
+        <v>1132</v>
       </c>
       <c r="C613" s="5" t="s">
-        <v>1170</v>
+        <v>481</v>
       </c>
     </row>
     <row r="614" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B614" s="1" t="s">
-        <v>1140</v>
+        <v>1132</v>
       </c>
       <c r="C614" s="4" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="615" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A615" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B615" s="3" t="s">
         <v>1175</v>
       </c>
-      <c r="B615" s="3" t="s">
-        <v>1140</v>
-      </c>
       <c r="C615" s="5" t="s">
-        <v>484</v>
+        <v>795</v>
       </c>
     </row>
     <row r="616" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -11123,10 +11084,10 @@
         <v>1176</v>
       </c>
       <c r="B616" s="1" t="s">
-        <v>1140</v>
+        <v>1175</v>
       </c>
       <c r="C616" s="4" t="s">
-        <v>484</v>
+        <v>795</v>
       </c>
     </row>
     <row r="617" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -11134,10 +11095,10 @@
         <v>1177</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>1140</v>
+        <v>1175</v>
       </c>
       <c r="C617" s="5" t="s">
-        <v>484</v>
+        <v>795</v>
       </c>
     </row>
     <row r="618" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -11145,10 +11106,10 @@
         <v>1178</v>
       </c>
       <c r="B618" s="1" t="s">
-        <v>1140</v>
+        <v>1175</v>
       </c>
       <c r="C618" s="4" t="s">
-        <v>484</v>
+        <v>795</v>
       </c>
     </row>
     <row r="619" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -11156,282 +11117,282 @@
         <v>1179</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>1140</v>
+        <v>1180</v>
       </c>
       <c r="C619" s="5" t="s">
-        <v>484</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="620" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B620" s="1" t="s">
-        <v>1140</v>
+        <v>603</v>
       </c>
       <c r="C620" s="4" t="s">
-        <v>484</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="621" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A621" s="3" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>1140</v>
+        <v>1100</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>484</v>
+        <v>581</v>
       </c>
     </row>
     <row r="622" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="B622" s="1" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
       <c r="C622" s="4" t="s">
-        <v>801</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="623" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A623" s="3" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C623" s="5" t="s">
-        <v>801</v>
+        <v>0</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="624" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C624" s="4" t="s">
-        <v>801</v>
+        <v>0</v>
+      </c>
+      <c r="C624" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="625" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A625" s="3" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>801</v>
+        <v>130</v>
       </c>
     </row>
     <row r="626" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="B626" s="1" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="C626" s="4" t="s">
-        <v>1189</v>
+        <v>831</v>
       </c>
     </row>
     <row r="627" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A627" s="3" t="s">
-        <v>1190</v>
+        <v>1194</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>608</v>
+        <v>1195</v>
       </c>
       <c r="C627" s="5" t="s">
-        <v>1191</v>
+        <v>95</v>
       </c>
     </row>
     <row r="628" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
-        <v>1192</v>
+        <v>1196</v>
       </c>
       <c r="B628" s="1" t="s">
-        <v>1108</v>
+        <v>1197</v>
       </c>
       <c r="C628" s="4" t="s">
-        <v>586</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="629" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A629" s="3" t="s">
-        <v>1193</v>
+        <v>1199</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>1194</v>
+        <v>1200</v>
       </c>
       <c r="C629" s="5" t="s">
-        <v>1195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="630" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="B630" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C630" s="1" t="s">
-        <v>0</v>
+        <v>1202</v>
+      </c>
+      <c r="C630" s="4" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="631" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A631" s="3" t="s">
-        <v>1197</v>
+        <v>1203</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C631" s="3" t="s">
-        <v>0</v>
+        <v>1204</v>
+      </c>
+      <c r="C631" s="5" t="s">
+        <v>1205</v>
       </c>
     </row>
     <row r="632" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
       <c r="C632" s="4" t="s">
-        <v>130</v>
+        <v>390</v>
       </c>
     </row>
     <row r="633" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A633" s="3" t="s">
-        <v>1200</v>
+        <v>1206</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
       <c r="C633" s="5" t="s">
-        <v>839</v>
+        <v>706</v>
       </c>
     </row>
     <row r="634" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="C634" s="4" t="s">
-        <v>95</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A635" s="3" t="s">
-        <v>1204</v>
+        <v>1212</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>1205</v>
+        <v>1213</v>
       </c>
       <c r="C635" s="5" t="s">
-        <v>1206</v>
+        <v>963</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="C636" s="4" t="s">
-        <v>184</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="637" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A637" s="3" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>1210</v>
+        <v>1217</v>
       </c>
       <c r="C637" s="5" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
     </row>
     <row r="638" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
-        <v>1211</v>
+        <v>1218</v>
       </c>
       <c r="B638" s="1" t="s">
-        <v>1212</v>
+        <v>1219</v>
       </c>
       <c r="C638" s="4" t="s">
-        <v>1213</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="639" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A639" s="3" t="s">
-        <v>1214</v>
+        <v>1221</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>1215</v>
+        <v>1222</v>
       </c>
       <c r="C639" s="5" t="s">
-        <v>393</v>
+        <v>25</v>
       </c>
     </row>
     <row r="640" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="s">
-        <v>1214</v>
+        <v>1223</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>1216</v>
+        <v>1224</v>
       </c>
       <c r="C640" s="4" t="s">
-        <v>712</v>
+        <v>25</v>
       </c>
     </row>
     <row r="641" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A641" s="3" t="s">
-        <v>1217</v>
+        <v>1225</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>1218</v>
+        <v>1226</v>
       </c>
       <c r="C641" s="5" t="s">
-        <v>1219</v>
+        <v>279</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
-        <v>1220</v>
+        <v>1227</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>1221</v>
+        <v>1228</v>
       </c>
       <c r="C642" s="4" t="s">
-        <v>971</v>
+        <v>25</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A643" s="3" t="s">
-        <v>1222</v>
+        <v>1229</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>1223</v>
+        <v>1230</v>
       </c>
       <c r="C643" s="5" t="s">
-        <v>1125</v>
+        <v>25</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="s">
-        <v>1224</v>
+        <v>1231</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>1225</v>
+        <v>1232</v>
       </c>
       <c r="C644" s="4" t="s">
         <v>25</v>
@@ -11439,54 +11400,54 @@
     </row>
     <row r="645" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A645" s="3" t="s">
-        <v>1226</v>
+        <v>1233</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>1227</v>
+        <v>1234</v>
       </c>
       <c r="C645" s="5" t="s">
-        <v>1228</v>
+        <v>25</v>
       </c>
     </row>
     <row r="646" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="s">
-        <v>1229</v>
+        <v>1235</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1230</v>
+        <v>1236</v>
       </c>
       <c r="C646" s="4" t="s">
-        <v>25</v>
+        <v>390</v>
       </c>
     </row>
     <row r="647" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A647" s="3" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="C647" s="5" t="s">
-        <v>25</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="648" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A648" s="1" t="s">
-        <v>1233</v>
+        <v>1240</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>1234</v>
+        <v>1241</v>
       </c>
       <c r="C648" s="4" t="s">
-        <v>281</v>
+        <v>25</v>
       </c>
     </row>
     <row r="649" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A649" s="3" t="s">
-        <v>1235</v>
+        <v>1242</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>1236</v>
+        <v>1243</v>
       </c>
       <c r="C649" s="5" t="s">
         <v>25</v>
@@ -11494,21 +11455,21 @@
     </row>
     <row r="650" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A650" s="1" t="s">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>1238</v>
+        <v>1245</v>
       </c>
       <c r="C650" s="4" t="s">
-        <v>25</v>
+        <v>551</v>
       </c>
     </row>
     <row r="651" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A651" s="3" t="s">
-        <v>1239</v>
+        <v>1246</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>1240</v>
+        <v>1247</v>
       </c>
       <c r="C651" s="5" t="s">
         <v>25</v>
@@ -11516,10 +11477,10 @@
     </row>
     <row r="652" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A652" s="1" t="s">
-        <v>1241</v>
+        <v>1248</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>1242</v>
+        <v>1249</v>
       </c>
       <c r="C652" s="4" t="s">
         <v>25</v>
@@ -11527,32 +11488,32 @@
     </row>
     <row r="653" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A653" s="3" t="s">
-        <v>1243</v>
+        <v>1250</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="C653" s="5" t="s">
-        <v>393</v>
+        <v>25</v>
       </c>
     </row>
     <row r="654" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A654" s="1" t="s">
-        <v>1245</v>
+        <v>1252</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>1246</v>
+        <v>1253</v>
       </c>
       <c r="C654" s="4" t="s">
-        <v>1247</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="655" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A655" s="3" t="s">
-        <v>1248</v>
+        <v>1255</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>1249</v>
+        <v>1256</v>
       </c>
       <c r="C655" s="5" t="s">
         <v>25</v>
@@ -11560,10 +11521,10 @@
     </row>
     <row r="656" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A656" s="1" t="s">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B656" s="1" t="s">
-        <v>1251</v>
+        <v>1258</v>
       </c>
       <c r="C656" s="4" t="s">
         <v>25</v>
@@ -11571,21 +11532,21 @@
     </row>
     <row r="657" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A657" s="3" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>1253</v>
+        <v>1260</v>
       </c>
       <c r="C657" s="5" t="s">
-        <v>556</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="658" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A658" s="1" t="s">
-        <v>1254</v>
+        <v>1262</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1255</v>
+        <v>1263</v>
       </c>
       <c r="C658" s="4" t="s">
         <v>25</v>
@@ -11593,10 +11554,10 @@
     </row>
     <row r="659" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A659" s="3" t="s">
-        <v>1256</v>
+        <v>1264</v>
       </c>
       <c r="B659" s="3" t="s">
-        <v>1257</v>
+        <v>1265</v>
       </c>
       <c r="C659" s="5" t="s">
         <v>25</v>
@@ -11604,10 +11565,10 @@
     </row>
     <row r="660" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A660" s="1" t="s">
-        <v>1258</v>
+        <v>1266</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1259</v>
+        <v>1267</v>
       </c>
       <c r="C660" s="4" t="s">
         <v>25</v>
@@ -11615,65 +11576,65 @@
     </row>
     <row r="661" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A661" s="3" t="s">
-        <v>1260</v>
+        <v>1268</v>
       </c>
       <c r="B661" s="3" t="s">
-        <v>1261</v>
+        <v>1269</v>
       </c>
       <c r="C661" s="5" t="s">
-        <v>1262</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="662" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A662" s="1" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="C662" s="4" t="s">
-        <v>25</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="663" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A663" s="3" t="s">
-        <v>1265</v>
+        <v>1274</v>
       </c>
       <c r="B663" s="3" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="C663" s="5" t="s">
-        <v>25</v>
+        <v>551</v>
       </c>
     </row>
     <row r="664" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="s">
-        <v>1267</v>
+        <v>1276</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1268</v>
+        <v>1277</v>
       </c>
       <c r="C664" s="4" t="s">
-        <v>1269</v>
+        <v>311</v>
       </c>
     </row>
     <row r="665" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A665" s="3" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="B665" s="3" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="C665" s="5" t="s">
-        <v>25</v>
+        <v>396</v>
       </c>
     </row>
     <row r="666" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="s">
-        <v>1272</v>
+        <v>1280</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1273</v>
+        <v>1281</v>
       </c>
       <c r="C666" s="4" t="s">
         <v>25</v>
@@ -11681,10 +11642,10 @@
     </row>
     <row r="667" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A667" s="3" t="s">
-        <v>1274</v>
+        <v>1282</v>
       </c>
       <c r="B667" s="3" t="s">
-        <v>1275</v>
+        <v>1283</v>
       </c>
       <c r="C667" s="5" t="s">
         <v>25</v>
@@ -11692,231 +11653,150 @@
     </row>
     <row r="668" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A668" s="1" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="C668" s="4" t="s">
-        <v>1278</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="669" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A669" s="3" t="s">
-        <v>1279</v>
+        <v>1287</v>
       </c>
       <c r="B669" s="3" t="s">
-        <v>1280</v>
+        <v>1288</v>
       </c>
       <c r="C669" s="5" t="s">
-        <v>1281</v>
+        <v>25</v>
       </c>
     </row>
     <row r="670" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="s">
-        <v>1282</v>
+        <v>1289</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1283</v>
+        <v>1290</v>
       </c>
       <c r="C670" s="4" t="s">
-        <v>556</v>
+        <v>25</v>
       </c>
     </row>
     <row r="671" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A671" s="3" t="s">
-        <v>1284</v>
+        <v>1291</v>
       </c>
       <c r="B671" s="3" t="s">
-        <v>1285</v>
+        <v>1292</v>
       </c>
       <c r="C671" s="5" t="s">
-        <v>315</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="672" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A672" s="1" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="C672" s="4" t="s">
-        <v>399</v>
+        <v>95</v>
       </c>
     </row>
     <row r="673" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A673" s="3" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="B673" s="3" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="C673" s="5" t="s">
-        <v>25</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="674" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="s">
-        <v>1290</v>
+        <v>1298</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1291</v>
+        <v>1297</v>
       </c>
       <c r="C674" s="4" t="s">
-        <v>25</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="675" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A675" s="3" t="s">
-        <v>1292</v>
+        <v>1299</v>
       </c>
       <c r="B675" s="3" t="s">
-        <v>1293</v>
+        <v>1300</v>
       </c>
       <c r="C675" s="5" t="s">
-        <v>1294</v>
+        <v>197</v>
       </c>
     </row>
     <row r="676" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="s">
-        <v>1295</v>
+        <v>1301</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1296</v>
+        <v>1302</v>
       </c>
       <c r="C676" s="4" t="s">
-        <v>25</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="677" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A677" s="3" t="s">
-        <v>1297</v>
+        <v>1304</v>
       </c>
       <c r="B677" s="3" t="s">
-        <v>1298</v>
+        <v>1305</v>
       </c>
       <c r="C677" s="5" t="s">
-        <v>25</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="678" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A678" s="1" t="s">
-        <v>1299</v>
+        <v>1307</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>1300</v>
+        <v>1308</v>
       </c>
       <c r="C678" s="4" t="s">
-        <v>1301</v>
+        <v>786</v>
       </c>
     </row>
     <row r="679" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A679" s="3" t="s">
-        <v>1302</v>
+        <v>1309</v>
       </c>
       <c r="B679" s="3" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C679" s="5" t="s">
-        <v>95</v>
+        <v>0</v>
+      </c>
+      <c r="C679" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="680" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A680" s="1" t="s">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="C680" s="4" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="681" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A681" s="3" t="s">
-        <v>1306</v>
-      </c>
-      <c r="B681" s="3" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C681" s="5" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="682" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A682" s="1" t="s">
-        <v>1307</v>
-      </c>
-      <c r="B682" s="1" t="s">
-        <v>1308</v>
-      </c>
-      <c r="C682" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="683" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A683" s="3" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B683" s="3" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C683" s="5" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="684" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A684" s="1" t="s">
-        <v>1312</v>
-      </c>
-      <c r="B684" s="1" t="s">
-        <v>1313</v>
-      </c>
-      <c r="C684" s="4" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="685" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A685" s="3" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B685" s="3" t="s">
-        <v>1316</v>
-      </c>
-      <c r="C685" s="5" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="686" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A686" s="1" t="s">
-        <v>1317</v>
-      </c>
-      <c r="B686" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C686" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="687" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A687" s="3" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B687" s="3" t="s">
-        <v>1319</v>
-      </c>
-      <c r="C687" s="5" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="688" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A688" s="6" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="689" ht="13.8" x14ac:dyDescent="0.3"/>
-    <row r="690" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+        <v>551</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="682" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="683" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/المواد.xlsx
+++ b/المواد.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1938" uniqueCount="1256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="1272">
   <si>
     <t/>
   </si>
@@ -120,6 +120,12 @@
     <t>FERRITIN Kit 24T Afias Boditech</t>
   </si>
   <si>
+    <t>EVA  FRVHA72X</t>
+  </si>
+  <si>
+    <t>12/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA FRVGA71X</t>
   </si>
   <si>
@@ -222,15 +228,18 @@
     <t>22/12/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA  TSVEA89X</t>
+  </si>
+  <si>
+    <t>29/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA TSVDA84X</t>
   </si>
   <si>
     <t>21/12/2026 12:00:00 ص</t>
   </si>
   <si>
-    <t>EVA TSVDA85X</t>
-  </si>
-  <si>
     <t>EVA TSVDA86X</t>
   </si>
   <si>
@@ -483,6 +492,9 @@
     <t>30/06/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>32410269</t>
+  </si>
+  <si>
     <t>Calcium kit 100T Agappe</t>
   </si>
   <si>
@@ -717,6 +729,12 @@
     <t>13/08/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>2025112154</t>
+  </si>
+  <si>
+    <t>20/11/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>Cuvette BS120 Chemistry Mindray</t>
   </si>
   <si>
@@ -867,6 +885,12 @@
     <t>196125097</t>
   </si>
   <si>
+    <t>196125228</t>
+  </si>
+  <si>
+    <t>16/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>Multi Sera Calibrator Chemistry Mindray</t>
   </si>
   <si>
@@ -912,6 +936,12 @@
     <t>150725010</t>
   </si>
   <si>
+    <t>150725011</t>
+  </si>
+  <si>
+    <t>27/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>Semi-cuvettes (steel ball included)/350 كيوفيت</t>
   </si>
   <si>
@@ -1026,6 +1056,12 @@
     <t>04/08/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>2025081151</t>
+  </si>
+  <si>
+    <t>10/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>M-62 LH Lyse Reagent 7-part 1L Hematology Mindray</t>
   </si>
   <si>
@@ -1044,6 +1080,12 @@
     <t>15/05/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>2025082653</t>
+  </si>
+  <si>
+    <t>25/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>HbA1c 5ul micro capillary tube</t>
   </si>
   <si>
@@ -1056,45 +1098,39 @@
     <t>حديدة فيتامين دي</t>
   </si>
   <si>
-    <t>FT4 kit 2×50T Cl900i Mindray</t>
+    <t>T3 kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2024100113</t>
+  </si>
+  <si>
+    <t>08/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>T4 kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025010111</t>
+  </si>
+  <si>
+    <t>08/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TSH  kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025060151</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Tg kit 2×50T CL900i Mindray</t>
   </si>
   <si>
     <t>2025070111</t>
   </si>
   <si>
-    <t>14/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>T3 kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2024100113</t>
-  </si>
-  <si>
-    <t>08/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>T4 kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025010111</t>
-  </si>
-  <si>
-    <t>08/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TSH  kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025060151</t>
-  </si>
-  <si>
-    <t>18/09/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Tg kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
     <t>09/03/2027 12:00:00 ص</t>
   </si>
   <si>
@@ -1206,9 +1242,6 @@
     <t>PROG kit 2×50T Cl900i Mindray</t>
   </si>
   <si>
-    <t>27/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>TESTO kit 2×50T Cl900i Mindray</t>
   </si>
   <si>
@@ -1236,141 +1269,138 @@
     <t>DHEA-S kit 2×50T Cl900i Mindray</t>
   </si>
   <si>
+    <t>2025080111</t>
+  </si>
+  <si>
+    <t>13/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Cortisol kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>TnI kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025080121</t>
+  </si>
+  <si>
+    <t>14/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>PTH kit 2×50T Cl900i  Mindray</t>
+  </si>
+  <si>
+    <t>2025040112</t>
+  </si>
+  <si>
+    <t>19/05/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>VB12 kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>Folate kit 50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025100121</t>
+  </si>
+  <si>
+    <t>10/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HBs Ag kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>04/06/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-HCV  kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025090113</t>
+  </si>
+  <si>
+    <t>HIV kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025060211</t>
+  </si>
+  <si>
+    <t>07/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Free T3 Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025050121</t>
+  </si>
+  <si>
+    <t>12/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Free T4 Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>ACTH kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>Total T3 Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>18/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TSH Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025080112</t>
+  </si>
+  <si>
+    <t>29/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Tg Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>28/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-Tg Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>30/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-TPO Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>16/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Free PSA Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>21/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Total BHCG Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>10/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>LH Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>17/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>FSH Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
     <t>2025040111</t>
   </si>
   <si>
-    <t>2025080111</t>
-  </si>
-  <si>
-    <t>13/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Cortisol kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>TnI kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025080121</t>
-  </si>
-  <si>
-    <t>14/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>PTH kit 2×50T Cl900i  Mindray</t>
-  </si>
-  <si>
-    <t>2025040112</t>
-  </si>
-  <si>
-    <t>19/05/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>VB12 kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>Folate kit 50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025100121</t>
-  </si>
-  <si>
-    <t>10/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HBs Ag kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>04/06/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-HCV  kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025090113</t>
-  </si>
-  <si>
-    <t>HIV kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025060211</t>
-  </si>
-  <si>
-    <t>07/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Free T3 Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025050121</t>
-  </si>
-  <si>
-    <t>12/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Free T4 Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>ACTH kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>Total T3 Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>18/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TSH Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025080112</t>
-  </si>
-  <si>
-    <t>29/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Tg Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>28/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-Tg Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>30/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-TPO Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>16/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Free PSA Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>21/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>AFP Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>Total BHCG Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>10/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>LH Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>17/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>FSH Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
     <t>22/11/2026 12:00:00 ص</t>
   </si>
   <si>
@@ -1572,6 +1602,9 @@
     <t>03/04/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA HSVHX03</t>
+  </si>
+  <si>
     <t>AMH Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -1758,12 +1791,21 @@
     <t>20/03/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA  VEVGC08X</t>
+  </si>
+  <si>
     <t>EVA VEVGC07X</t>
   </si>
   <si>
     <t>EVA VEVGC08X</t>
   </si>
   <si>
+    <t>EVA VEVHC09X</t>
+  </si>
+  <si>
+    <t>05/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>Rubella Virus IgG kit 2×50T  with cal.Cl900i  Mindray</t>
   </si>
   <si>
@@ -1851,6 +1893,9 @@
     <t>09/12/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA VEVCA11E</t>
+  </si>
+  <si>
     <t>EVA VEVCB02E</t>
   </si>
   <si>
@@ -1992,198 +2037,195 @@
     <t>( D- Bill (vox) kit Chemistry Mindray ( Large</t>
   </si>
   <si>
-    <t>140725008</t>
+    <t>140725013</t>
+  </si>
+  <si>
+    <t>( LDL-C kit  Chemistry Mindray  ( Large</t>
+  </si>
+  <si>
+    <t>142025008</t>
+  </si>
+  <si>
+    <t>11/07/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>( MG kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>148225004</t>
+  </si>
+  <si>
+    <t>( Phosphorus Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>142425004</t>
+  </si>
+  <si>
+    <t>( T-Bill vox kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140625015</t>
+  </si>
+  <si>
+    <t>( TP kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140825005</t>
+  </si>
+  <si>
+    <t>10/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>( UA  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>141225013</t>
+  </si>
+  <si>
+    <t>HBA1C Kit 10T Clover كلوفر</t>
+  </si>
+  <si>
+    <t>EVA B25D05D12EL</t>
+  </si>
+  <si>
+    <t>EVA B25E26H06DL</t>
+  </si>
+  <si>
+    <t>05/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA B25E27H06EL</t>
+  </si>
+  <si>
+    <t>EVA B25F01H07DL</t>
+  </si>
+  <si>
+    <t>06/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA B25F01H08DL</t>
+  </si>
+  <si>
+    <t>Ferritin Cal Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>152724011</t>
+  </si>
+  <si>
+    <t>06/05/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Urilyzer® Cell Cuvettes (600 PCS/BOX) analyticon</t>
+  </si>
+  <si>
+    <t>2411C100</t>
+  </si>
+  <si>
+    <t>31/10/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CombiScreen® 11SYS PLUS 150 strips per vial analyticon</t>
+  </si>
+  <si>
+    <t>2786/2010</t>
+  </si>
+  <si>
+    <t>IGRA-TB Tube 8T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA TBTVYA54</t>
+  </si>
+  <si>
+    <t>H.Pylori  Kit 10T  Mispa i3</t>
+  </si>
+  <si>
+    <t>32511197</t>
+  </si>
+  <si>
+    <t>24/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>32512294</t>
+  </si>
+  <si>
+    <t>30/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA  32509360</t>
+  </si>
+  <si>
+    <t>Microalbumin Kit 30T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512135</t>
+  </si>
+  <si>
+    <t>26/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>IgE Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA 32506314</t>
+  </si>
+  <si>
+    <t>Ceruloplasmin  Kit 10 T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509121</t>
+  </si>
+  <si>
+    <t>IgM Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509129</t>
+  </si>
+  <si>
+    <t>IgA Kit 10T  Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509126</t>
+  </si>
+  <si>
+    <t>IgG Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509298</t>
+  </si>
+  <si>
+    <t>PCT Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509132</t>
+  </si>
+  <si>
+    <t>IFOB Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA FOVEE02Z</t>
+  </si>
+  <si>
+    <t>D-DIMER NeO Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA KDVCE03EX</t>
+  </si>
+  <si>
+    <t>D-DIMER NeO Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA  KDVFA45X</t>
+  </si>
+  <si>
+    <t>EVA KDVCA40X</t>
+  </si>
+  <si>
+    <t>EVA KDVDA41X</t>
   </si>
   <si>
     <t>03/12/2026 12:00:00 ص</t>
   </si>
   <si>
-    <t>140725013</t>
-  </si>
-  <si>
-    <t>( LDL-C kit  Chemistry Mindray  ( Large</t>
-  </si>
-  <si>
-    <t>142025008</t>
-  </si>
-  <si>
-    <t>11/07/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>( MG kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>148225004</t>
-  </si>
-  <si>
-    <t>( Phosphorus Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>142425004</t>
-  </si>
-  <si>
-    <t>( T-Bill vox kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140625015</t>
-  </si>
-  <si>
-    <t>( TP kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140825005</t>
-  </si>
-  <si>
-    <t>10/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>( UA  Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>141225013</t>
-  </si>
-  <si>
-    <t>HBA1C Kit 10T Clover كلوفر</t>
-  </si>
-  <si>
-    <t>EVA B25D05D12EL</t>
-  </si>
-  <si>
-    <t>EVA B25E26H06DL</t>
-  </si>
-  <si>
-    <t>05/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA B25E27H06EL</t>
-  </si>
-  <si>
-    <t>EVA B25F01H07DL</t>
-  </si>
-  <si>
-    <t>06/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Ferritin Cal Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>152724011</t>
-  </si>
-  <si>
-    <t>06/05/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Urilyzer® Cell Cuvettes (600 PCS/BOX) analyticon</t>
-  </si>
-  <si>
-    <t>2411C100</t>
-  </si>
-  <si>
-    <t>31/10/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CombiScreen® 11SYS PLUS 150 strips per vial analyticon</t>
-  </si>
-  <si>
-    <t>2786/2010</t>
-  </si>
-  <si>
-    <t>IGRA-TB Tube 8T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA TBTVYA54</t>
-  </si>
-  <si>
-    <t>H.Pylori  Kit 10T  Mispa i3</t>
-  </si>
-  <si>
-    <t>32511197</t>
-  </si>
-  <si>
-    <t>24/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>32512294</t>
-  </si>
-  <si>
-    <t>30/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA  32509360</t>
-  </si>
-  <si>
-    <t>Microalbumin Kit 30T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512135</t>
-  </si>
-  <si>
-    <t>26/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>IgE Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA 32506314</t>
-  </si>
-  <si>
-    <t>Ceruloplasmin  Kit 10 T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509121</t>
-  </si>
-  <si>
-    <t>IgM Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509129</t>
-  </si>
-  <si>
-    <t>IgA Kit 10T  Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509126</t>
-  </si>
-  <si>
-    <t>IgG Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509298</t>
-  </si>
-  <si>
-    <t>PCT Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509132</t>
-  </si>
-  <si>
-    <t>IFOB Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA FOVEE02Z</t>
-  </si>
-  <si>
-    <t>D-DIMER NeO Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA KDVCE01EX</t>
-  </si>
-  <si>
-    <t>EVA KDVCE03EX</t>
-  </si>
-  <si>
-    <t>D-DIMER NeO Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA  KDVFA45X</t>
-  </si>
-  <si>
-    <t>EVA KDVCA40X</t>
-  </si>
-  <si>
-    <t>EVA KDVDA41X</t>
-  </si>
-  <si>
     <t>Free PSA Kit 25T iChroma Boditech</t>
   </si>
   <si>
@@ -2337,9 +2379,6 @@
     <t>EVA  CXVHA07G</t>
   </si>
   <si>
-    <t>12/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>CD-80 Detergent 2L</t>
   </si>
   <si>
@@ -2547,6 +2586,9 @@
     <t>EVA C00125070002</t>
   </si>
   <si>
+    <t>EVA C00125100003</t>
+  </si>
+  <si>
     <t>Myoglobin /ck-MB/Troponin I combo Cassette 25T hindering (WB/S/P)</t>
   </si>
   <si>
@@ -2559,6 +2601,9 @@
     <t>EVA T00625070003</t>
   </si>
   <si>
+    <t>EVA T00625100009</t>
+  </si>
+  <si>
     <t>PSA  Cassette 25T hindering (WB/S/P)</t>
   </si>
   <si>
@@ -2614,6 +2659,9 @@
   </si>
   <si>
     <t>01/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA KTVEC03EX</t>
   </si>
   <si>
     <t>dsDNA KIT BioCLIA 50 T</t>
@@ -4140,7 +4188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C649"/>
+  <dimension ref="A1:C660"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="30" customWidth="1"/>
@@ -4291,29 +4339,29 @@
     </row>
     <row r="14" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>43</v>
@@ -4324,95 +4372,95 @@
     </row>
     <row r="17" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>56</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>67</v>
@@ -4423,35 +4471,35 @@
     </row>
     <row r="26" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>69</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4467,21 +4515,21 @@
     </row>
     <row r="30" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>79</v>
@@ -4489,40 +4537,40 @@
     </row>
     <row r="32" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>88</v>
@@ -4533,18 +4581,18 @@
     </row>
     <row r="36" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>93</v>
@@ -4561,23 +4609,23 @@
         <v>96</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>100</v>
@@ -4610,68 +4658,68 @@
     </row>
     <row r="43" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>111</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4704,51 +4752,51 @@
         <v>128</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>104</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4764,68 +4812,68 @@
     </row>
     <row r="57" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>146</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>150</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4858,194 +4906,194 @@
         <v>159</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>161</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="C67" s="5" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>172</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>179</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>36</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>189</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>193</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5056,18 +5104,18 @@
         <v>195</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>197</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5083,35 +5131,35 @@
     </row>
     <row r="86" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C86" s="4" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="C87" s="5" t="s">
         <v>204</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5122,425 +5170,425 @@
         <v>208</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>209</v>
+        <v>166</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="C92" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C93" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>221</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C95" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C97" s="5" t="s">
         <v>230</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="4" t="s">
         <v>233</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C99" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="C100" s="4" t="s">
         <v>237</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="C101" s="5" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C102" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>0</v>
+      <c r="C103" s="5" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>0</v>
+        <v>239</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>0</v>
+        <v>247</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>248</v>
+        <v>0</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>251</v>
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>253</v>
+        <v>0</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C109" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C110" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C111" s="5" t="s">
         <v>259</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>264</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>265</v>
+        <v>151</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C114" s="4" t="s">
         <v>266</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B115" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C115" s="5" t="s">
         <v>269</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>47</v>
+        <v>279</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C120" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>285</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>290</v>
+        <v>49</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>79</v>
+        <v>289</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B124" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="C124" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>0</v>
+      <c r="C126" s="4" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5548,131 +5596,131 @@
         <v>299</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>304</v>
+        <v>82</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B130" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>0</v>
+      <c r="C130" s="4" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>308</v>
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>311</v>
+        <v>0</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>0</v>
+        <v>313</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>318</v>
+        <v>0</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>0</v>
+        <v>317</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B137" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B137" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>0</v>
+      <c r="C137" s="5" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>131</v>
+        <v>324</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>325</v>
+        <v>0</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5691,249 +5739,249 @@
         <v>329</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>331</v>
+        <v>0</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>334</v>
+        <v>0</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>337</v>
+        <v>134</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>0</v>
+        <v>340</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>79</v>
+        <v>357</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>361</v>
+        <v>0</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>360</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C155" s="5" t="s">
         <v>364</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="4" t="s">
         <v>367</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B157" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="C157" s="5" t="s">
         <v>370</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>374</v>
+        <v>82</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>42</v>
+        <v>380</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B163" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="C163" s="5" t="s">
         <v>383</v>
@@ -5941,35 +5989,35 @@
     </row>
     <row r="164" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B166" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5977,21 +6025,21 @@
         <v>391</v>
       </c>
       <c r="B167" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C167" s="5" t="s">
         <v>392</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>393</v>
+        <v>44</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5999,7 +6047,7 @@
         <v>394</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>395</v>
@@ -6007,21 +6055,21 @@
     </row>
     <row r="170" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="B170" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>346</v>
-      </c>
       <c r="C170" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B171" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>352</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>399</v>
@@ -6032,54 +6080,54 @@
         <v>400</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>346</v>
+        <v>401</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>352</v>
+        <v>404</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>403</v>
+        <v>13</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B174" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C174" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>406</v>
+        <v>369</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>407</v>
+        <v>306</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C176" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6087,95 +6135,95 @@
         <v>409</v>
       </c>
       <c r="B177" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C177" s="5" t="s">
         <v>410</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C178" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>406</v>
+        <v>363</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="C180" s="4" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>420</v>
+        <v>370</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C182" s="4" t="s">
         <v>421</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B183" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="C183" s="5" t="s">
         <v>424</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="C185" s="5" t="s">
         <v>428</v>
@@ -6183,13 +6231,13 @@
     </row>
     <row r="186" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C186" s="4" t="s">
         <v>430</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C186" s="4" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6197,10 +6245,10 @@
         <v>431</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>370</v>
+        <v>432</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>432</v>
+        <v>314</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6219,21 +6267,21 @@
         <v>436</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>376</v>
+        <v>437</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C190" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6241,95 +6289,95 @@
         <v>440</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>441</v>
+        <v>204</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C192" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B193" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="B193" s="3" t="s">
-        <v>406</v>
-      </c>
       <c r="C193" s="5" t="s">
-        <v>318</v>
+        <v>445</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>406</v>
+        <v>369</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>373</v>
+        <v>416</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>452</v>
+        <v>306</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>89</v>
+        <v>453</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>454</v>
+        <v>382</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>455</v>
@@ -6340,76 +6388,76 @@
         <v>456</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>454</v>
+        <v>416</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>140</v>
+        <v>457</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>405</v>
+        <v>459</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>25</v>
+        <v>460</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>460</v>
+        <v>92</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B205" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="B205" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="C205" s="5" t="s">
-        <v>273</v>
+        <v>143</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>467</v>
+        <v>25</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6417,21 +6465,21 @@
         <v>468</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C208" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6439,65 +6487,65 @@
         <v>471</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>376</v>
+        <v>472</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>407</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>473</v>
+        <v>279</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>376</v>
+        <v>475</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>454</v>
+        <v>416</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>434</v>
+        <v>388</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>478</v>
+        <v>101</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>480</v>
+        <v>388</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>481</v>
+        <v>417</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6505,7 +6553,7 @@
         <v>482</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>376</v>
+        <v>472</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>483</v>
@@ -6513,54 +6561,54 @@
     </row>
     <row r="216" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C216" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B217" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C217" s="5" t="s">
         <v>486</v>
-      </c>
-      <c r="C217" s="5" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C218" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="B218" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B219" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B219" s="3" t="s">
-        <v>489</v>
-      </c>
       <c r="C219" s="5" t="s">
-        <v>73</v>
+        <v>491</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>492</v>
+        <v>388</v>
       </c>
       <c r="C220" s="4" t="s">
         <v>493</v>
@@ -6571,32 +6619,32 @@
         <v>494</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>496</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>44</v>
+        <v>497</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>499</v>
+        <v>76</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6604,32 +6652,32 @@
         <v>500</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>502</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>28</v>
+        <v>503</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C226" s="4" t="s">
         <v>503</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6640,95 +6688,95 @@
         <v>506</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>507</v>
+        <v>46</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B228" s="1" t="s">
+      <c r="C228" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>511</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>512</v>
+        <v>89</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>311</v>
+        <v>28</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B231" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B231" s="3" t="s">
-        <v>515</v>
-      </c>
       <c r="C231" s="5" t="s">
-        <v>516</v>
+        <v>38</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C232" s="4" t="s">
         <v>517</v>
-      </c>
-      <c r="B232" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="C232" s="4" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="C233" s="5" t="s">
         <v>520</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="C234" s="4" t="s">
         <v>522</v>
-      </c>
-      <c r="B234" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C234" s="4" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>526</v>
+        <v>321</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6736,54 +6784,54 @@
         <v>524</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>352</v>
+        <v>525</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>454</v>
+        <v>527</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C238" s="4" t="s">
         <v>530</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C239" s="3" t="s">
-        <v>0</v>
+        <v>382</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C240" s="4" t="s">
         <v>534</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6791,18 +6839,18 @@
         <v>535</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>373</v>
+        <v>536</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>538</v>
@@ -6813,76 +6861,76 @@
         <v>539</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>370</v>
+        <v>464</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>76</v>
+        <v>540</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="C245" s="5" t="s">
-        <v>131</v>
+        <v>0</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>543</v>
+        <v>459</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C247" s="3" t="s">
-        <v>0</v>
+        <v>385</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>547</v>
+        <v>369</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>311</v>
+        <v>549</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>549</v>
+        <v>382</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>550</v>
+        <v>79</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6893,62 +6941,62 @@
         <v>552</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>86</v>
+        <v>553</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>554</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>555</v>
+        <v>134</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>13</v>
+        <v>134</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>559</v>
+        <v>0</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>406</v>
+        <v>558</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>561</v>
+        <v>321</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6956,87 +7004,87 @@
         <v>562</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>566</v>
+        <v>89</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>200</v>
+        <v>13</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>573</v>
+        <v>385</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C260" s="1" t="s">
-        <v>0</v>
+        <v>416</v>
+      </c>
+      <c r="C260" s="4" t="s">
+        <v>572</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>579</v>
-      </c>
       <c r="C262" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B263" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C263" s="5" t="s">
         <v>580</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7047,15 +7095,15 @@
         <v>582</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>583</v>
+        <v>204</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="B265" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="B265" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="C265" s="5" t="s">
         <v>585</v>
@@ -7066,10 +7114,10 @@
         <v>586</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>94</v>
+        <v>0</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7077,54 +7125,54 @@
         <v>587</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>454</v>
+        <v>588</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>411</v>
+        <v>589</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>454</v>
+        <v>590</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>589</v>
+        <v>392</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>591</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>206</v>
+        <v>392</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>186</v>
+        <v>594</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7132,10 +7180,10 @@
         <v>595</v>
       </c>
       <c r="B272" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="C272" s="4" t="s">
         <v>597</v>
-      </c>
-      <c r="C272" s="4" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7143,10 +7191,10 @@
         <v>598</v>
       </c>
       <c r="B273" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C273" s="5" t="s">
         <v>599</v>
-      </c>
-      <c r="C273" s="5" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7154,43 +7202,43 @@
         <v>600</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>601</v>
+        <v>382</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>603</v>
+        <v>464</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>104</v>
+        <v>421</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>605</v>
+        <v>464</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7198,43 +7246,43 @@
         <v>607</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>260</v>
+        <v>210</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>613</v>
+        <v>190</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>387</v>
+        <v>166</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7242,736 +7290,736 @@
         <v>614</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>618</v>
+        <v>16</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>542</v>
+        <v>107</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C284" s="4" t="s">
         <v>620</v>
-      </c>
-      <c r="B284" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="C284" s="4" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C285" s="5" t="s">
         <v>623</v>
-      </c>
-      <c r="B285" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="C285" s="5" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>206</v>
+        <v>266</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>629</v>
+        <v>266</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>337</v>
+        <v>628</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>634</v>
+        <v>399</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>637</v>
+        <v>257</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>640</v>
+        <v>553</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>22</v>
+        <v>169</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>318</v>
+        <v>210</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>652</v>
+        <v>349</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>397</v>
+        <v>655</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>116</v>
+        <v>657</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>622</v>
+        <v>22</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>383</v>
+        <v>328</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>265</v>
+        <v>667</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>137</v>
+        <v>670</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>677</v>
+        <v>408</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="B309" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="B309" s="3" t="s">
-        <v>678</v>
-      </c>
       <c r="C309" s="5" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>680</v>
+        <v>119</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>683</v>
+        <v>637</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>686</v>
+        <v>395</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>387</v>
+        <v>684</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>19</v>
+        <v>271</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>693</v>
+        <v>140</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B317" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="B317" s="3" t="s">
-        <v>696</v>
-      </c>
       <c r="C317" s="5" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>542</v>
+        <v>435</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>196</v>
+        <v>697</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>196</v>
+        <v>700</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>196</v>
+        <v>399</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>693</v>
+        <v>19</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>196</v>
+        <v>707</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>13</v>
+        <v>709</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>123</v>
+        <v>707</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>25</v>
+        <v>713</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>507</v>
+        <v>553</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="B329" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="B329" s="3" t="s">
-        <v>719</v>
-      </c>
       <c r="C329" s="5" t="s">
-        <v>63</v>
+        <v>200</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>658</v>
+        <v>200</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="B331" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="B331" s="3" t="s">
-        <v>722</v>
-      </c>
       <c r="C331" s="5" t="s">
-        <v>91</v>
+        <v>200</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B332" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B332" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="C332" s="4" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>728</v>
+        <v>200</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>731</v>
+        <v>13</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>734</v>
+        <v>25</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>737</v>
+        <v>517</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>403</v>
+        <v>65</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>744</v>
+        <v>736</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>745</v>
+        <v>94</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>39</v>
+        <v>742</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>629</v>
+        <v>745</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>759</v>
+        <v>414</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>0</v>
+        <v>755</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C347" s="3" t="s">
-        <v>0</v>
+        <v>758</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>759</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="C348" s="4" t="s">
         <v>762</v>
-      </c>
-      <c r="B348" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7979,131 +8027,131 @@
         <v>763</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C349" s="3" t="s">
-        <v>0</v>
+        <v>764</v>
+      </c>
+      <c r="C349" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B350" s="1" t="s">
         <v>765</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>766</v>
+        <v>644</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="B351" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="B351" s="3" t="s">
+      <c r="C351" s="5" t="s">
         <v>768</v>
-      </c>
-      <c r="C351" s="5" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B352" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="B352" s="1" t="s">
+      <c r="C352" s="4" t="s">
         <v>771</v>
-      </c>
-      <c r="C352" s="4" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="C353" s="5" t="s">
         <v>773</v>
-      </c>
-      <c r="B353" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="C353" s="5" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>777</v>
-      </c>
-      <c r="C354" s="4" t="s">
-        <v>481</v>
+        <v>0</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C355" s="5" t="s">
-        <v>521</v>
+        <v>0</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="C356" s="4" t="s">
-        <v>371</v>
+        <v>0</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="C357" s="5" t="s">
-        <v>371</v>
+        <v>0</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C358" s="1" t="s">
-        <v>0</v>
+        <v>779</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>780</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C359" s="3" t="s">
-        <v>0</v>
+        <v>782</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>783</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B360" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="B360" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C360" s="1" t="s">
-        <v>0</v>
+      <c r="C360" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8119,35 +8167,35 @@
     </row>
     <row r="362" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>788</v>
+        <v>491</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C363" s="3" t="s">
-        <v>0</v>
+        <v>792</v>
+      </c>
+      <c r="C363" s="5" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>34</v>
+        <v>383</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8155,10 +8203,10 @@
         <v>793</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>795</v>
+        <v>383</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8166,703 +8214,703 @@
         <v>796</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="C366" s="4" t="s">
-        <v>606</v>
+        <v>0</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="C367" s="5" t="s">
-        <v>578</v>
+        <v>0</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="C368" s="4" t="s">
-        <v>802</v>
+        <v>0</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="C371" s="5" t="s">
-        <v>802</v>
+        <v>0</v>
+      </c>
+      <c r="C371" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>802</v>
+        <v>36</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>802</v>
+        <v>808</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>802</v>
+        <v>620</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>802</v>
+        <v>589</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>802</v>
+        <v>820</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="B386" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="B386" s="1" t="s">
-        <v>838</v>
-      </c>
       <c r="C386" s="4" t="s">
-        <v>839</v>
+        <v>815</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>802</v>
+        <v>820</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="B395" s="3" t="s">
         <v>854</v>
       </c>
-      <c r="B395" s="3" t="s">
-        <v>857</v>
-      </c>
       <c r="C395" s="5" t="s">
-        <v>856</v>
+        <v>815</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>860</v>
+        <v>820</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>485</v>
+        <v>815</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>864</v>
+        <v>815</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>153</v>
+        <v>820</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>869</v>
+        <v>815</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>140</v>
+        <v>815</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>873</v>
+        <v>866</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>874</v>
+        <v>815</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>876</v>
+        <v>868</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>877</v>
+        <v>815</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>328</v>
+        <v>871</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>880</v>
+        <v>869</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>883</v>
+        <v>873</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>884</v>
+        <v>874</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>120</v>
+        <v>875</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>109</v>
+        <v>495</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>888</v>
+        <v>878</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>353</v>
+        <v>879</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>889</v>
+        <v>876</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>890</v>
+        <v>880</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>891</v>
+        <v>495</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>894</v>
+        <v>156</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>895</v>
+        <v>883</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>896</v>
+        <v>886</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>897</v>
+        <v>887</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>898</v>
+        <v>143</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>899</v>
+        <v>888</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>900</v>
+        <v>889</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>901</v>
+        <v>890</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>903</v>
+        <v>892</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>613</v>
+        <v>893</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>904</v>
+        <v>894</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>906</v>
+        <v>338</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>908</v>
+        <v>897</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>473</v>
+        <v>898</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>909</v>
+        <v>899</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>910</v>
+        <v>900</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>911</v>
+        <v>123</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>912</v>
+        <v>901</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>914</v>
+        <v>112</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>915</v>
+        <v>903</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>916</v>
+        <v>904</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>917</v>
+        <v>364</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>918</v>
+        <v>905</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>919</v>
+        <v>906</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>921</v>
+        <v>908</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>276</v>
+        <v>910</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>0</v>
+        <v>906</v>
+      </c>
+      <c r="C422" s="4" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C423" s="3" t="s">
-        <v>0</v>
+        <v>913</v>
+      </c>
+      <c r="C423" s="5" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>925</v>
+        <v>915</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C424" s="1" t="s">
-        <v>0</v>
+        <v>916</v>
+      </c>
+      <c r="C424" s="4" t="s">
+        <v>917</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C425" s="3" t="s">
-        <v>0</v>
+        <v>919</v>
+      </c>
+      <c r="C425" s="5" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>866</v>
+        <v>921</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>153</v>
+        <v>922</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>866</v>
+        <v>924</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>153</v>
+        <v>483</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>866</v>
+        <v>926</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>153</v>
+        <v>927</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B429" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="C429" s="5" t="s">
         <v>930</v>
-      </c>
-      <c r="B429" s="3" t="s">
-        <v>868</v>
-      </c>
-      <c r="C429" s="5" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8870,876 +8918,876 @@
         <v>931</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>868</v>
+        <v>932</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>869</v>
+        <v>933</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>868</v>
+        <v>935</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>869</v>
+        <v>936</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>871</v>
+        <v>938</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>140</v>
+        <v>282</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="C433" s="5" t="s">
-        <v>140</v>
+        <v>0</v>
+      </c>
+      <c r="C433" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>140</v>
+        <v>0</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>936</v>
+        <v>941</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>873</v>
-      </c>
-      <c r="C435" s="5" t="s">
-        <v>874</v>
+        <v>0</v>
+      </c>
+      <c r="C435" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>937</v>
+        <v>942</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="C436" s="4" t="s">
-        <v>874</v>
+        <v>0</v>
+      </c>
+      <c r="C436" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>873</v>
+        <v>882</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>874</v>
+        <v>156</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>877</v>
+        <v>156</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
-        <v>940</v>
+        <v>945</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>877</v>
+        <v>156</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>941</v>
+        <v>946</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>879</v>
+        <v>884</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>328</v>
+        <v>885</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>943</v>
+        <v>948</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>944</v>
+        <v>884</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>583</v>
+        <v>885</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>882</v>
+        <v>143</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>882</v>
+        <v>143</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>882</v>
+        <v>143</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>120</v>
+        <v>890</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>120</v>
+        <v>890</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>120</v>
+        <v>890</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>109</v>
+        <v>893</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>109</v>
+        <v>893</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>109</v>
+        <v>893</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>888</v>
+        <v>960</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>353</v>
+        <v>597</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>353</v>
+        <v>898</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>957</v>
+        <v>962</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>958</v>
+        <v>963</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
-        <v>959</v>
+        <v>964</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>894</v>
+        <v>123</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>898</v>
+        <v>123</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
-        <v>961</v>
+        <v>966</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>898</v>
+        <v>123</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>962</v>
+        <v>967</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>897</v>
+        <v>902</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>898</v>
+        <v>112</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
-        <v>963</v>
+        <v>968</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>901</v>
+        <v>112</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>964</v>
+        <v>969</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>901</v>
+        <v>112</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>901</v>
+        <v>364</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>966</v>
+        <v>971</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>890</v>
+        <v>904</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>891</v>
+        <v>364</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
-        <v>967</v>
+        <v>972</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>890</v>
+        <v>904</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>891</v>
+        <v>364</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
-        <v>971</v>
+        <v>976</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>890</v>
+        <v>913</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>891</v>
+        <v>914</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>973</v>
+        <v>913</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>613</v>
+        <v>914</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>974</v>
+        <v>913</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>613</v>
+        <v>914</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>613</v>
+        <v>917</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>903</v>
+        <v>916</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>613</v>
+        <v>917</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>978</v>
+        <v>916</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>906</v>
+        <v>917</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>613</v>
+        <v>907</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>913</v>
+        <v>906</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>910</v>
+        <v>989</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>911</v>
+        <v>628</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>910</v>
+        <v>990</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>911</v>
+        <v>628</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
-        <v>986</v>
+        <v>991</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>987</v>
+        <v>919</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>988</v>
+        <v>628</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>987</v>
+        <v>919</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>988</v>
+        <v>628</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>988</v>
+        <v>922</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>908</v>
+        <v>921</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>473</v>
+        <v>922</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>473</v>
+        <v>628</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>473</v>
+        <v>930</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>995</v>
+        <v>929</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>996</v>
+        <v>930</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>995</v>
+        <v>929</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>996</v>
+        <v>930</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>995</v>
+        <v>926</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>996</v>
+        <v>927</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>1000</v>
+        <v>926</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>1001</v>
+        <v>927</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C493" s="3" t="s">
-        <v>0</v>
+        <v>926</v>
+      </c>
+      <c r="C493" s="5" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B494" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="B494" s="1" t="s">
+      <c r="C494" s="4" t="s">
         <v>1004</v>
-      </c>
-      <c r="C494" s="4" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>582</v>
+        <v>1003</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>582</v>
+        <v>924</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>318</v>
+        <v>483</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>1013</v>
+        <v>924</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>1014</v>
+        <v>483</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C499" s="3" t="s">
-        <v>0</v>
+        <v>924</v>
+      </c>
+      <c r="C499" s="5" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>869</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>386</v>
+        <v>1011</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>148</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1020</v>
+        <v>1011</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>273</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>337</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C504" s="4" t="s">
-        <v>629</v>
+        <v>0</v>
+      </c>
+      <c r="C504" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>629</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B507" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="C507" s="5" t="s">
         <v>1026</v>
-      </c>
-      <c r="B507" s="3" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C507" s="5" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1032</v>
+        <v>596</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>1030</v>
+        <v>328</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="C509" s="5" t="s">
         <v>1030</v>
@@ -9747,57 +9795,57 @@
     </row>
     <row r="510" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C510" s="4" t="s">
-        <v>1030</v>
+        <v>0</v>
+      </c>
+      <c r="C510" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>995</v>
+        <v>1033</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>996</v>
+        <v>885</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>900</v>
+        <v>398</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>901</v>
+        <v>151</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>900</v>
+        <v>1036</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>901</v>
+        <v>279</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B514" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="B514" s="1" t="s">
-        <v>900</v>
-      </c>
       <c r="C514" s="4" t="s">
-        <v>901</v>
+        <v>349</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9805,65 +9853,65 @@
         <v>1039</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>900</v>
+        <v>1040</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>901</v>
+        <v>644</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B516" s="1" t="s">
         <v>1041</v>
       </c>
       <c r="C516" s="4" t="s">
-        <v>1042</v>
+        <v>644</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B517" s="3" t="s">
         <v>1043</v>
       </c>
-      <c r="B517" s="3" t="s">
+      <c r="C517" s="5" t="s">
         <v>1044</v>
-      </c>
-      <c r="C517" s="5" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B518" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="B518" s="1" t="s">
-        <v>1044</v>
-      </c>
       <c r="C518" s="4" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B519" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C519" s="5" t="s">
         <v>1046</v>
-      </c>
-      <c r="B519" s="3" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C519" s="5" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B520" s="1" t="s">
         <v>1048</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9874,7 +9922,7 @@
         <v>1048</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9882,10 +9930,10 @@
         <v>1051</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1048</v>
+        <v>1011</v>
       </c>
       <c r="C522" s="4" t="s">
-        <v>1049</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9893,10 +9941,10 @@
         <v>1052</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>1048</v>
+        <v>916</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>1049</v>
+        <v>917</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9904,54 +9952,54 @@
         <v>1053</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1054</v>
+        <v>916</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>561</v>
+        <v>917</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>1054</v>
+        <v>916</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>561</v>
+        <v>917</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1054</v>
+        <v>916</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>561</v>
+        <v>917</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B527" s="3" t="s">
         <v>1057</v>
       </c>
-      <c r="B527" s="3" t="s">
-        <v>1054</v>
-      </c>
       <c r="C527" s="5" t="s">
-        <v>561</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C528" s="4" t="s">
         <v>1058</v>
-      </c>
-      <c r="B528" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C528" s="4" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9959,10 +10007,10 @@
         <v>1061</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9970,10 +10018,10 @@
         <v>1062</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9981,65 +10029,65 @@
         <v>1063</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>1059</v>
+        <v>1064</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>1060</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B532" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="B532" s="1" t="s">
+      <c r="C532" s="4" t="s">
         <v>1065</v>
-      </c>
-      <c r="C532" s="4" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B533" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C533" s="5" t="s">
         <v>1065</v>
-      </c>
-      <c r="C533" s="5" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B534" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C534" s="4" t="s">
         <v>1065</v>
-      </c>
-      <c r="C534" s="4" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>1065</v>
+        <v>1070</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="B536" s="1" t="s">
         <v>1070</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>1071</v>
+        <v>572</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10050,7 +10098,7 @@
         <v>1070</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>1071</v>
+        <v>572</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10061,7 +10109,7 @@
         <v>1070</v>
       </c>
       <c r="C538" s="4" t="s">
-        <v>1071</v>
+        <v>572</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10069,21 +10117,21 @@
         <v>1074</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>1070</v>
+        <v>1075</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B540" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="B540" s="1" t="s">
+      <c r="C540" s="4" t="s">
         <v>1076</v>
-      </c>
-      <c r="C540" s="4" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10091,10 +10139,10 @@
         <v>1078</v>
       </c>
       <c r="B541" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C541" s="5" t="s">
         <v>1076</v>
-      </c>
-      <c r="C541" s="5" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10102,10 +10150,10 @@
         <v>1079</v>
       </c>
       <c r="B542" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C542" s="4" t="s">
         <v>1076</v>
-      </c>
-      <c r="C542" s="4" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10113,854 +10161,854 @@
         <v>1080</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>1076</v>
+        <v>1081</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>1077</v>
+        <v>575</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B544" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="B544" s="1" t="s">
-        <v>987</v>
-      </c>
       <c r="C544" s="4" t="s">
-        <v>988</v>
+        <v>575</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>987</v>
+        <v>1081</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>988</v>
+        <v>575</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>987</v>
+        <v>1081</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>988</v>
+        <v>575</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>987</v>
+        <v>1086</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>988</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="B548" s="1" t="s">
         <v>1086</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>463</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B549" s="3" t="s">
         <v>1086</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>463</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B550" s="1" t="s">
         <v>1086</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>463</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>463</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>873</v>
+        <v>1092</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>874</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>873</v>
+        <v>1092</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>874</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B554" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="B554" s="1" t="s">
-        <v>873</v>
-      </c>
       <c r="C554" s="4" t="s">
-        <v>874</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>873</v>
+        <v>1003</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>874</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>876</v>
+        <v>1003</v>
       </c>
       <c r="C556" s="4" t="s">
-        <v>877</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>876</v>
+        <v>1003</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>877</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>876</v>
+        <v>1003</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>877</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>876</v>
+        <v>1102</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>877</v>
+        <v>473</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1059</v>
+        <v>1102</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>1060</v>
+        <v>473</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>1059</v>
+        <v>1102</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>1060</v>
+        <v>473</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1059</v>
+        <v>1102</v>
       </c>
       <c r="C562" s="4" t="s">
-        <v>1060</v>
+        <v>473</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>871</v>
+        <v>889</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>140</v>
+        <v>890</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>871</v>
+        <v>889</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>140</v>
+        <v>890</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
-        <v>1103</v>
+        <v>1108</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>871</v>
+        <v>889</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>140</v>
+        <v>890</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
-        <v>1104</v>
+        <v>1109</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>871</v>
+        <v>889</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>140</v>
+        <v>890</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>1106</v>
+        <v>892</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>1107</v>
+        <v>893</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1106</v>
+        <v>892</v>
       </c>
       <c r="C568" s="4" t="s">
-        <v>1107</v>
+        <v>893</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>1106</v>
+        <v>892</v>
       </c>
       <c r="C569" s="5" t="s">
-        <v>1107</v>
+        <v>893</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1106</v>
+        <v>892</v>
       </c>
       <c r="C570" s="4" t="s">
-        <v>1107</v>
+        <v>893</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>1054</v>
+        <v>1075</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>561</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>1054</v>
+        <v>1075</v>
       </c>
       <c r="C572" s="4" t="s">
-        <v>561</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>1054</v>
+        <v>1075</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>561</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1115</v>
+        <v>887</v>
       </c>
       <c r="C574" s="4" t="s">
-        <v>1116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>1115</v>
+        <v>887</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>1116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="576" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>1115</v>
+        <v>887</v>
       </c>
       <c r="C576" s="4" t="s">
-        <v>1116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="577" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>1115</v>
+        <v>887</v>
       </c>
       <c r="C577" s="5" t="s">
-        <v>1116</v>
+        <v>143</v>
       </c>
     </row>
     <row r="578" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1086</v>
+        <v>1122</v>
       </c>
       <c r="C578" s="4" t="s">
-        <v>463</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="579" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B579" s="3" t="s">
-        <v>1086</v>
+        <v>1122</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>463</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="580" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B580" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="B580" s="1" t="s">
-        <v>1086</v>
-      </c>
       <c r="C580" s="4" t="s">
-        <v>463</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="581" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B581" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C581" s="5" t="s">
         <v>1123</v>
-      </c>
-      <c r="B581" s="3" t="s">
-        <v>1086</v>
-      </c>
-      <c r="C581" s="5" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="582" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1086</v>
+        <v>1070</v>
       </c>
       <c r="C582" s="4" t="s">
-        <v>463</v>
+        <v>572</v>
       </c>
     </row>
     <row r="583" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>1086</v>
+        <v>1070</v>
       </c>
       <c r="C583" s="5" t="s">
-        <v>463</v>
+        <v>572</v>
       </c>
     </row>
     <row r="584" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>1086</v>
+        <v>1070</v>
       </c>
       <c r="C584" s="4" t="s">
-        <v>463</v>
+        <v>572</v>
       </c>
     </row>
     <row r="585" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>1086</v>
+        <v>1131</v>
       </c>
       <c r="C585" s="5" t="s">
-        <v>463</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="C586" s="4" t="s">
-        <v>754</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="587" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A587" s="3" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>754</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="588" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B588" s="1" t="s">
         <v>1131</v>
       </c>
-      <c r="B588" s="1" t="s">
-        <v>1129</v>
-      </c>
       <c r="C588" s="4" t="s">
-        <v>754</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="589" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>1129</v>
+        <v>1102</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>754</v>
+        <v>473</v>
       </c>
     </row>
     <row r="590" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>1134</v>
+        <v>1102</v>
       </c>
       <c r="C590" s="4" t="s">
-        <v>1135</v>
+        <v>473</v>
       </c>
     </row>
     <row r="591" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>582</v>
+        <v>1102</v>
       </c>
       <c r="C591" s="5" t="s">
-        <v>1137</v>
+        <v>473</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>1054</v>
+        <v>1102</v>
       </c>
       <c r="C592" s="4" t="s">
-        <v>561</v>
+        <v>473</v>
       </c>
     </row>
     <row r="593" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>1140</v>
+        <v>1102</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>1141</v>
+        <v>473</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C594" s="1" t="s">
-        <v>0</v>
+        <v>1102</v>
+      </c>
+      <c r="C594" s="4" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="595" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A595" s="3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C595" s="3" t="s">
-        <v>0</v>
+        <v>1102</v>
+      </c>
+      <c r="C595" s="5" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B596" s="1" t="s">
-        <v>1145</v>
+        <v>1102</v>
       </c>
       <c r="C596" s="4" t="s">
-        <v>1146</v>
+        <v>473</v>
       </c>
     </row>
     <row r="597" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A597" s="3" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="C597" s="5" t="s">
-        <v>788</v>
+        <v>768</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="C598" s="4" t="s">
-        <v>89</v>
+        <v>768</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A599" s="3" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="B599" s="3" t="s">
-        <v>1152</v>
+        <v>1145</v>
       </c>
       <c r="C599" s="5" t="s">
-        <v>1153</v>
+        <v>768</v>
       </c>
     </row>
     <row r="600" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>1155</v>
+        <v>1145</v>
       </c>
       <c r="C600" s="4" t="s">
-        <v>173</v>
+        <v>768</v>
       </c>
     </row>
     <row r="601" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A601" s="3" t="s">
-        <v>1156</v>
+        <v>1149</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>1157</v>
+        <v>1150</v>
       </c>
       <c r="C601" s="5" t="s">
-        <v>101</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="B602" s="1" t="s">
-        <v>1159</v>
+        <v>596</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>1160</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A603" s="3" t="s">
-        <v>1161</v>
+        <v>1154</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>1162</v>
+        <v>1070</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>1163</v>
+        <v>572</v>
       </c>
     </row>
     <row r="604" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>1164</v>
+        <v>1156</v>
       </c>
       <c r="C604" s="4" t="s">
-        <v>671</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="605" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A605" s="3" t="s">
-        <v>1165</v>
+        <v>1158</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C605" s="5" t="s">
-        <v>1167</v>
+        <v>0</v>
+      </c>
+      <c r="C605" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="606" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
-        <v>1168</v>
+        <v>1159</v>
       </c>
       <c r="B606" s="1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C606" s="4" t="s">
-        <v>917</v>
+        <v>0</v>
+      </c>
+      <c r="C606" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="607" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A607" s="3" t="s">
-        <v>1170</v>
+        <v>1160</v>
       </c>
       <c r="B607" s="3" t="s">
-        <v>1171</v>
+        <v>1161</v>
       </c>
       <c r="C607" s="5" t="s">
-        <v>1071</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="608" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
-        <v>1172</v>
+        <v>1163</v>
       </c>
       <c r="B608" s="1" t="s">
-        <v>1173</v>
+        <v>1164</v>
       </c>
       <c r="C608" s="4" t="s">
-        <v>22</v>
+        <v>801</v>
       </c>
     </row>
     <row r="609" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A609" s="3" t="s">
-        <v>1174</v>
+        <v>1165</v>
       </c>
       <c r="B609" s="3" t="s">
-        <v>1175</v>
+        <v>1166</v>
       </c>
       <c r="C609" s="5" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
     </row>
     <row r="610" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
-        <v>1176</v>
+        <v>1167</v>
       </c>
       <c r="B610" s="1" t="s">
-        <v>1177</v>
+        <v>1168</v>
       </c>
       <c r="C610" s="4" t="s">
-        <v>265</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="611" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A611" s="3" t="s">
-        <v>1178</v>
+        <v>1170</v>
       </c>
       <c r="B611" s="3" t="s">
-        <v>1179</v>
+        <v>1171</v>
       </c>
       <c r="C611" s="5" t="s">
-        <v>22</v>
+        <v>177</v>
       </c>
     </row>
     <row r="612" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
-        <v>1180</v>
+        <v>1172</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>1181</v>
+        <v>1173</v>
       </c>
       <c r="C612" s="4" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
     </row>
     <row r="613" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A613" s="3" t="s">
-        <v>1182</v>
+        <v>1174</v>
       </c>
       <c r="B613" s="3" t="s">
-        <v>1183</v>
+        <v>1175</v>
       </c>
       <c r="C613" s="5" t="s">
-        <v>22</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="614" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="B614" s="1" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="C614" s="4" t="s">
-        <v>22</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="615" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A615" s="3" t="s">
-        <v>1186</v>
+        <v>1177</v>
       </c>
       <c r="B615" s="3" t="s">
-        <v>1187</v>
+        <v>1180</v>
       </c>
       <c r="C615" s="5" t="s">
-        <v>1163</v>
+        <v>684</v>
       </c>
     </row>
     <row r="616" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="s">
-        <v>1188</v>
+        <v>1181</v>
       </c>
       <c r="B616" s="1" t="s">
-        <v>1189</v>
+        <v>1182</v>
       </c>
       <c r="C616" s="4" t="s">
-        <v>1190</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="617" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A617" s="3" t="s">
-        <v>1191</v>
+        <v>1184</v>
       </c>
       <c r="B617" s="3" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="C617" s="5" t="s">
-        <v>22</v>
+        <v>933</v>
       </c>
     </row>
     <row r="618" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
-        <v>1193</v>
+        <v>1186</v>
       </c>
       <c r="B618" s="1" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
       <c r="C618" s="4" t="s">
-        <v>22</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="619" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A619" s="3" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="B619" s="3" t="s">
-        <v>1196</v>
+        <v>1189</v>
       </c>
       <c r="C619" s="5" t="s">
-        <v>532</v>
+        <v>22</v>
       </c>
     </row>
     <row r="620" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
-        <v>1197</v>
+        <v>1190</v>
       </c>
       <c r="B620" s="1" t="s">
-        <v>1198</v>
+        <v>1191</v>
       </c>
       <c r="C620" s="4" t="s">
         <v>22</v>
@@ -10968,21 +11016,21 @@
     </row>
     <row r="621" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A621" s="3" t="s">
-        <v>1199</v>
+        <v>1192</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>1200</v>
+        <v>1193</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>22</v>
+        <v>271</v>
       </c>
     </row>
     <row r="622" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
-        <v>1201</v>
+        <v>1194</v>
       </c>
       <c r="B622" s="1" t="s">
-        <v>1202</v>
+        <v>1195</v>
       </c>
       <c r="C622" s="4" t="s">
         <v>22</v>
@@ -10990,21 +11038,21 @@
     </row>
     <row r="623" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A623" s="3" t="s">
-        <v>1203</v>
+        <v>1196</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>1204</v>
+        <v>1197</v>
       </c>
       <c r="C623" s="5" t="s">
-        <v>1205</v>
+        <v>22</v>
       </c>
     </row>
     <row r="624" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
-        <v>1206</v>
+        <v>1198</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>1207</v>
+        <v>1199</v>
       </c>
       <c r="C624" s="4" t="s">
         <v>22</v>
@@ -11012,43 +11060,43 @@
     </row>
     <row r="625" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A625" s="3" t="s">
-        <v>1208</v>
+        <v>1200</v>
       </c>
       <c r="B625" s="3" t="s">
-        <v>1209</v>
+        <v>1201</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>1210</v>
+        <v>22</v>
       </c>
     </row>
     <row r="626" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
-        <v>1211</v>
+        <v>1202</v>
       </c>
       <c r="B626" s="1" t="s">
-        <v>1212</v>
+        <v>1203</v>
       </c>
       <c r="C626" s="4" t="s">
-        <v>22</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="627" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A627" s="3" t="s">
-        <v>1213</v>
+        <v>1204</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>1214</v>
+        <v>1205</v>
       </c>
       <c r="C627" s="5" t="s">
-        <v>22</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="628" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
-        <v>1215</v>
+        <v>1207</v>
       </c>
       <c r="B628" s="1" t="s">
-        <v>1216</v>
+        <v>1208</v>
       </c>
       <c r="C628" s="4" t="s">
         <v>22</v>
@@ -11056,54 +11104,54 @@
     </row>
     <row r="629" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A629" s="3" t="s">
-        <v>1217</v>
+        <v>1209</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>1218</v>
+        <v>1210</v>
       </c>
       <c r="C629" s="5" t="s">
-        <v>1219</v>
+        <v>22</v>
       </c>
     </row>
     <row r="630" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
-        <v>1220</v>
+        <v>1211</v>
       </c>
       <c r="B630" s="1" t="s">
-        <v>1221</v>
+        <v>1212</v>
       </c>
       <c r="C630" s="4" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
     </row>
     <row r="631" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A631" s="3" t="s">
-        <v>1222</v>
+        <v>1213</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>1223</v>
+        <v>1214</v>
       </c>
       <c r="C631" s="5" t="s">
-        <v>294</v>
+        <v>22</v>
       </c>
     </row>
     <row r="632" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
-        <v>1224</v>
+        <v>1215</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>1225</v>
+        <v>1216</v>
       </c>
       <c r="C632" s="4" t="s">
-        <v>377</v>
+        <v>22</v>
       </c>
     </row>
     <row r="633" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A633" s="3" t="s">
-        <v>1226</v>
+        <v>1217</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>1227</v>
+        <v>1218</v>
       </c>
       <c r="C633" s="5" t="s">
         <v>22</v>
@@ -11111,150 +11159,271 @@
     </row>
     <row r="634" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
-        <v>1228</v>
+        <v>1219</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1229</v>
+        <v>1220</v>
       </c>
       <c r="C634" s="4" t="s">
-        <v>22</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A635" s="3" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
       <c r="C635" s="5" t="s">
-        <v>1232</v>
+        <v>22</v>
       </c>
     </row>
     <row r="636" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
-        <v>1233</v>
+        <v>1224</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>1234</v>
+        <v>1225</v>
       </c>
       <c r="C636" s="4" t="s">
-        <v>22</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="637" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A637" s="3" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
       <c r="C637" s="5" t="s">
-        <v>1237</v>
+        <v>22</v>
       </c>
     </row>
     <row r="638" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A638" s="1" t="s">
-        <v>1238</v>
+        <v>1229</v>
       </c>
       <c r="B638" s="1" t="s">
-        <v>1239</v>
+        <v>1230</v>
       </c>
       <c r="C638" s="4" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
     </row>
     <row r="639" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A639" s="3" t="s">
-        <v>1240</v>
+        <v>1231</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>1241</v>
+        <v>1232</v>
       </c>
       <c r="C639" s="5" t="s">
-        <v>1014</v>
+        <v>22</v>
       </c>
     </row>
     <row r="640" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A640" s="1" t="s">
-        <v>1242</v>
+        <v>1233</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>1241</v>
+        <v>1234</v>
       </c>
       <c r="C640" s="4" t="s">
-        <v>1014</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="641" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A641" s="3" t="s">
-        <v>1243</v>
+        <v>1236</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>1244</v>
+        <v>1237</v>
       </c>
       <c r="C641" s="5" t="s">
-        <v>186</v>
+        <v>543</v>
       </c>
     </row>
     <row r="642" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A642" s="1" t="s">
-        <v>1245</v>
+        <v>1238</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>1246</v>
+        <v>1239</v>
       </c>
       <c r="C642" s="4" t="s">
-        <v>1247</v>
+        <v>302</v>
       </c>
     </row>
     <row r="643" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A643" s="3" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
       <c r="C643" s="5" t="s">
-        <v>1250</v>
+        <v>389</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="s">
-        <v>1251</v>
+        <v>1242</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>1252</v>
+        <v>1243</v>
       </c>
       <c r="C644" s="4" t="s">
-        <v>745</v>
+        <v>22</v>
       </c>
     </row>
     <row r="645" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A645" s="3" t="s">
-        <v>1253</v>
+        <v>1244</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C645" s="3" t="s">
-        <v>0</v>
+        <v>1245</v>
+      </c>
+      <c r="C645" s="5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="646" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C646" s="4" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A647" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B647" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C647" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A648" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B648" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C648" s="4" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A649" s="3" t="s">
         <v>1254</v>
       </c>
-      <c r="B646" s="1" t="s">
+      <c r="B649" s="3" t="s">
         <v>1255</v>
       </c>
-      <c r="C646" s="4" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="647" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
-    <row r="648" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
-    <row r="649" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="C649" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A650" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B650" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C650" s="4" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A651" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B651" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C651" s="5" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A652" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C652" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A653" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C653" s="5" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A654" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B654" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C654" s="4" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A655" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B655" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C655" s="5" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A656" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C656" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A657" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B657" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C657" s="5" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="659" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="660" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/المواد.xlsx
+++ b/المواد.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="1245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="1244">
   <si>
     <t/>
   </si>
@@ -546,114 +546,117 @@
     <t>Cholestrol kit 125 T Agappe</t>
   </si>
   <si>
-    <t>32410315</t>
+    <t>32512040</t>
+  </si>
+  <si>
+    <t>20/11/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Creatinine kit 200T Agappe</t>
+  </si>
+  <si>
+    <t>32410244</t>
+  </si>
+  <si>
+    <t>17/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>32411104</t>
+  </si>
+  <si>
+    <t>03/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HDL-Cholestrol kit 100T Agappe</t>
+  </si>
+  <si>
+    <t>32411147</t>
+  </si>
+  <si>
+    <t>06/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Phosphorous kit 100T Agappe</t>
+  </si>
+  <si>
+    <t>32410228</t>
+  </si>
+  <si>
+    <t>13/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>32411216</t>
+  </si>
+  <si>
+    <t>10/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Potassium kit 60T Agappe</t>
+  </si>
+  <si>
+    <t>32410174</t>
+  </si>
+  <si>
+    <t>30/04/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>32411148</t>
+  </si>
+  <si>
+    <t>RF kit 100T Agappe</t>
+  </si>
+  <si>
+    <t>32512213</t>
+  </si>
+  <si>
+    <t>Sodium kit 60T Agappe</t>
+  </si>
+  <si>
+    <t>32410245</t>
+  </si>
+  <si>
+    <t>32411199</t>
+  </si>
+  <si>
+    <t>32411205</t>
+  </si>
+  <si>
+    <t>32502152</t>
+  </si>
+  <si>
+    <t>Total Protein kit 200T Agappe</t>
+  </si>
+  <si>
+    <t>32410267</t>
+  </si>
+  <si>
+    <t>32411230</t>
+  </si>
+  <si>
+    <t>32503037</t>
+  </si>
+  <si>
+    <t>31/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Urea kit 200T Agappe</t>
+  </si>
+  <si>
+    <t>32507134</t>
+  </si>
+  <si>
+    <t>Uric Acid kit 100T Agappe</t>
+  </si>
+  <si>
+    <t>32410203</t>
+  </si>
+  <si>
+    <t>32411174</t>
   </si>
   <si>
     <t>30/09/2026 12:00:00 ص</t>
   </si>
   <si>
-    <t>Creatinine kit 200T Agappe</t>
-  </si>
-  <si>
-    <t>32410244</t>
-  </si>
-  <si>
-    <t>17/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>32411104</t>
-  </si>
-  <si>
-    <t>03/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HDL-Cholestrol kit 100T Agappe</t>
-  </si>
-  <si>
-    <t>32411147</t>
-  </si>
-  <si>
-    <t>06/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Phosphorous kit 100T Agappe</t>
-  </si>
-  <si>
-    <t>32410228</t>
-  </si>
-  <si>
-    <t>13/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>32411216</t>
-  </si>
-  <si>
-    <t>10/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Potassium kit 60T Agappe</t>
-  </si>
-  <si>
-    <t>32410174</t>
-  </si>
-  <si>
-    <t>30/04/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>32411148</t>
-  </si>
-  <si>
-    <t>RF kit 100T Agappe</t>
-  </si>
-  <si>
-    <t>32512213</t>
-  </si>
-  <si>
-    <t>Sodium kit 60T Agappe</t>
-  </si>
-  <si>
-    <t>32410245</t>
-  </si>
-  <si>
-    <t>32411199</t>
-  </si>
-  <si>
-    <t>32411205</t>
-  </si>
-  <si>
-    <t>32502152</t>
-  </si>
-  <si>
-    <t>Total Protein kit 200T Agappe</t>
-  </si>
-  <si>
-    <t>32410267</t>
-  </si>
-  <si>
-    <t>32411230</t>
-  </si>
-  <si>
-    <t>32503037</t>
-  </si>
-  <si>
-    <t>31/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Urea kit 200T Agappe</t>
-  </si>
-  <si>
-    <t>32507134</t>
-  </si>
-  <si>
-    <t>Uric Acid kit 100T Agappe</t>
-  </si>
-  <si>
-    <t>32410203</t>
-  </si>
-  <si>
-    <t>32411174</t>
-  </si>
-  <si>
     <t>Magnesium kit 100T Agappe</t>
   </si>
   <si>
@@ -726,15 +729,12 @@
     <t>M-30 Diluent Reagent 3-part 20L Hematology Mindray</t>
   </si>
   <si>
-    <t>2025082952</t>
+    <t>2025082954</t>
   </si>
   <si>
     <t>28/08/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>2025082954</t>
-  </si>
-  <si>
     <t>M-30R Rinse Reagent 3-part 20L Hematology Mindray</t>
   </si>
   <si>
@@ -768,9 +768,6 @@
     <t>2025112154</t>
   </si>
   <si>
-    <t>20/11/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>Cuvette BS120 Chemistry Mindray</t>
   </si>
   <si>
@@ -882,6 +879,9 @@
     <t>28/08/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>141325023</t>
+  </si>
+  <si>
     <t>Amylase kit  Chemistry Mindray</t>
   </si>
   <si>
@@ -939,273 +939,270 @@
     <t>150725010</t>
   </si>
   <si>
-    <t>150725011</t>
+    <t>Semi-cuvettes (steel ball included)/350 كيوفيت</t>
+  </si>
+  <si>
+    <t>Mispa i2 Instrument agappe</t>
+  </si>
+  <si>
+    <t>CYBOW 3</t>
+  </si>
+  <si>
+    <t>EVA 251027</t>
+  </si>
+  <si>
+    <t>26/10/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CYBOW 10</t>
+  </si>
+  <si>
+    <t>241118</t>
+  </si>
+  <si>
+    <t>17/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>ichamber</t>
+  </si>
+  <si>
+    <t>IgM kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>144225003</t>
+  </si>
+  <si>
+    <t>Lipids Calibrator Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>150425013</t>
+  </si>
+  <si>
+    <t>23/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Aqappe 30ml Nano Detergent</t>
+  </si>
+  <si>
+    <t>32410142</t>
+  </si>
+  <si>
+    <t>Afias-6 paper + i chroma 11</t>
+  </si>
+  <si>
+    <t>Capillary tube 15ul  25/tube</t>
+  </si>
+  <si>
+    <t>BC-10-3part Instrument Auto Hematology Mindray</t>
+  </si>
+  <si>
+    <t>Creatinine kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>141125018</t>
+  </si>
+  <si>
+    <t>M-62 FN Dye Reagent 7-part 12mL Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025061351</t>
+  </si>
+  <si>
+    <t>12/06/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 FD Dye Reagent 7-part 12mL Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025073051</t>
+  </si>
+  <si>
+    <t>29/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 LD Lyse Reagent 7-part 1L Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025081151</t>
+  </si>
+  <si>
+    <t>10/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 LH Lyse Reagent 7-part 1L Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025050951</t>
+  </si>
+  <si>
+    <t>08/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 DS Diluent Reagent 7-part 20L Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025082653</t>
+  </si>
+  <si>
+    <t>25/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HbA1c 5ul micro capillary tube</t>
+  </si>
+  <si>
+    <t>CP05TAA01</t>
+  </si>
+  <si>
+    <t>12/01/2028 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>حديدة فيتامين دي</t>
+  </si>
+  <si>
+    <t>T3 kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2024100113</t>
+  </si>
+  <si>
+    <t>08/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>T4 kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025010111</t>
+  </si>
+  <si>
+    <t>08/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TSH  kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025060151</t>
+  </si>
+  <si>
+    <t>18/09/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Tg kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025070111</t>
+  </si>
+  <si>
+    <t>09/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-Tg kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025100111</t>
+  </si>
+  <si>
+    <t>13/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-TPO kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>02/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CA19-9 kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>11/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>T-PSA kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025070131</t>
+  </si>
+  <si>
+    <t>15/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>FPSA kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025050111</t>
+  </si>
+  <si>
+    <t>27/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CEA kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>28/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>AFP  kit 2×50T Cl-900i Mindray</t>
+  </si>
+  <si>
+    <t>2025060111</t>
+  </si>
+  <si>
+    <t>12/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Ferritin  kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025090111</t>
+  </si>
+  <si>
+    <t>2025090131</t>
+  </si>
+  <si>
+    <t>Total β HCG kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>23/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>LH  kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>24/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>2025070111.</t>
+  </si>
+  <si>
+    <t>FSH kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025030111</t>
+  </si>
+  <si>
+    <t>28/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>PRL kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025030211</t>
+  </si>
+  <si>
+    <t>19/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Free T3 kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025060112</t>
+  </si>
+  <si>
+    <t>PROG kit 2×50T Cl900i Mindray</t>
   </si>
   <si>
     <t>27/03/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>Semi-cuvettes (steel ball included)/350 كيوفيت</t>
-  </si>
-  <si>
-    <t>Mispa i2 Instrument agappe</t>
-  </si>
-  <si>
-    <t>CYBOW 3</t>
-  </si>
-  <si>
-    <t>EVA 251027</t>
-  </si>
-  <si>
-    <t>26/10/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CYBOW 10</t>
-  </si>
-  <si>
-    <t>241118</t>
-  </si>
-  <si>
-    <t>17/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>ichamber</t>
-  </si>
-  <si>
-    <t>IgM kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>144225003</t>
-  </si>
-  <si>
-    <t>Lipids Calibrator Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>150425013</t>
-  </si>
-  <si>
-    <t>23/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Aqappe 30ml Nano Detergent</t>
-  </si>
-  <si>
-    <t>32410142</t>
-  </si>
-  <si>
-    <t>Afias-6 paper + i chroma 11</t>
-  </si>
-  <si>
-    <t>Capillary tube 15ul  25/tube</t>
-  </si>
-  <si>
-    <t>BC-10-3part Instrument Auto Hematology Mindray</t>
-  </si>
-  <si>
-    <t>Creatinine kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>141125018</t>
-  </si>
-  <si>
-    <t>M-62 FN Dye Reagent 7-part 12mL Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025061351</t>
-  </si>
-  <si>
-    <t>12/06/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 FD Dye Reagent 7-part 12mL Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025073051</t>
-  </si>
-  <si>
-    <t>29/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 LD Lyse Reagent 7-part 1L Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025081151</t>
-  </si>
-  <si>
-    <t>10/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 LH Lyse Reagent 7-part 1L Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025050951</t>
-  </si>
-  <si>
-    <t>08/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 DS Diluent Reagent 7-part 20L Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025082653</t>
-  </si>
-  <si>
-    <t>25/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HbA1c 5ul micro capillary tube</t>
-  </si>
-  <si>
-    <t>CP05TAA01</t>
-  </si>
-  <si>
-    <t>12/01/2028 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>حديدة فيتامين دي</t>
-  </si>
-  <si>
-    <t>T3 kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2024100113</t>
-  </si>
-  <si>
-    <t>08/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>T4 kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025010111</t>
-  </si>
-  <si>
-    <t>08/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TSH  kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025060151</t>
-  </si>
-  <si>
-    <t>18/09/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Tg kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025070111</t>
-  </si>
-  <si>
-    <t>09/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-Tg kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025100111</t>
-  </si>
-  <si>
-    <t>13/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-TPO kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>02/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CA19-9 kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>11/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>T-PSA kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025070131</t>
-  </si>
-  <si>
-    <t>15/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>FPSA kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025050111</t>
-  </si>
-  <si>
-    <t>27/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CEA kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>28/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>AFP  kit 2×50T Cl-900i Mindray</t>
-  </si>
-  <si>
-    <t>2025060111</t>
-  </si>
-  <si>
-    <t>12/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Ferritin  kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025090111</t>
-  </si>
-  <si>
-    <t>2025090131</t>
-  </si>
-  <si>
-    <t>Total β HCG kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>23/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>LH  kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>24/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>2025070111.</t>
-  </si>
-  <si>
-    <t>FSH kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025030111</t>
-  </si>
-  <si>
-    <t>28/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>PRL kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025030211</t>
-  </si>
-  <si>
-    <t>19/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Free T3 kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025060112</t>
-  </si>
-  <si>
-    <t>PROG kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
     <t>TESTO kit 2×50T Cl900i Mindray</t>
   </si>
   <si>
@@ -1326,54 +1323,60 @@
     <t>Anti-TPO Calibrator 2ml Cl900i Mindray</t>
   </si>
   <si>
+    <t>Free PSA Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>21/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Total BHCG Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>10/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>LH Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>17/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>FSH Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025040111</t>
+  </si>
+  <si>
+    <t>22/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Prolactin Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>Progesterone Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025020111</t>
+  </si>
+  <si>
+    <t>24/09/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Testosterone Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>Estradiol Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>18/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Insulin Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
     <t>16/10/2026 12:00:00 ص</t>
   </si>
   <si>
-    <t>Total BHCG Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>10/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>LH Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>17/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>FSH Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025040111</t>
-  </si>
-  <si>
-    <t>22/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Prolactin Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>Progesterone Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025020111</t>
-  </si>
-  <si>
-    <t>24/09/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Testosterone Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>Estradiol Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>18/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Insulin Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
     <t>DHEA-S Calibrator 2ml Cl900i Mindray</t>
   </si>
   <si>
@@ -1482,9 +1485,6 @@
     <t>Amylase kit 40T Agappe</t>
   </si>
   <si>
-    <t>32410127</t>
-  </si>
-  <si>
     <t>32503003</t>
   </si>
   <si>
@@ -1968,6 +1968,12 @@
     <t>( D- Bill (vox) kit Chemistry Mindray ( Large</t>
   </si>
   <si>
+    <t>140725008</t>
+  </si>
+  <si>
+    <t>03/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
     <t>140725013</t>
   </si>
   <si>
@@ -1986,6 +1992,12 @@
     <t>148225004</t>
   </si>
   <si>
+    <t>( Phosphorus Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>142425004</t>
+  </si>
+  <si>
     <t>( T-Bill vox kit Chemistry Mindray ( Large</t>
   </si>
   <si>
@@ -2664,6 +2676,12 @@
     <t>29/08/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>Cardiolipin IgG KIT BioCLIA 50 T</t>
+  </si>
+  <si>
+    <t>EVA 20250730</t>
+  </si>
+  <si>
     <t>Cardiolipin IgM KIT BioCLIA 50 T</t>
   </si>
   <si>
@@ -2832,9 +2850,6 @@
     <t>Cardiolipin IgG Calibrator Set BioCLIA HOB</t>
   </si>
   <si>
-    <t>EVA 20250730</t>
-  </si>
-  <si>
     <t>IgE Specific Cal and Control Set BioCLIA Allergy 50T HOB</t>
   </si>
   <si>
@@ -3390,15 +3405,6 @@
     <t>CCP  Calibrator Set BioCLIA HOB</t>
   </si>
   <si>
-    <t>hs-cTnI Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2024090111</t>
-  </si>
-  <si>
-    <t>21/03/2026 12:00:00 ص</t>
-  </si>
-  <si>
     <t>Growth hormone kit with cal 2×50T Cl900i Mindray</t>
   </si>
   <si>
@@ -3694,15 +3700,6 @@
   </si>
   <si>
     <t>EVA A32A4F4</t>
-  </si>
-  <si>
-    <t>Toxo IgG  Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>XGUGA03G</t>
-  </si>
-  <si>
-    <t>23/03/2026 12:00:00 ص</t>
   </si>
   <si>
     <t>Kappa/Lambda Free Light Chain Level 1(1 ml ) Mispa i3</t>
@@ -5089,15 +5086,15 @@
         <v>210</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>166</v>
@@ -5105,10 +5102,10 @@
     </row>
     <row r="91" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>166</v>
@@ -5116,43 +5113,43 @@
     </row>
     <row r="92" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>205</v>
@@ -5160,123 +5157,123 @@
     </row>
     <row r="96" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>246</v>
+        <v>176</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="C106" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5284,21 +5281,21 @@
         <v>253</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5306,21 +5303,21 @@
         <v>257</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>260</v>
+        <v>0</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5350,98 +5347,98 @@
         <v>263</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>0</v>
+        <v>264</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>272</v>
+        <v>161</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>161</v>
+        <v>276</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>286</v>
+        <v>187</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5523,18 +5520,18 @@
     </row>
     <row r="129" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>307</v>
+        <v>0</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>0</v>
@@ -5545,57 +5542,57 @@
     </row>
     <row r="131" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B131" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B131" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>0</v>
+      <c r="C131" s="5" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>312</v>
+        <v>0</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B135" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B135" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C135" s="3" t="s">
-        <v>0</v>
+      <c r="C135" s="5" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5606,18 +5603,18 @@
         <v>318</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>100</v>
+        <v>319</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>321</v>
+        <v>46</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5625,15 +5622,15 @@
         <v>322</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>46</v>
+        <v>0</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>0</v>
@@ -5644,7 +5641,7 @@
     </row>
     <row r="140" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>0</v>
@@ -5655,13 +5652,13 @@
     </row>
     <row r="141" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B141" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>0</v>
+      <c r="C141" s="5" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5672,147 +5669,147 @@
         <v>328</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>136</v>
+        <v>329</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>346</v>
+        <v>0</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B149" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B149" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>0</v>
+      <c r="C149" s="5" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>359</v>
+        <v>84</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C154" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>362</v>
@@ -5823,7 +5820,7 @@
         <v>363</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>364</v>
@@ -5834,29 +5831,29 @@
         <v>365</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C159" s="5" t="s">
         <v>372</v>
@@ -5867,29 +5864,29 @@
         <v>373</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>377</v>
+        <v>48</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>48</v>
@@ -5897,13 +5894,13 @@
     </row>
     <row r="163" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B163" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C163" s="5" t="s">
         <v>380</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5911,7 +5908,7 @@
         <v>381</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>382</v>
@@ -5919,57 +5916,57 @@
     </row>
     <row r="165" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B165" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="B165" s="3" t="s">
-        <v>358</v>
-      </c>
       <c r="C165" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>385</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>391</v>
+        <v>13</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5977,10 +5974,10 @@
         <v>392</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>35</v>
+        <v>393</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5988,65 +5985,65 @@
         <v>394</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>307</v>
+        <v>395</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>352</v>
+        <v>403</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>404</v>
+        <v>374</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>405</v>
+        <v>357</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6054,29 +6051,29 @@
         <v>406</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>376</v>
+        <v>407</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>359</v>
+        <v>408</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>411</v>
+        <v>356</v>
       </c>
       <c r="C179" s="5" t="s">
         <v>412</v>
@@ -6084,13 +6081,13 @@
     </row>
     <row r="180" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6098,98 +6095,98 @@
         <v>414</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>416</v>
-      </c>
       <c r="C182" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>419</v>
+        <v>313</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>315</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>423</v>
+        <v>369</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>371</v>
+        <v>429</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>430</v>
+        <v>356</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>433</v>
+        <v>393</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6197,7 +6194,7 @@
         <v>434</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>435</v>
@@ -6205,57 +6202,57 @@
     </row>
     <row r="191" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>404</v>
+        <v>369</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>307</v>
+        <v>437</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>404</v>
+        <v>441</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>441</v>
+        <v>377</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>442</v>
+        <v>153</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>379</v>
+        <v>445</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>153</v>
+        <v>446</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6263,10 +6260,10 @@
         <v>444</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>445</v>
+        <v>356</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>446</v>
+        <v>76</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6296,18 +6293,18 @@
         <v>450</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>32</v>
@@ -6315,43 +6312,43 @@
     </row>
     <row r="201" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C204" s="4" t="s">
         <v>104</v>
@@ -6359,65 +6356,65 @@
     </row>
     <row r="205" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>445</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C210" s="4" t="s">
         <v>79</v>
@@ -6425,65 +6422,65 @@
     </row>
     <row r="211" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C215" s="5" t="s">
         <v>480</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C216" s="4" t="s">
         <v>51</v>
@@ -6491,57 +6488,57 @@
     </row>
     <row r="217" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>91</v>
+        <v>489</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>489</v>
+        <v>43</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>43</v>
+        <v>494</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6549,65 +6546,65 @@
         <v>495</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>504</v>
+        <v>369</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>371</v>
+        <v>441</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>441</v>
+        <v>511</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6615,21 +6612,21 @@
         <v>510</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>511</v>
+        <v>350</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>352</v>
+        <v>515</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6637,7 +6634,7 @@
         <v>514</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C230" s="4" t="s">
         <v>516</v>
@@ -6645,79 +6642,79 @@
     </row>
     <row r="231" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>516</v>
+        <v>0</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C232" s="1" t="s">
-        <v>0</v>
+        <v>374</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>376</v>
+        <v>441</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>76</v>
+        <v>161</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>441</v>
+        <v>374</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>161</v>
+        <v>522</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>524</v>
+        <v>82</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>371</v>
+        <v>527</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>82</v>
+        <v>528</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6725,15 +6722,15 @@
         <v>526</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>528</v>
+        <v>136</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>529</v>
@@ -6744,112 +6741,112 @@
     </row>
     <row r="240" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>136</v>
+        <v>0</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C241" s="3" t="s">
-        <v>0</v>
+        <v>533</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>321</v>
+        <v>536</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>536</v>
+        <v>91</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>91</v>
+        <v>541</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>544</v>
+        <v>13</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>546</v>
+        <v>374</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>13</v>
+        <v>548</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>404</v>
+        <v>552</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6857,21 +6854,21 @@
         <v>551</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6879,54 +6876,54 @@
         <v>556</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>558</v>
+        <v>46</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>46</v>
+        <v>222</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>221</v>
+        <v>564</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>564</v>
+        <v>0</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C256" s="1" t="s">
-        <v>0</v>
+        <v>567</v>
+      </c>
+      <c r="C256" s="4" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6934,10 +6931,10 @@
         <v>566</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6945,7 +6942,7 @@
         <v>566</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C258" s="4" t="s">
         <v>570</v>
@@ -6953,68 +6950,68 @@
     </row>
     <row r="259" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>573</v>
+        <v>356</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>576</v>
+        <v>97</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>371</v>
+        <v>445</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>97</v>
+        <v>408</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>445</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>409</v>
+        <v>580</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>445</v>
+        <v>582</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>580</v>
+        <v>228</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7022,76 +7019,76 @@
         <v>581</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>176</v>
+        <v>268</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>269</v>
+        <v>16</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>110</v>
+        <v>594</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7099,10 +7096,10 @@
         <v>595</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7110,7 +7107,7 @@
         <v>595</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C273" s="5" t="s">
         <v>599</v>
@@ -7121,7 +7118,7 @@
         <v>595</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>599</v>
@@ -7129,24 +7126,24 @@
     </row>
     <row r="275" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>604</v>
+        <v>386</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7154,10 +7151,10 @@
         <v>605</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>388</v>
+        <v>608</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7165,65 +7162,65 @@
         <v>605</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>613</v>
+        <v>181</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>181</v>
+        <v>228</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>227</v>
+        <v>620</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>620</v>
+        <v>271</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7231,43 +7228,43 @@
         <v>621</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>272</v>
+        <v>338</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>340</v>
+        <v>626</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7286,76 +7283,76 @@
         <v>630</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>634</v>
+        <v>29</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>29</v>
+        <v>639</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>639</v>
+        <v>27</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>27</v>
+        <v>644</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7363,29 +7360,29 @@
         <v>648</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>120</v>
@@ -7393,420 +7390,420 @@
     </row>
     <row r="299" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>384</v>
+        <v>613</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>659</v>
+        <v>382</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>277</v>
+        <v>663</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>143</v>
+        <v>276</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>665</v>
+        <v>143</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>424</v>
+        <v>671</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>60</v>
+        <v>423</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>673</v>
+        <v>60</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>388</v>
+        <v>680</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>24</v>
+        <v>386</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>683</v>
+        <v>24</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="C315" s="5" t="s">
         <v>687</v>
-      </c>
-      <c r="B315" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="C315" s="5" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>528</v>
+        <v>698</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>388</v>
+        <v>528</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>217</v>
+        <v>386</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>181</v>
+        <v>218</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>683</v>
+        <v>181</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>217</v>
+        <v>687</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>449</v>
+        <v>218</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>494</v>
+        <v>449</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>94</v>
+        <v>494</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>505</v>
+        <v>94</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>715</v>
+        <v>505</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>402</v>
+        <v>734</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>735</v>
+        <v>401</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>505</v>
+        <v>739</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7814,43 +7811,43 @@
         <v>737</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>739</v>
+        <v>505</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>620</v>
+        <v>749</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7858,48 +7855,48 @@
         <v>747</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>749</v>
+        <v>620</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>0</v>
+        <v>757</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>0</v>
@@ -7910,7 +7907,7 @@
     </row>
     <row r="346" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>0</v>
@@ -7921,7 +7918,7 @@
     </row>
     <row r="347" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>0</v>
@@ -7932,117 +7929,117 @@
     </row>
     <row r="348" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="C348" s="4" t="s">
-        <v>761</v>
+        <v>0</v>
+      </c>
+      <c r="C348" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>652</v>
+        <v>768</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>41</v>
+        <v>654</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>772</v>
+        <v>19</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>472</v>
+        <v>776</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>507</v>
+        <v>473</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>372</v>
+        <v>507</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C357" s="3" t="s">
-        <v>0</v>
+        <v>782</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B358" s="1" t="s">
         <v>0</v>
@@ -8053,7 +8050,7 @@
     </row>
     <row r="359" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>0</v>
@@ -8064,321 +8061,321 @@
     </row>
     <row r="360" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>783</v>
-      </c>
-      <c r="C360" s="4" t="s">
-        <v>784</v>
+        <v>0</v>
+      </c>
+      <c r="C360" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C362" s="1" t="s">
-        <v>0</v>
+        <v>789</v>
+      </c>
+      <c r="C362" s="4" t="s">
+        <v>790</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="C363" s="5" t="s">
-        <v>243</v>
+        <v>0</v>
+      </c>
+      <c r="C363" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>792</v>
+        <v>243</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>46</v>
+        <v>796</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>797</v>
+        <v>46</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>594</v>
+        <v>801</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>802</v>
+        <v>594</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B372" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="C372" s="4" t="s">
         <v>812</v>
-      </c>
-      <c r="C372" s="4" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>845</v>
+        <v>812</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8386,120 +8383,120 @@
         <v>846</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>813</v>
+        <v>849</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>808</v>
+        <v>817</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>863</v>
+        <v>812</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>405</v>
+        <v>867</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>867</v>
+        <v>404</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8507,142 +8504,142 @@
         <v>868</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>474</v>
+        <v>871</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>166</v>
+        <v>475</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>875</v>
+        <v>166</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>149</v>
+        <v>879</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>880</v>
+        <v>149</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>124</v>
+        <v>332</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>113</v>
+        <v>889</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>890</v>
+        <v>124</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>890</v>
+        <v>113</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="B412" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="B412" s="1" t="s">
+      <c r="C412" s="4" t="s">
         <v>896</v>
-      </c>
-      <c r="C412" s="4" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8653,51 +8650,51 @@
         <v>899</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>604</v>
+        <v>900</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>463</v>
+        <v>604</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>910</v>
+        <v>464</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8730,34 +8727,34 @@
         <v>918</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>286</v>
+        <v>919</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C421" s="3" t="s">
-        <v>0</v>
+        <v>921</v>
+      </c>
+      <c r="C421" s="5" t="s">
+        <v>922</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>0</v>
+        <v>924</v>
+      </c>
+      <c r="C422" s="4" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>0</v>
@@ -8768,7 +8765,7 @@
     </row>
     <row r="424" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>0</v>
@@ -8779,54 +8776,54 @@
     </row>
     <row r="425" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>872</v>
-      </c>
-      <c r="C425" s="5" t="s">
-        <v>166</v>
+        <v>0</v>
+      </c>
+      <c r="C425" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>874</v>
-      </c>
-      <c r="C426" s="4" t="s">
-        <v>875</v>
+        <v>0</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>149</v>
+        <v>879</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="C429" s="5" t="s">
         <v>149</v>
@@ -8834,153 +8831,153 @@
     </row>
     <row r="430" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>880</v>
+        <v>149</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>880</v>
+        <v>149</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>932</v>
+        <v>883</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>933</v>
+        <v>884</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>932</v>
+        <v>883</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>933</v>
+        <v>884</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>334</v>
+        <v>939</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="B437" s="3" t="s">
         <v>938</v>
       </c>
-      <c r="B437" s="3" t="s">
+      <c r="C437" s="5" t="s">
         <v>939</v>
-      </c>
-      <c r="C437" s="5" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>883</v>
+        <v>332</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>882</v>
+        <v>944</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>883</v>
+        <v>574</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>124</v>
+        <v>889</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>124</v>
+        <v>889</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="C443" s="5" t="s">
         <v>124</v>
@@ -8988,32 +8985,32 @@
     </row>
     <row r="444" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="C446" s="4" t="s">
         <v>113</v>
@@ -9021,24 +9018,24 @@
     </row>
     <row r="447" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>950</v>
+        <v>893</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>353</v>
+        <v>113</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>952</v>
+        <v>893</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>953</v>
+        <v>113</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9046,356 +9043,356 @@
         <v>954</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>893</v>
+        <v>955</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>894</v>
+        <v>351</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>893</v>
+        <v>957</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>894</v>
+        <v>958</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>893</v>
+        <v>899</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>890</v>
+        <v>903</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>890</v>
+        <v>903</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>967</v>
+        <v>895</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>604</v>
+        <v>896</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>968</v>
+        <v>895</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>604</v>
+        <v>896</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>902</v>
+        <v>604</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>901</v>
+        <v>973</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>902</v>
+        <v>604</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>899</v>
+        <v>975</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>604</v>
+        <v>908</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>910</v>
+        <v>604</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>909</v>
+        <v>915</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>906</v>
+        <v>915</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>907</v>
+        <v>916</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>906</v>
+        <v>912</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>979</v>
+        <v>912</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>980</v>
+        <v>913</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>979</v>
+        <v>912</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>980</v>
+        <v>913</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>904</v>
+        <v>984</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>463</v>
+        <v>985</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B476" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="B476" s="1" t="s">
-        <v>904</v>
-      </c>
       <c r="C476" s="4" t="s">
-        <v>463</v>
+        <v>985</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>904</v>
+        <v>910</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>987</v>
+        <v>910</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>988</v>
+        <v>464</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>987</v>
+        <v>910</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>988</v>
+        <v>464</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>988</v>
+        <v>993</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B481" s="3" t="s">
         <v>992</v>
@@ -9406,35 +9403,35 @@
     </row>
     <row r="482" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C482" s="1" t="s">
-        <v>0</v>
+        <v>992</v>
+      </c>
+      <c r="C482" s="4" t="s">
+        <v>993</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>999</v>
-      </c>
-      <c r="C484" s="4" t="s">
-        <v>146</v>
+        <v>0</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9442,142 +9439,142 @@
         <v>1000</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>573</v>
+        <v>1001</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>573</v>
+        <v>1004</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>639</v>
+        <v>146</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>1004</v>
+        <v>573</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C488" s="1" t="s">
-        <v>0</v>
+        <v>573</v>
+      </c>
+      <c r="C488" s="4" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>875</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C490" s="4" t="s">
-        <v>161</v>
+        <v>0</v>
+      </c>
+      <c r="C490" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>1012</v>
+        <v>879</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>1014</v>
+        <v>385</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>340</v>
+        <v>161</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>499</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>620</v>
+        <v>338</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>620</v>
+        <v>499</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>1021</v>
+        <v>620</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>1023</v>
+        <v>620</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9588,106 +9585,106 @@
         <v>1025</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>1023</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B501" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C501" s="5" t="s">
         <v>1028</v>
-      </c>
-      <c r="B501" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="C501" s="5" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>896</v>
+        <v>1030</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>897</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>896</v>
+        <v>992</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>897</v>
+        <v>993</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1034</v>
+        <v>902</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>1035</v>
+        <v>903</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>1037</v>
+        <v>902</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>1035</v>
+        <v>903</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9695,95 +9692,95 @@
         <v>1038</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>1037</v>
+        <v>1042</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B510" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C510" s="4" t="s">
         <v>1040</v>
-      </c>
-      <c r="B510" s="1" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C510" s="4" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>1041</v>
+        <v>1046</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>1042</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B514" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="B514" s="1" t="s">
+      <c r="C514" s="4" t="s">
         <v>1047</v>
-      </c>
-      <c r="C514" s="4" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B515" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C515" s="5" t="s">
         <v>1047</v>
-      </c>
-      <c r="C515" s="5" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="C516" s="4" t="s">
         <v>550</v>
@@ -9791,10 +9788,10 @@
     </row>
     <row r="517" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="C517" s="5" t="s">
         <v>550</v>
@@ -9802,76 +9799,76 @@
     </row>
     <row r="518" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B518" s="1" t="s">
         <v>1052</v>
       </c>
       <c r="C518" s="4" t="s">
-        <v>1053</v>
+        <v>550</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B519" s="3" t="s">
         <v>1052</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>1053</v>
+        <v>550</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B522" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="B522" s="1" t="s">
+      <c r="C522" s="4" t="s">
         <v>1058</v>
-      </c>
-      <c r="C522" s="4" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B523" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C523" s="5" t="s">
         <v>1058</v>
-      </c>
-      <c r="C523" s="5" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="C524" s="4" t="s">
         <v>553</v>
@@ -9879,10 +9876,10 @@
     </row>
     <row r="525" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>1058</v>
+        <v>1063</v>
       </c>
       <c r="C525" s="5" t="s">
         <v>553</v>
@@ -9890,329 +9887,329 @@
     </row>
     <row r="526" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B526" s="1" t="s">
         <v>1063</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>413</v>
+        <v>553</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B527" s="3" t="s">
         <v>1063</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>413</v>
+        <v>553</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>1063</v>
+        <v>1068</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>1068</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>1069</v>
+        <v>412</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B531" s="3" t="s">
         <v>1068</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>1069</v>
+        <v>412</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>1068</v>
+        <v>1073</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>1069</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B534" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="B534" s="1" t="s">
-        <v>979</v>
-      </c>
       <c r="C534" s="4" t="s">
-        <v>980</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B535" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C535" s="5" t="s">
         <v>1074</v>
-      </c>
-      <c r="B535" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="C535" s="5" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>979</v>
+        <v>984</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>980</v>
+        <v>985</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1078</v>
+        <v>984</v>
       </c>
       <c r="C538" s="4" t="s">
-        <v>454</v>
+        <v>985</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>1078</v>
+        <v>984</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>454</v>
+        <v>985</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>879</v>
+        <v>1083</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>880</v>
+        <v>455</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B543" s="3" t="s">
         <v>1083</v>
       </c>
-      <c r="B543" s="3" t="s">
-        <v>879</v>
-      </c>
       <c r="C543" s="5" t="s">
-        <v>880</v>
+        <v>455</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>932</v>
+        <v>883</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>933</v>
+        <v>884</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>932</v>
+        <v>883</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>933</v>
+        <v>884</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>933</v>
+        <v>939</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1052</v>
+        <v>938</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>1053</v>
+        <v>939</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>1052</v>
+        <v>938</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>1053</v>
+        <v>939</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>1053</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>877</v>
+        <v>1057</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>149</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>877</v>
+        <v>1057</v>
       </c>
       <c r="C554" s="4" t="s">
-        <v>149</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="C555" s="5" t="s">
         <v>149</v>
@@ -10220,10 +10217,10 @@
     </row>
     <row r="556" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="C556" s="4" t="s">
         <v>149</v>
@@ -10231,76 +10228,76 @@
     </row>
     <row r="557" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>1098</v>
+        <v>881</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>1099</v>
+        <v>149</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1098</v>
+        <v>881</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>1099</v>
+        <v>149</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>1099</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B561" s="3" t="s">
         <v>1103</v>
       </c>
-      <c r="B561" s="3" t="s">
-        <v>1047</v>
-      </c>
       <c r="C561" s="5" t="s">
-        <v>550</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B562" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C562" s="4" t="s">
         <v>1104</v>
-      </c>
-      <c r="B562" s="1" t="s">
-        <v>1047</v>
-      </c>
-      <c r="C562" s="4" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>1047</v>
+        <v>1052</v>
       </c>
       <c r="C563" s="5" t="s">
         <v>550</v>
@@ -10308,178 +10305,178 @@
     </row>
     <row r="564" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1107</v>
+        <v>1052</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>1108</v>
+        <v>550</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>1107</v>
+        <v>1052</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>1108</v>
+        <v>550</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>1107</v>
+        <v>1112</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>1108</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B568" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="B568" s="1" t="s">
-        <v>1078</v>
-      </c>
       <c r="C568" s="4" t="s">
-        <v>454</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B569" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C569" s="5" t="s">
         <v>1113</v>
-      </c>
-      <c r="B569" s="3" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C569" s="5" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="C570" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="C572" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="C574" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>1078</v>
+        <v>1083</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="576" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>1121</v>
+        <v>1083</v>
       </c>
       <c r="C576" s="4" t="s">
-        <v>749</v>
+        <v>455</v>
       </c>
     </row>
     <row r="577" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>1121</v>
+        <v>1083</v>
       </c>
       <c r="C577" s="5" t="s">
-        <v>749</v>
+        <v>455</v>
       </c>
     </row>
     <row r="578" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C578" s="4" t="s">
-        <v>1125</v>
+        <v>753</v>
       </c>
     </row>
     <row r="579" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B579" s="3" t="s">
         <v>1126</v>
       </c>
-      <c r="B579" s="3" t="s">
-        <v>573</v>
-      </c>
       <c r="C579" s="5" t="s">
-        <v>1127</v>
+        <v>753</v>
       </c>
     </row>
     <row r="580" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10487,37 +10484,37 @@
         <v>1128</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>1047</v>
+        <v>573</v>
       </c>
       <c r="C580" s="4" t="s">
-        <v>550</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="581" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B581" s="3" t="s">
-        <v>1130</v>
+        <v>1052</v>
       </c>
       <c r="C581" s="5" t="s">
-        <v>1131</v>
+        <v>550</v>
       </c>
     </row>
     <row r="582" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B582" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="B582" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C582" s="1" t="s">
-        <v>0</v>
+      <c r="C582" s="4" t="s">
+        <v>1133</v>
       </c>
     </row>
     <row r="583" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B583" s="3" t="s">
         <v>0</v>
@@ -10528,24 +10525,24 @@
     </row>
     <row r="584" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>1135</v>
-      </c>
-      <c r="C584" s="4" t="s">
-        <v>1136</v>
+        <v>0</v>
+      </c>
+      <c r="C584" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="585" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B585" s="3" t="s">
         <v>1137</v>
       </c>
-      <c r="B585" s="3" t="s">
+      <c r="C585" s="5" t="s">
         <v>1138</v>
-      </c>
-      <c r="C585" s="5" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10556,7 +10553,7 @@
         <v>1140</v>
       </c>
       <c r="C586" s="4" t="s">
-        <v>153</v>
+        <v>788</v>
       </c>
     </row>
     <row r="587" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10567,18 +10564,18 @@
         <v>1142</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>1143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="588" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B588" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="B588" s="1" t="s">
+      <c r="C588" s="4" t="s">
         <v>1145</v>
-      </c>
-      <c r="C588" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="589" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10589,7 +10586,7 @@
         <v>1147</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>107</v>
+        <v>189</v>
       </c>
     </row>
     <row r="590" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10600,51 +10597,51 @@
         <v>1149</v>
       </c>
       <c r="C590" s="4" t="s">
-        <v>1150</v>
+        <v>107</v>
       </c>
     </row>
     <row r="591" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B591" s="3" t="s">
         <v>1151</v>
       </c>
-      <c r="B591" s="3" t="s">
+      <c r="C591" s="5" t="s">
         <v>1152</v>
-      </c>
-      <c r="C591" s="5" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C592" s="4" t="s">
-        <v>659</v>
+        <v>372</v>
       </c>
     </row>
     <row r="593" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B593" s="3" t="s">
         <v>1155</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>1156</v>
+        <v>663</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B594" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="B594" s="1" t="s">
+      <c r="C594" s="4" t="s">
         <v>1158</v>
-      </c>
-      <c r="C594" s="4" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="595" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10655,7 +10652,7 @@
         <v>1160</v>
       </c>
       <c r="C595" s="5" t="s">
-        <v>413</v>
+        <v>919</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10666,7 +10663,7 @@
         <v>1162</v>
       </c>
       <c r="C596" s="4" t="s">
-        <v>29</v>
+        <v>412</v>
       </c>
     </row>
     <row r="597" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10688,7 +10685,7 @@
         <v>1166</v>
       </c>
       <c r="C598" s="4" t="s">
-        <v>277</v>
+        <v>29</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10699,7 +10696,7 @@
         <v>1168</v>
       </c>
       <c r="C599" s="5" t="s">
-        <v>29</v>
+        <v>276</v>
       </c>
     </row>
     <row r="600" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10743,7 +10740,7 @@
         <v>1176</v>
       </c>
       <c r="C603" s="5" t="s">
-        <v>374</v>
+        <v>29</v>
       </c>
     </row>
     <row r="604" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10754,18 +10751,18 @@
         <v>1178</v>
       </c>
       <c r="C604" s="4" t="s">
-        <v>1179</v>
+        <v>372</v>
       </c>
     </row>
     <row r="605" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A605" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B605" s="3" t="s">
         <v>1180</v>
       </c>
-      <c r="B605" s="3" t="s">
+      <c r="C605" s="5" t="s">
         <v>1181</v>
-      </c>
-      <c r="C605" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="606" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10787,7 +10784,7 @@
         <v>1185</v>
       </c>
       <c r="C607" s="5" t="s">
-        <v>516</v>
+        <v>29</v>
       </c>
     </row>
     <row r="608" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10798,7 +10795,7 @@
         <v>1187</v>
       </c>
       <c r="C608" s="4" t="s">
-        <v>29</v>
+        <v>516</v>
       </c>
     </row>
     <row r="609" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10831,18 +10828,18 @@
         <v>1193</v>
       </c>
       <c r="C611" s="5" t="s">
-        <v>1194</v>
+        <v>29</v>
       </c>
     </row>
     <row r="612" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B612" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="B612" s="1" t="s">
+      <c r="C612" s="4" t="s">
         <v>1196</v>
-      </c>
-      <c r="C612" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="613" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10853,18 +10850,18 @@
         <v>1198</v>
       </c>
       <c r="C613" s="5" t="s">
-        <v>1199</v>
+        <v>29</v>
       </c>
     </row>
     <row r="614" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B614" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="B614" s="1" t="s">
+      <c r="C614" s="4" t="s">
         <v>1201</v>
-      </c>
-      <c r="C614" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="615" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10897,18 +10894,18 @@
         <v>1207</v>
       </c>
       <c r="C617" s="5" t="s">
-        <v>1208</v>
+        <v>29</v>
       </c>
     </row>
     <row r="618" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B618" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="B618" s="1" t="s">
+      <c r="C618" s="4" t="s">
         <v>1210</v>
-      </c>
-      <c r="C618" s="4" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="619" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10919,18 +10916,18 @@
         <v>1212</v>
       </c>
       <c r="C619" s="5" t="s">
-        <v>1213</v>
+        <v>516</v>
       </c>
     </row>
     <row r="620" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B620" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="B620" s="1" t="s">
+      <c r="C620" s="4" t="s">
         <v>1215</v>
-      </c>
-      <c r="C620" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="621" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10941,7 +10938,7 @@
         <v>1217</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="622" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10963,18 +10960,18 @@
         <v>1221</v>
       </c>
       <c r="C623" s="5" t="s">
-        <v>1222</v>
+        <v>29</v>
       </c>
     </row>
     <row r="624" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B624" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="B624" s="1" t="s">
+      <c r="C624" s="4" t="s">
         <v>1224</v>
-      </c>
-      <c r="C624" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="625" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10985,37 +10982,37 @@
         <v>1226</v>
       </c>
       <c r="C625" s="5" t="s">
-        <v>1227</v>
+        <v>29</v>
       </c>
     </row>
     <row r="626" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B626" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="B626" s="1" t="s">
-        <v>1229</v>
-      </c>
       <c r="C626" s="4" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="627" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A627" s="3" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B627" s="3" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="C627" s="5" t="s">
-        <v>1005</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="628" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B628" s="1" t="s">
         <v>1231</v>
-      </c>
-      <c r="B628" s="1" t="s">
-        <v>1232</v>
       </c>
       <c r="C628" s="4" t="s">
         <v>205</v>
@@ -11023,40 +11020,40 @@
     </row>
     <row r="629" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A629" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B629" s="3" t="s">
         <v>1233</v>
       </c>
-      <c r="B629" s="3" t="s">
+      <c r="C629" s="5" t="s">
         <v>1234</v>
-      </c>
-      <c r="C629" s="5" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="630" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A630" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B630" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="B630" s="1" t="s">
+      <c r="C630" s="4" t="s">
         <v>1237</v>
-      </c>
-      <c r="C630" s="4" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="631" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A631" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B631" s="3" t="s">
         <v>1239</v>
       </c>
-      <c r="B631" s="3" t="s">
-        <v>1240</v>
-      </c>
       <c r="C631" s="5" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
     <row r="632" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B632" s="1" t="s">
         <v>0</v>
@@ -11067,10 +11064,10 @@
     </row>
     <row r="633" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A633" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B633" s="3" t="s">
         <v>1242</v>
-      </c>
-      <c r="B633" s="3" t="s">
-        <v>1243</v>
       </c>
       <c r="C633" s="5" t="s">
         <v>516</v>
@@ -11078,7 +11075,7 @@
     </row>
     <row r="634" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B634" s="1" t="s">
         <v>0</v>

--- a/المواد.xlsx
+++ b/المواد.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8328"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19368" windowHeight="8328"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="1241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="1240">
   <si>
     <t/>
   </si>
@@ -723,12 +723,15 @@
     <t>M-30 Diluent Reagent 3-part 20L Hematology Mindray</t>
   </si>
   <si>
+    <t>2025082953</t>
+  </si>
+  <si>
+    <t>28/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>2025082954</t>
   </si>
   <si>
-    <t>28/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>M-30R Rinse Reagent 3-part 20L Hematology Mindray</t>
   </si>
   <si>
@@ -1167,12 +1170,12 @@
     <t>LH  kit 2×50T Cl900i Mindray</t>
   </si>
   <si>
+    <t>24/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>2025070111.</t>
   </si>
   <si>
-    <t>24/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>FSH kit 2×50T Cl900i Mindray</t>
   </si>
   <si>
@@ -1944,6 +1947,15 @@
     <t>140125021</t>
   </si>
   <si>
+    <t>( AST (GOT) kit  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140225017</t>
+  </si>
+  <si>
+    <t>13/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>( Ca kit Chemistry Mindray ( Large</t>
   </si>
   <si>
@@ -2457,12 +2469,6 @@
     <t>01/06/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>H.P Ag Cassette 25T hindering (feces)</t>
-  </si>
-  <si>
-    <t>EVA I02125070010</t>
-  </si>
-  <si>
     <t>syphilis Cassette 25T hindering (WB/S/P)</t>
   </si>
   <si>
@@ -2850,12 +2856,6 @@
     <t>Cardiolipin IgM Calibrator Set BioCLIA HOB</t>
   </si>
   <si>
-    <t>Cardiolipin IgM Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Cardiolipin IgM Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
     <t>Cardiolipin Screen Calibrator Set BioCLIA HOB</t>
   </si>
   <si>
@@ -3034,9 +3034,6 @@
   </si>
   <si>
     <t>NT-PROBNP kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>13/03/2027 12:00:00 ص</t>
   </si>
   <si>
     <t>LIPISE kit Chemistry Mindray</t>
@@ -5181,68 +5178,68 @@
     </row>
     <row r="99" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="C99" s="5" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C100" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C101" s="5" t="s">
         <v>242</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C102" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="C103" s="5" t="s">
-        <v>249</v>
+        <v>175</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C104" s="4" t="s">
         <v>250</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5250,21 +5247,21 @@
         <v>251</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C106" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5272,21 +5269,21 @@
         <v>255</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>258</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5316,172 +5313,172 @@
         <v>261</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>263</v>
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C112" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C113" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="B113" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C114" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="B115" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B115" s="3" t="s">
-        <v>273</v>
-      </c>
       <c r="C115" s="5" t="s">
-        <v>274</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C116" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C118" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B119" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>284</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>286</v>
-      </c>
       <c r="C120" s="4" t="s">
-        <v>287</v>
+        <v>186</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>288</v>
-      </c>
-      <c r="B121" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C122" s="4" t="s">
         <v>291</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C123" s="5" t="s">
         <v>294</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C124" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>300</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>84</v>
@@ -5489,13 +5486,13 @@
     </row>
     <row r="127" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B127" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>0</v>
+      <c r="C127" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5514,43 +5511,43 @@
         <v>306</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>308</v>
+        <v>0</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C130" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>0</v>
+        <v>308</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5558,43 +5555,43 @@
         <v>313</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B134" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="C134" s="4" t="s">
-        <v>317</v>
+        <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C135" s="5" t="s">
         <v>318</v>
-      </c>
-      <c r="B135" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B136" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>0</v>
+      <c r="C136" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5624,87 +5621,87 @@
         <v>323</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>135</v>
+        <v>0</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="C140" s="4" t="s">
-        <v>327</v>
+        <v>135</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C141" s="5" t="s">
         <v>328</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C143" s="5" t="s">
         <v>334</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C144" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C145" s="5" t="s">
         <v>340</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>343</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5712,659 +5709,659 @@
         <v>344</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>346</v>
+        <v>0</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C148" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C149" s="5" t="s">
         <v>350</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C150" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C151" s="5" t="s">
         <v>356</v>
-      </c>
-      <c r="B151" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>358</v>
+        <v>84</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C153" s="5" t="s">
         <v>359</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C154" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C155" s="5" t="s">
         <v>364</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="C156" s="4" t="s">
         <v>366</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C157" s="5" t="s">
         <v>369</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C158" s="4" t="s">
         <v>372</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C159" s="5" t="s">
         <v>374</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>377</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B161" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="B161" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="C161" s="5" t="s">
-        <v>380</v>
+        <v>48</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C162" s="4" t="s">
         <v>381</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C162" s="4" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>385</v>
+        <v>355</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>13</v>
+        <v>387</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>390</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>394</v>
+        <v>13</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>396</v>
+        <v>35</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>404</v>
+        <v>355</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>355</v>
+        <v>403</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>411</v>
+        <v>376</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>412</v>
+        <v>356</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C176" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>416</v>
+        <v>355</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>311</v>
+        <v>418</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>370</v>
+        <v>422</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>426</v>
+        <v>312</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>392</v>
+        <v>424</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>220</v>
+        <v>425</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>431</v>
+        <v>393</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>432</v>
+        <v>220</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>354</v>
+        <v>432</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>354</v>
+        <v>405</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>404</v>
+        <v>355</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>447</v>
+        <v>371</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>152</v>
+        <v>446</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>354</v>
+        <v>448</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>76</v>
+        <v>449</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>452</v>
+        <v>393</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>447</v>
+        <v>355</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>454</v>
+        <v>76</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>392</v>
+        <v>453</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>456</v>
+        <v>148</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>370</v>
+        <v>448</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>32</v>
+        <v>455</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>459</v>
+        <v>393</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>462</v>
+        <v>371</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>463</v>
+        <v>32</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C202" s="4" t="s">
         <v>461</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>392</v>
+        <v>465</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>104</v>
+        <v>466</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>392</v>
+        <v>463</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>405</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>459</v>
+        <v>393</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>471</v>
+        <v>104</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6372,318 +6369,318 @@
         <v>470</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>472</v>
+        <v>406</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>431</v>
+        <v>393</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>370</v>
+        <v>453</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>79</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>479</v>
+        <v>432</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>462</v>
+        <v>371</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>482</v>
+        <v>79</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C213" s="5" t="s">
         <v>481</v>
-      </c>
-      <c r="B213" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>51</v>
+        <v>485</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>495</v>
+        <v>51</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>43</v>
+        <v>493</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>503</v>
+        <v>43</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>370</v>
+        <v>506</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>447</v>
+        <v>509</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>515</v>
+        <v>371</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C226" s="4" t="s">
         <v>514</v>
-      </c>
-      <c r="B226" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C226" s="4" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C228" s="4" t="s">
         <v>518</v>
-      </c>
-      <c r="B228" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>0</v>
+        <v>520</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>375</v>
+        <v>522</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>76</v>
+        <v>521</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>160</v>
+        <v>0</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>526</v>
+        <v>76</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>354</v>
+        <v>448</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>528</v>
+        <v>160</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>82</v>
+        <v>527</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>531</v>
+        <v>355</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6691,208 +6688,208 @@
         <v>530</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>533</v>
+        <v>371</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B237" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C237" s="5" t="s">
         <v>533</v>
-      </c>
-      <c r="C237" s="5" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>0</v>
+        <v>534</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>317</v>
+        <v>135</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>540</v>
+        <v>0</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>91</v>
+        <v>318</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>548</v>
+        <v>91</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>13</v>
+        <v>546</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>375</v>
+        <v>548</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>404</v>
+        <v>551</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>554</v>
+        <v>13</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>556</v>
+        <v>376</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C248" s="4" t="s">
         <v>555</v>
-      </c>
-      <c r="B248" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="C248" s="4" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C250" s="4" t="s">
         <v>560</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="C250" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>220</v>
+        <v>563</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>568</v>
+        <v>46</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C253" s="3" t="s">
-        <v>0</v>
+        <v>566</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6900,604 +6897,604 @@
         <v>570</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>574</v>
+        <v>0</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>354</v>
+        <v>576</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>370</v>
+        <v>578</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>97</v>
+        <v>579</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>452</v>
+        <v>355</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>409</v>
+        <v>581</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>452</v>
+        <v>371</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>584</v>
+        <v>97</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>586</v>
+        <v>453</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>226</v>
+        <v>410</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="C263" s="5" t="s">
         <v>585</v>
-      </c>
-      <c r="B263" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>266</v>
+        <v>226</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>16</v>
+        <v>209</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>110</v>
+        <v>267</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>598</v>
+        <v>16</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>601</v>
+        <v>110</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="C270" s="4" t="s">
         <v>599</v>
-      </c>
-      <c r="B270" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="C270" s="4" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>386</v>
+        <v>604</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="C275" s="5" t="s">
         <v>609</v>
-      </c>
-      <c r="B275" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="C275" s="5" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>614</v>
+        <v>387</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>180</v>
+        <v>615</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>226</v>
+        <v>618</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>624</v>
+        <v>180</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="C282" s="4" t="s">
         <v>625</v>
-      </c>
-      <c r="B282" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="C282" s="4" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>630</v>
+        <v>270</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>633</v>
+        <v>337</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="C286" s="4" t="s">
         <v>634</v>
-      </c>
-      <c r="B286" s="1" t="s">
-        <v>635</v>
-      </c>
-      <c r="C286" s="4" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B287" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="C287" s="5" t="s">
         <v>637</v>
-      </c>
-      <c r="C287" s="5" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>29</v>
+        <v>637</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>27</v>
+        <v>639</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>645</v>
+        <v>29</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>651</v>
+        <v>27</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C293" s="5" t="s">
         <v>649</v>
-      </c>
-      <c r="B293" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="C293" s="5" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>120</v>
+        <v>655</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>617</v>
+        <v>397</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>383</v>
+        <v>659</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>664</v>
+        <v>120</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>274</v>
+        <v>618</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>142</v>
+        <v>383</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B301" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="B301" s="3" t="s">
-        <v>669</v>
-      </c>
       <c r="C301" s="5" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>670</v>
+        <v>275</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>672</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>424</v>
+        <v>142</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>673</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>60</v>
+        <v>674</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>675</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>679</v>
+        <v>425</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>386</v>
+        <v>60</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>24</v>
+        <v>680</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7505,117 +7502,117 @@
         <v>684</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>688</v>
+        <v>387</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>686</v>
+        <v>24</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C312" s="4" t="s">
         <v>690</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="C312" s="4" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B314" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="B314" s="1" t="s">
-        <v>696</v>
-      </c>
       <c r="C314" s="4" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>532</v>
+        <v>696</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B316" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="C316" s="4" t="s">
         <v>699</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="C316" s="4" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="C317" s="5" t="s">
         <v>701</v>
-      </c>
-      <c r="B317" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="C317" s="5" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>180</v>
+        <v>533</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>686</v>
+        <v>387</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C320" s="4" t="s">
         <v>216</v>
@@ -7623,35 +7620,35 @@
     </row>
     <row r="321" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>454</v>
+        <v>180</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>500</v>
+        <v>690</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>94</v>
+        <v>216</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7659,224 +7656,224 @@
         <v>713</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>509</v>
+        <v>455</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="B325" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="B325" s="3" t="s">
-        <v>717</v>
-      </c>
       <c r="C325" s="5" t="s">
-        <v>718</v>
+        <v>501</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>721</v>
+        <v>94</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>724</v>
+        <v>510</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>402</v>
+        <v>731</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="B333" s="3" t="s">
         <v>736</v>
       </c>
-      <c r="B333" s="3" t="s">
-        <v>739</v>
-      </c>
       <c r="C333" s="5" t="s">
-        <v>509</v>
+        <v>737</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>742</v>
+        <v>403</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>748</v>
+        <v>510</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="C337" s="5" t="s">
         <v>746</v>
-      </c>
-      <c r="B337" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="C337" s="5" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="B340" s="1" t="s">
-        <v>756</v>
-      </c>
       <c r="C340" s="4" t="s">
-        <v>757</v>
+        <v>625</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C341" s="3" t="s">
-        <v>0</v>
+        <v>755</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C342" s="4" t="s">
         <v>759</v>
-      </c>
-      <c r="B342" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C342" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="B343" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="B343" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C343" s="3" t="s">
-        <v>0</v>
+      <c r="C343" s="5" t="s">
+        <v>761</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>0</v>
@@ -7887,123 +7884,123 @@
     </row>
     <row r="345" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="C345" s="5" t="s">
-        <v>764</v>
+        <v>0</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="C346" s="4" t="s">
-        <v>767</v>
+        <v>0</v>
+      </c>
+      <c r="C346" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="C347" s="5" t="s">
-        <v>655</v>
+        <v>0</v>
+      </c>
+      <c r="C347" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B348" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="C348" s="4" t="s">
         <v>768</v>
-      </c>
-      <c r="B348" s="1" t="s">
-        <v>770</v>
-      </c>
-      <c r="C348" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="C349" s="5" t="s">
         <v>771</v>
-      </c>
-      <c r="B349" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C349" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B350" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="B350" s="1" t="s">
-        <v>774</v>
-      </c>
       <c r="C350" s="4" t="s">
-        <v>775</v>
+        <v>659</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>480</v>
+        <v>41</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>511</v>
+        <v>19</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>371</v>
+        <v>779</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>0</v>
+        <v>781</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B355" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="B355" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C355" s="3" t="s">
-        <v>0</v>
+      <c r="C355" s="5" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8011,37 +8008,37 @@
         <v>784</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C356" s="1" t="s">
-        <v>0</v>
+        <v>785</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="C357" s="5" t="s">
-        <v>787</v>
+        <v>0</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>788</v>
-      </c>
-      <c r="C358" s="4" t="s">
-        <v>789</v>
+        <v>0</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>0</v>
@@ -8052,277 +8049,277 @@
     </row>
     <row r="360" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="C360" s="4" t="s">
         <v>791</v>
-      </c>
-      <c r="B360" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="C360" s="4" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="C361" s="5" t="s">
         <v>793</v>
-      </c>
-      <c r="B361" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="C361" s="5" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="C362" s="4" t="s">
-        <v>46</v>
+        <v>0</v>
+      </c>
+      <c r="C362" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>800</v>
+        <v>242</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>598</v>
+        <v>799</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>805</v>
+        <v>46</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>811</v>
+        <v>599</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8330,43 +8327,43 @@
         <v>845</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>848</v>
+        <v>815</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>811</v>
+        <v>850</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8374,87 +8371,87 @@
         <v>853</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="B390" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="B390" s="1" t="s">
-        <v>857</v>
-      </c>
       <c r="C390" s="4" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>866</v>
+        <v>815</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>405</v>
+        <v>815</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>482</v>
+        <v>868</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8462,252 +8459,252 @@
         <v>869</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>482</v>
+        <v>406</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="B398" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="B398" s="1" t="s">
-        <v>873</v>
-      </c>
       <c r="C398" s="4" t="s">
-        <v>165</v>
+        <v>483</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>876</v>
+        <v>483</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>330</v>
+        <v>148</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>123</v>
+        <v>331</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>113</v>
+        <v>888</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>893</v>
+        <v>123</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>892</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>893</v>
+        <v>113</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="B408" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="C408" s="4" t="s">
         <v>895</v>
-      </c>
-      <c r="B408" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="C408" s="4" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>608</v>
+        <v>899</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>471</v>
+        <v>609</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>913</v>
+        <v>472</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>283</v>
+        <v>918</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C418" s="1" t="s">
-        <v>0</v>
+        <v>920</v>
+      </c>
+      <c r="C418" s="4" t="s">
+        <v>921</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="B419" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="B419" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C419" s="3" t="s">
-        <v>0</v>
+      <c r="C419" s="5" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8737,10 +8734,10 @@
         <v>926</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>873</v>
-      </c>
-      <c r="C422" s="4" t="s">
-        <v>165</v>
+        <v>0</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8748,10 +8745,10 @@
         <v>927</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="C423" s="5" t="s">
-        <v>876</v>
+        <v>0</v>
+      </c>
+      <c r="C423" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8759,10 +8756,10 @@
         <v>928</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8770,10 +8767,10 @@
         <v>929</v>
       </c>
       <c r="B425" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="C425" s="5" t="s">
         <v>878</v>
-      </c>
-      <c r="C425" s="5" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8781,7 +8778,7 @@
         <v>930</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C426" s="4" t="s">
         <v>148</v>
@@ -8795,7 +8792,7 @@
         <v>880</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>881</v>
+        <v>148</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8806,7 +8803,7 @@
         <v>880</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>881</v>
+        <v>148</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8814,10 +8811,10 @@
         <v>933</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8825,32 +8822,32 @@
         <v>934</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>935</v>
+        <v>882</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>936</v>
+        <v>883</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>935</v>
+        <v>882</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>936</v>
+        <v>883</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B432" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="C432" s="4" t="s">
         <v>938</v>
-      </c>
-      <c r="B432" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="C432" s="4" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8858,10 +8855,10 @@
         <v>939</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>883</v>
+        <v>937</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>330</v>
+        <v>938</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8869,32 +8866,32 @@
         <v>940</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>578</v>
+        <v>938</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>885</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>886</v>
+        <v>331</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="B436" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="B436" s="1" t="s">
-        <v>885</v>
-      </c>
       <c r="C436" s="4" t="s">
-        <v>886</v>
+        <v>579</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8902,10 +8899,10 @@
         <v>944</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8913,7 +8910,7 @@
         <v>945</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C438" s="4" t="s">
         <v>123</v>
@@ -8924,7 +8921,7 @@
         <v>946</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C439" s="5" t="s">
         <v>123</v>
@@ -8935,7 +8932,7 @@
         <v>947</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C440" s="4" t="s">
         <v>123</v>
@@ -8946,7 +8943,7 @@
         <v>948</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C441" s="5" t="s">
         <v>113</v>
@@ -8957,7 +8954,7 @@
         <v>949</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C442" s="4" t="s">
         <v>113</v>
@@ -8968,7 +8965,7 @@
         <v>950</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C443" s="5" t="s">
         <v>113</v>
@@ -8982,7 +8979,7 @@
         <v>952</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9001,10 +8998,10 @@
         <v>956</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9012,10 +9009,10 @@
         <v>957</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9023,10 +9020,10 @@
         <v>958</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9034,10 +9031,10 @@
         <v>959</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9045,10 +9042,10 @@
         <v>960</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9056,10 +9053,10 @@
         <v>961</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9067,10 +9064,10 @@
         <v>962</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9078,10 +9075,10 @@
         <v>963</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9089,10 +9086,10 @@
         <v>964</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9100,10 +9097,10 @@
         <v>965</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9111,10 +9108,10 @@
         <v>966</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9122,10 +9119,10 @@
         <v>967</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9136,7 +9133,7 @@
         <v>969</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9147,7 +9144,7 @@
         <v>970</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9158,7 +9155,7 @@
         <v>972</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9166,10 +9163,10 @@
         <v>971</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9177,10 +9174,10 @@
         <v>973</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9188,10 +9185,10 @@
         <v>974</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9199,10 +9196,10 @@
         <v>975</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9210,10 +9207,10 @@
         <v>976</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9221,10 +9218,10 @@
         <v>977</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9232,10 +9229,10 @@
         <v>978</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9243,10 +9240,10 @@
         <v>979</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9287,10 +9284,10 @@
         <v>985</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9298,10 +9295,10 @@
         <v>986</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9309,10 +9306,10 @@
         <v>987</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9397,7 +9394,7 @@
         <v>1002</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C482" s="4" t="s">
         <v>1003</v>
@@ -9408,26 +9405,26 @@
         <v>1004</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>1005</v>
+        <v>644</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B484" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="B484" s="1" t="s">
+      <c r="C484" s="4" t="s">
         <v>1007</v>
-      </c>
-      <c r="C484" s="4" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>0</v>
@@ -9438,128 +9435,128 @@
     </row>
     <row r="486" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B486" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="B486" s="1" t="s">
-        <v>1011</v>
-      </c>
       <c r="C486" s="4" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B487" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="B487" s="3" t="s">
-        <v>1013</v>
-      </c>
       <c r="C487" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B488" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="B488" s="1" t="s">
-        <v>1015</v>
-      </c>
       <c r="C488" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B489" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C489" s="5" t="s">
         <v>1016</v>
-      </c>
-      <c r="C489" s="5" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B490" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="B490" s="1" t="s">
-        <v>1019</v>
-      </c>
       <c r="C490" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B492" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="B492" s="1" t="s">
+      <c r="C492" s="4" t="s">
         <v>1022</v>
-      </c>
-      <c r="C492" s="4" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B493" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C493" s="5" t="s">
         <v>1024</v>
-      </c>
-      <c r="C493" s="5" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B494" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="B494" s="1" t="s">
-        <v>1027</v>
-      </c>
       <c r="C494" s="4" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>989</v>
@@ -9570,359 +9567,359 @@
     </row>
     <row r="498" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B502" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="B502" s="1" t="s">
+      <c r="C502" s="4" t="s">
         <v>1036</v>
-      </c>
-      <c r="C502" s="4" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B503" s="3" t="s">
         <v>1038</v>
       </c>
-      <c r="B503" s="3" t="s">
-        <v>1039</v>
-      </c>
       <c r="C503" s="5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B506" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="B506" s="1" t="s">
+      <c r="C506" s="4" t="s">
         <v>1043</v>
-      </c>
-      <c r="C506" s="4" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B507" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C507" s="5" t="s">
         <v>1043</v>
-      </c>
-      <c r="C507" s="5" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B508" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C508" s="4" t="s">
         <v>1043</v>
-      </c>
-      <c r="C508" s="4" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B509" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C509" s="5" t="s">
         <v>1043</v>
-      </c>
-      <c r="C509" s="5" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B510" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="B510" s="1" t="s">
-        <v>1049</v>
-      </c>
       <c r="C510" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B514" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="B514" s="1" t="s">
+      <c r="C514" s="4" t="s">
         <v>1054</v>
-      </c>
-      <c r="C514" s="4" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B515" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C515" s="5" t="s">
         <v>1054</v>
-      </c>
-      <c r="C515" s="5" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B516" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C516" s="4" t="s">
         <v>1054</v>
-      </c>
-      <c r="C516" s="4" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B517" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C517" s="5" t="s">
         <v>1054</v>
-      </c>
-      <c r="C517" s="5" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B518" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="B518" s="1" t="s">
-        <v>1060</v>
-      </c>
       <c r="C518" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B522" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="B522" s="1" t="s">
-        <v>1065</v>
-      </c>
       <c r="C522" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B526" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="B526" s="1" t="s">
+      <c r="C526" s="4" t="s">
         <v>1070</v>
-      </c>
-      <c r="C526" s="4" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B527" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C527" s="5" t="s">
         <v>1070</v>
-      </c>
-      <c r="C527" s="5" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B528" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C528" s="4" t="s">
         <v>1070</v>
-      </c>
-      <c r="C528" s="4" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B529" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C529" s="5" t="s">
         <v>1070</v>
-      </c>
-      <c r="C529" s="5" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B530" s="1" t="s">
         <v>981</v>
@@ -9933,7 +9930,7 @@
     </row>
     <row r="531" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B531" s="3" t="s">
         <v>981</v>
@@ -9944,7 +9941,7 @@
     </row>
     <row r="532" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B532" s="1" t="s">
         <v>981</v>
@@ -9955,7 +9952,7 @@
     </row>
     <row r="533" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B533" s="3" t="s">
         <v>981</v>
@@ -9966,175 +9963,175 @@
     </row>
     <row r="534" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B534" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="B534" s="1" t="s">
-        <v>1080</v>
-      </c>
       <c r="C534" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C538" s="4" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B546" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C546" s="4" t="s">
         <v>1054</v>
-      </c>
-      <c r="C546" s="4" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B547" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C547" s="5" t="s">
         <v>1054</v>
-      </c>
-      <c r="C547" s="5" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B548" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C548" s="4" t="s">
         <v>1054</v>
-      </c>
-      <c r="C548" s="4" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C549" s="5" t="s">
         <v>148</v>
@@ -10142,10 +10139,10 @@
     </row>
     <row r="550" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C550" s="4" t="s">
         <v>148</v>
@@ -10153,10 +10150,10 @@
     </row>
     <row r="551" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C551" s="5" t="s">
         <v>148</v>
@@ -10164,10 +10161,10 @@
     </row>
     <row r="552" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C552" s="4" t="s">
         <v>148</v>
@@ -10175,271 +10172,271 @@
     </row>
     <row r="553" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B553" s="3" t="s">
         <v>1099</v>
       </c>
-      <c r="B553" s="3" t="s">
+      <c r="C553" s="5" t="s">
         <v>1100</v>
-      </c>
-      <c r="C553" s="5" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B554" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C554" s="4" t="s">
         <v>1100</v>
-      </c>
-      <c r="C554" s="4" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B555" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C555" s="5" t="s">
         <v>1100</v>
-      </c>
-      <c r="C555" s="5" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B556" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C556" s="4" t="s">
         <v>1100</v>
-      </c>
-      <c r="C556" s="4" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B560" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="B560" s="1" t="s">
+      <c r="C560" s="4" t="s">
         <v>1109</v>
-      </c>
-      <c r="C560" s="4" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B561" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C561" s="5" t="s">
         <v>1109</v>
-      </c>
-      <c r="C561" s="5" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B562" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C562" s="4" t="s">
         <v>1109</v>
-      </c>
-      <c r="C562" s="4" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B563" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C563" s="5" t="s">
         <v>1109</v>
-      </c>
-      <c r="C563" s="5" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C568" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C569" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C570" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B572" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="B572" s="1" t="s">
-        <v>1123</v>
-      </c>
       <c r="C572" s="4" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C574" s="4" t="s">
         <v>1125</v>
-      </c>
-      <c r="B574" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="C574" s="4" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="576" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B576" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="B576" s="1" t="s">
+      <c r="C576" s="4" t="s">
         <v>1129</v>
-      </c>
-      <c r="C576" s="4" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="577" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B577" s="3" t="s">
         <v>0</v>
@@ -10450,7 +10447,7 @@
     </row>
     <row r="578" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B578" s="1" t="s">
         <v>0</v>
@@ -10461,32 +10458,32 @@
     </row>
     <row r="579" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B579" s="3" t="s">
         <v>1133</v>
       </c>
-      <c r="B579" s="3" t="s">
+      <c r="C579" s="5" t="s">
         <v>1134</v>
-      </c>
-      <c r="C579" s="5" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="580" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B580" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B580" s="1" t="s">
-        <v>1137</v>
-      </c>
       <c r="C580" s="4" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
     </row>
     <row r="581" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B581" s="3" t="s">
         <v>1138</v>
-      </c>
-      <c r="B581" s="3" t="s">
-        <v>1139</v>
       </c>
       <c r="C581" s="5" t="s">
         <v>152</v>
@@ -10494,21 +10491,21 @@
     </row>
     <row r="582" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B582" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="B582" s="1" t="s">
+      <c r="C582" s="4" t="s">
         <v>1141</v>
-      </c>
-      <c r="C582" s="4" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="583" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B583" s="3" t="s">
         <v>1143</v>
-      </c>
-      <c r="B583" s="3" t="s">
-        <v>1144</v>
       </c>
       <c r="C583" s="5" t="s">
         <v>188</v>
@@ -10516,10 +10513,10 @@
     </row>
     <row r="584" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B584" s="1" t="s">
         <v>1145</v>
-      </c>
-      <c r="B584" s="1" t="s">
-        <v>1146</v>
       </c>
       <c r="C584" s="4" t="s">
         <v>107</v>
@@ -10527,76 +10524,76 @@
     </row>
     <row r="585" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B585" s="3" t="s">
         <v>1147</v>
       </c>
-      <c r="B585" s="3" t="s">
+      <c r="C585" s="5" t="s">
         <v>1148</v>
-      </c>
-      <c r="C585" s="5" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B586" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="B586" s="1" t="s">
-        <v>1151</v>
-      </c>
       <c r="C586" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="587" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A587" s="3" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
     <row r="588" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B588" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="B588" s="1" t="s">
+      <c r="C588" s="4" t="s">
         <v>1154</v>
-      </c>
-      <c r="C588" s="4" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="589" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B589" s="3" t="s">
         <v>1156</v>
       </c>
-      <c r="B589" s="3" t="s">
-        <v>1157</v>
-      </c>
       <c r="C589" s="5" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="590" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B590" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B590" s="1" t="s">
-        <v>1159</v>
-      </c>
       <c r="C590" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="591" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B591" s="3" t="s">
         <v>1160</v>
-      </c>
-      <c r="B591" s="3" t="s">
-        <v>1161</v>
       </c>
       <c r="C591" s="5" t="s">
         <v>29</v>
@@ -10604,10 +10601,10 @@
     </row>
     <row r="592" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B592" s="1" t="s">
         <v>1162</v>
-      </c>
-      <c r="B592" s="1" t="s">
-        <v>1163</v>
       </c>
       <c r="C592" s="4" t="s">
         <v>29</v>
@@ -10615,21 +10612,21 @@
     </row>
     <row r="593" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B593" s="3" t="s">
         <v>1164</v>
       </c>
-      <c r="B593" s="3" t="s">
-        <v>1165</v>
-      </c>
       <c r="C593" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B594" s="1" t="s">
         <v>1166</v>
-      </c>
-      <c r="B594" s="1" t="s">
-        <v>1167</v>
       </c>
       <c r="C594" s="4" t="s">
         <v>29</v>
@@ -10637,10 +10634,10 @@
     </row>
     <row r="595" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A595" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B595" s="3" t="s">
         <v>1168</v>
-      </c>
-      <c r="B595" s="3" t="s">
-        <v>1169</v>
       </c>
       <c r="C595" s="5" t="s">
         <v>29</v>
@@ -10648,10 +10645,10 @@
     </row>
     <row r="596" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B596" s="1" t="s">
         <v>1170</v>
-      </c>
-      <c r="B596" s="1" t="s">
-        <v>1171</v>
       </c>
       <c r="C596" s="4" t="s">
         <v>29</v>
@@ -10659,10 +10656,10 @@
     </row>
     <row r="597" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A597" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B597" s="3" t="s">
         <v>1172</v>
-      </c>
-      <c r="B597" s="3" t="s">
-        <v>1173</v>
       </c>
       <c r="C597" s="5" t="s">
         <v>29</v>
@@ -10670,32 +10667,32 @@
     </row>
     <row r="598" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B598" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="B598" s="1" t="s">
-        <v>1175</v>
-      </c>
       <c r="C598" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A599" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B599" s="3" t="s">
         <v>1176</v>
       </c>
-      <c r="B599" s="3" t="s">
+      <c r="C599" s="5" t="s">
         <v>1177</v>
-      </c>
-      <c r="C599" s="5" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="600" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B600" s="1" t="s">
         <v>1179</v>
-      </c>
-      <c r="B600" s="1" t="s">
-        <v>1180</v>
       </c>
       <c r="C600" s="4" t="s">
         <v>29</v>
@@ -10703,10 +10700,10 @@
     </row>
     <row r="601" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A601" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B601" s="3" t="s">
         <v>1181</v>
-      </c>
-      <c r="B601" s="3" t="s">
-        <v>1182</v>
       </c>
       <c r="C601" s="5" t="s">
         <v>29</v>
@@ -10714,21 +10711,21 @@
     </row>
     <row r="602" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B602" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="B602" s="1" t="s">
-        <v>1184</v>
-      </c>
       <c r="C602" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A603" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B603" s="3" t="s">
         <v>1185</v>
-      </c>
-      <c r="B603" s="3" t="s">
-        <v>1186</v>
       </c>
       <c r="C603" s="5" t="s">
         <v>29</v>
@@ -10736,10 +10733,10 @@
     </row>
     <row r="604" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B604" s="1" t="s">
         <v>1187</v>
-      </c>
-      <c r="B604" s="1" t="s">
-        <v>1188</v>
       </c>
       <c r="C604" s="4" t="s">
         <v>29</v>
@@ -10747,10 +10744,10 @@
     </row>
     <row r="605" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A605" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B605" s="3" t="s">
         <v>1189</v>
-      </c>
-      <c r="B605" s="3" t="s">
-        <v>1190</v>
       </c>
       <c r="C605" s="5" t="s">
         <v>29</v>
@@ -10758,21 +10755,21 @@
     </row>
     <row r="606" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B606" s="1" t="s">
         <v>1191</v>
       </c>
-      <c r="B606" s="1" t="s">
+      <c r="C606" s="4" t="s">
         <v>1192</v>
-      </c>
-      <c r="C606" s="4" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="607" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A607" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B607" s="3" t="s">
         <v>1194</v>
-      </c>
-      <c r="B607" s="3" t="s">
-        <v>1195</v>
       </c>
       <c r="C607" s="5" t="s">
         <v>29</v>
@@ -10780,21 +10777,21 @@
     </row>
     <row r="608" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A608" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B608" s="1" t="s">
         <v>1196</v>
       </c>
-      <c r="B608" s="1" t="s">
+      <c r="C608" s="4" t="s">
         <v>1197</v>
-      </c>
-      <c r="C608" s="4" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="609" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A609" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B609" s="3" t="s">
         <v>1199</v>
-      </c>
-      <c r="B609" s="3" t="s">
-        <v>1200</v>
       </c>
       <c r="C609" s="5" t="s">
         <v>29</v>
@@ -10802,10 +10799,10 @@
     </row>
     <row r="610" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B610" s="1" t="s">
         <v>1201</v>
-      </c>
-      <c r="B610" s="1" t="s">
-        <v>1202</v>
       </c>
       <c r="C610" s="4" t="s">
         <v>29</v>
@@ -10813,10 +10810,10 @@
     </row>
     <row r="611" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A611" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B611" s="3" t="s">
         <v>1203</v>
-      </c>
-      <c r="B611" s="3" t="s">
-        <v>1204</v>
       </c>
       <c r="C611" s="5" t="s">
         <v>29</v>
@@ -10824,43 +10821,43 @@
     </row>
     <row r="612" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B612" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="B612" s="1" t="s">
+      <c r="C612" s="4" t="s">
         <v>1206</v>
-      </c>
-      <c r="C612" s="4" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="613" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A613" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B613" s="3" t="s">
         <v>1208</v>
       </c>
-      <c r="B613" s="3" t="s">
-        <v>1209</v>
-      </c>
       <c r="C613" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="614" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A614" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B614" s="1" t="s">
         <v>1210</v>
       </c>
-      <c r="B614" s="1" t="s">
+      <c r="C614" s="4" t="s">
         <v>1211</v>
-      </c>
-      <c r="C614" s="4" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="615" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A615" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B615" s="3" t="s">
         <v>1213</v>
-      </c>
-      <c r="B615" s="3" t="s">
-        <v>1214</v>
       </c>
       <c r="C615" s="5" t="s">
         <v>48</v>
@@ -10868,10 +10865,10 @@
     </row>
     <row r="616" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A616" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B616" s="1" t="s">
         <v>1215</v>
-      </c>
-      <c r="B616" s="1" t="s">
-        <v>1216</v>
       </c>
       <c r="C616" s="4" t="s">
         <v>29</v>
@@ -10879,10 +10876,10 @@
     </row>
     <row r="617" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A617" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B617" s="3" t="s">
         <v>1217</v>
-      </c>
-      <c r="B617" s="3" t="s">
-        <v>1218</v>
       </c>
       <c r="C617" s="5" t="s">
         <v>29</v>
@@ -10890,21 +10887,21 @@
     </row>
     <row r="618" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B618" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="B618" s="1" t="s">
+      <c r="C618" s="4" t="s">
         <v>1220</v>
-      </c>
-      <c r="C618" s="4" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="619" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A619" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B619" s="3" t="s">
         <v>1222</v>
-      </c>
-      <c r="B619" s="3" t="s">
-        <v>1223</v>
       </c>
       <c r="C619" s="5" t="s">
         <v>29</v>
@@ -10912,32 +10909,32 @@
     </row>
     <row r="620" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B620" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="B620" s="1" t="s">
-        <v>1225</v>
-      </c>
       <c r="C620" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="621" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A621" s="3" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B621" s="3" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C621" s="5" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="622" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A622" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B622" s="1" t="s">
         <v>1227</v>
-      </c>
-      <c r="B622" s="1" t="s">
-        <v>1228</v>
       </c>
       <c r="C622" s="4" t="s">
         <v>203</v>
@@ -10945,40 +10942,40 @@
     </row>
     <row r="623" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A623" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B623" s="3" t="s">
         <v>1229</v>
       </c>
-      <c r="B623" s="3" t="s">
+      <c r="C623" s="5" t="s">
         <v>1230</v>
-      </c>
-      <c r="C623" s="5" t="s">
-        <v>1231</v>
       </c>
     </row>
     <row r="624" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B624" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="B624" s="1" t="s">
+      <c r="C624" s="4" t="s">
         <v>1233</v>
-      </c>
-      <c r="C624" s="4" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="625" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A625" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B625" s="3" t="s">
         <v>1235</v>
       </c>
-      <c r="B625" s="3" t="s">
-        <v>1236</v>
-      </c>
       <c r="C625" s="5" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="626" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A626" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B626" s="1" t="s">
         <v>0</v>
@@ -10989,18 +10986,18 @@
     </row>
     <row r="627" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A627" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B627" s="3" t="s">
         <v>1238</v>
       </c>
-      <c r="B627" s="3" t="s">
-        <v>1239</v>
-      </c>
       <c r="C627" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="628" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A628" s="1" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B628" s="1" t="s">
         <v>0</v>

--- a/المواد.xlsx
+++ b/المواد.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8328"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="4908"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,24 +19,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="1202">
-  <si>
-    <t>ارصدة المخازن</t>
-  </si>
-  <si>
-    <t>الى تاريخ :06/04/2026 12:00:00 ص</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="1197">
   <si>
     <t/>
-  </si>
-  <si>
-    <t>المخزن : الكل</t>
-  </si>
-  <si>
-    <t>العلامة التجارية : الكل</t>
-  </si>
-  <si>
-    <t>ادخل المجهز  : الكل</t>
   </si>
   <si>
     <t>اسم المادة</t>
@@ -3986,84 +3971,84 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="3" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>20</v>
@@ -4085,95 +4070,95 @@
     </row>
     <row r="10" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>46</v>
@@ -4195,73 +4180,73 @@
     </row>
     <row r="20" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>69</v>
@@ -4272,101 +4257,101 @@
     </row>
     <row r="27" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="C27" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>76</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4388,128 +4373,128 @@
         <v>99</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>107</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="C43" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="C46" s="4" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4520,29 +4505,29 @@
         <v>126</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>127</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>52</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4550,32 +4535,32 @@
         <v>130</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4583,37 +4568,37 @@
         <v>135</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>139</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>64</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>144</v>
@@ -4624,18 +4609,18 @@
     </row>
     <row r="59" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>149</v>
@@ -4646,40 +4631,40 @@
     </row>
     <row r="61" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="C63" s="5" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>158</v>
@@ -4690,10 +4675,10 @@
     </row>
     <row r="65" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>159</v>
@@ -4701,13 +4686,13 @@
     </row>
     <row r="66" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4715,7 +4700,7 @@
         <v>162</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>164</v>
@@ -4726,7 +4711,7 @@
         <v>162</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>164</v>
@@ -4734,24 +4719,24 @@
     </row>
     <row r="69" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="C69" s="5" t="s">
-        <v>169</v>
+        <v>39</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>170</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4762,45 +4747,45 @@
         <v>172</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>44</v>
+        <v>173</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>181</v>
@@ -4811,7 +4796,7 @@
     </row>
     <row r="76" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>183</v>
@@ -4833,13 +4818,13 @@
     </row>
     <row r="78" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4850,40 +4835,40 @@
         <v>191</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>145</v>
+        <v>187</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4891,10 +4876,10 @@
         <v>195</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4902,21 +4887,21 @@
         <v>195</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>192</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4924,10 +4909,10 @@
         <v>200</v>
       </c>
       <c r="B86" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>202</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4949,7 +4934,7 @@
         <v>206</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4957,98 +4942,98 @@
         <v>205</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C89" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="C90" s="4" t="s">
-        <v>204</v>
+        <v>159</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>213</v>
+        <v>159</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="C93" s="5" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B96" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="C96" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>224</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5059,18 +5044,18 @@
         <v>226</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="C99" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5081,73 +5066,73 @@
         <v>231</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>182</v>
+        <v>232</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>236</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="C103" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>241</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>247</v>
+        <v>170</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5163,24 +5148,24 @@
     </row>
     <row r="108" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B108" s="1" t="s">
-        <v>252</v>
-      </c>
       <c r="C108" s="4" t="s">
-        <v>175</v>
+        <v>250</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5188,7 +5173,7 @@
         <v>253</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>255</v>
@@ -5196,101 +5181,101 @@
     </row>
     <row r="111" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="4" t="s">
         <v>259</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>255</v>
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>264</v>
+        <v>0</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>2</v>
+        <v>264</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B117" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B117" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>2</v>
+      <c r="C117" s="5" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>273</v>
+        <v>154</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5306,13 +5291,13 @@
     </row>
     <row r="121" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="C121" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5350,211 +5335,211 @@
     </row>
     <row r="125" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>290</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>291</v>
+        <v>182</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B127" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="C127" s="5" t="s">
         <v>293</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>295</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>187</v>
+        <v>50</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="C129" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B130" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="C130" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="C130" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>314</v>
+        <v>0</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>317</v>
+        <v>0</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>2</v>
+        <v>316</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B138" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>2</v>
+      <c r="C138" s="4" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>325</v>
+        <v>0</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B141" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="B141" s="3" t="s">
-        <v>321</v>
-      </c>
       <c r="C141" s="5" t="s">
-        <v>322</v>
+        <v>92</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C142" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B143" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="C143" s="5" t="s">
         <v>328</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5565,202 +5550,202 @@
         <v>330</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>331</v>
+        <v>42</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>333</v>
+        <v>0</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>47</v>
+        <v>0</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>2</v>
+        <v>336</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>2</v>
+        <v>337</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B151" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="C151" s="5" t="s">
         <v>341</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>355</v>
+        <v>0</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="B157" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="C157" s="5" t="s">
         <v>357</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>2</v>
+      <c r="C158" s="4" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>361</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>362</v>
+        <v>106</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="C160" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>366</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>111</v>
+        <v>367</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>369</v>
@@ -5768,43 +5753,43 @@
     </row>
     <row r="163" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B163" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="C163" s="5" t="s">
         <v>371</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C164" s="4" t="s">
         <v>373</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B165" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C165" s="5" t="s">
         <v>375</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>378</v>
@@ -5812,10 +5797,10 @@
     </row>
     <row r="167" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B167" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>371</v>
       </c>
       <c r="C167" s="5" t="s">
         <v>380</v>
@@ -5834,10 +5819,10 @@
     </row>
     <row r="169" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>385</v>
@@ -5881,7 +5866,7 @@
         <v>394</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>395</v>
@@ -5900,10 +5885,10 @@
     </row>
     <row r="175" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B175" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>371</v>
       </c>
       <c r="C175" s="5" t="s">
         <v>400</v>
@@ -5922,13 +5907,13 @@
     </row>
     <row r="177" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>405</v>
+        <v>204</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5936,73 +5921,73 @@
         <v>406</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>407</v>
+        <v>366</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>408</v>
+        <v>312</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>410</v>
+        <v>366</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>209</v>
+        <v>408</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>317</v>
+        <v>278</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>283</v>
+        <v>413</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C183" s="5" t="s">
         <v>415</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B184" s="1" t="s">
         <v>417</v>
-      </c>
-      <c r="B184" s="1" t="s">
-        <v>404</v>
       </c>
       <c r="C184" s="4" t="s">
         <v>418</v>
@@ -6013,7 +5998,7 @@
         <v>419</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="C185" s="5" t="s">
         <v>420</v>
@@ -6024,32 +6009,32 @@
         <v>421</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C187" s="5" t="s">
         <v>424</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C187" s="5" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C188" s="4" t="s">
         <v>426</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C188" s="4" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6060,15 +6045,15 @@
         <v>428</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>429</v>
+        <v>320</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B190" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>428</v>
       </c>
       <c r="C190" s="4" t="s">
         <v>431</v>
@@ -6079,10 +6064,10 @@
         <v>432</v>
       </c>
       <c r="B191" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C191" s="5" t="s">
         <v>433</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6101,7 +6086,7 @@
         <v>437</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="C193" s="5" t="s">
         <v>438</v>
@@ -6112,139 +6097,139 @@
         <v>439</v>
       </c>
       <c r="B194" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C194" s="4" t="s">
         <v>440</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>443</v>
+        <v>312</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>445</v>
+        <v>65</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>317</v>
+        <v>444</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>70</v>
+        <v>173</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>404</v>
+        <v>366</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>152</v>
+        <v>451</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>454</v>
+        <v>27</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C205" s="5" t="s">
         <v>457</v>
-      </c>
-      <c r="B205" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C205" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B206" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="B206" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="C206" s="4" t="s">
         <v>459</v>
@@ -6255,76 +6240,76 @@
         <v>460</v>
       </c>
       <c r="B207" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C207" s="5" t="s">
         <v>461</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B208" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C208" s="4" t="s">
         <v>463</v>
-      </c>
-      <c r="C208" s="4" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>461</v>
+        <v>405</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>468</v>
+        <v>413</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B211" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="B211" s="3" t="s">
-        <v>410</v>
-      </c>
       <c r="C211" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>418</v>
+        <v>469</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>472</v>
+        <v>382</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>473</v>
+        <v>74</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6332,40 +6317,40 @@
         <v>471</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>410</v>
+        <v>472</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C215" s="5" t="s">
         <v>475</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="C216" s="4" t="s">
         <v>477</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B217" s="3" t="s">
         <v>479</v>
-      </c>
-      <c r="B217" s="3" t="s">
-        <v>461</v>
       </c>
       <c r="C217" s="5" t="s">
         <v>480</v>
@@ -6373,18 +6358,18 @@
     </row>
     <row r="218" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>484</v>
@@ -6401,81 +6386,81 @@
         <v>487</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>488</v>
+        <v>300</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>489</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>490</v>
+        <v>39</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="C222" s="4" t="s">
-        <v>305</v>
+        <v>106</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B223" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="C223" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="C224" s="4" t="s">
-        <v>111</v>
+        <v>326</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B225" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="C225" s="5" t="s">
         <v>498</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>500</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>331</v>
+        <v>501</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>502</v>
+        <v>382</v>
       </c>
       <c r="C227" s="5" t="s">
         <v>503</v>
@@ -6486,18 +6471,18 @@
         <v>504</v>
       </c>
       <c r="B228" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C228" s="4" t="s">
         <v>505</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B229" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>387</v>
       </c>
       <c r="C229" s="5" t="s">
         <v>508</v>
@@ -6505,32 +6490,32 @@
     </row>
     <row r="230" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C230" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="B230" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C230" s="4" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B231" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="B231" s="3" t="s">
-        <v>512</v>
-      </c>
       <c r="C231" s="5" t="s">
-        <v>513</v>
+        <v>179</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>364</v>
+        <v>513</v>
       </c>
       <c r="C232" s="4" t="s">
         <v>514</v>
@@ -6538,24 +6523,24 @@
     </row>
     <row r="233" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B233" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="B233" s="3" t="s">
-        <v>516</v>
-      </c>
       <c r="C233" s="5" t="s">
-        <v>184</v>
+        <v>514</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="C234" s="4" t="s">
-        <v>519</v>
+        <v>0</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6563,87 +6548,87 @@
         <v>517</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>520</v>
+        <v>361</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>519</v>
+        <v>70</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>2</v>
+        <v>377</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>75</v>
+        <v>520</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>159</v>
+        <v>449</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>371</v>
+        <v>524</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>454</v>
+        <v>525</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>404</v>
+        <v>526</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>519</v>
+        <v>47</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>530</v>
+        <v>47</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6651,32 +6636,32 @@
         <v>528</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="C243" s="5" t="s">
-        <v>52</v>
+        <v>0</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>52</v>
+        <v>326</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C245" s="5" t="s">
         <v>533</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C245" s="3" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6687,7 +6672,7 @@
         <v>535</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>331</v>
+        <v>83</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6709,26 +6694,26 @@
         <v>540</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>88</v>
+        <v>541</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>545</v>
+        <v>361</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>546</v>
@@ -6739,18 +6724,18 @@
         <v>547</v>
       </c>
       <c r="B251" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C251" s="5" t="s">
         <v>548</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="B252" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>551</v>
@@ -6761,10 +6746,10 @@
         <v>552</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>404</v>
+        <v>553</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>553</v>
+        <v>42</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6775,18 +6760,18 @@
         <v>555</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>556</v>
+        <v>222</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B255" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="B255" s="3" t="s">
+      <c r="C255" s="5" t="s">
         <v>558</v>
-      </c>
-      <c r="C255" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6794,51 +6779,51 @@
         <v>559</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="C256" s="4" t="s">
-        <v>227</v>
+        <v>0</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B257" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="B257" s="3" t="s">
+      <c r="C257" s="5" t="s">
         <v>562</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C258" s="1" t="s">
-        <v>2</v>
+        <v>563</v>
+      </c>
+      <c r="C258" s="4" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="B259" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="C259" s="5" t="s">
         <v>565</v>
-      </c>
-      <c r="B259" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="C259" s="5" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>568</v>
+        <v>366</v>
       </c>
       <c r="C260" s="4" t="s">
         <v>567</v>
@@ -6846,68 +6831,68 @@
     </row>
     <row r="261" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>569</v>
+        <v>382</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>570</v>
+        <v>89</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>371</v>
+        <v>570</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>572</v>
+        <v>418</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>387</v>
+        <v>570</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>94</v>
+        <v>572</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="C264" s="4" t="s">
-        <v>423</v>
+        <v>177</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B265" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="B265" s="3" t="s">
-        <v>575</v>
-      </c>
       <c r="C265" s="5" t="s">
-        <v>577</v>
+        <v>208</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="B266" s="1" t="s">
+      <c r="C266" s="4" t="s">
         <v>579</v>
-      </c>
-      <c r="C266" s="4" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6918,7 +6903,7 @@
         <v>581</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>213</v>
+        <v>369</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6940,12 +6925,12 @@
         <v>586</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>374</v>
+        <v>587</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>588</v>
@@ -6956,62 +6941,62 @@
     </row>
     <row r="271" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B271" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="B271" s="3" t="s">
-        <v>591</v>
-      </c>
       <c r="C271" s="5" t="s">
-        <v>592</v>
+        <v>378</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B272" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="C272" s="4" t="s">
         <v>593</v>
-      </c>
-      <c r="C272" s="4" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>595</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="B274" s="1" t="s">
+      <c r="C274" s="4" t="s">
         <v>597</v>
-      </c>
-      <c r="C274" s="4" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B275" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C275" s="5" t="s">
         <v>599</v>
-      </c>
-      <c r="B275" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C275" s="5" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>601</v>
@@ -7022,24 +7007,24 @@
     </row>
     <row r="277" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>607</v>
+        <v>177</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7061,7 +7046,7 @@
         <v>612</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>182</v>
+        <v>271</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7083,29 +7068,29 @@
         <v>617</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>276</v>
+        <v>618</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B283" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="C283" s="5" t="s">
         <v>618</v>
-      </c>
-      <c r="B283" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="C283" s="5" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7127,29 +7112,29 @@
         <v>624</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>625</v>
+        <v>438</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B287" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="B287" s="3" t="s">
+      <c r="C287" s="5" t="s">
         <v>627</v>
-      </c>
-      <c r="C287" s="5" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B288" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="C288" s="4" t="s">
         <v>629</v>
-      </c>
-      <c r="C288" s="4" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7160,12 +7145,12 @@
         <v>631</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>632</v>
+        <v>24</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>633</v>
@@ -7176,13 +7161,13 @@
     </row>
     <row r="291" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B291" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B291" s="3" t="s">
+      <c r="C291" s="5" t="s">
         <v>636</v>
-      </c>
-      <c r="C291" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7204,40 +7189,40 @@
         <v>640</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>641</v>
+        <v>265</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>643</v>
-      </c>
       <c r="C294" s="4" t="s">
-        <v>644</v>
+        <v>408</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>270</v>
+        <v>122</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B296" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="B296" s="1" t="s">
+      <c r="C296" s="4" t="s">
         <v>647</v>
-      </c>
-      <c r="C296" s="4" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7248,150 +7233,150 @@
         <v>649</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>127</v>
+        <v>650</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>651</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>652</v>
+        <v>112</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="B299" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="B299" s="3" t="s">
-        <v>654</v>
-      </c>
       <c r="C299" s="5" t="s">
-        <v>655</v>
+        <v>602</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>117</v>
+        <v>395</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B301" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="B301" s="3" t="s">
-        <v>658</v>
-      </c>
       <c r="C301" s="5" t="s">
-        <v>607</v>
+        <v>400</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>660</v>
-      </c>
       <c r="C302" s="4" t="s">
-        <v>400</v>
+        <v>276</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="B303" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="B303" s="3" t="s">
+      <c r="C303" s="5" t="s">
         <v>662</v>
-      </c>
-      <c r="C303" s="5" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="B304" s="1" t="s">
+      <c r="C304" s="4" t="s">
         <v>664</v>
-      </c>
-      <c r="C304" s="4" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="B305" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="B305" s="3" t="s">
-        <v>666</v>
-      </c>
       <c r="C305" s="5" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>669</v>
+        <v>431</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B308" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="C308" s="4" t="s">
         <v>671</v>
-      </c>
-      <c r="C308" s="4" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>676</v>
+        <v>398</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7402,40 +7387,40 @@
         <v>678</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>679</v>
+        <v>21</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="B312" s="1" t="s">
+      <c r="C312" s="4" t="s">
         <v>681</v>
-      </c>
-      <c r="C312" s="4" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="B313" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="B313" s="3" t="s">
-        <v>683</v>
-      </c>
       <c r="C313" s="5" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7443,109 +7428,109 @@
         <v>684</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>207</v>
+        <v>378</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B316" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="C316" s="4" t="s">
         <v>688</v>
-      </c>
-      <c r="C316" s="4" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="B317" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="B317" s="3" t="s">
+      <c r="C317" s="5" t="s">
         <v>690</v>
-      </c>
-      <c r="C317" s="5" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="B318" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="B318" s="1" t="s">
-        <v>692</v>
-      </c>
       <c r="C318" s="4" t="s">
-        <v>693</v>
+        <v>525</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>695</v>
+        <v>398</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>530</v>
+        <v>218</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B321" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="B321" s="3" t="s">
-        <v>698</v>
-      </c>
       <c r="C321" s="5" t="s">
-        <v>403</v>
+        <v>605</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="B322" s="1" t="s">
-        <v>700</v>
-      </c>
       <c r="C322" s="4" t="s">
-        <v>223</v>
+        <v>681</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="B323" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="B323" s="3" t="s">
-        <v>702</v>
-      </c>
       <c r="C323" s="5" t="s">
-        <v>610</v>
+        <v>218</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="B324" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="B324" s="1" t="s">
+      <c r="C324" s="4" t="s">
         <v>704</v>
-      </c>
-      <c r="C324" s="4" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7556,7 +7541,7 @@
         <v>706</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>223</v>
+        <v>451</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7567,62 +7552,62 @@
         <v>708</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>709</v>
+        <v>106</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>456</v>
+        <v>106</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="B329" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="B329" s="3" t="s">
-        <v>714</v>
-      </c>
       <c r="C329" s="5" t="s">
-        <v>111</v>
+        <v>501</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="C330" s="4" t="s">
         <v>715</v>
-      </c>
-      <c r="B330" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="C330" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>717</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>506</v>
+        <v>215</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7644,29 +7629,29 @@
         <v>722</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>220</v>
+        <v>723</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>728</v>
+        <v>411</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7682,145 +7667,145 @@
     </row>
     <row r="337" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="B337" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="B337" s="3" t="s">
-        <v>733</v>
-      </c>
       <c r="C337" s="5" t="s">
-        <v>416</v>
+        <v>501</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B338" s="1" t="s">
+      <c r="C338" s="4" t="s">
         <v>735</v>
-      </c>
-      <c r="C338" s="4" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>737</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>506</v>
+        <v>738</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>742</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>743</v>
+        <v>610</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B342" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="B342" s="1" t="s">
+      <c r="C342" s="4" t="s">
         <v>745</v>
-      </c>
-      <c r="C342" s="4" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>747</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>615</v>
+        <v>748</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="C344" s="4" t="s">
-        <v>750</v>
+        <v>0</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="C345" s="5" t="s">
-        <v>753</v>
+        <v>0</v>
+      </c>
+      <c r="C345" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C347" s="3" t="s">
-        <v>2</v>
+        <v>753</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="B348" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>2</v>
+      <c r="C348" s="4" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>759</v>
+        <v>647</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7842,84 +7827,84 @@
         <v>764</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>652</v>
+        <v>765</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>766</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>767</v>
+        <v>473</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="B353" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="B353" s="3" t="s">
-        <v>769</v>
-      </c>
       <c r="C353" s="5" t="s">
-        <v>770</v>
+        <v>503</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>478</v>
+        <v>383</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="C355" s="5" t="s">
-        <v>508</v>
+        <v>0</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="C356" s="4" t="s">
-        <v>388</v>
+        <v>0</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C357" s="3" t="s">
-        <v>2</v>
+        <v>774</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="C358" s="4" t="s">
         <v>777</v>
-      </c>
-      <c r="B358" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C358" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7927,43 +7912,43 @@
         <v>778</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="C359" s="5" t="s">
-        <v>780</v>
+        <v>0</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B360" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="C360" s="4" t="s">
         <v>781</v>
-      </c>
-      <c r="C360" s="4" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B361" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="B361" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C361" s="3" t="s">
-        <v>2</v>
+      <c r="C361" s="5" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>786</v>
+        <v>42</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7985,7 +7970,7 @@
         <v>791</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>47</v>
+        <v>584</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8007,29 +7992,29 @@
         <v>796</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>589</v>
+        <v>797</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="C368" s="4" t="s">
         <v>800</v>
-      </c>
-      <c r="B368" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="C368" s="4" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8045,10 +8030,10 @@
     </row>
     <row r="370" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="B370" s="1" t="s">
         <v>806</v>
-      </c>
-      <c r="B370" s="1" t="s">
-        <v>807</v>
       </c>
       <c r="C370" s="4" t="s">
         <v>805</v>
@@ -8056,120 +8041,120 @@
     </row>
     <row r="371" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="B371" s="3" t="s">
         <v>808</v>
       </c>
-      <c r="B371" s="3" t="s">
-        <v>809</v>
-      </c>
       <c r="C371" s="5" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="B373" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="B373" s="3" t="s">
-        <v>813</v>
-      </c>
       <c r="C373" s="5" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="B374" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="B374" s="1" t="s">
-        <v>815</v>
-      </c>
       <c r="C374" s="4" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="B375" s="3" t="s">
         <v>816</v>
       </c>
-      <c r="B375" s="3" t="s">
-        <v>817</v>
-      </c>
       <c r="C375" s="5" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="B376" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="B376" s="1" t="s">
-        <v>819</v>
-      </c>
       <c r="C376" s="4" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="B377" s="3" t="s">
         <v>820</v>
       </c>
-      <c r="B377" s="3" t="s">
-        <v>821</v>
-      </c>
       <c r="C377" s="5" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="B378" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="B378" s="1" t="s">
-        <v>823</v>
-      </c>
       <c r="C378" s="4" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="B379" s="3" t="s">
         <v>824</v>
       </c>
-      <c r="B379" s="3" t="s">
-        <v>825</v>
-      </c>
       <c r="C379" s="5" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="B380" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="B380" s="1" t="s">
-        <v>827</v>
-      </c>
       <c r="C380" s="4" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C381" s="5" t="s">
         <v>805</v>
@@ -8177,24 +8162,24 @@
     </row>
     <row r="382" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="C382" s="4" t="s">
         <v>830</v>
-      </c>
-      <c r="B382" s="1" t="s">
-        <v>831</v>
-      </c>
-      <c r="C382" s="4" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>832</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8205,128 +8190,128 @@
         <v>834</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>835</v>
+        <v>800</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="B385" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="B385" s="3" t="s">
-        <v>837</v>
-      </c>
       <c r="C385" s="5" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="B386" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="B386" s="1" t="s">
-        <v>839</v>
-      </c>
       <c r="C386" s="4" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="B387" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="C387" s="5" t="s">
         <v>840</v>
-      </c>
-      <c r="B387" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="C387" s="5" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="B388" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="B388" s="1" t="s">
-        <v>843</v>
-      </c>
       <c r="C388" s="4" t="s">
-        <v>805</v>
+        <v>830</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>844</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>845</v>
+        <v>800</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="B390" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="B390" s="1" t="s">
-        <v>847</v>
-      </c>
       <c r="C390" s="4" t="s">
-        <v>835</v>
+        <v>805</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="B391" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="B391" s="3" t="s">
-        <v>849</v>
-      </c>
       <c r="C391" s="5" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="B392" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="B392" s="1" t="s">
-        <v>851</v>
-      </c>
       <c r="C392" s="4" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="B393" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="B393" s="3" t="s">
-        <v>853</v>
-      </c>
       <c r="C393" s="5" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B394" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="B394" s="1" t="s">
-        <v>855</v>
-      </c>
       <c r="C394" s="4" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="B395" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="B395" s="3" t="s">
+      <c r="C395" s="5" t="s">
         <v>857</v>
-      </c>
-      <c r="C395" s="5" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8337,7 +8322,7 @@
         <v>859</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>805</v>
+        <v>413</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8348,29 +8333,29 @@
         <v>861</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>862</v>
+        <v>475</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>418</v>
+        <v>475</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>480</v>
+        <v>159</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8378,10 +8363,10 @@
         <v>865</v>
       </c>
       <c r="B400" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="C400" s="4" t="s">
         <v>867</v>
-      </c>
-      <c r="C400" s="4" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8392,7 +8377,7 @@
         <v>869</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8414,18 +8399,18 @@
         <v>874</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>148</v>
+        <v>875</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>877</v>
+        <v>116</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8436,18 +8421,18 @@
         <v>879</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>880</v>
+        <v>103</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="B406" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="B406" s="1" t="s">
+      <c r="C406" s="4" t="s">
         <v>882</v>
-      </c>
-      <c r="C406" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8458,18 +8443,18 @@
         <v>884</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>108</v>
+        <v>885</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>887</v>
+        <v>593</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8491,7 +8476,7 @@
         <v>892</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>598</v>
+        <v>468</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8513,40 +8498,40 @@
         <v>897</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>473</v>
+        <v>898</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>906</v>
+        <v>289</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8554,252 +8539,252 @@
         <v>907</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>908</v>
-      </c>
-      <c r="C416" s="4" t="s">
-        <v>909</v>
+        <v>0</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>911</v>
-      </c>
-      <c r="C417" s="5" t="s">
-        <v>294</v>
+        <v>0</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C419" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C420" s="1" t="s">
-        <v>2</v>
+        <v>864</v>
+      </c>
+      <c r="C420" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C421" s="3" t="s">
-        <v>2</v>
+        <v>866</v>
+      </c>
+      <c r="C421" s="5" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>869</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>872</v>
+        <v>143</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>148</v>
+        <v>872</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>148</v>
+        <v>872</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>876</v>
+        <v>920</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>877</v>
+        <v>921</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>876</v>
+        <v>920</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>877</v>
+        <v>921</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="B430" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="B430" s="1" t="s">
+      <c r="C430" s="4" t="s">
         <v>925</v>
-      </c>
-      <c r="C430" s="4" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="B431" s="3" t="s">
         <v>927</v>
       </c>
-      <c r="B431" s="3" t="s">
-        <v>925</v>
-      </c>
       <c r="C431" s="5" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>929</v>
+        <v>874</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>930</v>
+        <v>875</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>932</v>
+        <v>877</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>933</v>
+        <v>116</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>880</v>
+        <v>116</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>882</v>
+        <v>935</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>121</v>
+        <v>360</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="C438" s="4" t="s">
         <v>938</v>
-      </c>
-      <c r="B438" s="1" t="s">
-        <v>884</v>
-      </c>
-      <c r="C438" s="4" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8807,307 +8792,307 @@
         <v>939</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>940</v>
+        <v>881</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>365</v>
+        <v>882</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>942</v>
+        <v>881</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>943</v>
+        <v>882</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>889</v>
+        <v>946</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>890</v>
+        <v>593</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>889</v>
+        <v>947</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>890</v>
+        <v>593</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>598</v>
+        <v>890</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>952</v>
+        <v>889</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>598</v>
+        <v>890</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>954</v>
+        <v>887</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>895</v>
+        <v>593</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>892</v>
+        <v>897</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>598</v>
+        <v>898</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>902</v>
+        <v>894</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>899</v>
+        <v>958</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>900</v>
+        <v>959</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>899</v>
+        <v>958</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>900</v>
+        <v>959</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>963</v>
+        <v>892</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>964</v>
+        <v>468</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>963</v>
+        <v>892</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>964</v>
+        <v>468</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>897</v>
+        <v>965</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>473</v>
+        <v>966</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>897</v>
+        <v>965</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>473</v>
+        <v>966</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>970</v>
-      </c>
-      <c r="C464" s="4" t="s">
-        <v>971</v>
+        <v>0</v>
+      </c>
+      <c r="C464" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="B466" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="B466" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C466" s="1" t="s">
-        <v>2</v>
+      <c r="C466" s="4" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9126,98 +9111,98 @@
         <v>978</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>145</v>
+        <v>627</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="B469" s="3" t="s">
         <v>980</v>
       </c>
-      <c r="B469" s="3" t="s">
-        <v>981</v>
-      </c>
       <c r="C469" s="5" t="s">
-        <v>982</v>
+        <v>867</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>632</v>
+        <v>457</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="B471" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="B471" s="3" t="s">
-        <v>985</v>
-      </c>
       <c r="C471" s="5" t="s">
-        <v>872</v>
+        <v>347</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B472" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="C472" s="4" t="s">
         <v>986</v>
-      </c>
-      <c r="B472" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="C472" s="4" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="B473" s="3" t="s">
         <v>988</v>
       </c>
-      <c r="B473" s="3" t="s">
-        <v>989</v>
-      </c>
       <c r="C473" s="5" t="s">
-        <v>352</v>
+        <v>610</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>991</v>
+        <v>610</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="B475" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="C475" s="5" t="s">
         <v>992</v>
-      </c>
-      <c r="B475" s="3" t="s">
-        <v>993</v>
-      </c>
-      <c r="C475" s="5" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B476" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="C476" s="4" t="s">
         <v>994</v>
-      </c>
-      <c r="C476" s="4" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9228,106 +9213,106 @@
         <v>996</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1001</v>
+        <v>965</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>999</v>
+        <v>966</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>1001</v>
+        <v>884</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>999</v>
+        <v>885</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>970</v>
+        <v>884</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>971</v>
+        <v>885</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>889</v>
+        <v>1005</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>890</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B486" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="B486" s="1" t="s">
-        <v>889</v>
-      </c>
       <c r="C486" s="4" t="s">
-        <v>890</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9335,868 +9320,868 @@
         <v>1009</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="B489" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C489" s="5" t="s">
         <v>1013</v>
-      </c>
-      <c r="C489" s="5" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B490" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C490" s="4" t="s">
         <v>1013</v>
-      </c>
-      <c r="C490" s="4" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>1018</v>
+        <v>548</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>1018</v>
+        <v>548</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>1023</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>553</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B498" s="1" t="s">
         <v>1023</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>553</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>1035</v>
+        <v>420</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>1035</v>
+        <v>420</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="B509" s="3" t="s">
         <v>1040</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>425</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B510" s="1" t="s">
         <v>1040</v>
       </c>
       <c r="C510" s="4" t="s">
-        <v>425</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>1045</v>
+        <v>958</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>1046</v>
+        <v>959</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>1045</v>
+        <v>958</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>1046</v>
+        <v>959</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="C516" s="4" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>963</v>
+        <v>1050</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>964</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>963</v>
+        <v>1050</v>
       </c>
       <c r="C518" s="4" t="s">
-        <v>964</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>1055</v>
+        <v>871</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>1056</v>
+        <v>872</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1055</v>
+        <v>871</v>
       </c>
       <c r="C522" s="4" t="s">
-        <v>1056</v>
+        <v>872</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>876</v>
+        <v>920</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>877</v>
+        <v>921</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>876</v>
+        <v>920</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>877</v>
+        <v>921</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>925</v>
+        <v>1023</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>926</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>925</v>
+        <v>1023</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>926</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>1028</v>
+        <v>869</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>1029</v>
+        <v>143</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1028</v>
+        <v>869</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>1029</v>
+        <v>143</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="C534" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>874</v>
+        <v>1070</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>148</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>874</v>
+        <v>1070</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>148</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="C538" s="4" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>1075</v>
+        <v>1018</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>1076</v>
+        <v>548</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1075</v>
+        <v>1018</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>1076</v>
+        <v>548</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1023</v>
+        <v>1079</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>553</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>1023</v>
+        <v>1079</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>553</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1084</v>
+        <v>1050</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>1085</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>1084</v>
+        <v>1050</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>1085</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1055</v>
+        <v>1093</v>
       </c>
       <c r="C554" s="4" t="s">
-        <v>1056</v>
+        <v>745</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>1055</v>
+        <v>1093</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>1056</v>
+        <v>745</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1098</v>
+        <v>976</v>
       </c>
       <c r="C556" s="4" t="s">
-        <v>750</v>
+        <v>454</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>1098</v>
+        <v>1018</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>750</v>
+        <v>548</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>981</v>
+        <v>1098</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>459</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C559" s="5" t="s">
-        <v>553</v>
+        <v>0</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1103</v>
-      </c>
-      <c r="C560" s="4" t="s">
-        <v>1104</v>
+        <v>0</v>
+      </c>
+      <c r="C560" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C561" s="3" t="s">
-        <v>2</v>
+        <v>1103</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C562" s="1" t="s">
-        <v>2</v>
+        <v>1104</v>
+      </c>
+      <c r="C562" s="4" t="s">
+        <v>1105</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B563" s="3" t="s">
         <v>1107</v>
       </c>
-      <c r="B563" s="3" t="s">
-        <v>1108</v>
-      </c>
       <c r="C563" s="5" t="s">
-        <v>669</v>
+        <v>775</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B564" s="1" t="s">
         <v>1109</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>1110</v>
+        <v>147</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B565" s="3" t="s">
         <v>1111</v>
       </c>
-      <c r="B565" s="3" t="s">
+      <c r="C565" s="5" t="s">
         <v>1112</v>
-      </c>
-      <c r="C565" s="5" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10207,7 +10192,7 @@
         <v>1114</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10218,40 +10203,40 @@
         <v>1116</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>1117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B568" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="B568" s="1" t="s">
-        <v>1119</v>
-      </c>
       <c r="C568" s="4" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B569" s="3" t="s">
         <v>1120</v>
       </c>
-      <c r="B569" s="3" t="s">
-        <v>1121</v>
-      </c>
       <c r="C569" s="5" t="s">
-        <v>102</v>
+        <v>364</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B570" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="B570" s="1" t="s">
+      <c r="C570" s="4" t="s">
         <v>1123</v>
-      </c>
-      <c r="C570" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10262,40 +10247,40 @@
         <v>1125</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>369</v>
+        <v>56</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B572" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="B572" s="1" t="s">
-        <v>1127</v>
-      </c>
       <c r="C572" s="4" t="s">
-        <v>1128</v>
+        <v>400</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B573" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C573" s="5" t="s">
         <v>1129</v>
-      </c>
-      <c r="B573" s="3" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C573" s="5" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B574" s="1" t="s">
         <v>1131</v>
       </c>
       <c r="C574" s="4" t="s">
-        <v>405</v>
+        <v>901</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10306,128 +10291,128 @@
         <v>1133</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>1134</v>
+        <v>420</v>
       </c>
     </row>
     <row r="576" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B576" s="1" t="s">
         <v>1135</v>
       </c>
-      <c r="B576" s="1" t="s">
-        <v>1136</v>
-      </c>
       <c r="C576" s="4" t="s">
-        <v>906</v>
+        <v>623</v>
       </c>
     </row>
     <row r="577" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B577" s="3" t="s">
         <v>1137</v>
       </c>
-      <c r="B577" s="3" t="s">
-        <v>1138</v>
-      </c>
       <c r="C577" s="5" t="s">
-        <v>425</v>
+        <v>623</v>
       </c>
     </row>
     <row r="578" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B578" s="1" t="s">
         <v>1139</v>
       </c>
-      <c r="B578" s="1" t="s">
-        <v>1140</v>
-      </c>
       <c r="C578" s="4" t="s">
-        <v>628</v>
+        <v>56</v>
       </c>
     </row>
     <row r="579" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B579" s="3" t="s">
         <v>1141</v>
       </c>
-      <c r="B579" s="3" t="s">
-        <v>1142</v>
-      </c>
       <c r="C579" s="5" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="580" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B580" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="B580" s="1" t="s">
-        <v>1144</v>
-      </c>
       <c r="C580" s="4" t="s">
-        <v>61</v>
+        <v>623</v>
       </c>
     </row>
     <row r="581" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B581" s="3" t="s">
         <v>1145</v>
       </c>
-      <c r="B581" s="3" t="s">
-        <v>1146</v>
-      </c>
       <c r="C581" s="5" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
     </row>
     <row r="582" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B582" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="B582" s="1" t="s">
-        <v>1148</v>
-      </c>
       <c r="C582" s="4" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="583" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B583" s="3" t="s">
         <v>1149</v>
       </c>
-      <c r="B583" s="3" t="s">
-        <v>1150</v>
-      </c>
       <c r="C583" s="5" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="584" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B584" s="1" t="s">
         <v>1151</v>
       </c>
-      <c r="B584" s="1" t="s">
-        <v>1152</v>
-      </c>
       <c r="C584" s="4" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="585" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B585" s="3" t="s">
         <v>1153</v>
       </c>
-      <c r="B585" s="3" t="s">
-        <v>1154</v>
-      </c>
       <c r="C585" s="5" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B586" s="1" t="s">
         <v>1155</v>
       </c>
-      <c r="B586" s="1" t="s">
+      <c r="C586" s="4" t="s">
         <v>1156</v>
-      </c>
-      <c r="C586" s="4" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="587" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10438,7 +10423,7 @@
         <v>1158</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="588" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10449,73 +10434,73 @@
         <v>1160</v>
       </c>
       <c r="C588" s="4" t="s">
-        <v>1161</v>
+        <v>623</v>
       </c>
     </row>
     <row r="589" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B589" s="3" t="s">
         <v>1162</v>
       </c>
-      <c r="B589" s="3" t="s">
-        <v>1163</v>
-      </c>
       <c r="C589" s="5" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="590" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B590" s="1" t="s">
         <v>1164</v>
       </c>
-      <c r="B590" s="1" t="s">
-        <v>1165</v>
-      </c>
       <c r="C590" s="4" t="s">
-        <v>628</v>
+        <v>514</v>
       </c>
     </row>
     <row r="591" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B591" s="3" t="s">
         <v>1166</v>
       </c>
-      <c r="B591" s="3" t="s">
-        <v>1167</v>
-      </c>
       <c r="C591" s="5" t="s">
-        <v>628</v>
+        <v>309</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B592" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="B592" s="1" t="s">
-        <v>1169</v>
-      </c>
       <c r="C592" s="4" t="s">
-        <v>519</v>
+        <v>388</v>
       </c>
     </row>
     <row r="593" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B593" s="3" t="s">
         <v>1170</v>
       </c>
-      <c r="B593" s="3" t="s">
-        <v>1171</v>
-      </c>
       <c r="C593" s="5" t="s">
-        <v>314</v>
+        <v>623</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B594" s="1" t="s">
         <v>1172</v>
       </c>
-      <c r="B594" s="1" t="s">
+      <c r="C594" s="4" t="s">
         <v>1173</v>
-      </c>
-      <c r="C594" s="4" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="595" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10526,7 +10511,7 @@
         <v>1175</v>
       </c>
       <c r="C595" s="5" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10545,32 +10530,32 @@
         <v>1179</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C597" s="5" t="s">
-        <v>628</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B598" s="1" t="s">
         <v>1181</v>
       </c>
-      <c r="B598" s="1" t="s">
-        <v>1182</v>
-      </c>
       <c r="C598" s="4" t="s">
-        <v>1183</v>
+        <v>199</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A599" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B599" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C599" s="5" t="s">
         <v>1184</v>
-      </c>
-      <c r="B599" s="3" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C599" s="5" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="600" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10581,18 +10566,18 @@
         <v>1186</v>
       </c>
       <c r="C600" s="4" t="s">
-        <v>204</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="601" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A601" s="3" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="C601" s="5" t="s">
-        <v>1189</v>
+        <v>735</v>
       </c>
     </row>
     <row r="602" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10603,75 +10588,55 @@
         <v>1191</v>
       </c>
       <c r="C602" s="4" t="s">
-        <v>1192</v>
+        <v>777</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A603" s="3" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B603" s="3" t="s">
-        <v>1194</v>
-      </c>
-      <c r="C603" s="5" t="s">
-        <v>740</v>
+        <v>0</v>
+      </c>
+      <c r="C603" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="604" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B604" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C604" s="4" t="s">
-        <v>782</v>
+        <v>0</v>
+      </c>
+      <c r="C604" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="605" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A605" s="3" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="B605" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C605" s="3" t="s">
-        <v>2</v>
+        <v>1195</v>
+      </c>
+      <c r="C605" s="5" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="606" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="B606" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C606" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A607" s="3" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B607" s="3" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C607" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="608" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A608" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="B608" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C608" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="608" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
     <row r="609" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/المواد.xlsx
+++ b/المواد.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="1166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="1176">
   <si>
     <t/>
   </si>
@@ -222,12 +222,15 @@
     <t>T4 Kit 24T Afias Boditech</t>
   </si>
   <si>
+    <t>EVA  T4VEA35X</t>
+  </si>
+  <si>
+    <t>21/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA T4VEA35X</t>
   </si>
   <si>
-    <t>21/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>TSH Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -270,6 +273,9 @@
     <t>07/05/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA TNVXD74X</t>
+  </si>
+  <si>
     <t>B-HCG Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -300,6 +306,12 @@
     <t>Progesterone Kit 25T iChroma Boditech</t>
   </si>
   <si>
+    <t>EVA  DPGVHD04</t>
+  </si>
+  <si>
+    <t>28/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA DPGVDD02</t>
   </si>
   <si>
@@ -414,6 +426,12 @@
     <t>14/12/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA  DLHVHD05</t>
+  </si>
+  <si>
+    <t>07/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>Microalbumin Kit 25T iChroma Boditech</t>
   </si>
   <si>
@@ -693,6 +711,12 @@
     <t>01/08/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>2025111051</t>
+  </si>
+  <si>
+    <t>09/11/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>M-30 Diluent Reagent 3-part 20L Hematology Mindray</t>
   </si>
   <si>
@@ -705,12 +729,6 @@
     <t>M-30R Rinse Reagent 3-part 20L Hematology Mindray</t>
   </si>
   <si>
-    <t>2025111051</t>
-  </si>
-  <si>
-    <t>09/11/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>M-52 Diff Lyse Reagent 5-part 500ml Hematology Mindray</t>
   </si>
   <si>
@@ -867,6 +885,9 @@
     <t>27/05/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>I-Chroma 2-Instrument used Boditech</t>
+  </si>
+  <si>
     <t>cleanser CD-80 محلول تنظيف (1L)</t>
   </si>
   <si>
@@ -918,12 +939,15 @@
     <t>044625010</t>
   </si>
   <si>
-    <t>07/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>Specific Protein Calibrator Chemistry Mindray</t>
   </si>
   <si>
+    <t>150725010</t>
+  </si>
+  <si>
+    <t>08/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>150725011</t>
   </si>
   <si>
@@ -1005,6 +1029,12 @@
     <t>25/11/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>Semi-auto BA-88A used</t>
+  </si>
+  <si>
+    <t>i-chamber -used</t>
+  </si>
+  <si>
     <t>Creatinine kit  Chemistry Mindray</t>
   </si>
   <si>
@@ -1023,6 +1053,15 @@
     <t>12/06/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>M-62 FR Dye Reagent 7-part 12mL Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025080652</t>
+  </si>
+  <si>
+    <t>05/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
     <t>M-62 LD Lyse Reagent 7-part 1L Hematology Mindray</t>
   </si>
   <si>
@@ -1098,9 +1137,6 @@
     <t>Anti-Tg kit 2×50T CL900i Mindray</t>
   </si>
   <si>
-    <t>08/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>2025100111</t>
   </si>
   <si>
@@ -1491,12 +1527,15 @@
     <t>AMH Kit 25T iChroma Boditech</t>
   </si>
   <si>
+    <t>EVA  MHVXC12E</t>
+  </si>
+  <si>
+    <t>04/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA MHVXC12E</t>
   </si>
   <si>
-    <t>04/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>M-62 DR Diluent Reagent 7-part 1L Hematology Mindray</t>
   </si>
   <si>
@@ -1776,9 +1815,6 @@
     <t>140125022</t>
   </si>
   <si>
-    <t>28/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>( AST (GOT) kit  Chemistry Mindray ( Large</t>
   </si>
   <si>
@@ -1824,18 +1860,18 @@
     <t>( LDL-C kit  Chemistry Mindray  ( Large</t>
   </si>
   <si>
+    <t>142025008</t>
+  </si>
+  <si>
+    <t>11/07/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>142025010</t>
   </si>
   <si>
     <t>17/09/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>( MG kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>148225004</t>
-  </si>
-  <si>
     <t>( T-Bill vox kit Chemistry Mindray ( Large</t>
   </si>
   <si>
@@ -2154,6 +2190,9 @@
     <t>HEMATOLOGY PRINTER (NEW)</t>
   </si>
   <si>
+    <t>HEMATOLOGY PRINTER (USED)</t>
+  </si>
+  <si>
     <t>Penkid Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -2163,19 +2202,10 @@
     <t>16/06/2026 12:00:00 ص</t>
   </si>
   <si>
-    <t>Insulin Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>INVYA09G</t>
-  </si>
-  <si>
     <t>Ca19-9 Kit 24T Afias Boditech</t>
   </si>
   <si>
     <t>CXVKA08G</t>
-  </si>
-  <si>
-    <t>11/07/2027 12:00:00 ص</t>
   </si>
   <si>
     <t>Daily check  (Clover A1c Plus)</t>
@@ -3870,7 +3900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C582"/>
+  <dimension ref="A1:C593"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="30" customWidth="1"/>
@@ -4153,233 +4183,233 @@
     </row>
     <row r="26" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="C26" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>74</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="C29" s="5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="C35" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>113</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4387,10 +4417,10 @@
         <v>117</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4398,98 +4428,98 @@
         <v>117</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>123</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>11</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>135</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="C54" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4497,32 +4527,32 @@
         <v>139</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>141</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="C58" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4530,10 +4560,10 @@
         <v>145</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>149</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4541,216 +4571,216 @@
         <v>145</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>151</v>
+        <v>62</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C68" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>43</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>181</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>182</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>43</v>
+        <v>190</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="C79" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>32</v>
@@ -4758,13 +4788,13 @@
     </row>
     <row r="81" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>194</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4772,21 +4802,21 @@
         <v>197</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>200</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4794,32 +4824,32 @@
         <v>201</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>164</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="C85" s="5" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4827,565 +4857,565 @@
         <v>207</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>200</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>213</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>229</v>
+        <v>185</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>173</v>
+        <v>231</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>240</v>
+        <v>179</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>0</v>
+        <v>247</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C105" s="3" t="s">
-        <v>0</v>
+        <v>245</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>0</v>
+        <v>250</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>261</v>
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>159</v>
+        <v>0</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>266</v>
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>184</v>
+        <v>272</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>51</v>
+        <v>277</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>290</v>
+        <v>190</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>296</v>
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>299</v>
+        <v>51</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>0</v>
+        <v>294</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C127" s="3" t="s">
-        <v>0</v>
+        <v>296</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>307</v>
+        <v>136</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C131" s="3" t="s">
-        <v>0</v>
+        <v>307</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>100</v>
+        <v>310</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>316</v>
+        <v>0</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>318</v>
+        <v>0</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>0</v>
+        <v>317</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>0</v>
+        <v>314</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>0</v>
@@ -5396,2086 +5426,2086 @@
     </row>
     <row r="139" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>327</v>
+        <v>104</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>339</v>
+        <v>0</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>342</v>
+        <v>0</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>345</v>
+        <v>0</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>0</v>
+        <v>334</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>349</v>
+        <v>0</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>115</v>
+        <v>0</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>371</v>
+        <v>0</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>376</v>
+        <v>119</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>65</v>
+        <v>367</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>383</v>
+        <v>308</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>14</v>
+        <v>373</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>302</v>
+        <v>375</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>268</v>
+        <v>383</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>394</v>
+        <v>364</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>399</v>
+        <v>65</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>408</v>
+        <v>14</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>410</v>
+        <v>369</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>411</v>
+        <v>310</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>302</v>
+        <v>403</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>176</v>
+        <v>274</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>151</v>
+        <v>409</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>351</v>
+        <v>413</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>356</v>
+        <v>422</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>431</v>
+        <v>310</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>356</v>
+        <v>402</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>434</v>
+        <v>391</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>437</v>
+        <v>157</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>424</v>
+        <v>369</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>440</v>
+        <v>364</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>444</v>
+        <v>403</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>447</v>
+        <v>369</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>450</v>
+        <v>402</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>288</v>
+        <v>441</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>452</v>
+        <v>402</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>43</v>
+        <v>443</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>454</v>
+        <v>369</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>458</v>
+        <v>402</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>316</v>
+        <v>449</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>473</v>
+        <v>295</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>394</v>
+        <v>464</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>474</v>
+        <v>43</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>477</v>
+        <v>119</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C208" s="1" t="s">
-        <v>0</v>
+        <v>470</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>351</v>
+        <v>472</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>73</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>356</v>
+        <v>474</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>420</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>379</v>
+        <v>477</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>135</v>
+        <v>482</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>135</v>
+        <v>485</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C215" s="3" t="s">
-        <v>0</v>
+        <v>406</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C216" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="B216" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>91</v>
+        <v>0</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>498</v>
+        <v>364</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>500</v>
+        <v>369</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>501</v>
+        <v>432</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>503</v>
+        <v>391</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>79</v>
+        <v>489</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>351</v>
+        <v>496</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>508</v>
+        <v>141</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>511</v>
+        <v>141</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>511</v>
+        <v>0</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>321</v>
+        <v>503</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>0</v>
+        <v>506</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>299</v>
+        <v>93</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>299</v>
+        <v>83</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>402</v>
+        <v>80</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>526</v>
+        <v>364</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>179</v>
+        <v>521</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>194</v>
+        <v>524</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>200</v>
+        <v>524</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>536</v>
+        <v>329</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="C239" s="5" t="s">
-        <v>359</v>
+        <v>0</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>546</v>
+        <v>136</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>546</v>
+        <v>414</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>553</v>
+        <v>185</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>556</v>
+        <v>200</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>558</v>
+        <v>206</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>179</v>
+        <v>308</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>568</v>
+        <v>116</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>261</v>
+        <v>559</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>8</v>
+        <v>559</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>581</v>
+        <v>567</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>590</v>
+        <v>185</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>26</v>
+        <v>581</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>595</v>
+        <v>267</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>255</v>
+        <v>586</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>388</v>
+        <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>603</v>
+        <v>589</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>604</v>
+        <v>590</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>121</v>
+        <v>591</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>606</v>
+        <v>592</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>65</v>
+        <v>593</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>380</v>
+        <v>596</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>609</v>
+        <v>594</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>266</v>
+        <v>96</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>408</v>
+        <v>26</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>115</v>
+        <v>261</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="B276" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="C276" s="4" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>556</v>
+        <v>65</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>631</v>
+        <v>392</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>634</v>
+        <v>272</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>638</v>
+        <v>623</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>546</v>
+        <v>420</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>573</v>
+        <v>119</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>485</v>
+        <v>385</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>556</v>
+        <v>635</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>209</v>
+        <v>638</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>209</v>
+        <v>648</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>461</v>
+        <v>559</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>666</v>
+        <v>586</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>115</v>
+        <v>497</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>668</v>
+        <v>657</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>669</v>
+        <v>658</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>94</v>
+        <v>569</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>466</v>
+        <v>215</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>673</v>
+        <v>576</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>674</v>
+        <v>663</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>206</v>
+        <v>646</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>681</v>
+        <v>215</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>687</v>
+        <v>473</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>689</v>
+        <v>674</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>395</v>
+        <v>675</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>466</v>
+        <v>119</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>696</v>
+        <v>98</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>53</v>
+        <v>478</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>699</v>
+        <v>683</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>700</v>
+        <v>684</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>701</v>
+        <v>685</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>702</v>
+        <v>686</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>704</v>
+        <v>212</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>705</v>
+        <v>688</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>706</v>
+        <v>689</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>707</v>
+        <v>690</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>708</v>
+        <v>691</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C315" s="3" t="s">
-        <v>0</v>
+        <v>692</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>709</v>
+        <v>694</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>0</v>
+        <v>695</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C317" s="3" t="s">
-        <v>0</v>
+        <v>698</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>699</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>713</v>
+        <v>407</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>435</v>
+        <v>704</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>718</v>
+        <v>478</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>528</v>
+        <v>53</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="C326" s="4" t="s">
-        <v>733</v>
+        <v>0</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="C327" s="5" t="s">
-        <v>53</v>
+        <v>0</v>
+      </c>
+      <c r="C327" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>736</v>
+        <v>722</v>
       </c>
       <c r="B328" s="1" t="s">
         <v>0</v>
@@ -7486,7 +7516,7 @@
     </row>
     <row r="329" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>737</v>
+        <v>723</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>0</v>
@@ -7497,1811 +7527,1811 @@
     </row>
     <row r="330" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>738</v>
+        <v>724</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>0</v>
+        <v>725</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>726</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>741</v>
+        <v>614</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>0</v>
+        <v>730</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>743</v>
+        <v>729</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>745</v>
+        <v>541</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>746</v>
+        <v>729</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>747</v>
+        <v>733</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>749</v>
+        <v>735</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>750</v>
+        <v>736</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>321</v>
+        <v>737</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>112</v>
+        <v>743</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>466</v>
+        <v>53</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="C339" s="5" t="s">
-        <v>759</v>
+        <v>0</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="C340" s="4" t="s">
-        <v>762</v>
+        <v>0</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="C341" s="5" t="s">
-        <v>765</v>
+        <v>0</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>766</v>
+        <v>749</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>767</v>
+        <v>750</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>768</v>
+        <v>752</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="C343" s="5" t="s">
-        <v>770</v>
+        <v>0</v>
+      </c>
+      <c r="C343" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>773</v>
+        <v>756</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>774</v>
+        <v>757</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>765</v>
+        <v>758</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>776</v>
+        <v>760</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>765</v>
+        <v>329</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>777</v>
+        <v>761</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>765</v>
+        <v>116</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>770</v>
+        <v>478</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>783</v>
+        <v>766</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>790</v>
+        <v>777</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>791</v>
+        <v>779</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>770</v>
+        <v>780</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>794</v>
+        <v>775</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>795</v>
+        <v>783</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>796</v>
+        <v>784</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>797</v>
+        <v>785</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>798</v>
+        <v>786</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>799</v>
+        <v>787</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>802</v>
+        <v>790</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>803</v>
+        <v>792</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>804</v>
+        <v>780</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>805</v>
+        <v>793</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>794</v>
+        <v>775</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>807</v>
+        <v>795</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>808</v>
+        <v>796</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>809</v>
+        <v>797</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>810</v>
+        <v>798</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>770</v>
+        <v>775</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>812</v>
+        <v>799</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>813</v>
+        <v>801</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>765</v>
+        <v>780</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>814</v>
+        <v>802</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>815</v>
+        <v>803</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>765</v>
+        <v>804</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>765</v>
+        <v>775</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>820</v>
+        <v>809</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>821</v>
+        <v>810</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>822</v>
+        <v>775</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>823</v>
+        <v>811</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>824</v>
+        <v>812</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>825</v>
+        <v>775</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>826</v>
+        <v>811</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>439</v>
+        <v>814</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>826</v>
+        <v>815</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>828</v>
+        <v>816</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>439</v>
+        <v>804</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>829</v>
+        <v>817</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>830</v>
+        <v>818</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>164</v>
+        <v>775</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>831</v>
+        <v>819</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>832</v>
+        <v>820</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>833</v>
+        <v>775</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>834</v>
+        <v>819</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>835</v>
+        <v>821</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>147</v>
+        <v>780</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>836</v>
+        <v>822</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>837</v>
+        <v>823</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>838</v>
+        <v>775</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>839</v>
+        <v>824</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>841</v>
+        <v>775</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>842</v>
+        <v>826</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>843</v>
+        <v>827</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>125</v>
+        <v>775</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>844</v>
+        <v>828</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>845</v>
+        <v>829</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>846</v>
+        <v>775</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>847</v>
+        <v>830</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>848</v>
+        <v>831</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>849</v>
+        <v>832</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>850</v>
+        <v>833</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>851</v>
+        <v>834</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>852</v>
+        <v>835</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>853</v>
+        <v>836</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>854</v>
+        <v>837</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>553</v>
+        <v>451</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>855</v>
+        <v>836</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>856</v>
+        <v>838</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>857</v>
+        <v>451</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>858</v>
+        <v>839</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>859</v>
+        <v>840</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>860</v>
+        <v>170</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>861</v>
+        <v>841</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>862</v>
+        <v>842</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>863</v>
+        <v>843</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>864</v>
+        <v>844</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>865</v>
+        <v>845</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>866</v>
+        <v>153</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>867</v>
+        <v>846</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>868</v>
+        <v>847</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>869</v>
+        <v>848</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>870</v>
+        <v>849</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>871</v>
+        <v>850</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>872</v>
+        <v>851</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>873</v>
+        <v>852</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>874</v>
+        <v>853</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>875</v>
+        <v>129</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>876</v>
+        <v>854</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C390" s="1" t="s">
-        <v>0</v>
+        <v>855</v>
+      </c>
+      <c r="C390" s="4" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>877</v>
+        <v>857</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C391" s="3" t="s">
-        <v>0</v>
+        <v>858</v>
+      </c>
+      <c r="C391" s="5" t="s">
+        <v>859</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>878</v>
+        <v>860</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C392" s="1" t="s">
-        <v>0</v>
+        <v>861</v>
+      </c>
+      <c r="C392" s="4" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>879</v>
+        <v>863</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C393" s="3" t="s">
-        <v>0</v>
+        <v>864</v>
+      </c>
+      <c r="C393" s="5" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>830</v>
+        <v>866</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>164</v>
+        <v>867</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>881</v>
+        <v>868</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>832</v>
+        <v>869</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>833</v>
+        <v>870</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>882</v>
+        <v>871</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>835</v>
+        <v>872</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>147</v>
+        <v>873</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>835</v>
+        <v>875</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>147</v>
+        <v>876</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>835</v>
+        <v>878</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>147</v>
+        <v>879</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>837</v>
+        <v>881</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>838</v>
+        <v>882</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>837</v>
+        <v>884</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>838</v>
+        <v>885</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="C401" s="5" t="s">
-        <v>838</v>
+        <v>0</v>
+      </c>
+      <c r="C401" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="C402" s="4" t="s">
-        <v>890</v>
+        <v>0</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="C403" s="5" t="s">
-        <v>890</v>
+        <v>0</v>
+      </c>
+      <c r="C403" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>893</v>
-      </c>
-      <c r="C404" s="4" t="s">
-        <v>894</v>
+        <v>0</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>896</v>
+        <v>840</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>524</v>
+        <v>170</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>903</v>
+        <v>847</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>904</v>
+        <v>848</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>905</v>
+        <v>897</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>906</v>
+        <v>847</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>907</v>
+        <v>848</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>848</v>
+        <v>899</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>849</v>
+        <v>900</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>909</v>
+        <v>901</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>848</v>
+        <v>899</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>849</v>
+        <v>900</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>910</v>
+        <v>902</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>848</v>
+        <v>903</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>849</v>
+        <v>904</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>851</v>
+        <v>906</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>852</v>
+        <v>537</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="B417" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="C417" s="5" t="s">
         <v>851</v>
-      </c>
-      <c r="C417" s="5" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>852</v>
+        <v>129</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>915</v>
+        <v>853</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>553</v>
+        <v>129</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>916</v>
+        <v>853</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>553</v>
+        <v>129</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>918</v>
+        <v>855</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>856</v>
+        <v>913</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>857</v>
+        <v>914</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>854</v>
+        <v>916</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>553</v>
+        <v>917</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B427" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="C427" s="5" t="s">
         <v>862</v>
-      </c>
-      <c r="C427" s="5" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B428" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="C428" s="4" t="s">
         <v>862</v>
-      </c>
-      <c r="C428" s="4" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B429" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="C429" s="5" t="s">
         <v>862</v>
-      </c>
-      <c r="C429" s="5" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>928</v>
+        <v>566</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>928</v>
+        <v>566</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>859</v>
+        <v>928</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>860</v>
+        <v>566</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>934</v>
+        <v>875</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>935</v>
+        <v>876</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>934</v>
+        <v>875</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>935</v>
+        <v>876</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>934</v>
+        <v>875</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>935</v>
+        <v>876</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>0</v>
+        <v>872</v>
+      </c>
+      <c r="C438" s="4" t="s">
+        <v>873</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>940</v>
+        <v>872</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>941</v>
+        <v>873</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>942</v>
+        <v>935</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>943</v>
+        <v>872</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>144</v>
+        <v>873</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>946</v>
+        <v>938</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>947</v>
+        <v>939</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>945</v>
+        <v>937</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>588</v>
+        <v>938</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>948</v>
+        <v>940</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>949</v>
+        <v>869</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>950</v>
+        <v>870</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>951</v>
+        <v>941</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>952</v>
+        <v>869</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>833</v>
+        <v>870</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>954</v>
+        <v>869</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>425</v>
+        <v>870</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>955</v>
+        <v>943</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>956</v>
+        <v>944</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>339</v>
+        <v>945</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>958</v>
+        <v>945</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>959</v>
+        <v>947</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>960</v>
+        <v>944</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>568</v>
+        <v>945</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>961</v>
+        <v>948</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>962</v>
-      </c>
-      <c r="C449" s="5" t="s">
-        <v>963</v>
+        <v>0</v>
+      </c>
+      <c r="C449" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>961</v>
+        <v>949</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>965</v>
+        <v>951</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>966</v>
+        <v>952</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>967</v>
+        <v>953</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>965</v>
+        <v>150</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>968</v>
+        <v>954</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>969</v>
+        <v>957</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>967</v>
+        <v>955</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>965</v>
+        <v>600</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>970</v>
+        <v>958</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>934</v>
+        <v>959</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>935</v>
+        <v>960</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>971</v>
+        <v>961</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>851</v>
+        <v>962</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>851</v>
+        <v>964</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>852</v>
+        <v>437</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>851</v>
+        <v>966</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>852</v>
+        <v>352</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>851</v>
+        <v>967</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>852</v>
+        <v>968</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>977</v>
+        <v>581</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>978</v>
+        <v>971</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>979</v>
+        <v>972</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>983</v>
+        <v>944</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>984</v>
+        <v>945</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>983</v>
+        <v>861</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>984</v>
+        <v>862</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>989</v>
+        <v>861</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>990</v>
+        <v>862</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>991</v>
+        <v>983</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>989</v>
+        <v>861</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>990</v>
+        <v>862</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>989</v>
+        <v>861</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>990</v>
+        <v>862</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>993</v>
+        <v>985</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
-        <v>998</v>
+        <v>991</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>999</v>
+        <v>992</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
-        <v>1010</v>
+        <v>1003</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>1017</v>
+        <v>1010</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>927</v>
+        <v>1011</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>928</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>927</v>
+        <v>1011</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>928</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>927</v>
+        <v>1011</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>928</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>927</v>
+        <v>1017</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>928</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>1023</v>
@@ -9312,942 +9342,1063 @@
     </row>
     <row r="495" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>837</v>
+        <v>1023</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>838</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>837</v>
+        <v>1023</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>838</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>837</v>
+        <v>1023</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>838</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>837</v>
+        <v>937</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>838</v>
+        <v>938</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>889</v>
+        <v>937</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>890</v>
+        <v>938</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>889</v>
+        <v>937</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>890</v>
+        <v>938</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>889</v>
+        <v>937</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>890</v>
+        <v>938</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>889</v>
+        <v>1033</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>890</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>995</v>
+        <v>1033</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>996</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>995</v>
+        <v>1033</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>996</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>835</v>
+        <v>1033</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>147</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>147</v>
+        <v>848</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>147</v>
+        <v>848</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>147</v>
+        <v>848</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>1043</v>
+        <v>847</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>1044</v>
+        <v>848</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1043</v>
+        <v>899</v>
       </c>
       <c r="C510" s="4" t="s">
-        <v>1044</v>
+        <v>900</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>1043</v>
+        <v>899</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>1044</v>
+        <v>900</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1043</v>
+        <v>899</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>1044</v>
+        <v>900</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>989</v>
+        <v>899</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>990</v>
+        <v>900</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>989</v>
+        <v>1005</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>990</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>989</v>
+        <v>1005</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>990</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>1052</v>
+        <v>845</v>
       </c>
       <c r="C516" s="4" t="s">
-        <v>1053</v>
+        <v>153</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>1052</v>
+        <v>845</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>1053</v>
+        <v>153</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1052</v>
+        <v>845</v>
       </c>
       <c r="C518" s="4" t="s">
-        <v>1053</v>
+        <v>153</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>1052</v>
+        <v>845</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>1053</v>
+        <v>153</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1023</v>
+        <v>1053</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>1024</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>1023</v>
+        <v>1053</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>1024</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1023</v>
+        <v>1053</v>
       </c>
       <c r="C522" s="4" t="s">
-        <v>1024</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>1023</v>
+        <v>1053</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>1024</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>1023</v>
+        <v>999</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>1024</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>1023</v>
+        <v>999</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>1024</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1023</v>
+        <v>999</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>1024</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>1023</v>
+        <v>1062</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>1024</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>704</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>704</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>379</v>
+        <v>1062</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>34</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>945</v>
+        <v>1033</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>422</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>989</v>
+        <v>1033</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>990</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>1072</v>
+        <v>1033</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>1073</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C534" s="1" t="s">
-        <v>0</v>
+        <v>1033</v>
+      </c>
+      <c r="C534" s="4" t="s">
+        <v>1034</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C535" s="3" t="s">
-        <v>0</v>
+        <v>1033</v>
+      </c>
+      <c r="C535" s="5" t="s">
+        <v>1034</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1077</v>
+        <v>1033</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>1078</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>1080</v>
+        <v>1033</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>1081</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1083</v>
+        <v>1033</v>
       </c>
       <c r="C538" s="4" t="s">
-        <v>151</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>1084</v>
+        <v>1075</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>1085</v>
+        <v>1076</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>1086</v>
+        <v>716</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
-        <v>1087</v>
+        <v>1077</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1088</v>
+        <v>1076</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>186</v>
+        <v>716</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
-        <v>1089</v>
+        <v>1078</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>1090</v>
+        <v>391</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>106</v>
+        <v>34</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1092</v>
+        <v>955</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>186</v>
+        <v>434</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>1093</v>
+        <v>1080</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>1094</v>
+        <v>999</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>354</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
-        <v>1095</v>
+        <v>1081</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1096</v>
+        <v>1082</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>1097</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>1098</v>
+        <v>1084</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C545" s="5" t="s">
-        <v>48</v>
+        <v>0</v>
+      </c>
+      <c r="C545" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C546" s="4" t="s">
-        <v>380</v>
+        <v>0</v>
+      </c>
+      <c r="C546" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1101</v>
+        <v>1086</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>1102</v>
+        <v>1087</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>1103</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
-        <v>1104</v>
+        <v>1089</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1105</v>
+        <v>1090</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>869</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1106</v>
+        <v>1092</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>1107</v>
+        <v>1093</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>1008</v>
+        <v>157</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
-        <v>1108</v>
+        <v>1094</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1109</v>
+        <v>1095</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>583</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>1110</v>
+        <v>1097</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>1111</v>
+        <v>1098</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>583</v>
+        <v>192</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
-        <v>1112</v>
+        <v>1099</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1113</v>
+        <v>1100</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>1114</v>
+        <v>1101</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>1115</v>
+        <v>1102</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>590</v>
+        <v>192</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
-        <v>1116</v>
+        <v>1103</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1117</v>
+        <v>1104</v>
       </c>
       <c r="C554" s="4" t="s">
-        <v>583</v>
+        <v>367</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
-        <v>1118</v>
+        <v>1105</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>1119</v>
+        <v>1106</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>583</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1121</v>
+        <v>1109</v>
       </c>
       <c r="C556" s="4" t="s">
-        <v>583</v>
+        <v>48</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
-        <v>1122</v>
+        <v>1108</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>1123</v>
+        <v>1110</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>583</v>
+        <v>392</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
-        <v>1124</v>
+        <v>1111</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>583</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>1127</v>
+        <v>1115</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>583</v>
+        <v>879</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1129</v>
+        <v>1117</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>1130</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>1131</v>
+        <v>1118</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>1132</v>
+        <v>1119</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
-        <v>1133</v>
+        <v>1120</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1134</v>
+        <v>1121</v>
       </c>
       <c r="C562" s="4" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>1135</v>
+        <v>1122</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>1136</v>
+        <v>1123</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>583</v>
+        <v>48</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
-        <v>1137</v>
+        <v>1124</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1138</v>
+        <v>1125</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>477</v>
+        <v>602</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
-        <v>1139</v>
+        <v>1126</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>1140</v>
+        <v>1127</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>299</v>
+        <v>596</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
-        <v>1141</v>
+        <v>1128</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>1142</v>
+        <v>1129</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>376</v>
+        <v>596</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
-        <v>1143</v>
+        <v>1130</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>1144</v>
+        <v>1131</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
-        <v>1145</v>
+        <v>1132</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1146</v>
+        <v>1133</v>
       </c>
       <c r="C568" s="4" t="s">
-        <v>1147</v>
+        <v>596</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
-        <v>1148</v>
+        <v>1134</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>1149</v>
+        <v>1135</v>
       </c>
       <c r="C569" s="5" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
-        <v>1150</v>
+        <v>1136</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1151</v>
+        <v>1137</v>
       </c>
       <c r="C570" s="4" t="s">
-        <v>950</v>
+        <v>596</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
-        <v>1152</v>
+        <v>1138</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>1151</v>
+        <v>1139</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>950</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
-        <v>1153</v>
+        <v>1141</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="C572" s="4" t="s">
-        <v>1155</v>
+        <v>596</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
-        <v>1156</v>
+        <v>1143</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>1157</v>
+        <v>1144</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>696</v>
+        <v>596</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
-        <v>1158</v>
+        <v>1145</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1159</v>
+        <v>1146</v>
       </c>
       <c r="C574" s="4" t="s">
-        <v>376</v>
+        <v>596</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>1160</v>
+        <v>1147</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>335</v>
+        <v>1148</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>336</v>
+        <v>489</v>
       </c>
     </row>
     <row r="576" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
-        <v>1161</v>
+        <v>1149</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C576" s="1" t="s">
-        <v>0</v>
+        <v>1150</v>
+      </c>
+      <c r="C576" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="577" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
-        <v>1162</v>
+        <v>1151</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C577" s="3" t="s">
-        <v>0</v>
+        <v>1152</v>
+      </c>
+      <c r="C577" s="5" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="578" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
-        <v>1163</v>
+        <v>1153</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1164</v>
+        <v>1154</v>
       </c>
       <c r="C578" s="4" t="s">
-        <v>477</v>
+        <v>596</v>
       </c>
     </row>
     <row r="579" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B579" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C579" s="5" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A580" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C580" s="4" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A581" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B581" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C581" s="5" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A582" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C582" s="4" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A583" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B583" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C583" s="5" t="s">
         <v>1165</v>
       </c>
-      <c r="B579" s="3" t="s">
+    </row>
+    <row r="584" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A584" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C584" s="4" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A585" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B585" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C585" s="5" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A586" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C586" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A587" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B587" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C579" s="3" t="s">
+      <c r="C587" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
-    <row r="581" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
-    <row r="582" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="588" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A588" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A589" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B589" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C589" s="5" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A590" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B590" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C590" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="592" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="593" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/المواد.xlsx
+++ b/المواد.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8328"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="4908"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="1199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="1189">
   <si>
     <t/>
   </si>
@@ -804,1537 +804,1507 @@
     <t>20/08/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>C4 kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>144025005</t>
+    <t>فحوصات ESR فشن</t>
+  </si>
+  <si>
+    <t>محلول M-68 Probe Cleanser 50mL 5 Part Diff مايندري</t>
+  </si>
+  <si>
+    <t>2025112051</t>
+  </si>
+  <si>
+    <t>19/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>BC-30s-3part Instrument Auto Hematology Mindray</t>
+  </si>
+  <si>
+    <t>BA-88A Instrument Semi-Auto chemistry Mindray</t>
+  </si>
+  <si>
+    <t>I-Chroma 2 Instrument Boditech</t>
+  </si>
+  <si>
+    <t>Fe (Re +Calibrator)  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>145325011</t>
+  </si>
+  <si>
+    <t>24/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>GLU kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>141525011</t>
+  </si>
+  <si>
+    <t>05/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>141525012</t>
+  </si>
+  <si>
+    <t>HDL kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>142125009</t>
+  </si>
+  <si>
+    <t>20/06/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>142125012</t>
+  </si>
+  <si>
+    <t>03/09/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>IgG kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>144325004</t>
+  </si>
+  <si>
+    <t>31/07/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>RF II  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>147025008</t>
+  </si>
+  <si>
+    <t>TC  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>141625012</t>
+  </si>
+  <si>
+    <t>10/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>141625014</t>
+  </si>
+  <si>
+    <t>141625015</t>
+  </si>
+  <si>
+    <t>15/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TG kit Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>141725010</t>
+  </si>
+  <si>
+    <t>05/09/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>141725011</t>
+  </si>
+  <si>
+    <t>24/09/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>UIBC Chemistry Mindray kit with cal</t>
+  </si>
+  <si>
+    <t>146725006</t>
+  </si>
+  <si>
+    <t>29/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>146725008</t>
+  </si>
+  <si>
+    <t>17/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>كيوفيت Microcuvettes -Hemo هيمو كروما</t>
+  </si>
+  <si>
+    <t>HBPVK88</t>
+  </si>
+  <si>
+    <t>23/11/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Urea kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>141325023</t>
+  </si>
+  <si>
+    <t>Amylase kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>142825003</t>
+  </si>
+  <si>
+    <t>27/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>cleanser CD-80 محلول تنظيف (1L)</t>
+  </si>
+  <si>
+    <t>196125097</t>
+  </si>
+  <si>
+    <t>196125228</t>
+  </si>
+  <si>
+    <t>16/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Multi Sera Calibrator Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>150125010</t>
+  </si>
+  <si>
+    <t>09/10/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>150125011</t>
+  </si>
+  <si>
+    <t>19/10/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CC. M Control Chemistry Mindray level 1</t>
+  </si>
+  <si>
+    <t>059325009</t>
+  </si>
+  <si>
+    <t>06/09/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>059325010</t>
+  </si>
+  <si>
+    <t>28/10/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HbA1c Calibrator  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>155125002</t>
+  </si>
+  <si>
+    <t>13/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>155125014</t>
+  </si>
+  <si>
+    <t>12/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HBA1c (R) kit Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>044625009</t>
+  </si>
+  <si>
+    <t>044625010</t>
+  </si>
+  <si>
+    <t>Specific Protein Calibrator Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>150725010</t>
+  </si>
+  <si>
+    <t>150725011</t>
+  </si>
+  <si>
+    <t>27/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Semi-cuvettes (steel ball included)/350 كيوفيت</t>
+  </si>
+  <si>
+    <t>Mispa i2 Instrument agappe</t>
+  </si>
+  <si>
+    <t>CYBOW 3</t>
+  </si>
+  <si>
+    <t>EVA 251027</t>
+  </si>
+  <si>
+    <t>26/10/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CYBOW 10</t>
+  </si>
+  <si>
+    <t>241118</t>
+  </si>
+  <si>
+    <t>17/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>ichamber</t>
+  </si>
+  <si>
+    <t>IgM kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>144225003</t>
+  </si>
+  <si>
+    <t>Lipids Calibrator Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>150425013</t>
+  </si>
+  <si>
+    <t>23/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Aqappe 30ml Nano Detergent</t>
+  </si>
+  <si>
+    <t>32410142</t>
+  </si>
+  <si>
+    <t>Afias-6 paper + i chroma 11</t>
+  </si>
+  <si>
+    <t>RF II cal - Mindray</t>
+  </si>
+  <si>
+    <t>158925010</t>
+  </si>
+  <si>
+    <t>13/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Capillary tube 15ul  25/tube</t>
+  </si>
+  <si>
+    <t>BC-10-3part Instrument Auto Hematology Mindray</t>
+  </si>
+  <si>
+    <t>Hba1c Control Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>052425012</t>
+  </si>
+  <si>
+    <t>09/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-10CFL Lyse 3-part 500ml Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025112651</t>
+  </si>
+  <si>
+    <t>25/11/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Creatinine kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>141125020</t>
+  </si>
+  <si>
+    <t>23/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 FN Dye Reagent 7-part 12mL Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025061351</t>
+  </si>
+  <si>
+    <t>12/06/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 FR Dye Reagent 7-part 12mL Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025080652</t>
+  </si>
+  <si>
+    <t>05/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 LD Lyse Reagent 7-part 1L Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025081151</t>
+  </si>
+  <si>
+    <t>10/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 LH Lyse Reagent 7-part 1L Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025050951</t>
+  </si>
+  <si>
+    <t>08/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 DS Diluent Reagent 7-part 20L Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025082653</t>
+  </si>
+  <si>
+    <t>25/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HbA1c 5ul micro capillary tube</t>
+  </si>
+  <si>
+    <t>CP05TAA01</t>
+  </si>
+  <si>
+    <t>12/01/2028 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>حديدة فيتامين دي</t>
+  </si>
+  <si>
+    <t>T3 kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2024100113</t>
+  </si>
+  <si>
+    <t>08/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>T4 kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025060111</t>
+  </si>
+  <si>
+    <t>Tg kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025070111</t>
+  </si>
+  <si>
+    <t>Anti-Tg kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025100111</t>
+  </si>
+  <si>
+    <t>13/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-TPO kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>02/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CA19-9 kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>11/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>T-PSA kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025070131</t>
+  </si>
+  <si>
+    <t>15/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>FPSA kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025050111</t>
+  </si>
+  <si>
+    <t>27/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>AFP  kit 2×50T Cl-900i Mindray</t>
+  </si>
+  <si>
+    <t>12/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Ferritin  kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025090131</t>
+  </si>
+  <si>
+    <t>17/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>LH  kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>FSH kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025080111</t>
+  </si>
+  <si>
+    <t>10/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>PRL kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025030211</t>
+  </si>
+  <si>
+    <t>19/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Free T3 kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025060112</t>
+  </si>
+  <si>
+    <t>PROG kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>TESTO kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>18/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>E2 kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025090111</t>
+  </si>
+  <si>
+    <t>06/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Insulin kit 2×50T Cl900 Mindray</t>
+  </si>
+  <si>
+    <t>C-Peptide kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025010111</t>
+  </si>
+  <si>
+    <t>26/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>DHEA-S kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>13/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Cortisol kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>08/06/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TnI kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>15/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>2025080121</t>
+  </si>
+  <si>
+    <t>14/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>PTH kit 2×50T Cl900i  Mindray</t>
+  </si>
+  <si>
+    <t>2025040112</t>
+  </si>
+  <si>
+    <t>19/05/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Folate kit 50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025100121</t>
+  </si>
+  <si>
+    <t>10/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HIV kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025060211</t>
+  </si>
+  <si>
+    <t>07/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TSH Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025080112</t>
+  </si>
+  <si>
+    <t>29/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-Tg Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>30/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-TPO Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>Total BHCG Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>LH Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>17/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Prolactin Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>Testosterone Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>04/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Cortisol Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>25/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TnI Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025070101</t>
+  </si>
+  <si>
+    <t>2025100101</t>
+  </si>
+  <si>
+    <t>OH-25 Vitamin D Total Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>26/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>19/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Folate Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2024120111</t>
+  </si>
+  <si>
+    <t>03/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>29/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HBsAg Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>Substrate Solution Consumables Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025110521</t>
+  </si>
+  <si>
+    <t>14/06/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Tumor Marker Multi Control L 1*5ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>23/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Cardiac Marker Multi Control H 1*2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>20/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>2025110101</t>
+  </si>
+  <si>
+    <t>25/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Wash Buffer Consumables 1X10L Cl-900i Mindray</t>
+  </si>
+  <si>
+    <t>2025111915</t>
+  </si>
+  <si>
+    <t>18/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>2025111918</t>
+  </si>
+  <si>
+    <t>Immunoassay Cuvette Consumables 2*88 Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>531351125</t>
+  </si>
+  <si>
+    <t>01/01/2032 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>6517791532</t>
+  </si>
+  <si>
+    <t>01/04/2031 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Amylase kit 40T Agappe</t>
+  </si>
+  <si>
+    <t>32510237</t>
+  </si>
+  <si>
+    <t>Lipase kit 25T Agappe</t>
+  </si>
+  <si>
+    <t>32410226</t>
+  </si>
+  <si>
+    <t>NT-proBNP Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA NBVFF11E</t>
+  </si>
+  <si>
+    <t>Calprotectin Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>CPTYB10Z</t>
+  </si>
+  <si>
+    <t>24/06/2025 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA CPVFD03Z</t>
+  </si>
+  <si>
+    <t>AMH Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>MHVYA27G</t>
+  </si>
+  <si>
+    <t>15/06/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>MYO kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025040111</t>
+  </si>
+  <si>
+    <t>09/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-HBc kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2024070131</t>
+  </si>
+  <si>
+    <t>13/05/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>26/09/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Total Ige Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  TEVHF05EX</t>
+  </si>
+  <si>
+    <t>24/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA TEVHF05EX</t>
+  </si>
+  <si>
+    <t>BC-10-3part Instrument used Auto Hematology Mindray</t>
+  </si>
+  <si>
+    <t>ALD kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>Renin Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>04/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>VD-T kit 2×50T Cl900i  Mindray</t>
+  </si>
+  <si>
+    <t>ASO/CRP/RF II Triple Control L 1mL Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>059224011</t>
+  </si>
+  <si>
+    <t>02/06/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>059225008</t>
+  </si>
+  <si>
+    <t>ASO/CRP/RF II Triple Control H 1mL Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>Epithod 616- HBA1C Standard Cartridge  DX-Gen</t>
+  </si>
+  <si>
+    <t>AMH Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  MHVXC12E</t>
+  </si>
+  <si>
+    <t>04/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA MHVXC12E</t>
+  </si>
+  <si>
+    <t>M-62 DR Diluent Reagent 7-part 1L Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025091151</t>
+  </si>
+  <si>
+    <t>10/09/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>AMH kit 2×50T with cal. CL900i Mindray</t>
+  </si>
+  <si>
+    <t>2025010221</t>
+  </si>
+  <si>
+    <t>06/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-CCP plus Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA  ACVXA35G</t>
+  </si>
+  <si>
+    <t>Troponin T Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>TAVYA23G</t>
+  </si>
+  <si>
+    <t>29/06/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Total Ige Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA TEVXA15X</t>
+  </si>
+  <si>
+    <t>CT  kit 2×50T CL900i Mindray</t>
+  </si>
+  <si>
+    <t>21/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>MXA/CRP Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA MRVDA17X</t>
+  </si>
+  <si>
+    <t>08/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Infliximab Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA  FMVXA26G</t>
+  </si>
+  <si>
+    <t>01/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>FMVXA26G</t>
+  </si>
+  <si>
+    <t>Progesterone Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>PGWAA13X</t>
+  </si>
+  <si>
+    <t>HCY II kit with cal. Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>148025011</t>
+  </si>
+  <si>
+    <t>01/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>IgE kit with cal. Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>145925003</t>
+  </si>
+  <si>
+    <t>02/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Clover A1C plus Analyzer</t>
+  </si>
+  <si>
+    <t>Vitamin D  NeO Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA  VEVHC14X</t>
+  </si>
+  <si>
+    <t>EVA VEVHC12X</t>
+  </si>
+  <si>
+    <t>EVA VEVHC13X</t>
+  </si>
+  <si>
+    <t>Rubella Virus IgG kit 2×50T  with cal.Cl900i  Mindray</t>
+  </si>
+  <si>
+    <t>2025070141</t>
+  </si>
+  <si>
+    <t>14/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CMV IgM kit 2×50T with cal.Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>26/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CMV IgG kit  2×50T with cal.Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025020111</t>
+  </si>
+  <si>
+    <t>07/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>ZINC kit 20T Agappe</t>
+  </si>
+  <si>
+    <t>32512383</t>
+  </si>
+  <si>
+    <t>Iron kit 100T Agappe</t>
+  </si>
+  <si>
+    <t>32411254</t>
+  </si>
+  <si>
+    <t>32411296</t>
+  </si>
+  <si>
+    <t>IGRA -TB  Kit 8T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA TBVYA30G</t>
+  </si>
+  <si>
+    <t>free T4  Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>F4VLA50G</t>
+  </si>
+  <si>
+    <t>11/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Free T4 Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  F4VGF04</t>
+  </si>
+  <si>
+    <t>CA19-9 Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  CXVHB05EX</t>
+  </si>
+  <si>
+    <t>Vitamin D  Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  VEVCB06E</t>
+  </si>
+  <si>
+    <t>26/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA  VEVDB07E</t>
+  </si>
+  <si>
+    <t>09/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>C3 Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509120</t>
+  </si>
+  <si>
+    <t>23/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CRP Kit 60T Mispa i3</t>
+  </si>
+  <si>
+    <t>32511199</t>
+  </si>
+  <si>
+    <t>28/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>32512330</t>
+  </si>
+  <si>
+    <t>04/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Ferritin Kit 30T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512316</t>
+  </si>
+  <si>
+    <t>03/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HbA1c Kit 30T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512125</t>
+  </si>
+  <si>
+    <t>C4 Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA 32506489</t>
+  </si>
+  <si>
+    <t>15/06/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Washing solution 1*50 ml  Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509067</t>
+  </si>
+  <si>
+    <t>probe cleanser Mispa i3</t>
+  </si>
+  <si>
+    <t>32512329</t>
+  </si>
+  <si>
+    <t>30/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>( ALB Kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>148325013</t>
+  </si>
+  <si>
+    <t>05/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>148325014</t>
+  </si>
+  <si>
+    <t>( ALP kit  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140325004</t>
+  </si>
+  <si>
+    <t>12/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>140325010</t>
+  </si>
+  <si>
+    <t>18/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>( ALT  (GPT) kit  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140125021</t>
+  </si>
+  <si>
+    <t>10/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>140125022</t>
+  </si>
+  <si>
+    <t>( AST (GOT) kit  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140225017</t>
+  </si>
+  <si>
+    <t>140225018</t>
+  </si>
+  <si>
+    <t>25/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>( Ca kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>142225007</t>
+  </si>
+  <si>
+    <t>( CRP kit  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>148925009</t>
+  </si>
+  <si>
+    <t>11/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>148925011</t>
+  </si>
+  <si>
+    <t>( D- Bill (vox) kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140725012</t>
+  </si>
+  <si>
+    <t>01/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>140725013</t>
+  </si>
+  <si>
+    <t>( LDL-C kit  Chemistry Mindray  ( Large</t>
+  </si>
+  <si>
+    <t>142025008</t>
+  </si>
+  <si>
+    <t>11/07/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>142025010</t>
+  </si>
+  <si>
+    <t>17/09/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>( MG kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>148225004</t>
+  </si>
+  <si>
+    <t>( T-Bill vox kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140625015</t>
+  </si>
+  <si>
+    <t>( TP kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140825005</t>
+  </si>
+  <si>
+    <t>( UA  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>141225013</t>
+  </si>
+  <si>
+    <t>HBA1C Kit 10T Clover كلوفر</t>
+  </si>
+  <si>
+    <t>EVA B25D05D12EL</t>
+  </si>
+  <si>
+    <t>11/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA B25D14E13DL</t>
+  </si>
+  <si>
+    <t>12/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA B25F03H12DL</t>
+  </si>
+  <si>
+    <t>EVA B25F03H13DL</t>
+  </si>
+  <si>
+    <t>EVA B25F03H14DL</t>
+  </si>
+  <si>
+    <t>13/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA B25F04H12EL</t>
+  </si>
+  <si>
+    <t>Ferritin Cal Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>152725001</t>
+  </si>
+  <si>
+    <t>10/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Urilyzer® Cell Cuvettes (600 PCS/BOX) analyticon</t>
+  </si>
+  <si>
+    <t>2411C100</t>
+  </si>
+  <si>
+    <t>CombiScreen® 11SYS PLUS 150 strips per vial analyticon</t>
+  </si>
+  <si>
+    <t>2786/2010</t>
+  </si>
+  <si>
+    <t>IGRA-TB Tube 8T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA TBTVYA54</t>
+  </si>
+  <si>
+    <t>22/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>H.Pylori  Kit 10T  Mispa i3</t>
+  </si>
+  <si>
+    <t>32511197</t>
+  </si>
+  <si>
+    <t>24/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>32512294</t>
+  </si>
+  <si>
+    <t>EVA  32509360</t>
+  </si>
+  <si>
+    <t>Microalbumin Kit 30T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512135</t>
+  </si>
+  <si>
+    <t>IgE Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32507209</t>
+  </si>
+  <si>
+    <t>06/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA  32509128</t>
+  </si>
+  <si>
+    <t>20/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA 32506314</t>
+  </si>
+  <si>
+    <t>Ceruloplasmin  Kit 10 T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512117</t>
+  </si>
+  <si>
+    <t>IgM Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509129</t>
+  </si>
+  <si>
+    <t>IgA Kit 10T  Mispa i3</t>
+  </si>
+  <si>
+    <t>32512129</t>
+  </si>
+  <si>
+    <t>IgG Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509298</t>
+  </si>
+  <si>
+    <t>PCT Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512137</t>
+  </si>
+  <si>
+    <t>27/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA  32509132</t>
+  </si>
+  <si>
+    <t>IFOB Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  FOVXE06Z</t>
+  </si>
+  <si>
+    <t>03/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>D-DIMER NeO Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA KDVCE03EX</t>
+  </si>
+  <si>
+    <t>EVA KDVHF03EX</t>
+  </si>
+  <si>
+    <t>06/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>D-DIMER NeO Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA  KDVHA47X</t>
+  </si>
+  <si>
+    <t>20/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA KDVFA45X</t>
+  </si>
+  <si>
+    <t>Free PSA Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA F1VDB02EX</t>
+  </si>
+  <si>
+    <t>F1VYB03EX</t>
+  </si>
+  <si>
+    <t>Rubella Igm Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>RMULA09EX</t>
+  </si>
+  <si>
+    <t>12/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Rubella Igg Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  RGVXA09EX</t>
+  </si>
+  <si>
+    <t>CMV Igm Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  VMVHA07EX</t>
+  </si>
+  <si>
+    <t>04/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CMV Igg Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  VGVFA09EX</t>
+  </si>
+  <si>
+    <t>01/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Free PSA Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>F1VLA10G</t>
+  </si>
+  <si>
+    <t>14/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>AFP Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>AFVKB06EX</t>
+  </si>
+  <si>
+    <t>10/07/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CEA Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA CEVFB03EX</t>
+  </si>
+  <si>
+    <t>CK-MB Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA KCVBA12EX</t>
+  </si>
+  <si>
+    <t>05/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>KCVYB05EX</t>
+  </si>
+  <si>
+    <t>Toxo igm Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA XMVXA05EX</t>
+  </si>
+  <si>
+    <t>23/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>ASO Kit 30T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512110</t>
+  </si>
+  <si>
+    <t>19/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>RF Kit 30T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32508451</t>
+  </si>
+  <si>
+    <t>11/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Myoglobin NeO Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA KMVDB05EX</t>
+  </si>
+  <si>
+    <t>06/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>UPS 1500 VA OFFLINE (NEW)</t>
+  </si>
+  <si>
+    <t>UPS 1500 VA OFFLINE (USED)</t>
+  </si>
+  <si>
+    <t>HEMATOLOGY PRINTER (NEW)</t>
+  </si>
+  <si>
+    <t>Ca19-9 Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>CXVKA08G</t>
+  </si>
+  <si>
+    <t>Daily check  (Clover A1c Plus)</t>
+  </si>
+  <si>
+    <t>PK24F27</t>
+  </si>
+  <si>
+    <t>26/06/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>PK24J08</t>
+  </si>
+  <si>
+    <t>PK25L03</t>
+  </si>
+  <si>
+    <t>02/12/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CD-80 Detergent 2L</t>
+  </si>
+  <si>
+    <t>196125193</t>
+  </si>
+  <si>
+    <t>26/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>PSA NeO Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA PSVEB08EX</t>
   </si>
   <si>
     <t>15/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>فحوصات ESR فشن</t>
-  </si>
-  <si>
-    <t>محلول M-68 Probe Cleanser 50mL 5 Part Diff مايندري</t>
-  </si>
-  <si>
-    <t>2025112051</t>
-  </si>
-  <si>
-    <t>19/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>BC-30s-3part Instrument Auto Hematology Mindray</t>
-  </si>
-  <si>
-    <t>BA-88A Instrument Semi-Auto chemistry Mindray</t>
-  </si>
-  <si>
-    <t>I-Chroma 2 Instrument Boditech</t>
-  </si>
-  <si>
-    <t>Fe (Re +Calibrator)  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>145325011</t>
-  </si>
-  <si>
-    <t>24/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>GLU kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>141525011</t>
-  </si>
-  <si>
-    <t>05/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>141525012</t>
-  </si>
-  <si>
-    <t>HDL kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>142125009</t>
-  </si>
-  <si>
-    <t>20/06/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>142125012</t>
-  </si>
-  <si>
-    <t>03/09/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>IgG kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>144325004</t>
-  </si>
-  <si>
-    <t>31/07/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>RF II  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>147025008</t>
-  </si>
-  <si>
-    <t>TC  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>141625012</t>
-  </si>
-  <si>
-    <t>10/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>141625014</t>
-  </si>
-  <si>
-    <t>141625015</t>
-  </si>
-  <si>
-    <t>15/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TG kit Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>141725010</t>
-  </si>
-  <si>
-    <t>05/09/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>141725011</t>
-  </si>
-  <si>
-    <t>24/09/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>UIBC Chemistry Mindray kit with cal</t>
-  </si>
-  <si>
-    <t>146725006</t>
-  </si>
-  <si>
-    <t>29/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>146725008</t>
-  </si>
-  <si>
-    <t>17/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>كيوفيت Microcuvettes -Hemo هيمو كروما</t>
-  </si>
-  <si>
-    <t>HBPVK88</t>
-  </si>
-  <si>
-    <t>23/11/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Urea kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>141325023</t>
-  </si>
-  <si>
-    <t>Amylase kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>142825003</t>
-  </si>
-  <si>
-    <t>27/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>cleanser CD-80 محلول تنظيف (1L)</t>
-  </si>
-  <si>
-    <t>196125097</t>
-  </si>
-  <si>
-    <t>196125228</t>
-  </si>
-  <si>
-    <t>16/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Multi Sera Calibrator Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>150125010</t>
-  </si>
-  <si>
-    <t>09/10/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>150125011</t>
-  </si>
-  <si>
-    <t>19/10/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CC. M Control Chemistry Mindray level 1</t>
-  </si>
-  <si>
-    <t>059325009</t>
-  </si>
-  <si>
-    <t>06/09/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>059325010</t>
-  </si>
-  <si>
-    <t>28/10/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HbA1c Calibrator  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>155125002</t>
-  </si>
-  <si>
-    <t>13/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>155125014</t>
-  </si>
-  <si>
-    <t>12/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HBA1c (R) kit Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>044625009</t>
-  </si>
-  <si>
-    <t>044625010</t>
-  </si>
-  <si>
-    <t>Specific Protein Calibrator Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>150725010</t>
-  </si>
-  <si>
-    <t>150725011</t>
-  </si>
-  <si>
-    <t>27/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Semi-cuvettes (steel ball included)/350 كيوفيت</t>
-  </si>
-  <si>
-    <t>Mispa i2 Instrument agappe</t>
-  </si>
-  <si>
-    <t>CYBOW 3</t>
-  </si>
-  <si>
-    <t>EVA 251027</t>
-  </si>
-  <si>
-    <t>26/10/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CYBOW 10</t>
-  </si>
-  <si>
-    <t>241118</t>
-  </si>
-  <si>
-    <t>17/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>ichamber</t>
-  </si>
-  <si>
-    <t>IgM kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>144225003</t>
-  </si>
-  <si>
-    <t>Lipids Calibrator Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>150425013</t>
-  </si>
-  <si>
-    <t>23/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Aqappe 30ml Nano Detergent</t>
-  </si>
-  <si>
-    <t>32410142</t>
-  </si>
-  <si>
-    <t>Afias-6 paper + i chroma 11</t>
-  </si>
-  <si>
-    <t>RF II cal - Mindray</t>
-  </si>
-  <si>
-    <t>158925010</t>
-  </si>
-  <si>
-    <t>13/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Capillary tube 15ul  25/tube</t>
-  </si>
-  <si>
-    <t>BC-10-3part Instrument Auto Hematology Mindray</t>
-  </si>
-  <si>
-    <t>Hba1c Control Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>052425012</t>
-  </si>
-  <si>
-    <t>09/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-10CFL Lyse 3-part 500ml Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025112651</t>
-  </si>
-  <si>
-    <t>25/11/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Creatinine kit  Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>141125020</t>
-  </si>
-  <si>
-    <t>23/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 FN Dye Reagent 7-part 12mL Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025061351</t>
-  </si>
-  <si>
-    <t>12/06/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 FR Dye Reagent 7-part 12mL Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025080652</t>
-  </si>
-  <si>
-    <t>05/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 LD Lyse Reagent 7-part 1L Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025081151</t>
-  </si>
-  <si>
-    <t>10/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 LH Lyse Reagent 7-part 1L Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025050951</t>
-  </si>
-  <si>
-    <t>08/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>M-62 DS Diluent Reagent 7-part 20L Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025082653</t>
-  </si>
-  <si>
-    <t>25/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HbA1c 5ul micro capillary tube</t>
-  </si>
-  <si>
-    <t>CP05TAA01</t>
-  </si>
-  <si>
-    <t>12/01/2028 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>حديدة فيتامين دي</t>
-  </si>
-  <si>
-    <t>T3 kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2024100113</t>
-  </si>
-  <si>
-    <t>08/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>T4 kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025060111</t>
-  </si>
-  <si>
-    <t>Tg kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025070111</t>
-  </si>
-  <si>
-    <t>Anti-Tg kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025100111</t>
-  </si>
-  <si>
-    <t>13/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-TPO kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>02/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CA19-9 kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>11/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>T-PSA kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025070131</t>
-  </si>
-  <si>
-    <t>15/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>FPSA kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025050111</t>
-  </si>
-  <si>
-    <t>27/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>AFP  kit 2×50T Cl-900i Mindray</t>
-  </si>
-  <si>
-    <t>12/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Ferritin  kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025090131</t>
-  </si>
-  <si>
-    <t>17/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>LH  kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>FSH kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025080111</t>
-  </si>
-  <si>
-    <t>10/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>PRL kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025030211</t>
-  </si>
-  <si>
-    <t>19/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Free T3 kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025060112</t>
-  </si>
-  <si>
-    <t>PROG kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>TESTO kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>18/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>E2 kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025090111</t>
-  </si>
-  <si>
-    <t>06/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Insulin kit 2×50T Cl900 Mindray</t>
-  </si>
-  <si>
-    <t>C-Peptide kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025010111</t>
-  </si>
-  <si>
-    <t>26/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>DHEA-S kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>13/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Cortisol kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>08/06/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TnI kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>15/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>2025080121</t>
-  </si>
-  <si>
-    <t>14/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>PTH kit 2×50T Cl900i  Mindray</t>
-  </si>
-  <si>
-    <t>2025040112</t>
-  </si>
-  <si>
-    <t>19/05/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Folate kit 50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025100121</t>
-  </si>
-  <si>
-    <t>10/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HIV kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025060211</t>
-  </si>
-  <si>
-    <t>07/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TSH Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025080112</t>
-  </si>
-  <si>
-    <t>29/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-Tg Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>30/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-TPO Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>Total BHCG Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>LH Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>17/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Prolactin Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>Testosterone Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>04/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Cortisol Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>25/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TnI Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025070101</t>
-  </si>
-  <si>
-    <t>2025100101</t>
-  </si>
-  <si>
-    <t>OH-25 Vitamin D Total Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>26/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>19/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Folate Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2024120111</t>
-  </si>
-  <si>
-    <t>03/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>29/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HBsAg Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>Substrate Solution Consumables Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025110521</t>
-  </si>
-  <si>
-    <t>14/06/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Tumor Marker Multi Control L 1*5ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>23/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Cardiac Marker Multi Control H 1*2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>20/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>2025110101</t>
-  </si>
-  <si>
-    <t>25/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Wash Buffer Consumables 1X10L Cl-900i Mindray</t>
-  </si>
-  <si>
-    <t>2025111915</t>
-  </si>
-  <si>
-    <t>18/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>2025111918</t>
-  </si>
-  <si>
-    <t>Immunoassay Cuvette Consumables 2*88 Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>531351125</t>
-  </si>
-  <si>
-    <t>01/01/2032 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>6517791532</t>
-  </si>
-  <si>
-    <t>01/04/2031 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Amylase kit 40T Agappe</t>
-  </si>
-  <si>
-    <t>32510237</t>
-  </si>
-  <si>
-    <t>Lipase kit 25T Agappe</t>
-  </si>
-  <si>
-    <t>32410226</t>
-  </si>
-  <si>
-    <t>NT-proBNP Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA NBVFF11E</t>
-  </si>
-  <si>
-    <t>Calprotectin Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>CPTYB10Z</t>
-  </si>
-  <si>
-    <t>24/06/2025 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA CPVFD03Z</t>
-  </si>
-  <si>
-    <t>H. Pylori SA Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA HSVCH02</t>
-  </si>
-  <si>
-    <t>EVA HSVHX03</t>
-  </si>
-  <si>
-    <t>03/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>AMH Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>MHVYA27G</t>
-  </si>
-  <si>
-    <t>15/06/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>MYO kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025040111</t>
-  </si>
-  <si>
-    <t>09/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-HBc kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2024070131</t>
-  </si>
-  <si>
-    <t>13/05/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>26/09/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Total Ige Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  TEVHF05EX</t>
-  </si>
-  <si>
-    <t>24/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA TEVHF05EX</t>
-  </si>
-  <si>
-    <t>BC-10-3part Instrument used Auto Hematology Mindray</t>
-  </si>
-  <si>
-    <t>ALD kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>Renin Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>04/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Renin kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>VD-T kit 2×50T Cl900i  Mindray</t>
-  </si>
-  <si>
-    <t>ASO/CRP/RF II Triple Control L 1mL Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>059224011</t>
-  </si>
-  <si>
-    <t>02/06/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>059225008</t>
-  </si>
-  <si>
-    <t>ASO/CRP/RF II Triple Control H 1mL Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>Epithod 616- HBA1C Standard Cartridge  DX-Gen</t>
-  </si>
-  <si>
-    <t>AMH Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  MHVXC12E</t>
-  </si>
-  <si>
-    <t>04/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA MHVXC12E</t>
-  </si>
-  <si>
-    <t>M-62 DR Diluent Reagent 7-part 1L Hematology Mindray</t>
-  </si>
-  <si>
-    <t>2025091151</t>
-  </si>
-  <si>
-    <t>10/09/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>AMH kit 2×50T with cal. CL900i Mindray</t>
-  </si>
-  <si>
-    <t>2025010221</t>
-  </si>
-  <si>
-    <t>06/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-CCP plus Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA  ACVXA35G</t>
-  </si>
-  <si>
-    <t>Troponin T Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>TAVYA23G</t>
-  </si>
-  <si>
-    <t>29/06/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Total Ige Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA TEVXA15X</t>
-  </si>
-  <si>
-    <t>CT  kit 2×50T CL900i Mindray</t>
-  </si>
-  <si>
-    <t>21/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>MXA/CRP Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA MRVDA17X</t>
-  </si>
-  <si>
-    <t>08/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Infliximab Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA  FMVXA26G</t>
-  </si>
-  <si>
-    <t>01/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>FMVXA26G</t>
-  </si>
-  <si>
-    <t>Progesterone Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>PGWAA13X</t>
-  </si>
-  <si>
-    <t>HCY II kit with cal. Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>148025011</t>
-  </si>
-  <si>
-    <t>01/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>IgE kit with cal. Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>145925003</t>
-  </si>
-  <si>
-    <t>02/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Clover A1C plus Analyzer</t>
-  </si>
-  <si>
-    <t>Vitamin D  NeO Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA  VEVHC14X</t>
-  </si>
-  <si>
-    <t>EVA VEVHC12X</t>
-  </si>
-  <si>
-    <t>EVA VEVHC13X</t>
-  </si>
-  <si>
-    <t>Rubella Virus IgG kit 2×50T  with cal.Cl900i  Mindray</t>
-  </si>
-  <si>
-    <t>2025070141</t>
-  </si>
-  <si>
-    <t>14/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CMV IgM kit 2×50T with cal.Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>26/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CMV IgG kit  2×50T with cal.Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025020111</t>
-  </si>
-  <si>
-    <t>07/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>ZINC kit 20T Agappe</t>
-  </si>
-  <si>
-    <t>32512383</t>
-  </si>
-  <si>
-    <t>Iron kit 100T Agappe</t>
-  </si>
-  <si>
-    <t>32411254</t>
-  </si>
-  <si>
-    <t>32411296</t>
-  </si>
-  <si>
-    <t>IGRA -TB  Kit 8T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA TBVYA30G</t>
-  </si>
-  <si>
-    <t>free T4  Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>F4VLA50G</t>
-  </si>
-  <si>
-    <t>11/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Free T4 Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  F4VGF04</t>
-  </si>
-  <si>
-    <t>CA19-9 Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  CXVHB05EX</t>
-  </si>
-  <si>
-    <t>Vitamin D  Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  VEVCB06E</t>
-  </si>
-  <si>
-    <t>26/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA  VEVDB07E</t>
-  </si>
-  <si>
-    <t>09/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>C3 Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509120</t>
-  </si>
-  <si>
-    <t>23/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CRP Kit 60T Mispa i3</t>
-  </si>
-  <si>
-    <t>32511199</t>
-  </si>
-  <si>
-    <t>28/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>32512330</t>
-  </si>
-  <si>
-    <t>04/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA  32508384</t>
-  </si>
-  <si>
-    <t>06/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Ferritin Kit 30T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512316</t>
-  </si>
-  <si>
-    <t>03/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HbA1c Kit 30T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512125</t>
-  </si>
-  <si>
-    <t>C4 Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA 32506489</t>
-  </si>
-  <si>
-    <t>15/06/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Washing solution 1*50 ml  Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509067</t>
-  </si>
-  <si>
-    <t>probe cleanser Mispa i3</t>
-  </si>
-  <si>
-    <t>32512329</t>
-  </si>
-  <si>
-    <t>30/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>( ALB Kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>148325013</t>
-  </si>
-  <si>
-    <t>05/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>148325014</t>
-  </si>
-  <si>
-    <t>( ALP kit  Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140325004</t>
-  </si>
-  <si>
-    <t>12/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>140325010</t>
-  </si>
-  <si>
-    <t>18/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>( ALT  (GPT) kit  Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140125021</t>
-  </si>
-  <si>
-    <t>10/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>140125022</t>
-  </si>
-  <si>
-    <t>( AST (GOT) kit  Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140225017</t>
-  </si>
-  <si>
-    <t>140225018</t>
-  </si>
-  <si>
-    <t>25/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>( Ca kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>142225007</t>
-  </si>
-  <si>
-    <t>( CRP kit  Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>148925009</t>
-  </si>
-  <si>
-    <t>11/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>148925011</t>
-  </si>
-  <si>
-    <t>( D- Bill (vox) kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140725012</t>
-  </si>
-  <si>
-    <t>01/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>140725013</t>
-  </si>
-  <si>
-    <t>( LDL-C kit  Chemistry Mindray  ( Large</t>
-  </si>
-  <si>
-    <t>142025008</t>
-  </si>
-  <si>
-    <t>11/07/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>142025010</t>
-  </si>
-  <si>
-    <t>17/09/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>( MG kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>148225004</t>
-  </si>
-  <si>
-    <t>( T-Bill vox kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140625015</t>
-  </si>
-  <si>
-    <t>( TP kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140825005</t>
-  </si>
-  <si>
-    <t>( UA  Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>141225011</t>
-  </si>
-  <si>
-    <t>27/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>141225013</t>
-  </si>
-  <si>
-    <t>HBA1C Kit 10T Clover كلوفر</t>
-  </si>
-  <si>
-    <t>EVA B25D05D12EL</t>
-  </si>
-  <si>
-    <t>11/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA B25D14E13DL</t>
-  </si>
-  <si>
-    <t>12/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA B25F03H12DL</t>
-  </si>
-  <si>
-    <t>EVA B25F03H13DL</t>
-  </si>
-  <si>
-    <t>EVA B25F03H14DL</t>
-  </si>
-  <si>
-    <t>13/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA B25F04H12EL</t>
-  </si>
-  <si>
-    <t>Urilyzer® Cell Cuvettes (600 PCS/BOX) analyticon</t>
-  </si>
-  <si>
-    <t>2411C100</t>
-  </si>
-  <si>
-    <t>CombiScreen® 11SYS PLUS 150 strips per vial analyticon</t>
-  </si>
-  <si>
-    <t>2786/2010</t>
-  </si>
-  <si>
-    <t>IGRA-TB Tube 8T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA TBTVYA54</t>
-  </si>
-  <si>
-    <t>22/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>H.Pylori  Kit 10T  Mispa i3</t>
-  </si>
-  <si>
-    <t>32511197</t>
-  </si>
-  <si>
-    <t>24/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>32512294</t>
-  </si>
-  <si>
-    <t>EVA  32509360</t>
-  </si>
-  <si>
-    <t>Microalbumin Kit 30T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512135</t>
-  </si>
-  <si>
-    <t>IgE Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32507209</t>
-  </si>
-  <si>
-    <t>06/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA  32509128</t>
-  </si>
-  <si>
-    <t>20/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA 32506314</t>
-  </si>
-  <si>
-    <t>Ceruloplasmin  Kit 10 T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512117</t>
-  </si>
-  <si>
-    <t>IgM Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509129</t>
-  </si>
-  <si>
-    <t>IgA Kit 10T  Mispa i3</t>
-  </si>
-  <si>
-    <t>32512129</t>
-  </si>
-  <si>
-    <t>IgG Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509298</t>
-  </si>
-  <si>
-    <t>PCT Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512137</t>
-  </si>
-  <si>
-    <t>27/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA  32509132</t>
-  </si>
-  <si>
-    <t>IFOB Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  FOVXE06Z</t>
-  </si>
-  <si>
-    <t>03/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>D-DIMER NeO Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA KDVCE03EX</t>
-  </si>
-  <si>
-    <t>EVA KDVHF03EX</t>
-  </si>
-  <si>
-    <t>06/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>D-DIMER NeO Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA  KDVHA47X</t>
-  </si>
-  <si>
-    <t>20/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA KDVFA45X</t>
-  </si>
-  <si>
-    <t>Free PSA Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA F1VDB02EX</t>
-  </si>
-  <si>
-    <t>F1VYB03EX</t>
-  </si>
-  <si>
-    <t>Rubella Igm Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>RMULA09EX</t>
-  </si>
-  <si>
-    <t>12/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Rubella Igg Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  RGVXA09EX</t>
-  </si>
-  <si>
-    <t>CMV Igm Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  VMVHA07EX</t>
-  </si>
-  <si>
-    <t>04/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CMV Igg Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  VGVFA09EX</t>
-  </si>
-  <si>
-    <t>01/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Free PSA Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>F1VLA10G</t>
-  </si>
-  <si>
-    <t>14/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>AFP Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>AFVKB06EX</t>
-  </si>
-  <si>
-    <t>10/07/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CEA Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA CEVFB03EX</t>
-  </si>
-  <si>
-    <t>CK-MB Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA KCVBA12EX</t>
-  </si>
-  <si>
-    <t>05/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>KCVYB05EX</t>
-  </si>
-  <si>
-    <t>Toxo igm Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA XMVXA05EX</t>
-  </si>
-  <si>
-    <t>23/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Toxo igg Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA XGVYA06EX</t>
-  </si>
-  <si>
-    <t>ASO Kit 30T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512110</t>
-  </si>
-  <si>
-    <t>19/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>RF Kit 30T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32508451</t>
-  </si>
-  <si>
-    <t>11/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Myoglobin NeO Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA KMVDB05EX</t>
-  </si>
-  <si>
-    <t>06/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>UPS 1500 VA OFFLINE (NEW)</t>
-  </si>
-  <si>
-    <t>UPS 1500 VA OFFLINE (USED)</t>
-  </si>
-  <si>
-    <t>HEMATOLOGY PRINTER (NEW)</t>
-  </si>
-  <si>
-    <t>Ca19-9 Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>CXVKA08G</t>
-  </si>
-  <si>
-    <t>Daily check  (Clover A1c Plus)</t>
-  </si>
-  <si>
-    <t>PK24F27</t>
-  </si>
-  <si>
-    <t>26/06/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>PK24J08</t>
-  </si>
-  <si>
-    <t>PK25L03</t>
-  </si>
-  <si>
-    <t>02/12/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CD-80 Detergent 2L</t>
-  </si>
-  <si>
-    <t>196125193</t>
-  </si>
-  <si>
-    <t>26/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>PSA NeO Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA PSVEB08EX</t>
   </si>
   <si>
     <t>PSA NeO Kit 24T Afias Boditech</t>
@@ -3969,12 +3939,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C608"/>
+  <dimension ref="A1:C602"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.21875" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="1" max="3" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5214,21 +5182,21 @@
         <v>261</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C114" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5236,15 +5204,15 @@
         <v>265</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>267</v>
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>0</v>
@@ -5255,7 +5223,7 @@
     </row>
     <row r="117" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>0</v>
@@ -5266,13 +5234,13 @@
     </row>
     <row r="118" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C118" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5288,40 +5256,40 @@
     </row>
     <row r="120" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C120" s="4" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B121" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>277</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>281</v>
@@ -5338,45 +5306,45 @@
         <v>284</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>285</v>
+        <v>173</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B125" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="C125" s="5" t="s">
         <v>287</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B126" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="C126" s="4" t="s">
-        <v>290</v>
+        <v>67</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>67</v>
+        <v>290</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>292</v>
@@ -5387,18 +5355,18 @@
     </row>
     <row r="129" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="C129" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>297</v>
@@ -5409,18 +5377,18 @@
     </row>
     <row r="131" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B131" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="C131" s="5" t="s">
         <v>300</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>302</v>
@@ -5437,18 +5405,18 @@
         <v>305</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>306</v>
+        <v>194</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B134" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="C134" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="C134" s="4" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5459,23 +5427,23 @@
         <v>310</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>311</v>
+        <v>56</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C136" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>314</v>
@@ -5486,18 +5454,18 @@
     </row>
     <row r="138" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B138" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="C138" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>319</v>
@@ -5508,18 +5476,18 @@
     </row>
     <row r="140" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>324</v>
@@ -5530,35 +5498,35 @@
     </row>
     <row r="142" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B142" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B142" s="1" t="s">
+      <c r="C142" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>329</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>330</v>
+        <v>129</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5566,37 +5534,37 @@
         <v>331</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>334</v>
-      </c>
-      <c r="B146" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>337</v>
+        <v>0</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>0</v>
@@ -5607,13 +5575,13 @@
     </row>
     <row r="149" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C149" s="5" t="s">
         <v>339</v>
-      </c>
-      <c r="B149" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C149" s="3" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5629,13 +5597,13 @@
     </row>
     <row r="151" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5643,32 +5611,32 @@
         <v>343</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>342</v>
+        <v>0</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C153" s="3" t="s">
-        <v>0</v>
+        <v>345</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B154" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="C154" s="4" t="s">
         <v>348</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5679,29 +5647,29 @@
         <v>350</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>351</v>
+        <v>49</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>49</v>
+        <v>0</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C157" s="5" t="s">
         <v>354</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5709,15 +5677,15 @@
         <v>355</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C158" s="4" t="s">
-        <v>357</v>
+        <v>0</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>0</v>
@@ -5728,13 +5696,13 @@
     </row>
     <row r="160" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>359</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5830,21 +5798,21 @@
         <v>384</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>386</v>
+        <v>0</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C170" s="4" t="s">
         <v>387</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5855,40 +5823,40 @@
         <v>389</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>390</v>
+        <v>120</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B172" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="C172" s="4" t="s">
-        <v>120</v>
+        <v>359</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>362</v>
+        <v>129</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B174" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C174" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="C174" s="4" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5896,29 +5864,29 @@
         <v>395</v>
       </c>
       <c r="B175" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C175" s="5" t="s">
         <v>396</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C176" s="4" t="s">
         <v>398</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C176" s="4" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B177" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="C177" s="5" t="s">
         <v>401</v>
@@ -5940,18 +5908,18 @@
         <v>405</v>
       </c>
       <c r="B179" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C179" s="5" t="s">
         <v>406</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>392</v>
       </c>
       <c r="C180" s="4" t="s">
         <v>409</v>
@@ -5962,21 +5930,21 @@
         <v>410</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>412</v>
+        <v>72</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C182" s="4" t="s">
         <v>413</v>
-      </c>
-      <c r="B182" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C182" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5998,37 +5966,37 @@
         <v>418</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>419</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>19</v>
+        <v>334</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>337</v>
+        <v>421</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B187" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="B187" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="C187" s="5" t="s">
         <v>424</v>
@@ -6039,21 +6007,21 @@
         <v>425</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>426</v>
+        <v>391</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>427</v>
+        <v>290</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C189" s="5" t="s">
         <v>428</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="C189" s="5" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6061,48 +6029,48 @@
         <v>429</v>
       </c>
       <c r="B190" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C190" s="4" t="s">
         <v>430</v>
-      </c>
-      <c r="C190" s="4" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C191" s="5" t="s">
         <v>432</v>
-      </c>
-      <c r="B191" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C191" s="5" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C192" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C192" s="4" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C193" s="5" t="s">
         <v>436</v>
-      </c>
-      <c r="B193" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>438</v>
@@ -6149,98 +6117,98 @@
         <v>449</v>
       </c>
       <c r="B198" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C198" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>453</v>
+        <v>334</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>337</v>
+        <v>186</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>186</v>
+        <v>454</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>457</v>
+        <v>163</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>426</v>
+        <v>391</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>163</v>
+        <v>457</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C204" s="4" t="s">
         <v>459</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C204" s="4" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B205" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="B205" s="3" t="s">
-        <v>392</v>
-      </c>
       <c r="C205" s="5" t="s">
-        <v>462</v>
+        <v>300</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>303</v>
+        <v>424</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6248,21 +6216,21 @@
         <v>463</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>465</v>
+        <v>391</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>427</v>
+        <v>464</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6270,7 +6238,7 @@
         <v>466</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>426</v>
+        <v>467</v>
       </c>
       <c r="C209" s="5" t="s">
         <v>468</v>
@@ -6278,35 +6246,35 @@
     </row>
     <row r="210" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C210" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="B210" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="C210" s="4" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>426</v>
+        <v>391</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>472</v>
+        <v>94</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="C212" s="4" t="s">
         <v>473</v>
-      </c>
-      <c r="B212" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="C212" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6314,37 +6282,37 @@
         <v>474</v>
       </c>
       <c r="B213" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C213" s="5" t="s">
         <v>475</v>
-      </c>
-      <c r="C213" s="5" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C214" s="4" t="s">
         <v>477</v>
-      </c>
-      <c r="B214" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="C214" s="4" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C215" s="5" t="s">
         <v>479</v>
-      </c>
-      <c r="B215" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="C215" s="5" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>481</v>
@@ -6355,101 +6323,101 @@
     </row>
     <row r="217" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B217" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="B217" s="3" t="s">
-        <v>484</v>
-      </c>
       <c r="C217" s="5" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B218" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C218" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B219" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="B219" s="3" t="s">
+      <c r="C219" s="5" t="s">
         <v>488</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>490</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>491</v>
+        <v>315</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="B221" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="B221" s="3" t="s">
-        <v>493</v>
-      </c>
       <c r="C221" s="5" t="s">
-        <v>318</v>
+        <v>46</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="C222" s="4" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B223" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="C223" s="5" t="s">
         <v>497</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B224" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="C224" s="4" t="s">
-        <v>500</v>
+        <v>348</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B225" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C225" s="5" t="s">
         <v>501</v>
-      </c>
-      <c r="C225" s="5" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6460,26 +6428,26 @@
         <v>503</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>135</v>
+        <v>504</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>507</v>
+        <v>427</v>
       </c>
       <c r="C228" s="4" t="s">
         <v>508</v>
@@ -6498,134 +6466,134 @@
     </row>
     <row r="230" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C230" s="4" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="C231" s="5" t="s">
-        <v>515</v>
+        <v>0</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>517</v>
+        <v>389</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>518</v>
+        <v>81</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C233" s="5" t="s">
         <v>516</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="C233" s="5" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C234" s="1" t="s">
-        <v>0</v>
+        <v>412</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>392</v>
+        <v>519</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>81</v>
+        <v>520</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>392</v>
+        <v>521</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>523</v>
+        <v>145</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>394</v>
+        <v>521</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>460</v>
+        <v>145</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>518</v>
+        <v>0</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C239" s="5" t="s">
         <v>526</v>
-      </c>
-      <c r="B239" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="C239" s="5" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C240" s="4" t="s">
         <v>526</v>
-      </c>
-      <c r="B240" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="C240" s="4" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>529</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>145</v>
+        <v>530</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6633,230 +6601,230 @@
         <v>531</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C242" s="1" t="s">
-        <v>0</v>
+        <v>532</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>533</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>534</v>
+        <v>88</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>538</v>
+        <v>85</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>540</v>
+        <v>389</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>88</v>
+        <v>545</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B249" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="C249" s="5" t="s">
         <v>548</v>
-      </c>
-      <c r="C249" s="5" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>392</v>
+        <v>551</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>550</v>
+        <v>49</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="C253" s="5" t="s">
-        <v>556</v>
+        <v>0</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>49</v>
+        <v>430</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>561</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>562</v>
+        <v>140</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>565</v>
+        <v>140</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C257" s="3" t="s">
-        <v>0</v>
+        <v>564</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>565</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C258" s="4" t="s">
         <v>567</v>
-      </c>
-      <c r="B258" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="C258" s="4" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>569</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>140</v>
+        <v>570</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>573</v>
+        <v>205</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>426</v>
+        <v>575</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>575</v>
+        <v>211</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6867,18 +6835,18 @@
         <v>577</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>578</v>
+        <v>277</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B264" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B264" s="1" t="s">
+      <c r="C264" s="4" t="s">
         <v>580</v>
-      </c>
-      <c r="C264" s="4" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6889,62 +6857,62 @@
         <v>582</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>205</v>
+        <v>129</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>211</v>
+        <v>117</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>280</v>
+        <v>587</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>129</v>
+        <v>592</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>117</v>
+        <v>595</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6952,76 +6920,76 @@
         <v>593</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>600</v>
+        <v>189</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>605</v>
+        <v>282</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7029,81 +6997,81 @@
         <v>611</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>189</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="B280" s="1" t="s">
+      <c r="C280" s="4" t="s">
         <v>617</v>
-      </c>
-      <c r="C280" s="4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B281" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B281" s="3" t="s">
+      <c r="C281" s="5" t="s">
         <v>619</v>
-      </c>
-      <c r="C281" s="5" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B282" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B282" s="1" t="s">
+      <c r="C282" s="4" t="s">
         <v>622</v>
-      </c>
-      <c r="C282" s="4" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>8</v>
+        <v>97</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>626</v>
-      </c>
       <c r="C284" s="4" t="s">
-        <v>627</v>
+        <v>354</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>626</v>
@@ -7114,13 +7082,13 @@
     </row>
     <row r="286" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>629</v>
+        <v>31</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7142,7 +7110,7 @@
         <v>633</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>97</v>
+        <v>270</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7153,7 +7121,7 @@
         <v>635</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>357</v>
+        <v>636</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7161,10 +7129,10 @@
         <v>634</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>637</v>
+        <v>421</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7175,12 +7143,12 @@
         <v>639</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>31</v>
+        <v>640</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>641</v>
@@ -7191,216 +7159,216 @@
     </row>
     <row r="293" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>273</v>
+        <v>126</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>646</v>
+        <v>72</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>650</v>
+        <v>67</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>654</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>126</v>
+        <v>655</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>656</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B300" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="B300" s="1" t="s">
-        <v>658</v>
-      </c>
       <c r="C300" s="4" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="C301" s="5" t="s">
         <v>659</v>
-      </c>
-      <c r="B301" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="C301" s="5" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="B303" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C303" s="5" t="s">
         <v>663</v>
-      </c>
-      <c r="B303" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="C303" s="5" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>667</v>
+        <v>199</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>120</v>
+        <v>595</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>669</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>409</v>
+        <v>670</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>120</v>
+        <v>610</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C309" s="5" t="s">
         <v>673</v>
-      </c>
-      <c r="B309" s="3" t="s">
-        <v>674</v>
-      </c>
-      <c r="C309" s="5" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>681</v>
@@ -7411,101 +7379,101 @@
     </row>
     <row r="313" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>683</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>620</v>
+        <v>520</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>682</v>
+        <v>595</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>595</v>
+        <v>220</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>689</v>
+        <v>600</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>528</v>
+        <v>694</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>603</v>
+        <v>220</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>220</v>
+        <v>698</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>610</v>
+        <v>135</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7513,241 +7481,241 @@
         <v>699</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>682</v>
+        <v>702</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>220</v>
+        <v>120</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>707</v>
+        <v>99</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>709</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>135</v>
+        <v>501</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>714</v>
+        <v>217</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>120</v>
+        <v>717</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>99</v>
+        <v>720</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>508</v>
+        <v>723</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>217</v>
+        <v>457</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>729</v>
+        <v>501</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>460</v>
+        <v>741</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="C340" s="4" t="s">
-        <v>508</v>
+        <v>0</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="C341" s="5" t="s">
-        <v>744</v>
+        <v>0</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="C342" s="4" t="s">
-        <v>58</v>
+        <v>0</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>749</v>
+        <v>640</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7763,90 +7731,90 @@
     </row>
     <row r="345" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="B345" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="B345" s="3" t="s">
-        <v>754</v>
-      </c>
       <c r="C345" s="5" t="s">
-        <v>755</v>
+        <v>570</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C346" s="1" t="s">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>755</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="B347" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="B347" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C347" s="3" t="s">
-        <v>0</v>
+      <c r="C347" s="5" t="s">
+        <v>758</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>0</v>
+        <v>760</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>761</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>650</v>
+        <v>58</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="C350" s="4" t="s">
-        <v>763</v>
+        <v>0</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="C351" s="5" t="s">
-        <v>578</v>
+        <v>0</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>761</v>
+        <v>766</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="C352" s="4" t="s">
-        <v>766</v>
+        <v>0</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7865,21 +7833,21 @@
         <v>770</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="C354" s="4" t="s">
-        <v>263</v>
+        <v>0</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="B355" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="B355" s="3" t="s">
+      <c r="C355" s="5" t="s">
         <v>773</v>
-      </c>
-      <c r="C355" s="5" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7887,208 +7855,208 @@
         <v>774</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C356" s="1" t="s">
-        <v>0</v>
+        <v>775</v>
+      </c>
+      <c r="C356" s="4" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C357" s="3" t="s">
-        <v>0</v>
+        <v>778</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C358" s="1" t="s">
-        <v>0</v>
+        <v>780</v>
+      </c>
+      <c r="C358" s="4" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>777</v>
+        <v>782</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>779</v>
+        <v>117</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C360" s="1" t="s">
-        <v>0</v>
+        <v>785</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>784</v>
+        <v>789</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>785</v>
+        <v>790</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>786</v>
+        <v>791</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>49</v>
+        <v>791</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>789</v>
+        <v>794</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>790</v>
+        <v>795</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>791</v>
+        <v>796</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>792</v>
+        <v>797</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>117</v>
+        <v>791</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>794</v>
+        <v>799</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>508</v>
+        <v>791</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8096,109 +8064,109 @@
         <v>815</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>806</v>
+        <v>820</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>806</v>
+        <v>830</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8206,340 +8174,340 @@
         <v>835</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>840</v>
+        <v>791</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>830</v>
+        <v>791</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>801</v>
+        <v>848</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>806</v>
+        <v>851</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>801</v>
+        <v>853</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>801</v>
+        <v>477</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>801</v>
+        <v>477</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>801</v>
+        <v>166</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>861</v>
+        <v>159</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>863</v>
+        <v>298</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>480</v>
+        <v>868</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>480</v>
+        <v>132</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>166</v>
+        <v>873</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>870</v>
+        <v>875</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>871</v>
+        <v>876</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>873</v>
+        <v>878</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>159</v>
+        <v>879</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>301</v>
+        <v>592</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>880</v>
+        <v>886</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>132</v>
+        <v>468</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>881</v>
+        <v>887</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>882</v>
+        <v>888</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>883</v>
+        <v>889</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>884</v>
+        <v>890</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>885</v>
+        <v>891</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>600</v>
+        <v>898</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="C412" s="4" t="s">
-        <v>471</v>
+        <v>0</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>898</v>
-      </c>
-      <c r="C413" s="5" t="s">
-        <v>899</v>
+        <v>0</v>
+      </c>
+      <c r="C413" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="C414" s="4" t="s">
-        <v>902</v>
+        <v>0</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>904</v>
-      </c>
-      <c r="C415" s="5" t="s">
-        <v>905</v>
+        <v>0</v>
+      </c>
+      <c r="C415" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8547,131 +8515,131 @@
         <v>906</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>907</v>
+        <v>858</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>908</v>
+        <v>166</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>910</v>
+        <v>860</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>911</v>
+        <v>861</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C418" s="1" t="s">
-        <v>0</v>
+        <v>863</v>
+      </c>
+      <c r="C418" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C419" s="3" t="s">
-        <v>0</v>
+        <v>863</v>
+      </c>
+      <c r="C419" s="5" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C420" s="1" t="s">
-        <v>0</v>
+        <v>863</v>
+      </c>
+      <c r="C420" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C421" s="3" t="s">
-        <v>0</v>
+        <v>865</v>
+      </c>
+      <c r="C421" s="5" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>166</v>
+        <v>298</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>871</v>
+        <v>298</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>873</v>
+        <v>915</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>159</v>
+        <v>434</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>873</v>
+        <v>915</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>159</v>
+        <v>434</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>873</v>
+        <v>918</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>159</v>
+        <v>919</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="B427" s="3" t="s">
         <v>921</v>
       </c>
-      <c r="B427" s="3" t="s">
-        <v>875</v>
-      </c>
       <c r="C427" s="5" t="s">
-        <v>301</v>
+        <v>565</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8679,10 +8647,10 @@
         <v>922</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>875</v>
+        <v>867</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>301</v>
+        <v>868</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8690,10 +8658,10 @@
         <v>923</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>301</v>
+        <v>132</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8701,54 +8669,54 @@
         <v>924</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>925</v>
+        <v>870</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>437</v>
+        <v>132</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>925</v>
+        <v>870</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>437</v>
+        <v>132</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>928</v>
+        <v>872</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>929</v>
+        <v>873</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>573</v>
+        <v>929</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B434" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="C434" s="4" t="s">
         <v>932</v>
-      </c>
-      <c r="B434" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8756,10 +8724,10 @@
         <v>933</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>132</v>
+        <v>876</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8767,10 +8735,10 @@
         <v>934</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>132</v>
+        <v>876</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8778,10 +8746,10 @@
         <v>935</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>132</v>
+        <v>876</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8789,10 +8757,10 @@
         <v>936</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8800,208 +8768,208 @@
         <v>937</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>938</v>
+        <v>878</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>939</v>
+        <v>879</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>941</v>
+        <v>878</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>942</v>
+        <v>879</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>885</v>
+        <v>940</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>886</v>
+        <v>592</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>885</v>
+        <v>941</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>886</v>
+        <v>592</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>885</v>
+        <v>943</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>889</v>
+        <v>592</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>950</v>
+        <v>891</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>600</v>
+        <v>892</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>951</v>
+        <v>891</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>600</v>
+        <v>892</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>953</v>
+        <v>888</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>600</v>
+        <v>889</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>901</v>
+        <v>952</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>902</v>
+        <v>953</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>901</v>
+        <v>952</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>902</v>
+        <v>953</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>901</v>
+        <v>886</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>902</v>
+        <v>468</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>899</v>
+        <v>468</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>898</v>
+        <v>886</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>899</v>
+        <v>468</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="B457" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="C457" s="5" t="s">
         <v>960</v>
-      </c>
-      <c r="B457" s="3" t="s">
-        <v>898</v>
-      </c>
-      <c r="C457" s="5" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9009,43 +8977,43 @@
         <v>961</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>896</v>
-      </c>
-      <c r="C460" s="4" t="s">
-        <v>471</v>
+        <v>0</v>
+      </c>
+      <c r="C460" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B461" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="C461" s="5" t="s">
         <v>966</v>
-      </c>
-      <c r="B461" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="C461" s="5" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9053,21 +9021,21 @@
         <v>967</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>896</v>
+        <v>968</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>471</v>
+        <v>969</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="B463" s="3" t="s">
         <v>968</v>
       </c>
-      <c r="B463" s="3" t="s">
-        <v>969</v>
-      </c>
       <c r="C463" s="5" t="s">
-        <v>970</v>
+        <v>354</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9075,76 +9043,76 @@
         <v>971</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>969</v>
+        <v>975</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>970</v>
+        <v>861</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C466" s="1" t="s">
-        <v>0</v>
+        <v>977</v>
+      </c>
+      <c r="C466" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>976</v>
+        <v>300</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>979</v>
+        <v>377</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>357</v>
+        <v>605</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9152,54 +9120,54 @@
         <v>984</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>871</v>
+        <v>988</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>173</v>
+        <v>988</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="B473" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="C473" s="5" t="s">
         <v>988</v>
-      </c>
-      <c r="B473" s="3" t="s">
-        <v>989</v>
-      </c>
-      <c r="C473" s="5" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B474" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="B474" s="1" t="s">
-        <v>991</v>
-      </c>
       <c r="C474" s="4" t="s">
-        <v>380</v>
+        <v>988</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>993</v>
+        <v>959</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>615</v>
+        <v>960</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9207,142 +9175,142 @@
         <v>994</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>995</v>
+        <v>878</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>996</v>
+        <v>879</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>997</v>
+        <v>878</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>998</v>
+        <v>879</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>1000</v>
+        <v>878</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>998</v>
+        <v>879</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>1000</v>
+        <v>878</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>998</v>
+        <v>879</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="B480" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="C480" s="4" t="s">
         <v>1000</v>
-      </c>
-      <c r="C480" s="4" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>969</v>
+        <v>1002</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>970</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>888</v>
+        <v>1002</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>889</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>888</v>
+        <v>1002</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>889</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B484" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="B484" s="1" t="s">
-        <v>888</v>
-      </c>
       <c r="C484" s="4" t="s">
-        <v>889</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B485" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C485" s="5" t="s">
         <v>1007</v>
-      </c>
-      <c r="B485" s="3" t="s">
-        <v>888</v>
-      </c>
-      <c r="C485" s="5" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B488" s="1" t="s">
         <v>1012</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9353,7 +9321,7 @@
         <v>1012</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9361,32 +9329,32 @@
         <v>1015</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B492" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C492" s="4" t="s">
         <v>1019</v>
-      </c>
-      <c r="B492" s="1" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C492" s="4" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9394,10 +9362,10 @@
         <v>1020</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9405,32 +9373,32 @@
         <v>1021</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C496" s="4" t="s">
         <v>1025</v>
-      </c>
-      <c r="B496" s="1" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C496" s="4" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9438,10 +9406,10 @@
         <v>1026</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9449,32 +9417,32 @@
         <v>1027</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B500" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C500" s="4" t="s">
         <v>1031</v>
-      </c>
-      <c r="B500" s="1" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C500" s="4" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9482,10 +9450,10 @@
         <v>1032</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9493,32 +9461,32 @@
         <v>1033</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B504" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C504" s="4" t="s">
         <v>1037</v>
-      </c>
-      <c r="B504" s="1" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C504" s="4" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9526,10 +9494,10 @@
         <v>1038</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9537,70 +9505,70 @@
         <v>1039</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1040</v>
+        <v>952</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>1041</v>
+        <v>953</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>1040</v>
+        <v>952</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>1041</v>
+        <v>953</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>1046</v>
+        <v>952</v>
       </c>
       <c r="C510" s="4" t="s">
-        <v>1047</v>
+        <v>953</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>1046</v>
+        <v>952</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>1047</v>
+        <v>953</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="B512" s="1" t="s">
         <v>1046</v>
@@ -9611,7 +9579,7 @@
     </row>
     <row r="513" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>1046</v>
@@ -9622,453 +9590,453 @@
     </row>
     <row r="514" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>962</v>
+        <v>1046</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>963</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>962</v>
+        <v>1046</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>963</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>962</v>
+        <v>865</v>
       </c>
       <c r="C516" s="4" t="s">
-        <v>963</v>
+        <v>298</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>962</v>
+        <v>865</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>963</v>
+        <v>298</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1056</v>
+        <v>865</v>
       </c>
       <c r="C518" s="4" t="s">
-        <v>1057</v>
+        <v>298</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>1056</v>
+        <v>865</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>1057</v>
+        <v>298</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1056</v>
+        <v>915</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>1057</v>
+        <v>434</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>1056</v>
+        <v>915</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>1057</v>
+        <v>434</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>875</v>
+        <v>915</v>
       </c>
       <c r="C522" s="4" t="s">
-        <v>301</v>
+        <v>434</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>875</v>
+        <v>915</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>301</v>
+        <v>434</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>875</v>
+        <v>1018</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>301</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>875</v>
+        <v>1018</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>301</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>925</v>
+        <v>863</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>437</v>
+        <v>159</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>925</v>
+        <v>863</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>437</v>
+        <v>159</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>925</v>
+        <v>863</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>437</v>
+        <v>159</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>925</v>
+        <v>863</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>437</v>
+        <v>159</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1028</v>
+        <v>1066</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>1029</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>1028</v>
+        <v>1066</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>1029</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>873</v>
+        <v>1066</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>159</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>873</v>
+        <v>1066</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>159</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>873</v>
+        <v>1012</v>
       </c>
       <c r="C534" s="4" t="s">
-        <v>159</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>873</v>
+        <v>1012</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>159</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1076</v>
+        <v>1012</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>1077</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="B537" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C537" s="5" t="s">
         <v>1076</v>
-      </c>
-      <c r="C537" s="5" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B538" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C538" s="4" t="s">
         <v>1076</v>
-      </c>
-      <c r="C538" s="4" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B539" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C539" s="5" t="s">
         <v>1076</v>
-      </c>
-      <c r="C539" s="5" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1022</v>
+        <v>1075</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>1023</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>1085</v>
+        <v>1046</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>1086</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1085</v>
+        <v>1046</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>1086</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>1085</v>
+        <v>1046</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>1086</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1085</v>
+        <v>1046</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>1086</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>1056</v>
+        <v>1046</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>1057</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1056</v>
+        <v>1046</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>1057</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>1056</v>
+        <v>1089</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>1057</v>
+        <v>741</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1056</v>
+        <v>1089</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>1057</v>
+        <v>741</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>1056</v>
+        <v>412</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>1057</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1056</v>
+        <v>968</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>1057</v>
+        <v>459</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>1056</v>
+        <v>1012</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>1057</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B554" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C554" s="4" t="s">
         <v>1097</v>
-      </c>
-      <c r="B554" s="1" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C554" s="4" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10076,29 +10044,29 @@
         <v>1098</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C555" s="5" t="s">
-        <v>752</v>
+        <v>0</v>
+      </c>
+      <c r="C555" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C556" s="4" t="s">
-        <v>752</v>
+        <v>0</v>
+      </c>
+      <c r="C556" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B557" s="3" t="s">
         <v>1101</v>
-      </c>
-      <c r="B557" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="C557" s="5" t="s">
         <v>1102</v>
@@ -10109,428 +10077,428 @@
         <v>1103</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>978</v>
+        <v>1104</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>462</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>1022</v>
+        <v>1107</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>1023</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>1107</v>
+        <v>196</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C561" s="3" t="s">
-        <v>0</v>
+        <v>1112</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C562" s="1" t="s">
-        <v>0</v>
+        <v>1114</v>
+      </c>
+      <c r="C562" s="4" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>1110</v>
+        <v>1115</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>1111</v>
+        <v>1116</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>1112</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
-        <v>1113</v>
+        <v>1118</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>1115</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>1118</v>
+        <v>52</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>196</v>
+        <v>413</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>111</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C568" s="4" t="s">
-        <v>196</v>
+        <v>895</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="C569" s="5" t="s">
-        <v>1127</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="C570" s="4" t="s">
-        <v>1130</v>
+        <v>622</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>52</v>
+        <v>622</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="C572" s="4" t="s">
-        <v>416</v>
+        <v>52</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>1136</v>
+        <v>627</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="C574" s="4" t="s">
-        <v>905</v>
+        <v>622</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="C575" s="5" t="s">
-        <v>1041</v>
+        <v>622</v>
       </c>
     </row>
     <row r="576" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="C576" s="4" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
     </row>
     <row r="577" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="C577" s="5" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
     </row>
     <row r="578" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="C578" s="4" t="s">
-        <v>52</v>
+        <v>622</v>
       </c>
     </row>
     <row r="579" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B579" s="3" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>637</v>
+        <v>622</v>
       </c>
     </row>
     <row r="580" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C580" s="4" t="s">
-        <v>632</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="581" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="B581" s="3" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="C581" s="5" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
     </row>
     <row r="582" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="C582" s="4" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
     </row>
     <row r="583" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="C583" s="5" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
     </row>
     <row r="584" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="C584" s="4" t="s">
-        <v>632</v>
+        <v>511</v>
       </c>
     </row>
     <row r="585" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="C585" s="5" t="s">
-        <v>632</v>
+        <v>140</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="C586" s="4" t="s">
-        <v>1163</v>
+        <v>409</v>
       </c>
     </row>
     <row r="587" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A587" s="3" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
     </row>
     <row r="588" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="C588" s="4" t="s">
-        <v>632</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="589" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
     </row>
     <row r="590" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="C590" s="4" t="s">
-        <v>518</v>
+        <v>973</v>
       </c>
     </row>
     <row r="591" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C591" s="5" t="s">
-        <v>140</v>
+        <v>973</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="C592" s="4" t="s">
-        <v>412</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="593" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>632</v>
+        <v>735</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="C594" s="4" t="s">
-        <v>1180</v>
+        <v>409</v>
       </c>
     </row>
     <row r="595" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A595" s="3" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>1182</v>
+        <v>373</v>
       </c>
       <c r="C595" s="5" t="s">
-        <v>632</v>
+        <v>374</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B596" s="1" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C596" s="4" t="s">
-        <v>983</v>
+        <v>0</v>
+      </c>
+      <c r="C596" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="597" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10538,10 +10506,10 @@
         <v>1185</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C597" s="5" t="s">
-        <v>983</v>
+        <v>0</v>
+      </c>
+      <c r="C597" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10552,89 +10520,23 @@
         <v>1187</v>
       </c>
       <c r="C598" s="4" t="s">
-        <v>1188</v>
+        <v>511</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A599" s="3" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B599" s="3" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C599" s="5" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="600" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A600" s="1" t="s">
-        <v>1191</v>
-      </c>
-      <c r="B600" s="1" t="s">
-        <v>1192</v>
-      </c>
-      <c r="C600" s="4" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="601" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A601" s="3" t="s">
-        <v>1193</v>
-      </c>
-      <c r="B601" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C601" s="5" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="602" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A602" s="1" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B602" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C602" s="1" t="s">
+      <c r="C599" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A603" s="3" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B603" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C603" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A604" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="B604" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C604" s="4" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="605" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A605" s="3" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B605" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C605" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="606" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
-    <row r="607" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
-    <row r="608" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="600" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="601" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="602" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/المواد.xlsx
+++ b/المواد.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="4908"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8328"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="1189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1857" uniqueCount="1213">
   <si>
     <t/>
   </si>
@@ -144,6 +144,12 @@
     <t>17/12/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA FSVYA28X</t>
+  </si>
+  <si>
+    <t>12/06/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>FERRITIN Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -156,6 +162,12 @@
     <t>EVA FRVXA73X</t>
   </si>
   <si>
+    <t>EVA FRVXA74X</t>
+  </si>
+  <si>
+    <t>28/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>FRUYA42X</t>
   </si>
   <si>
@@ -180,6 +192,18 @@
     <t>28/02/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA AAVGD56F</t>
+  </si>
+  <si>
+    <t>06/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA AAVGD58F</t>
+  </si>
+  <si>
+    <t>07/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>LH Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -222,9 +246,6 @@
     <t>EVA  PLVGA38X</t>
   </si>
   <si>
-    <t>07/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>EVA PLVFA37X</t>
   </si>
   <si>
@@ -249,6 +270,12 @@
     <t>21/01/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA  T4VFA37X</t>
+  </si>
+  <si>
+    <t>19/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA T4VEA35X</t>
   </si>
   <si>
@@ -276,9 +303,6 @@
     <t>EVA TTVXA23X</t>
   </si>
   <si>
-    <t>28/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>TNI PLUS Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -297,15 +321,15 @@
     <t>EVA  HCVXA61X</t>
   </si>
   <si>
+    <t>EVA HCVXA61X</t>
+  </si>
+  <si>
     <t>PRL Kit 25T iChroma Boditech</t>
   </si>
   <si>
     <t>EVA  DPLVFH02</t>
   </si>
   <si>
-    <t>19/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>Progesterone Kit 25T iChroma Boditech</t>
   </si>
   <si>
@@ -396,6 +420,12 @@
     <t>12/05/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA  DFRVGC01</t>
+  </si>
+  <si>
+    <t>08/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA DFRVFB10</t>
   </si>
   <si>
@@ -408,9 +438,6 @@
     <t>EVA DFRVGC01</t>
   </si>
   <si>
-    <t>08/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>HBsAg Kit 25T iChroma Boditech</t>
   </si>
   <si>
@@ -432,18 +459,18 @@
     <t>LH Kit 25T iChroma Boditech</t>
   </si>
   <si>
-    <t>EVA  DLHVDD02</t>
+    <t>EVA  DLHVHD05</t>
+  </si>
+  <si>
+    <t>07/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA DLHVDD02</t>
   </si>
   <si>
     <t>14/12/2026 12:00:00 ص</t>
   </si>
   <si>
-    <t>EVA  DLHVHD05</t>
-  </si>
-  <si>
-    <t>07/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>Microalbumin Kit 25T iChroma Boditech</t>
   </si>
   <si>
@@ -459,6 +486,12 @@
     <t>22/02/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA  RFVHH09EX</t>
+  </si>
+  <si>
+    <t>06/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA RFVFH05EX</t>
   </si>
   <si>
@@ -1110,6 +1143,9 @@
     <t>25/11/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>Semi-auto BA-88A used</t>
+  </si>
+  <si>
     <t>Creatinine kit  Chemistry Mindray</t>
   </si>
   <si>
@@ -1263,15 +1299,6 @@
     <t>10/03/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>PRL kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025030211</t>
-  </si>
-  <si>
-    <t>19/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>Free T3 kit 2×50T CL900i Mindray</t>
   </si>
   <si>
@@ -1332,15 +1359,6 @@
     <t>14/10/2026 12:00:00 ص</t>
   </si>
   <si>
-    <t>PTH kit 2×50T Cl900i  Mindray</t>
-  </si>
-  <si>
-    <t>2025040112</t>
-  </si>
-  <si>
-    <t>19/05/2026 12:00:00 ص</t>
-  </si>
-  <si>
     <t>Folate kit 50T Cl900i Mindray</t>
   </si>
   <si>
@@ -1518,6 +1536,12 @@
     <t>EVA CPVFD03Z</t>
   </si>
   <si>
+    <t>H. Pylori SA Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA HSVCH02</t>
+  </si>
+  <si>
     <t>AMH Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -1641,6 +1665,9 @@
     <t>Total Ige Kit 24T Afias Boditech</t>
   </si>
   <si>
+    <t>EVA TEVEA14X</t>
+  </si>
+  <si>
     <t>EVA TEVXA15X</t>
   </si>
   <si>
@@ -1704,6 +1731,12 @@
     <t>EVA  VEVHC14X</t>
   </si>
   <si>
+    <t>EVA VEVGC08X</t>
+  </si>
+  <si>
+    <t>22/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA VEVHC12X</t>
   </si>
   <si>
@@ -1737,6 +1770,9 @@
     <t>ZINC kit 20T Agappe</t>
   </si>
   <si>
+    <t>32412054</t>
+  </si>
+  <si>
     <t>32512383</t>
   </si>
   <si>
@@ -1791,6 +1827,12 @@
     <t>09/12/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA VEVCA12E</t>
+  </si>
+  <si>
+    <t>25/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
     <t>C3 Kit 10T Mispa i3</t>
   </si>
   <si>
@@ -1881,6 +1923,9 @@
     <t>18/01/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>140325012</t>
+  </si>
+  <si>
     <t>( ALT  (GPT) kit  Chemistry Mindray ( Large</t>
   </si>
   <si>
@@ -1938,339 +1983,345 @@
     <t>( LDL-C kit  Chemistry Mindray  ( Large</t>
   </si>
   <si>
-    <t>142025008</t>
+    <t>142025010</t>
+  </si>
+  <si>
+    <t>17/09/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>( MG kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>148225004</t>
+  </si>
+  <si>
+    <t>( T-Bill vox kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140625015</t>
+  </si>
+  <si>
+    <t>140625016</t>
+  </si>
+  <si>
+    <t>( TP kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140825005</t>
+  </si>
+  <si>
+    <t>( UA  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>141225013</t>
+  </si>
+  <si>
+    <t>HBA1C Kit 10T Clover كلوفر</t>
+  </si>
+  <si>
+    <t>EVA B25D05D12EL</t>
+  </si>
+  <si>
+    <t>11/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA B25D14E13DL</t>
+  </si>
+  <si>
+    <t>12/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA B25F03H12DL</t>
+  </si>
+  <si>
+    <t>EVA B25F03H14DL</t>
+  </si>
+  <si>
+    <t>13/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA B25F04H12EL</t>
+  </si>
+  <si>
+    <t>EVA B25F09H14EL</t>
+  </si>
+  <si>
+    <t>EVA B25F10H18DL</t>
+  </si>
+  <si>
+    <t>17/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Ferritin Cal Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>152725001</t>
+  </si>
+  <si>
+    <t>10/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Urilyzer® Cell Cuvettes (600 PCS/BOX) analyticon</t>
+  </si>
+  <si>
+    <t>2411C100</t>
+  </si>
+  <si>
+    <t>CombiScreen® 11SYS PLUS 150 strips per vial analyticon</t>
+  </si>
+  <si>
+    <t>2786/2010</t>
+  </si>
+  <si>
+    <t>IGRA-TB Tube 8T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA TBTVYA54</t>
+  </si>
+  <si>
+    <t>22/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>H.Pylori  Kit 10T  Mispa i3</t>
+  </si>
+  <si>
+    <t>32511197</t>
+  </si>
+  <si>
+    <t>24/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>32512294</t>
+  </si>
+  <si>
+    <t>EVA  32509360</t>
+  </si>
+  <si>
+    <t>Microalbumin Kit 30T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512135</t>
+  </si>
+  <si>
+    <t>IgE Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32507209</t>
+  </si>
+  <si>
+    <t>06/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA  32509128</t>
+  </si>
+  <si>
+    <t>20/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA 32506314</t>
+  </si>
+  <si>
+    <t>Ceruloplasmin  Kit 10 T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512117</t>
+  </si>
+  <si>
+    <t>IgM Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509129</t>
+  </si>
+  <si>
+    <t>IgA Kit 10T  Mispa i3</t>
+  </si>
+  <si>
+    <t>32512129</t>
+  </si>
+  <si>
+    <t>IgG Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509298</t>
+  </si>
+  <si>
+    <t>PCT Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512137</t>
+  </si>
+  <si>
+    <t>27/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA  32509132</t>
+  </si>
+  <si>
+    <t>IFOB Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  FOVXE06Z</t>
+  </si>
+  <si>
+    <t>03/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>D-DIMER NeO Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  KDVFE11EX</t>
+  </si>
+  <si>
+    <t>09/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA KDVCE03EX</t>
+  </si>
+  <si>
+    <t>EVA KDVHF03EX</t>
+  </si>
+  <si>
+    <t>D-DIMER NeO Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA  KDVHA47X</t>
+  </si>
+  <si>
+    <t>20/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Free PSA Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA F1VDB02EX</t>
+  </si>
+  <si>
+    <t>F1VYB03EX</t>
+  </si>
+  <si>
+    <t>Rubella Igm Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>RMULA09EX</t>
+  </si>
+  <si>
+    <t>12/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Rubella Igg Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  RGVXA09EX</t>
+  </si>
+  <si>
+    <t>CMV Igm Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  VMVHA07EX</t>
+  </si>
+  <si>
+    <t>04/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CMV Igg Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  VGVFA09EX</t>
+  </si>
+  <si>
+    <t>01/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Free PSA Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>F1VLA10G</t>
+  </si>
+  <si>
+    <t>14/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>AFP Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>AFVKB06EX</t>
+  </si>
+  <si>
+    <t>10/07/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CEA Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA CEVFB03EX</t>
+  </si>
+  <si>
+    <t>CK-MB Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA KCVBA12EX</t>
+  </si>
+  <si>
+    <t>05/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>KCVYB05EX</t>
+  </si>
+  <si>
+    <t>Toxo igm Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA XMVXA05EX</t>
+  </si>
+  <si>
+    <t>23/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>ASO Kit 30T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512110</t>
+  </si>
+  <si>
+    <t>19/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>RF Kit 30T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32508451</t>
+  </si>
+  <si>
+    <t>11/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Myoglobin NeO Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA KMVDB05EX</t>
+  </si>
+  <si>
+    <t>06/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>UPS 1500 VA OFFLINE (NEW)</t>
+  </si>
+  <si>
+    <t>UPS 1500 VA OFFLINE (USED)</t>
+  </si>
+  <si>
+    <t>HEMATOLOGY PRINTER (NEW)</t>
+  </si>
+  <si>
+    <t>Ca19-9 Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>CXVKA08G</t>
   </si>
   <si>
     <t>11/07/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>142025010</t>
-  </si>
-  <si>
-    <t>17/09/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>( MG kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>148225004</t>
-  </si>
-  <si>
-    <t>( T-Bill vox kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140625015</t>
-  </si>
-  <si>
-    <t>( TP kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140825005</t>
-  </si>
-  <si>
-    <t>( UA  Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>141225013</t>
-  </si>
-  <si>
-    <t>HBA1C Kit 10T Clover كلوفر</t>
-  </si>
-  <si>
-    <t>EVA B25D05D12EL</t>
-  </si>
-  <si>
-    <t>11/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA B25D14E13DL</t>
-  </si>
-  <si>
-    <t>12/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA B25F03H12DL</t>
-  </si>
-  <si>
-    <t>EVA B25F03H13DL</t>
-  </si>
-  <si>
-    <t>EVA B25F03H14DL</t>
-  </si>
-  <si>
-    <t>13/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA B25F04H12EL</t>
-  </si>
-  <si>
-    <t>Ferritin Cal Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>152725001</t>
-  </si>
-  <si>
-    <t>10/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Urilyzer® Cell Cuvettes (600 PCS/BOX) analyticon</t>
-  </si>
-  <si>
-    <t>2411C100</t>
-  </si>
-  <si>
-    <t>CombiScreen® 11SYS PLUS 150 strips per vial analyticon</t>
-  </si>
-  <si>
-    <t>2786/2010</t>
-  </si>
-  <si>
-    <t>IGRA-TB Tube 8T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA TBTVYA54</t>
-  </si>
-  <si>
-    <t>22/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>H.Pylori  Kit 10T  Mispa i3</t>
-  </si>
-  <si>
-    <t>32511197</t>
-  </si>
-  <si>
-    <t>24/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>32512294</t>
-  </si>
-  <si>
-    <t>EVA  32509360</t>
-  </si>
-  <si>
-    <t>Microalbumin Kit 30T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512135</t>
-  </si>
-  <si>
-    <t>IgE Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32507209</t>
-  </si>
-  <si>
-    <t>06/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA  32509128</t>
-  </si>
-  <si>
-    <t>20/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA 32506314</t>
-  </si>
-  <si>
-    <t>Ceruloplasmin  Kit 10 T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512117</t>
-  </si>
-  <si>
-    <t>IgM Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509129</t>
-  </si>
-  <si>
-    <t>IgA Kit 10T  Mispa i3</t>
-  </si>
-  <si>
-    <t>32512129</t>
-  </si>
-  <si>
-    <t>IgG Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509298</t>
-  </si>
-  <si>
-    <t>PCT Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512137</t>
-  </si>
-  <si>
-    <t>27/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA  32509132</t>
-  </si>
-  <si>
-    <t>IFOB Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  FOVXE06Z</t>
-  </si>
-  <si>
-    <t>03/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>D-DIMER NeO Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA KDVCE03EX</t>
-  </si>
-  <si>
-    <t>EVA KDVHF03EX</t>
-  </si>
-  <si>
-    <t>06/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>D-DIMER NeO Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA  KDVHA47X</t>
-  </si>
-  <si>
-    <t>20/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA KDVFA45X</t>
-  </si>
-  <si>
-    <t>Free PSA Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA F1VDB02EX</t>
-  </si>
-  <si>
-    <t>F1VYB03EX</t>
-  </si>
-  <si>
-    <t>Rubella Igm Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>RMULA09EX</t>
-  </si>
-  <si>
-    <t>12/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Rubella Igg Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  RGVXA09EX</t>
-  </si>
-  <si>
-    <t>CMV Igm Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  VMVHA07EX</t>
-  </si>
-  <si>
-    <t>04/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CMV Igg Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  VGVFA09EX</t>
-  </si>
-  <si>
-    <t>01/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Free PSA Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>F1VLA10G</t>
-  </si>
-  <si>
-    <t>14/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>AFP Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>AFVKB06EX</t>
-  </si>
-  <si>
-    <t>10/07/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CEA Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA CEVFB03EX</t>
-  </si>
-  <si>
-    <t>CK-MB Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA KCVBA12EX</t>
-  </si>
-  <si>
-    <t>05/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>KCVYB05EX</t>
-  </si>
-  <si>
-    <t>Toxo igm Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA XMVXA05EX</t>
-  </si>
-  <si>
-    <t>23/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>ASO Kit 30T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512110</t>
-  </si>
-  <si>
-    <t>19/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>RF Kit 30T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32508451</t>
-  </si>
-  <si>
-    <t>11/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Myoglobin NeO Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA KMVDB05EX</t>
-  </si>
-  <si>
-    <t>06/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>UPS 1500 VA OFFLINE (NEW)</t>
-  </si>
-  <si>
-    <t>UPS 1500 VA OFFLINE (USED)</t>
-  </si>
-  <si>
-    <t>HEMATOLOGY PRINTER (NEW)</t>
-  </si>
-  <si>
-    <t>Ca19-9 Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>CXVKA08G</t>
-  </si>
-  <si>
     <t>Daily check  (Clover A1c Plus)</t>
   </si>
   <si>
@@ -2307,6 +2358,12 @@
     <t>15/01/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>CK-MB NeO Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA KCUKA07X</t>
+  </si>
+  <si>
     <t>PSA NeO Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -2406,12 +2463,15 @@
     <t>syphilis Cassette 25T hindering (WB/S/P)</t>
   </si>
   <si>
+    <t>EVA I04425100005</t>
+  </si>
+  <si>
+    <t>27/10/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>I04425100005</t>
   </si>
   <si>
-    <t>27/10/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>Tuberculosis  (Tb) Cassette 25T hindering (WB/S/P)</t>
   </si>
   <si>
@@ -2547,6 +2607,9 @@
     <t>EVA O00425070002</t>
   </si>
   <si>
+    <t>EVA O00425100004</t>
+  </si>
+  <si>
     <t>Pregnancy (HCG) Dipstick 50T hindering (S/P/U)</t>
   </si>
   <si>
@@ -2562,6 +2625,9 @@
     <t>PCT Plus G Kit 25T iChroma Boditech</t>
   </si>
   <si>
+    <t>EVA  PPVGZ02EX</t>
+  </si>
+  <si>
     <t>EVA PPUYC02EX</t>
   </si>
   <si>
@@ -3337,6 +3403,12 @@
   </si>
   <si>
     <t>30/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TDR STAPH -96 10T Micrococcaceae including Staphylococcaceae mindray</t>
+  </si>
+  <si>
+    <t>20251112</t>
   </si>
   <si>
     <t>TDR NH -96 10T Neisseria Haemophilus mindray</t>
@@ -3939,7 +4011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C602"/>
+  <dimension ref="A1:C622"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="30" customWidth="1"/>
@@ -4112,73 +4184,73 @@
     </row>
     <row r="16" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>55</v>
@@ -4189,7 +4261,7 @@
     </row>
     <row r="23" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>57</v>
@@ -4200,68 +4272,68 @@
     </row>
     <row r="24" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="C24" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="C25" s="5" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="C27" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4269,21 +4341,21 @@
         <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4291,43 +4363,43 @@
         <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4335,7 +4407,7 @@
         <v>86</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>88</v>
@@ -4343,1316 +4415,1316 @@
     </row>
     <row r="37" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>97</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="C40" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>69</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>43</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="C68" s="4" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>168</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>171</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>173</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>46</v>
+        <v>177</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>37</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>37</v>
+        <v>200</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>217</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>220</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>224</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>231</v>
+        <v>177</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>234</v>
+        <v>177</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="C104" s="4" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C115" s="3" t="s">
-        <v>0</v>
+        <v>259</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>0</v>
+        <v>262</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>0</v>
+        <v>265</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C120" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C122" s="4" t="s">
         <v>275</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>282</v>
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C124" s="4" t="s">
-        <v>173</v>
+        <v>0</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>287</v>
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>67</v>
+        <v>281</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>303</v>
+        <v>184</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>194</v>
+        <v>298</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>308</v>
+        <v>60</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>56</v>
+        <v>301</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>325</v>
+        <v>205</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>129</v>
+        <v>64</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>140</v>
+        <v>323</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>129</v>
+        <v>326</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C147" s="3" t="s">
-        <v>0</v>
+        <v>330</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>0</v>
+        <v>332</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B151" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B151" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="C151" s="5" t="s">
-        <v>339</v>
+        <v>134</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>0</v>
+        <v>341</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>49</v>
+        <v>0</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>0</v>
@@ -5663,3269 +5735,3269 @@
     </row>
     <row r="157" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>0</v>
+        <v>352</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>0</v>
+        <v>349</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>359</v>
+        <v>0</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>362</v>
+        <v>113</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>368</v>
+        <v>53</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="C164" s="4" t="s">
-        <v>371</v>
+        <v>0</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C166" s="4" t="s">
-        <v>377</v>
+        <v>0</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>380</v>
+        <v>0</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>0</v>
+        <v>372</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="C170" s="4" t="s">
-        <v>387</v>
+        <v>0</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>120</v>
+        <v>377</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>129</v>
+        <v>383</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>391</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C178" s="4" t="s">
-        <v>404</v>
+        <v>0</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>409</v>
+        <v>128</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>72</v>
+        <v>370</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>413</v>
+        <v>134</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>19</v>
+        <v>408</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>334</v>
+        <v>410</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>290</v>
+        <v>418</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>430</v>
+        <v>79</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>393</v>
+        <v>424</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>434</v>
+        <v>19</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>435</v>
+        <v>403</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>436</v>
+        <v>345</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>438</v>
+        <v>403</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>444</v>
+        <v>403</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>445</v>
+        <v>301</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>334</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>186</v>
+        <v>443</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>163</v>
+        <v>448</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>391</v>
+        <v>450</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>389</v>
+        <v>453</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>461</v>
+        <v>403</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>300</v>
+        <v>456</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>462</v>
+        <v>424</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>424</v>
+        <v>345</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>391</v>
+        <v>432</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>464</v>
+        <v>197</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>467</v>
+        <v>432</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>468</v>
+        <v>174</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>94</v>
+        <v>465</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>473</v>
+        <v>311</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>475</v>
+        <v>433</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>461</v>
+        <v>403</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>478</v>
+        <v>432</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>483</v>
+        <v>432</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>485</v>
+        <v>403</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>486</v>
+        <v>84</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>490</v>
+        <v>432</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>315</v>
+        <v>481</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>46</v>
+        <v>483</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>120</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>348</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>507</v>
+        <v>326</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>427</v>
+        <v>498</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>508</v>
+        <v>50</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>511</v>
+        <v>128</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C231" s="3" t="s">
-        <v>0</v>
+        <v>504</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>389</v>
+        <v>506</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>81</v>
+        <v>144</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>389</v>
+        <v>508</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>412</v>
+        <v>511</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>521</v>
+        <v>436</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>145</v>
+        <v>516</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>145</v>
+        <v>519</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>0</v>
+        <v>520</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="C239" s="5" t="s">
-        <v>526</v>
+        <v>0</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>527</v>
+        <v>401</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>526</v>
+        <v>90</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>529</v>
+        <v>401</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>532</v>
+        <v>424</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>88</v>
+        <v>528</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>538</v>
+        <v>154</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>85</v>
+        <v>154</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C246" s="4" t="s">
-        <v>542</v>
+        <v>0</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>49</v>
+        <v>541</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>554</v>
+        <v>96</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C253" s="3" t="s">
-        <v>0</v>
+        <v>548</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>430</v>
+        <v>48</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>561</v>
+        <v>401</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>140</v>
+        <v>551</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>140</v>
+        <v>554</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>423</v>
+        <v>558</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>570</v>
+        <v>53</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>189</v>
+        <v>563</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>205</v>
+        <v>566</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="C262" s="4" t="s">
-        <v>211</v>
+        <v>0</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>277</v>
+        <v>439</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>583</v>
+        <v>568</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>588</v>
+        <v>432</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>593</v>
+        <v>579</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>594</v>
+        <v>432</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>597</v>
+        <v>200</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>600</v>
+        <v>200</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>601</v>
+        <v>585</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>605</v>
+        <v>222</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>606</v>
+        <v>588</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>607</v>
+        <v>589</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>608</v>
+        <v>590</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>609</v>
+        <v>591</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>610</v>
+        <v>592</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>613</v>
+        <v>134</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>8</v>
+        <v>125</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>616</v>
+        <v>598</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>617</v>
+        <v>599</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>615</v>
+        <v>597</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>623</v>
+        <v>608</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>97</v>
+        <v>609</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>625</v>
+        <v>610</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>354</v>
+        <v>611</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>627</v>
+        <v>614</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>31</v>
+        <v>200</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>632</v>
+        <v>619</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>421</v>
+        <v>627</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>640</v>
+        <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>642</v>
+        <v>631</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>643</v>
+        <v>629</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>644</v>
+        <v>630</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>126</v>
+        <v>631</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>72</v>
+        <v>633</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>647</v>
+        <v>629</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>648</v>
+        <v>634</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>649</v>
+        <v>635</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>650</v>
+        <v>636</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>67</v>
+        <v>637</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>653</v>
+        <v>105</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>654</v>
+        <v>640</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>655</v>
+        <v>365</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>656</v>
+        <v>641</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>120</v>
+        <v>642</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>406</v>
+        <v>31</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>120</v>
+        <v>281</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>664</v>
+        <v>649</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>199</v>
+        <v>430</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>595</v>
+        <v>655</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>670</v>
+        <v>136</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>673</v>
+        <v>79</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>610</v>
+        <v>571</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>673</v>
+        <v>425</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>587</v>
+        <v>60</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>520</v>
+        <v>128</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>684</v>
+        <v>665</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>595</v>
+        <v>672</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>686</v>
+        <v>665</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>220</v>
+        <v>128</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>688</v>
+        <v>665</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>689</v>
+        <v>674</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>600</v>
+        <v>672</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>690</v>
+        <v>665</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>691</v>
+        <v>675</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>693</v>
+        <v>678</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>694</v>
+        <v>679</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>698</v>
+        <v>609</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>700</v>
+        <v>685</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>135</v>
+        <v>686</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>705</v>
+        <v>624</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>703</v>
+        <v>687</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>706</v>
+        <v>691</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>120</v>
+        <v>689</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>708</v>
+        <v>693</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>99</v>
+        <v>599</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>501</v>
+        <v>696</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>710</v>
+        <v>694</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>713</v>
+        <v>694</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>714</v>
+        <v>699</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>217</v>
+        <v>528</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>716</v>
+        <v>701</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>717</v>
+        <v>609</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>720</v>
+        <v>231</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>721</v>
+        <v>704</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>723</v>
+        <v>614</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>726</v>
+        <v>689</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>727</v>
+        <v>708</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>728</v>
+        <v>709</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>457</v>
+        <v>710</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>729</v>
+        <v>708</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>731</v>
+        <v>231</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>501</v>
+        <v>714</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>736</v>
+        <v>715</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>738</v>
+        <v>144</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>739</v>
+        <v>715</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>740</v>
+        <v>719</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>741</v>
+        <v>156</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>743</v>
+        <v>721</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>744</v>
+        <v>722</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>745</v>
+        <v>723</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C340" s="1" t="s">
-        <v>0</v>
+        <v>724</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C341" s="3" t="s">
-        <v>0</v>
+        <v>725</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C342" s="1" t="s">
-        <v>0</v>
+        <v>727</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>640</v>
+        <v>228</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>750</v>
+        <v>731</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>750</v>
+        <v>734</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>570</v>
+        <v>736</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>754</v>
+        <v>738</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>755</v>
+        <v>739</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>756</v>
+        <v>740</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>757</v>
+        <v>741</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>758</v>
+        <v>742</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>759</v>
+        <v>743</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>761</v>
+        <v>463</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>763</v>
+        <v>746</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>58</v>
+        <v>747</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>764</v>
+        <v>745</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>0</v>
+        <v>748</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C351" s="3" t="s">
-        <v>0</v>
+        <v>750</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>0</v>
+        <v>753</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>754</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>0</v>
+        <v>759</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>760</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="C355" s="5" t="s">
-        <v>773</v>
+        <v>0</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="C356" s="4" t="s">
-        <v>776</v>
+        <v>0</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="C357" s="5" t="s">
-        <v>49</v>
+        <v>0</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>117</v>
+        <v>769</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>784</v>
+        <v>767</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>501</v>
+        <v>581</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>789</v>
+        <v>773</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>791</v>
+        <v>775</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>792</v>
+        <v>776</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>796</v>
+        <v>14</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>798</v>
+        <v>782</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>791</v>
+        <v>66</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>799</v>
+        <v>783</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="C366" s="4" t="s">
-        <v>791</v>
+        <v>0</v>
+      </c>
+      <c r="C366" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>801</v>
+        <v>784</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="C367" s="5" t="s">
-        <v>791</v>
+        <v>0</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>803</v>
+        <v>785</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>804</v>
-      </c>
-      <c r="C368" s="4" t="s">
-        <v>791</v>
+        <v>0</v>
+      </c>
+      <c r="C368" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>805</v>
+        <v>786</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>807</v>
+        <v>789</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>808</v>
-      </c>
-      <c r="C370" s="4" t="s">
-        <v>796</v>
+        <v>0</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>809</v>
+        <v>790</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>811</v>
+        <v>793</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>812</v>
+        <v>794</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>813</v>
+        <v>796</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>814</v>
+        <v>797</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>791</v>
+        <v>53</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>815</v>
+        <v>798</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>816</v>
+        <v>799</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>791</v>
+        <v>800</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>815</v>
+        <v>801</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>796</v>
+        <v>125</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>818</v>
+        <v>803</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>820</v>
+        <v>509</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>821</v>
+        <v>805</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>822</v>
+        <v>806</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>791</v>
+        <v>807</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>824</v>
+        <v>809</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>828</v>
+        <v>814</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>791</v>
+        <v>815</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>829</v>
+        <v>816</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>830</v>
+        <v>815</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>831</v>
+        <v>817</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>833</v>
+        <v>819</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>834</v>
+        <v>820</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>835</v>
+        <v>821</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>836</v>
+        <v>822</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>835</v>
+        <v>823</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>837</v>
+        <v>824</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>838</v>
+        <v>825</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>840</v>
+        <v>827</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>791</v>
+        <v>815</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>842</v>
+        <v>829</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>843</v>
+        <v>830</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>844</v>
+        <v>831</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>845</v>
+        <v>832</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>847</v>
+        <v>834</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>848</v>
+        <v>810</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>851</v>
+        <v>810</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>853</v>
+        <v>815</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>854</v>
+        <v>838</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>855</v>
+        <v>839</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>477</v>
+        <v>840</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>854</v>
+        <v>841</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>856</v>
+        <v>842</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>477</v>
+        <v>810</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>857</v>
+        <v>843</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>858</v>
+        <v>844</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>166</v>
+        <v>810</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>859</v>
+        <v>845</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>860</v>
+        <v>846</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>861</v>
+        <v>810</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>862</v>
+        <v>847</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>159</v>
+        <v>810</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>864</v>
+        <v>847</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>865</v>
+        <v>849</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>298</v>
+        <v>850</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>866</v>
+        <v>851</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>867</v>
+        <v>852</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>868</v>
+        <v>840</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>869</v>
+        <v>853</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>870</v>
+        <v>854</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>132</v>
+        <v>810</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>871</v>
+        <v>855</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>872</v>
+        <v>856</v>
       </c>
       <c r="C401" s="5" t="s">
-        <v>873</v>
+        <v>810</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>874</v>
+        <v>855</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>875</v>
+        <v>857</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>876</v>
+        <v>815</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>877</v>
+        <v>858</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>878</v>
+        <v>859</v>
       </c>
       <c r="C403" s="5" t="s">
-        <v>879</v>
+        <v>810</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>880</v>
+        <v>860</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>881</v>
+        <v>861</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>592</v>
+        <v>810</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>882</v>
+        <v>860</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>883</v>
+        <v>862</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>884</v>
+        <v>815</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>885</v>
+        <v>863</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>886</v>
+        <v>864</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>468</v>
+        <v>810</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>887</v>
+        <v>865</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>888</v>
+        <v>866</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>889</v>
+        <v>810</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>890</v>
+        <v>867</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>891</v>
+        <v>868</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>892</v>
+        <v>60</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>893</v>
+        <v>867</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>894</v>
+        <v>869</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>895</v>
+        <v>870</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>896</v>
+        <v>871</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>897</v>
+        <v>872</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>898</v>
+        <v>873</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>899</v>
+        <v>871</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>900</v>
+        <v>874</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>901</v>
+        <v>875</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>902</v>
+        <v>876</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C412" s="1" t="s">
-        <v>0</v>
+        <v>877</v>
+      </c>
+      <c r="C412" s="4" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>903</v>
+        <v>876</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C413" s="3" t="s">
-        <v>0</v>
+        <v>878</v>
+      </c>
+      <c r="C413" s="5" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>904</v>
+        <v>879</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C414" s="1" t="s">
-        <v>0</v>
+        <v>880</v>
+      </c>
+      <c r="C414" s="4" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>905</v>
+        <v>881</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C415" s="3" t="s">
-        <v>0</v>
+        <v>882</v>
+      </c>
+      <c r="C415" s="5" t="s">
+        <v>883</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>906</v>
+        <v>884</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>858</v>
+        <v>885</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>907</v>
+        <v>886</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>860</v>
+        <v>887</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>861</v>
+        <v>309</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>908</v>
+        <v>888</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>863</v>
+        <v>889</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>159</v>
+        <v>890</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>863</v>
+        <v>892</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>910</v>
+        <v>893</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>863</v>
+        <v>894</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>159</v>
+        <v>895</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>865</v>
+        <v>897</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>298</v>
+        <v>898</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>912</v>
+        <v>899</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>865</v>
+        <v>900</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>298</v>
+        <v>901</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>865</v>
+        <v>903</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>298</v>
+        <v>606</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>914</v>
+        <v>904</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>915</v>
+        <v>905</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>434</v>
+        <v>906</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>915</v>
+        <v>908</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>434</v>
+        <v>474</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>917</v>
+        <v>909</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>919</v>
+        <v>911</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>920</v>
+        <v>912</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>921</v>
+        <v>913</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>565</v>
+        <v>914</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>867</v>
+        <v>916</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>868</v>
+        <v>917</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>870</v>
+        <v>919</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>132</v>
+        <v>920</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>870</v>
+        <v>922</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>132</v>
+        <v>923</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="C431" s="5" t="s">
-        <v>132</v>
+        <v>0</v>
+      </c>
+      <c r="C431" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="C432" s="4" t="s">
-        <v>873</v>
+        <v>0</v>
+      </c>
+      <c r="C432" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>928</v>
-      </c>
-      <c r="C433" s="5" t="s">
-        <v>929</v>
+        <v>0</v>
+      </c>
+      <c r="C433" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>931</v>
-      </c>
-      <c r="C434" s="4" t="s">
-        <v>932</v>
+        <v>0</v>
+      </c>
+      <c r="C434" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>875</v>
+        <v>880</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>876</v>
+        <v>177</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>875</v>
+        <v>885</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>876</v>
+        <v>170</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>879</v>
+        <v>170</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>879</v>
+        <v>170</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>878</v>
+        <v>887</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>879</v>
+        <v>309</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>940</v>
+        <v>887</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>592</v>
+        <v>309</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>941</v>
+        <v>887</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>592</v>
+        <v>309</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>884</v>
+        <v>443</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>883</v>
+        <v>937</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>884</v>
+        <v>443</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>881</v>
+        <v>940</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>592</v>
+        <v>941</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>891</v>
+        <v>943</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>892</v>
+        <v>576</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>892</v>
+        <v>141</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C449" s="5" t="s">
-        <v>889</v>
+        <v>141</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>889</v>
+        <v>141</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>889</v>
+        <v>895</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B452" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="C452" s="4" t="s">
         <v>951</v>
-      </c>
-      <c r="B452" s="1" t="s">
-        <v>952</v>
-      </c>
-      <c r="C452" s="4" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="B453" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="C453" s="5" t="s">
         <v>954</v>
-      </c>
-      <c r="B453" s="3" t="s">
-        <v>952</v>
-      </c>
-      <c r="C453" s="5" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8933,10 +9005,10 @@
         <v>955</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>468</v>
+        <v>898</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8944,10 +9016,10 @@
         <v>956</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>468</v>
+        <v>898</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8955,10 +9027,10 @@
         <v>957</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>468</v>
+        <v>898</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8966,642 +9038,642 @@
         <v>958</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>959</v>
+        <v>900</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>960</v>
+        <v>901</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>959</v>
+        <v>900</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>960</v>
+        <v>901</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>959</v>
+        <v>900</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>960</v>
+        <v>901</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C460" s="1" t="s">
-        <v>0</v>
+        <v>962</v>
+      </c>
+      <c r="C460" s="4" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>966</v>
+        <v>606</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>969</v>
+        <v>906</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>968</v>
+        <v>905</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>354</v>
+        <v>906</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>972</v>
+        <v>903</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>973</v>
+        <v>606</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
-        <v>974</v>
+        <v>967</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>975</v>
+        <v>913</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>861</v>
+        <v>914</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>976</v>
+        <v>968</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>977</v>
+        <v>913</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>173</v>
+        <v>914</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>979</v>
+        <v>913</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>300</v>
+        <v>914</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>981</v>
+        <v>910</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>377</v>
+        <v>911</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
-        <v>982</v>
+        <v>971</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>983</v>
+        <v>910</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>605</v>
+        <v>911</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>984</v>
+        <v>972</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>985</v>
+        <v>910</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>986</v>
+        <v>911</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
-        <v>984</v>
+        <v>973</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>987</v>
+        <v>974</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>988</v>
+        <v>975</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>989</v>
+        <v>976</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>988</v>
+        <v>975</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
-        <v>991</v>
+        <v>977</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>990</v>
+        <v>908</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>988</v>
+        <v>474</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>992</v>
+        <v>978</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>990</v>
+        <v>908</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>988</v>
+        <v>474</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
-        <v>993</v>
+        <v>979</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>959</v>
+        <v>908</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>960</v>
+        <v>474</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
-        <v>994</v>
+        <v>980</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>878</v>
+        <v>981</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>879</v>
+        <v>982</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
-        <v>995</v>
+        <v>983</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>878</v>
+        <v>981</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>879</v>
+        <v>982</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>996</v>
+        <v>984</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>878</v>
+        <v>981</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>879</v>
+        <v>982</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
-        <v>997</v>
+        <v>985</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>878</v>
-      </c>
-      <c r="C479" s="5" t="s">
-        <v>879</v>
+        <v>0</v>
+      </c>
+      <c r="C479" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>998</v>
+        <v>986</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>999</v>
+        <v>987</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>1000</v>
+        <v>988</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
-        <v>1001</v>
+        <v>989</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>1000</v>
+        <v>991</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>1003</v>
+        <v>992</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>1002</v>
+        <v>990</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>1000</v>
+        <v>365</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
-        <v>1004</v>
+        <v>993</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>1007</v>
+        <v>883</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>1006</v>
+        <v>999</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>1007</v>
+        <v>184</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>1009</v>
+        <v>1000</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>1007</v>
+        <v>311</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>1007</v>
+        <v>389</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>1013</v>
+        <v>619</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>1015</v>
+        <v>1006</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>1012</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>1018</v>
+        <v>981</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>1019</v>
+        <v>982</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>1018</v>
+        <v>900</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>1019</v>
+        <v>901</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1024</v>
+        <v>900</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>1025</v>
+        <v>901</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>1024</v>
+        <v>900</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>1025</v>
+        <v>901</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
-        <v>1027</v>
+        <v>1019</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>1024</v>
+        <v>900</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>1025</v>
+        <v>901</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
-        <v>1032</v>
+        <v>1025</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1036</v>
+        <v>1028</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>1037</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>952</v>
+        <v>1034</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>953</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>952</v>
+        <v>1034</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>953</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>952</v>
+        <v>1034</v>
       </c>
       <c r="C510" s="4" t="s">
-        <v>953</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>952</v>
+        <v>1040</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>953</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="B515" s="3" t="s">
         <v>1046</v>
@@ -9612,376 +9684,376 @@
     </row>
     <row r="516" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>865</v>
+        <v>1046</v>
       </c>
       <c r="C516" s="4" t="s">
-        <v>298</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>865</v>
+        <v>1046</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>298</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>865</v>
+        <v>1046</v>
       </c>
       <c r="C518" s="4" t="s">
-        <v>298</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>865</v>
+        <v>1052</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>298</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>915</v>
+        <v>1052</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>434</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>915</v>
+        <v>1052</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>434</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>915</v>
+        <v>1052</v>
       </c>
       <c r="C522" s="4" t="s">
-        <v>434</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B523" s="3" t="s">
         <v>1058</v>
       </c>
-      <c r="B523" s="3" t="s">
-        <v>915</v>
-      </c>
       <c r="C523" s="5" t="s">
-        <v>434</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C524" s="4" t="s">
         <v>1059</v>
-      </c>
-      <c r="B524" s="1" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C524" s="4" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>1018</v>
+        <v>1058</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>1019</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>863</v>
+        <v>1058</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>159</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>863</v>
+        <v>974</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>159</v>
+        <v>975</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>863</v>
+        <v>974</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>159</v>
+        <v>975</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>863</v>
+        <v>974</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>159</v>
+        <v>975</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1066</v>
+        <v>974</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>1067</v>
+        <v>975</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B531" s="3" t="s">
         <v>1068</v>
       </c>
-      <c r="B531" s="3" t="s">
-        <v>1066</v>
-      </c>
       <c r="C531" s="5" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B532" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C532" s="4" t="s">
         <v>1069</v>
-      </c>
-      <c r="B532" s="1" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C532" s="4" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1012</v>
+        <v>1068</v>
       </c>
       <c r="C534" s="4" t="s">
-        <v>1013</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>1012</v>
+        <v>887</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>1013</v>
+        <v>309</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1012</v>
+        <v>887</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>1013</v>
+        <v>309</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>1075</v>
+        <v>887</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>1076</v>
+        <v>309</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1075</v>
+        <v>887</v>
       </c>
       <c r="C538" s="4" t="s">
-        <v>1076</v>
+        <v>309</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>1075</v>
+        <v>937</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>1076</v>
+        <v>443</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1075</v>
+        <v>937</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>1076</v>
+        <v>443</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>1046</v>
+        <v>937</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>1047</v>
+        <v>443</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1046</v>
+        <v>937</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>1047</v>
+        <v>443</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="C543" s="5" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="C544" s="4" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>1046</v>
+        <v>885</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>1047</v>
+        <v>170</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1046</v>
+        <v>885</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>1047</v>
+        <v>170</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>1046</v>
+        <v>885</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>1047</v>
+        <v>170</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1046</v>
+        <v>885</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>1047</v>
+        <v>170</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B549" s="3" t="s">
         <v>1088</v>
       </c>
-      <c r="B549" s="3" t="s">
+      <c r="C549" s="5" t="s">
         <v>1089</v>
-      </c>
-      <c r="C549" s="5" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9989,10 +10061,10 @@
         <v>1090</v>
       </c>
       <c r="B550" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C550" s="4" t="s">
         <v>1089</v>
-      </c>
-      <c r="C550" s="4" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -10000,543 +10072,763 @@
         <v>1091</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>412</v>
+        <v>1088</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>968</v>
+        <v>1088</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>459</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>1012</v>
+        <v>1034</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>1013</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1096</v>
+        <v>1034</v>
       </c>
       <c r="C554" s="4" t="s">
-        <v>1097</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C555" s="3" t="s">
-        <v>0</v>
+        <v>1034</v>
+      </c>
+      <c r="C555" s="5" t="s">
+        <v>1035</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C556" s="1" t="s">
-        <v>0</v>
+        <v>1097</v>
+      </c>
+      <c r="C556" s="4" t="s">
+        <v>1098</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1104</v>
+        <v>1097</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>1105</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>1107</v>
+        <v>1097</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>1108</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1110</v>
+        <v>1068</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>196</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>1111</v>
+        <v>1103</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>1112</v>
+        <v>1068</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>111</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
-        <v>1113</v>
+        <v>1104</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1114</v>
+        <v>1068</v>
       </c>
       <c r="C562" s="4" t="s">
-        <v>196</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>1116</v>
+        <v>1068</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>1117</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>1119</v>
+        <v>1068</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>1120</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
-        <v>1121</v>
+        <v>1107</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>1122</v>
+        <v>1068</v>
       </c>
       <c r="C565" s="5" t="s">
-        <v>52</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
-        <v>1121</v>
+        <v>1108</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>1123</v>
+        <v>1068</v>
       </c>
       <c r="C566" s="4" t="s">
-        <v>413</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
-        <v>1124</v>
+        <v>1109</v>
       </c>
       <c r="B567" s="3" t="s">
-        <v>1125</v>
+        <v>1068</v>
       </c>
       <c r="C567" s="5" t="s">
-        <v>1126</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
-        <v>1127</v>
+        <v>1110</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1128</v>
+        <v>1111</v>
       </c>
       <c r="C568" s="4" t="s">
-        <v>895</v>
+        <v>757</v>
       </c>
     </row>
     <row r="569" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
-        <v>1129</v>
+        <v>1112</v>
       </c>
       <c r="B569" s="3" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="C569" s="5" t="s">
-        <v>1031</v>
+        <v>757</v>
       </c>
     </row>
     <row r="570" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
-        <v>1131</v>
+        <v>1113</v>
       </c>
       <c r="B570" s="1" t="s">
-        <v>1132</v>
+        <v>424</v>
       </c>
       <c r="C570" s="4" t="s">
-        <v>622</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="571" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
-        <v>1133</v>
+        <v>1115</v>
       </c>
       <c r="B571" s="3" t="s">
-        <v>1134</v>
+        <v>990</v>
       </c>
       <c r="C571" s="5" t="s">
-        <v>622</v>
+        <v>465</v>
       </c>
     </row>
     <row r="572" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A572" s="1" t="s">
-        <v>1135</v>
+        <v>1116</v>
       </c>
       <c r="B572" s="1" t="s">
-        <v>1136</v>
+        <v>1034</v>
       </c>
       <c r="C572" s="4" t="s">
-        <v>52</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="573" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
-        <v>1137</v>
+        <v>1117</v>
       </c>
       <c r="B573" s="3" t="s">
-        <v>1138</v>
+        <v>1118</v>
       </c>
       <c r="C573" s="5" t="s">
-        <v>627</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="574" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A574" s="1" t="s">
-        <v>1139</v>
+        <v>1120</v>
       </c>
       <c r="B574" s="1" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C574" s="4" t="s">
-        <v>622</v>
+        <v>0</v>
+      </c>
+      <c r="C574" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="575" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>1141</v>
+        <v>1121</v>
       </c>
       <c r="B575" s="3" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C575" s="5" t="s">
-        <v>622</v>
+        <v>0</v>
+      </c>
+      <c r="C575" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="576" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A576" s="1" t="s">
-        <v>1143</v>
+        <v>1122</v>
       </c>
       <c r="B576" s="1" t="s">
-        <v>1144</v>
+        <v>1123</v>
       </c>
       <c r="C576" s="4" t="s">
-        <v>622</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="577" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
-        <v>1145</v>
+        <v>1125</v>
       </c>
       <c r="B577" s="3" t="s">
-        <v>1146</v>
+        <v>1126</v>
       </c>
       <c r="C577" s="5" t="s">
-        <v>622</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="578" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
-        <v>1147</v>
+        <v>1128</v>
       </c>
       <c r="B578" s="1" t="s">
-        <v>1148</v>
+        <v>1129</v>
       </c>
       <c r="C578" s="4" t="s">
-        <v>622</v>
+        <v>174</v>
       </c>
     </row>
     <row r="579" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
-        <v>1149</v>
+        <v>1130</v>
       </c>
       <c r="B579" s="3" t="s">
-        <v>1150</v>
+        <v>1131</v>
       </c>
       <c r="C579" s="5" t="s">
-        <v>622</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="580" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A580" s="1" t="s">
-        <v>1151</v>
+        <v>1133</v>
       </c>
       <c r="B580" s="1" t="s">
-        <v>1152</v>
+        <v>1134</v>
       </c>
       <c r="C580" s="4" t="s">
-        <v>1153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="581" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
-        <v>1154</v>
+        <v>1135</v>
       </c>
       <c r="B581" s="3" t="s">
-        <v>1155</v>
+        <v>1136</v>
       </c>
       <c r="C581" s="5" t="s">
-        <v>622</v>
+        <v>119</v>
       </c>
     </row>
     <row r="582" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
-        <v>1156</v>
+        <v>1137</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1157</v>
+        <v>1138</v>
       </c>
       <c r="C582" s="4" t="s">
-        <v>622</v>
+        <v>207</v>
       </c>
     </row>
     <row r="583" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
-        <v>1158</v>
+        <v>1139</v>
       </c>
       <c r="B583" s="3" t="s">
-        <v>1159</v>
+        <v>1140</v>
       </c>
       <c r="C583" s="5" t="s">
-        <v>622</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="584" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A584" s="1" t="s">
-        <v>1160</v>
+        <v>1142</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>1161</v>
+        <v>1143</v>
       </c>
       <c r="C584" s="4" t="s">
-        <v>511</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="585" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
-        <v>1162</v>
+        <v>1145</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>1163</v>
+        <v>1146</v>
       </c>
       <c r="C585" s="5" t="s">
-        <v>140</v>
+        <v>56</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
-        <v>1164</v>
+        <v>1145</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>1165</v>
+        <v>1147</v>
       </c>
       <c r="C586" s="4" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
     </row>
     <row r="587" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A587" s="3" t="s">
-        <v>1166</v>
+        <v>1148</v>
       </c>
       <c r="B587" s="3" t="s">
-        <v>1167</v>
+        <v>1149</v>
       </c>
       <c r="C587" s="5" t="s">
-        <v>622</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="588" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A588" s="1" t="s">
-        <v>1168</v>
+        <v>1151</v>
       </c>
       <c r="B588" s="1" t="s">
-        <v>1169</v>
+        <v>1152</v>
       </c>
       <c r="C588" s="4" t="s">
-        <v>1170</v>
+        <v>917</v>
       </c>
     </row>
     <row r="589" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
-        <v>1171</v>
+        <v>1153</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>1172</v>
+        <v>1154</v>
       </c>
       <c r="C589" s="5" t="s">
-        <v>622</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="590" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
-        <v>1173</v>
+        <v>1155</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>1174</v>
+        <v>1156</v>
       </c>
       <c r="C590" s="4" t="s">
-        <v>973</v>
+        <v>637</v>
       </c>
     </row>
     <row r="591" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
-        <v>1175</v>
+        <v>1157</v>
       </c>
       <c r="B591" s="3" t="s">
-        <v>1174</v>
+        <v>1158</v>
       </c>
       <c r="C591" s="5" t="s">
-        <v>973</v>
+        <v>637</v>
       </c>
     </row>
     <row r="592" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A592" s="1" t="s">
-        <v>1176</v>
+        <v>1159</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>1177</v>
+        <v>1160</v>
       </c>
       <c r="C592" s="4" t="s">
-        <v>1178</v>
+        <v>56</v>
       </c>
     </row>
     <row r="593" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
-        <v>1179</v>
+        <v>1161</v>
       </c>
       <c r="B593" s="3" t="s">
-        <v>1180</v>
+        <v>1162</v>
       </c>
       <c r="C593" s="5" t="s">
-        <v>735</v>
+        <v>642</v>
       </c>
     </row>
     <row r="594" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
-        <v>1181</v>
+        <v>1163</v>
       </c>
       <c r="B594" s="1" t="s">
-        <v>1182</v>
+        <v>1164</v>
       </c>
       <c r="C594" s="4" t="s">
-        <v>409</v>
+        <v>637</v>
       </c>
     </row>
     <row r="595" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A595" s="3" t="s">
-        <v>1183</v>
+        <v>1165</v>
       </c>
       <c r="B595" s="3" t="s">
-        <v>373</v>
+        <v>1166</v>
       </c>
       <c r="C595" s="5" t="s">
-        <v>374</v>
+        <v>637</v>
       </c>
     </row>
     <row r="596" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
-        <v>1184</v>
+        <v>1167</v>
       </c>
       <c r="B596" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C596" s="1" t="s">
-        <v>0</v>
+        <v>1168</v>
+      </c>
+      <c r="C596" s="4" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="597" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A597" s="3" t="s">
-        <v>1185</v>
+        <v>1169</v>
       </c>
       <c r="B597" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C597" s="3" t="s">
-        <v>0</v>
+        <v>1170</v>
+      </c>
+      <c r="C597" s="5" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
-        <v>1186</v>
+        <v>1171</v>
       </c>
       <c r="B598" s="1" t="s">
-        <v>1187</v>
+        <v>1172</v>
       </c>
       <c r="C598" s="4" t="s">
-        <v>511</v>
+        <v>637</v>
       </c>
     </row>
     <row r="599" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A599" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B599" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C599" s="5" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A600" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C600" s="4" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A601" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B601" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C601" s="5" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A602" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C602" s="4" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A603" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B603" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C603" s="5" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A604" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B604" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C604" s="4" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A605" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B605" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C605" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A606" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="B599" s="3" t="s">
+      <c r="B606" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C606" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A607" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B607" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C607" s="5" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A608" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B608" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C608" s="4" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A609" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B609" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C609" s="5" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A610" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B610" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C610" s="4" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A611" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B611" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C611" s="5" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A612" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B612" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C612" s="4" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A613" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B613" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C613" s="5" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A614" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B614" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C614" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A615" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B615" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C615" s="5" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A616" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B616" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C599" s="3" t="s">
+      <c r="C616" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
-    <row r="601" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
-    <row r="602" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="617" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A617" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B617" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C617" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A618" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B618" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C618" s="4" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A619" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B619" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C619" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="621" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="622" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/المواد.xlsx
+++ b/المواد.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="1179">
   <si>
     <t/>
   </si>
@@ -66,6 +66,12 @@
     <t>28/01/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA DTSVGY10</t>
+  </si>
+  <si>
+    <t>03/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>AFP Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -204,6 +210,12 @@
     <t>T3 Kit 24T Afias Boditech</t>
   </si>
   <si>
+    <t>EVA  T3VEA49X</t>
+  </si>
+  <si>
+    <t>22/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA  T3VFA50X</t>
   </si>
   <si>
@@ -219,12 +231,6 @@
     <t>19/02/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>EVA T4VEA35X</t>
-  </si>
-  <si>
-    <t>21/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>TSH Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -234,18 +240,27 @@
     <t>16/02/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA  TSVXB01X</t>
+  </si>
+  <si>
+    <t>04/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA TSVEA89X</t>
   </si>
   <si>
     <t>29/01/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>EVA TSVFA91X</t>
-  </si>
-  <si>
     <t>Testosterone Kit 24T Afias Boditech</t>
   </si>
   <si>
+    <t>EVA TTVEA20X</t>
+  </si>
+  <si>
+    <t>13/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA TTVXA23X</t>
   </si>
   <si>
@@ -285,30 +300,24 @@
     <t>28/04/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>ASO Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA ASVEB03EX</t>
+    <t>Cystatin C Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>CCVLB03EX</t>
+  </si>
+  <si>
+    <t>17/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-CCP Plus Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  ACVED09E</t>
   </si>
   <si>
     <t>14/01/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>Cystatin C Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>CCVLB03EX</t>
-  </si>
-  <si>
-    <t>17/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-CCP Plus Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  ACVED09E</t>
-  </si>
-  <si>
     <t>EVA ACVED09E</t>
   </si>
   <si>
@@ -393,6 +402,12 @@
     <t>18/11/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA AAVCU07</t>
+  </si>
+  <si>
+    <t>26/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
     <t>LH Kit 25T iChroma Boditech</t>
   </si>
   <si>
@@ -711,6 +726,9 @@
     <t>2025112454</t>
   </si>
   <si>
+    <t>2025112455</t>
+  </si>
+  <si>
     <t>M-30R Rinse Reagent 3-part 20L Hematology Mindray</t>
   </si>
   <si>
@@ -747,6 +765,12 @@
     <t>20/11/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>2025112253</t>
+  </si>
+  <si>
+    <t>21/11/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>Cuvette BS120 Chemistry Mindray</t>
   </si>
   <si>
@@ -771,6 +795,12 @@
     <t>20/08/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>C4 kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>144025006</t>
+  </si>
+  <si>
     <t>فحوصات ESR فشن</t>
   </si>
   <si>
@@ -783,12 +813,39 @@
     <t>19/05/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>2025112151</t>
+  </si>
+  <si>
+    <t>20/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>BC-30s-3part Instrument Auto Hematology Mindray</t>
+  </si>
+  <si>
     <t>BA-88A Instrument Semi-Auto chemistry Mindray</t>
   </si>
   <si>
     <t>I-Chroma 2 Instrument Boditech</t>
   </si>
   <si>
+    <t>Fe (Re +Calibrator)  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>145325017</t>
+  </si>
+  <si>
+    <t>04/06/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>GGT kit  Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>140425014</t>
+  </si>
+  <si>
+    <t>19/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>GLU kit  Chemistry Mindray</t>
   </si>
   <si>
@@ -822,12 +879,21 @@
     <t>147025008</t>
   </si>
   <si>
+    <t>147025009</t>
+  </si>
+  <si>
+    <t>25/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>147025016</t>
+  </si>
+  <si>
+    <t>09/05/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>TC  Chemistry Mindray</t>
   </si>
   <si>
-    <t>141625014</t>
-  </si>
-  <si>
     <t>141625015</t>
   </si>
   <si>
@@ -858,6 +924,12 @@
     <t>17/01/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>146726001</t>
+  </si>
+  <si>
+    <t>17/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>كيوفيت Microcuvettes -Hemo هيمو كروما</t>
   </si>
   <si>
@@ -978,6 +1050,15 @@
     <t>144225003</t>
   </si>
   <si>
+    <t>Lipids Calibrator Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>150425016</t>
+  </si>
+  <si>
+    <t>21/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>Aqappe 30ml Nano Detergent</t>
   </si>
   <si>
@@ -1002,6 +1083,12 @@
     <t>BC-10-3part Instrument Auto Hematology Mindray</t>
   </si>
   <si>
+    <t>Hba1c Control Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>052426002</t>
+  </si>
+  <si>
     <t>M-10CFL Lyse 3-part 500ml Hematology Mindray</t>
   </si>
   <si>
@@ -1029,6 +1116,21 @@
     <t>12/06/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>M-62 FD Dye Reagent 7-part 12mL Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2026010851</t>
+  </si>
+  <si>
+    <t>07/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>M-62 FR Dye Reagent 7-part 12mL Hematology Mindray</t>
+  </si>
+  <si>
+    <t>2025121551</t>
+  </si>
+  <si>
     <t>M-62 LD Lyse Reagent 7-part 1L Hematology Mindray</t>
   </si>
   <si>
@@ -1332,13 +1434,13 @@
     <t>Wash Buffer Consumables 1X10L Cl-900i Mindray</t>
   </si>
   <si>
-    <t>2025111915</t>
+    <t>2025111918</t>
   </si>
   <si>
     <t>18/05/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>2025111918</t>
+    <t>2025111921</t>
   </si>
   <si>
     <t>Immunoassay Cuvette Consumables 2*88 Cl900i Mindray</t>
@@ -1461,9 +1563,6 @@
     <t>EVA  MHVXC12E</t>
   </si>
   <si>
-    <t>04/05/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>EVA MHVXC12E</t>
   </si>
   <si>
@@ -1566,240 +1665,261 @@
     <t>EVA  VEVHC14X</t>
   </si>
   <si>
-    <t>EVA VEVGC08X</t>
+    <t>EVA  VEVXC18X</t>
+  </si>
+  <si>
+    <t>EVA VEVHC13X</t>
+  </si>
+  <si>
+    <t>Rubella Virus IgG kit 2×50T  with cal.Cl900i  Mindray</t>
+  </si>
+  <si>
+    <t>2025070141</t>
+  </si>
+  <si>
+    <t>14/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CMV IgM kit 2×50T with cal.Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>26/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CMV IgG kit  2×50T with cal.Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>ZINC kit 20T Agappe</t>
+  </si>
+  <si>
+    <t>32512383</t>
+  </si>
+  <si>
+    <t>Iron kit 100T Agappe</t>
+  </si>
+  <si>
+    <t>32411254</t>
+  </si>
+  <si>
+    <t>32411296</t>
+  </si>
+  <si>
+    <t>IGRA -TB  Kit 8T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA TBVYA30G</t>
+  </si>
+  <si>
+    <t>20/06/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>free T4  Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>F4VLA50G</t>
+  </si>
+  <si>
+    <t>11/08/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Free T4 Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  F4VGF04</t>
+  </si>
+  <si>
+    <t>CA19-9 Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  CXVHB05EX</t>
+  </si>
+  <si>
+    <t>Vitamin D  Neo Kit 25T iChroma Boditech</t>
+  </si>
+  <si>
+    <t>EVA  VEVCB06E</t>
+  </si>
+  <si>
+    <t>EVA  VEVDB07E</t>
+  </si>
+  <si>
+    <t>09/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA  VEVDB08E</t>
+  </si>
+  <si>
+    <t>EVA VEVDB08E</t>
+  </si>
+  <si>
+    <t>C3 Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509120</t>
+  </si>
+  <si>
+    <t>23/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CRP Kit 60T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512330</t>
+  </si>
+  <si>
+    <t>04/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Ferritin Kit 30T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512316</t>
+  </si>
+  <si>
+    <t>03/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HbA1c Kit 30T Mispa i3</t>
+  </si>
+  <si>
+    <t>32512125</t>
+  </si>
+  <si>
+    <t>C4 Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA 32506489</t>
+  </si>
+  <si>
+    <t>15/06/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Washing solution 1*50 ml  Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA  32509067</t>
+  </si>
+  <si>
+    <t>probe cleanser Mispa i3</t>
+  </si>
+  <si>
+    <t>32512329</t>
+  </si>
+  <si>
+    <t>30/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>( ALB Kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>148325013</t>
+  </si>
+  <si>
+    <t>05/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>148325014</t>
+  </si>
+  <si>
+    <t>( ALP kit  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140325004</t>
+  </si>
+  <si>
+    <t>12/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>140325012</t>
+  </si>
+  <si>
+    <t>( ALT  (GPT) kit  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140125021</t>
+  </si>
+  <si>
+    <t>10/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>140125022</t>
+  </si>
+  <si>
+    <t>( AST (GOT) kit  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140225017</t>
+  </si>
+  <si>
+    <t>( Ca kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>142225007</t>
+  </si>
+  <si>
+    <t>( CRP kit  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>148925011</t>
+  </si>
+  <si>
+    <t>( D- Bill (vox) kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140725012</t>
+  </si>
+  <si>
+    <t>01/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>140725013</t>
+  </si>
+  <si>
+    <t>( G6PD kit  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>146625008</t>
+  </si>
+  <si>
+    <t>( LDH kit  Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>142725009</t>
+  </si>
+  <si>
+    <t>( LDL-C kit  Chemistry Mindray  ( Large</t>
+  </si>
+  <si>
+    <t>142025010</t>
+  </si>
+  <si>
+    <t>17/09/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>( MG kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>148225004</t>
+  </si>
+  <si>
+    <t>( Phosphorus Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>142425005</t>
+  </si>
+  <si>
+    <t>( T-Bill vox kit Chemistry Mindray ( Large</t>
+  </si>
+  <si>
+    <t>140625015</t>
+  </si>
+  <si>
+    <t>140625016</t>
   </si>
   <si>
     <t>22/03/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>EVA VEVHC13X</t>
-  </si>
-  <si>
-    <t>Rubella Virus IgG kit 2×50T  with cal.Cl900i  Mindray</t>
-  </si>
-  <si>
-    <t>2025070141</t>
-  </si>
-  <si>
-    <t>14/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CMV IgM kit 2×50T with cal.Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>26/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CMV IgG kit  2×50T with cal.Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>ZINC kit 20T Agappe</t>
-  </si>
-  <si>
-    <t>32512383</t>
-  </si>
-  <si>
-    <t>Iron kit 100T Agappe</t>
-  </si>
-  <si>
-    <t>32411254</t>
-  </si>
-  <si>
-    <t>32411296</t>
-  </si>
-  <si>
-    <t>IGRA -TB  Kit 8T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA TBVYA30G</t>
-  </si>
-  <si>
-    <t>20/06/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>free T4  Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>F4VLA50G</t>
-  </si>
-  <si>
-    <t>11/08/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Free T4 Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  F4VGF04</t>
-  </si>
-  <si>
-    <t>CA19-9 Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  CXVHB05EX</t>
-  </si>
-  <si>
-    <t>Vitamin D  Neo Kit 25T iChroma Boditech</t>
-  </si>
-  <si>
-    <t>EVA  VEVCB06E</t>
-  </si>
-  <si>
-    <t>26/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA  VEVDB07E</t>
-  </si>
-  <si>
-    <t>09/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>C3 Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509120</t>
-  </si>
-  <si>
-    <t>23/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CRP Kit 60T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512330</t>
-  </si>
-  <si>
-    <t>04/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Ferritin Kit 30T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512316</t>
-  </si>
-  <si>
-    <t>03/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HbA1c Kit 30T Mispa i3</t>
-  </si>
-  <si>
-    <t>32512125</t>
-  </si>
-  <si>
-    <t>C4 Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA 32506489</t>
-  </si>
-  <si>
-    <t>15/06/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Washing solution 1*50 ml  Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA  32509067</t>
-  </si>
-  <si>
-    <t>probe cleanser Mispa i3</t>
-  </si>
-  <si>
-    <t>32512329</t>
-  </si>
-  <si>
-    <t>30/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>( ALB Kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>148325013</t>
-  </si>
-  <si>
-    <t>05/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>148325014</t>
-  </si>
-  <si>
-    <t>( ALP kit  Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140325004</t>
-  </si>
-  <si>
-    <t>12/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>140325012</t>
-  </si>
-  <si>
-    <t>( ALT  (GPT) kit  Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140125021</t>
-  </si>
-  <si>
-    <t>10/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>140125022</t>
-  </si>
-  <si>
-    <t>( AST (GOT) kit  Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140225017</t>
-  </si>
-  <si>
-    <t>( Ca kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>142225007</t>
-  </si>
-  <si>
-    <t>( CRP kit  Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>148925011</t>
-  </si>
-  <si>
-    <t>( D- Bill (vox) kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140725012</t>
-  </si>
-  <si>
-    <t>01/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>140725013</t>
-  </si>
-  <si>
-    <t>( LDL-C kit  Chemistry Mindray  ( Large</t>
-  </si>
-  <si>
-    <t>142025010</t>
-  </si>
-  <si>
-    <t>17/09/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>( MG kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>148225004</t>
-  </si>
-  <si>
-    <t>( T-Bill vox kit Chemistry Mindray ( Large</t>
-  </si>
-  <si>
-    <t>140625015</t>
-  </si>
-  <si>
-    <t>140625016</t>
-  </si>
-  <si>
     <t>( TP kit Chemistry Mindray ( Large</t>
   </si>
   <si>
@@ -1845,9 +1965,6 @@
     <t>EVA B25F10H18DL</t>
   </si>
   <si>
-    <t>17/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>Ferritin Cal Chemistry Mindray</t>
   </si>
   <si>
@@ -2568,6 +2685,15 @@
     <t>25/09/2026 12:00:00 ص</t>
   </si>
   <si>
+    <t>Sample Diluent I  BioCLOA 100 ml</t>
+  </si>
+  <si>
+    <t>EVA 20250829</t>
+  </si>
+  <si>
+    <t>28/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
     <t>BioCLIA Silicone gasket (small)</t>
   </si>
   <si>
@@ -2775,628 +2901,616 @@
     <t>NT-PROBNP kit 2×50T Cl900i Mindray</t>
   </si>
   <si>
-    <t>LIPISE kit Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>044825014</t>
+    <t>TRAb kit 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2024030411</t>
+  </si>
+  <si>
+    <t>TRAb Calibrators Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>2025030111</t>
+  </si>
+  <si>
+    <t>Ferritin kit Chemistry Mindray 84 T</t>
+  </si>
+  <si>
+    <t>046125013</t>
+  </si>
+  <si>
+    <t>H.Pylori SA Kit 24T Afias Boditech</t>
+  </si>
+  <si>
+    <t>EVA HSVXA07X</t>
+  </si>
+  <si>
+    <t>Haptoglobin Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>32506426</t>
+  </si>
+  <si>
+    <t>nRNP/Sm, KIT BioCLIA 50 T</t>
+  </si>
+  <si>
+    <t>20240621</t>
+  </si>
+  <si>
+    <t>20/06/2025 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA 20250708-1</t>
+  </si>
+  <si>
+    <t>07/07/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>nRNP/Sm Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250708</t>
+  </si>
+  <si>
+    <t>nRNP/Sm Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>nRNP/Sm Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>PCA KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>Jo-1 KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>Jo-1 Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Jo-1 Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Jo-1 Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Ro52 KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250828-1</t>
+  </si>
+  <si>
+    <t>27/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Ro52 Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250828</t>
+  </si>
+  <si>
+    <t>Ro52 Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Ro52 Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Scl-70 KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250831</t>
+  </si>
+  <si>
+    <t>30/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Scl-70 Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Scl-70 Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Scl-70 Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Ribosomal P KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250904</t>
+  </si>
+  <si>
+    <t>03/09/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Ribosomal P  Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Ribosomal P Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Ribosomal P Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>PCNA KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250822</t>
+  </si>
+  <si>
+    <t>21/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>PCNA Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>PCNA Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>PCNA Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>PM-Scl KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250921</t>
+  </si>
+  <si>
+    <t>20/09/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>PM-Scl Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>PM-Scl  Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>PM-Scl  Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Histone KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250902</t>
+  </si>
+  <si>
+    <t>01/09/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Histone  Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Histone  Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Histone Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>CENP-B KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250908</t>
+  </si>
+  <si>
+    <t>07/09/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CENP-B Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>CENP-B  Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>CENP-B  Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Nucleosome KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>Nucleosome Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Nucleosome Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>Nucleosome Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>GBM KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250923</t>
+  </si>
+  <si>
+    <t>22/09/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>GBM Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>GBM Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>GBM Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>gp210 KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>gp210 Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>gp210 Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>gp210 Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>sp100 KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>sp100 Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>sp100 Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>sp100 Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>LKM-1 Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>LKM-1 Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>LC-1 KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>LC-1 Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>LC-1 Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>LC-1 Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>SLA/LP  KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250821</t>
+  </si>
+  <si>
+    <t>20/08/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>SLA/LP Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>SLA/LP Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>SLA/LP Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF IgA Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF IgA  Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF IgA  Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF IgG KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250630</t>
+  </si>
+  <si>
+    <t>29/06/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>RF IgG Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF IgG  Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF IgG  Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF IgM KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>RF IgM Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF IgM Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF IgM Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF Screen  KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>RF Screen Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF Screen Control level 1 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>RF Screen Control level 2 BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>CCP KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>EVA 20250812</t>
+  </si>
+  <si>
+    <t>CCP  Calibrator Set BioCLIA HOB</t>
+  </si>
+  <si>
+    <t>hs-cTnI Calibrator 2ml Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>02/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Growth hormone kit with cal 2×50T Cl900i Mindray</t>
+  </si>
+  <si>
+    <t>RF IgA KIT BioCLIA 50 T HOB</t>
+  </si>
+  <si>
+    <t>Apo A 1 Kit 10T Mispa i3</t>
+  </si>
+  <si>
+    <t>EVA 32503263</t>
+  </si>
+  <si>
+    <t>30/11/2025 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Cuvette BS230 (120) Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>Cuvette BS230 (20) Chemistry Mindray</t>
+  </si>
+  <si>
+    <t>TDR ONE -96 10T Enterobacteriaceae mindray</t>
+  </si>
+  <si>
+    <t>20251121</t>
+  </si>
+  <si>
+    <t>20/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TDR STR -96 10T Streptococcus mindray</t>
+  </si>
+  <si>
+    <t>20251031</t>
+  </si>
+  <si>
+    <t>30/10/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TDR STAPH -96 10T Micrococcaceae including Staphylococcaceae mindray</t>
+  </si>
+  <si>
+    <t>20251112</t>
+  </si>
+  <si>
+    <t>TDR NH -96 10T Neisseria Haemophilus mindray</t>
+  </si>
+  <si>
+    <t>20251106</t>
+  </si>
+  <si>
+    <t>05/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>TDR NF -96 10T Non-fermentative bacteria  mindray</t>
+  </si>
+  <si>
+    <t>20251111</t>
+  </si>
+  <si>
+    <t>TDR YEAST -96 10T Yeast- like fungi  mindray</t>
+  </si>
+  <si>
+    <t>20250920</t>
+  </si>
+  <si>
+    <t>Anaerobic bottle (TDR Resin Aerobic)25 bottles mindray</t>
+  </si>
+  <si>
+    <t>BCBOKJ-1</t>
+  </si>
+  <si>
+    <t>09/11/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Lysing solution 50ml mindray</t>
+  </si>
+  <si>
+    <t>2024091051</t>
+  </si>
+  <si>
+    <t>09/09/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Sheath fluid solution 5L mindray</t>
+  </si>
+  <si>
+    <t>2025030151</t>
+  </si>
+  <si>
+    <t>28/02/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>2025031151</t>
+  </si>
+  <si>
+    <t>Urea U.V kit 100T Agappe</t>
+  </si>
+  <si>
+    <t>32503128</t>
+  </si>
+  <si>
+    <t>31/12/2026 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HBA1C 100 T كت مسبا</t>
+  </si>
+  <si>
+    <t>32511257</t>
+  </si>
+  <si>
+    <t>CRP 100 T كت مسبا</t>
+  </si>
+  <si>
+    <t>32511084</t>
+  </si>
+  <si>
+    <t>CD57 APC 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A33AA3</t>
+  </si>
+  <si>
+    <t>CD15 PE  100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A50AE4</t>
+  </si>
+  <si>
+    <t>CD56 PE-Cy7 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A192A2T1</t>
+  </si>
+  <si>
+    <t>CD25 APC 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A156SA1</t>
+  </si>
+  <si>
+    <t>25/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>CD16 FITC 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A14AF6</t>
+  </si>
+  <si>
+    <t>CD2 PE-Cy7 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A2S2T6</t>
+  </si>
+  <si>
+    <t>CD71 APC-Cy7 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A31S4T2</t>
+  </si>
+  <si>
+    <t>MPO FITC 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A123AF2</t>
+  </si>
+  <si>
+    <t>CD103 PE 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A331SE1</t>
+  </si>
+  <si>
+    <t>Anti-Lambda Light Chain PE 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A66AE10</t>
+  </si>
+  <si>
+    <t>CD1a FITC 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A115AF1</t>
+  </si>
+  <si>
+    <t>23/01/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>Anti-Kappa Light Chain FITC 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A48SF11</t>
+  </si>
+  <si>
+    <t>CD64 FITC 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A145AF4</t>
+  </si>
+  <si>
+    <t>CD81 APC-Cy7 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A332S4T1</t>
+  </si>
+  <si>
+    <t>CD30 FITC 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A221SF2</t>
+  </si>
+  <si>
+    <t>CD8 APC-Cy7 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A109S4T21</t>
+  </si>
+  <si>
+    <t>CD43 APC-Cy7 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A168A4T1</t>
+  </si>
+  <si>
+    <t>CD20 mFluor450 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A37A4F3</t>
+  </si>
+  <si>
+    <t>CD73 mFluor450 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A99A4F1</t>
+  </si>
+  <si>
+    <t>02/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>HLA-DR mFluor450 100Tests Caprico</t>
+  </si>
+  <si>
+    <t>EVA A32A4F4</t>
+  </si>
+  <si>
+    <t>Kappa/Lambda Free Light Chain Level 1(1 ml ) Mispa i3</t>
+  </si>
+  <si>
+    <t>32512260</t>
   </si>
   <si>
     <t>31/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TRAb kit 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2024030411</t>
-  </si>
-  <si>
-    <t>TRAb Calibrators Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>2025030111</t>
-  </si>
-  <si>
-    <t>Ferritin kit Chemistry Mindray 84 T</t>
-  </si>
-  <si>
-    <t>046125013</t>
-  </si>
-  <si>
-    <t>H.Pylori SA Kit 24T Afias Boditech</t>
-  </si>
-  <si>
-    <t>EVA HSVXA07X</t>
-  </si>
-  <si>
-    <t>Haptoglobin Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>32506426</t>
-  </si>
-  <si>
-    <t>nRNP/Sm, KIT BioCLIA 50 T</t>
-  </si>
-  <si>
-    <t>20240621</t>
-  </si>
-  <si>
-    <t>20/06/2025 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA 20250708-1</t>
-  </si>
-  <si>
-    <t>07/07/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>nRNP/Sm Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250708</t>
-  </si>
-  <si>
-    <t>nRNP/Sm Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>nRNP/Sm Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>PCA KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>Jo-1 KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>Jo-1 Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Jo-1 Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Jo-1 Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Ro52 KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250828-1</t>
-  </si>
-  <si>
-    <t>27/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Ro52 Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250828</t>
-  </si>
-  <si>
-    <t>Ro52 Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Ro52 Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Scl-70 KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250831</t>
-  </si>
-  <si>
-    <t>30/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Scl-70 Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Scl-70 Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Scl-70 Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Ribosomal P KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250904</t>
-  </si>
-  <si>
-    <t>03/09/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Ribosomal P  Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Ribosomal P Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Ribosomal P Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>PCNA KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250822</t>
-  </si>
-  <si>
-    <t>21/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>PCNA Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>PCNA Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>PCNA Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>PM-Scl KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250921</t>
-  </si>
-  <si>
-    <t>20/09/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>PM-Scl Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>PM-Scl  Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>PM-Scl  Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Histone KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250902</t>
-  </si>
-  <si>
-    <t>01/09/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Histone  Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Histone  Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Histone Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>CENP-B KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250908</t>
-  </si>
-  <si>
-    <t>07/09/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CENP-B Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>CENP-B  Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>CENP-B  Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Nucleosome KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>Nucleosome Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Nucleosome Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>Nucleosome Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>GBM KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250923</t>
-  </si>
-  <si>
-    <t>22/09/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>GBM Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>GBM Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>GBM Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>gp210 KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>gp210 Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>gp210 Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>gp210 Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>sp100 KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>sp100 Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>sp100 Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>sp100 Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>LKM-1 Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>LKM-1 Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>LC-1 KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>LC-1 Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>LC-1 Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>LC-1 Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>SLA/LP  KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250821</t>
-  </si>
-  <si>
-    <t>20/08/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>SLA/LP Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>SLA/LP Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>SLA/LP Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF IgA Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF IgA  Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF IgA  Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF IgG KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250630</t>
-  </si>
-  <si>
-    <t>29/06/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>RF IgG Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF IgG  Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF IgG  Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF IgM KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>RF IgM Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF IgM Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF IgM Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF Screen  KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>RF Screen Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF Screen Control level 1 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>RF Screen Control level 2 BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>CCP KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>EVA 20250812</t>
-  </si>
-  <si>
-    <t>CCP  Calibrator Set BioCLIA HOB</t>
-  </si>
-  <si>
-    <t>hs-cTnI Calibrator 2ml Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>02/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Growth hormone kit with cal 2×50T Cl900i Mindray</t>
-  </si>
-  <si>
-    <t>RF IgA KIT BioCLIA 50 T HOB</t>
-  </si>
-  <si>
-    <t>Apo A 1 Kit 10T Mispa i3</t>
-  </si>
-  <si>
-    <t>EVA 32503263</t>
-  </si>
-  <si>
-    <t>30/11/2025 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Cuvette BS230 (120) Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>Cuvette BS230 (20) Chemistry Mindray</t>
-  </si>
-  <si>
-    <t>TDR ONE -96 10T Enterobacteriaceae mindray</t>
-  </si>
-  <si>
-    <t>20251121</t>
-  </si>
-  <si>
-    <t>20/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TDR STR -96 10T Streptococcus mindray</t>
-  </si>
-  <si>
-    <t>20251031</t>
-  </si>
-  <si>
-    <t>30/10/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TDR STAPH -96 10T Micrococcaceae including Staphylococcaceae mindray</t>
-  </si>
-  <si>
-    <t>20251112</t>
-  </si>
-  <si>
-    <t>TDR NH -96 10T Neisseria Haemophilus mindray</t>
-  </si>
-  <si>
-    <t>20251106</t>
-  </si>
-  <si>
-    <t>05/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>TDR NF -96 10T Non-fermentative bacteria  mindray</t>
-  </si>
-  <si>
-    <t>20251111</t>
-  </si>
-  <si>
-    <t>TDR YEAST -96 10T Yeast- like fungi  mindray</t>
-  </si>
-  <si>
-    <t>20250920</t>
-  </si>
-  <si>
-    <t>Aerobic bottle (TDR Resin Aerobic)25 bottles mindray</t>
-  </si>
-  <si>
-    <t>BCBOKK-1</t>
-  </si>
-  <si>
-    <t>Anaerobic bottle (TDR Resin Aerobic)25 bottles mindray</t>
-  </si>
-  <si>
-    <t>BCBOKJ-1</t>
-  </si>
-  <si>
-    <t>09/11/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Lysing solution 50ml mindray</t>
-  </si>
-  <si>
-    <t>2024091051</t>
-  </si>
-  <si>
-    <t>09/09/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Sheath fluid solution 5L mindray</t>
-  </si>
-  <si>
-    <t>2025030151</t>
-  </si>
-  <si>
-    <t>28/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>2025031151</t>
-  </si>
-  <si>
-    <t>Urea U.V kit 100T Agappe</t>
-  </si>
-  <si>
-    <t>32503128</t>
-  </si>
-  <si>
-    <t>31/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HBA1C 100 T كت مسبا</t>
-  </si>
-  <si>
-    <t>32511257</t>
-  </si>
-  <si>
-    <t>CRP 100 T كت مسبا</t>
-  </si>
-  <si>
-    <t>32511084</t>
-  </si>
-  <si>
-    <t>CD57 APC 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A33AA3</t>
-  </si>
-  <si>
-    <t>CD15 PE  100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A50AE4</t>
-  </si>
-  <si>
-    <t>CD56 PE-Cy7 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A192A2T1</t>
-  </si>
-  <si>
-    <t>CD25 APC 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A156SA1</t>
-  </si>
-  <si>
-    <t>25/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>CD16 FITC 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A14AF6</t>
-  </si>
-  <si>
-    <t>CD2 PE-Cy7 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A2S2T6</t>
-  </si>
-  <si>
-    <t>CD71 APC-Cy7 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A31S4T2</t>
-  </si>
-  <si>
-    <t>MPO FITC 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A123AF2</t>
-  </si>
-  <si>
-    <t>CD103 PE 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A331SE1</t>
-  </si>
-  <si>
-    <t>Anti-Lambda Light Chain PE 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A66AE10</t>
-  </si>
-  <si>
-    <t>CD1a FITC 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A115AF1</t>
-  </si>
-  <si>
-    <t>23/01/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>Anti-Kappa Light Chain FITC 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A48SF11</t>
-  </si>
-  <si>
-    <t>CD64 FITC 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A145AF4</t>
-  </si>
-  <si>
-    <t>CD81 APC-Cy7 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A332S4T1</t>
-  </si>
-  <si>
-    <t>CD30 FITC 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A221SF2</t>
-  </si>
-  <si>
-    <t>CD8 APC-Cy7 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A109S4T21</t>
-  </si>
-  <si>
-    <t>CD43 APC-Cy7 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A168A4T1</t>
-  </si>
-  <si>
-    <t>CD20 mFluor450 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A37A4F3</t>
-  </si>
-  <si>
-    <t>CD73 mFluor450 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A99A4F1</t>
-  </si>
-  <si>
-    <t>02/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>HLA-DR mFluor450 100Tests Caprico</t>
-  </si>
-  <si>
-    <t>EVA A32A4F4</t>
-  </si>
-  <si>
-    <t>Kappa/Lambda Free Light Chain Level 1(1 ml ) Mispa i3</t>
-  </si>
-  <si>
-    <t>32512260</t>
   </si>
   <si>
     <t>Kappa/Lambda Free Light Chain Level 2(1 ml ) Mispa i3</t>
@@ -3795,7 +3909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C571"/>
+  <dimension ref="A1:C590"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="30" customWidth="1"/>
@@ -3858,95 +3972,95 @@
     </row>
     <row r="6" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>39</v>
@@ -3957,29 +4071,29 @@
     </row>
     <row r="15" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>47</v>
@@ -3990,46 +4104,46 @@
     </row>
     <row r="18" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="C18" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="C20" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4040,45 +4154,45 @@
         <v>61</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>71</v>
@@ -4089,79 +4203,79 @@
     </row>
     <row r="27" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>73</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4169,10 +4283,10 @@
         <v>85</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4183,51 +4297,51 @@
         <v>89</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4265,68 +4379,68 @@
     </row>
     <row r="43" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4370,12 +4484,12 @@
         <v>130</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>132</v>
@@ -4386,84 +4500,84 @@
     </row>
     <row r="54" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>147</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>149</v>
@@ -4474,18 +4588,18 @@
     </row>
     <row r="62" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>154</v>
@@ -4496,7 +4610,7 @@
     </row>
     <row r="64" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>156</v>
@@ -4535,62 +4649,62 @@
         <v>164</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>166</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>40</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4601,12 +4715,12 @@
         <v>177</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>178</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>179</v>
@@ -4650,13 +4764,13 @@
     </row>
     <row r="78" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="C78" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4667,128 +4781,128 @@
         <v>192</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>40</v>
+        <v>193</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>194</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>198</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>155</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>155</v>
+        <v>205</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>206</v>
+        <v>160</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>208</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>210</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>215</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4799,18 +4913,18 @@
         <v>217</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>178</v>
+        <v>218</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4821,23 +4935,23 @@
         <v>222</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="C94" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>227</v>
@@ -4848,76 +4962,76 @@
     </row>
     <row r="96" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>234</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>244</v>
@@ -4925,46 +5039,46 @@
     </row>
     <row r="103" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C103" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="C105" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>0</v>
+      <c r="C106" s="4" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4972,65 +5086,65 @@
         <v>255</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C107" s="3" t="s">
-        <v>0</v>
+        <v>256</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>258</v>
+        <v>50</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="C110" s="4" t="s">
         <v>263</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C111" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>48</v>
+        <v>0</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5038,197 +5152,197 @@
         <v>267</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>270</v>
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>273</v>
+        <v>0</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C115" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="B115" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>228</v>
+        <v>277</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>183</v>
+        <v>280</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>283</v>
-      </c>
-      <c r="B119" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>288</v>
+        <v>167</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B121" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B121" s="3" t="s">
-        <v>289</v>
-      </c>
       <c r="C121" s="5" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>297</v>
-      </c>
-      <c r="B125" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>114</v>
+        <v>300</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C127" s="5" t="s">
         <v>302</v>
-      </c>
-      <c r="B127" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>307</v>
+        <v>233</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>0</v>
+        <v>306</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C130" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5244,95 +5358,95 @@
     </row>
     <row r="132" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B132" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="C132" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>0</v>
+        <v>319</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>93</v>
+        <v>323</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>43</v>
+        <v>325</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C137" s="3" t="s">
-        <v>0</v>
+        <v>327</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>324</v>
+        <v>131</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C139" s="3" t="s">
-        <v>0</v>
+        <v>330</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>0</v>
@@ -5343,222 +5457,222 @@
     </row>
     <row r="141" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>329</v>
+        <v>0</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C144" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>341</v>
+        <v>0</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="C146" s="4" t="s">
-        <v>344</v>
+        <v>95</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C147" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="B147" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>0</v>
+        <v>347</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>351</v>
+        <v>0</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>108</v>
+        <v>351</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>356</v>
+        <v>0</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C152" s="4" t="s">
-        <v>114</v>
+        <v>0</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>359</v>
+        <v>34</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B154" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C154" s="4" t="s">
         <v>358</v>
-      </c>
-      <c r="C154" s="4" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C156" s="4" t="s">
         <v>364</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="C156" s="4" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C157" s="5" t="s">
         <v>367</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>371</v>
+        <v>133</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C159" s="5" t="s">
         <v>372</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C160" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5580,70 +5694,70 @@
         <v>380</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>14</v>
+        <v>381</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>307</v>
+        <v>0</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>355</v>
+        <v>384</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>386</v>
+        <v>111</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>391</v>
+        <v>117</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>392</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>393</v>
@@ -5654,7 +5768,7 @@
         <v>394</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>353</v>
+        <v>392</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>395</v>
@@ -5662,10 +5776,10 @@
     </row>
     <row r="170" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>397</v>
@@ -5698,18 +5812,18 @@
         <v>404</v>
       </c>
       <c r="B173" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C173" s="5" t="s">
         <v>405</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B174" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>355</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>408</v>
@@ -5720,10 +5834,10 @@
         <v>409</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>307</v>
+        <v>66</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5731,252 +5845,252 @@
         <v>410</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>175</v>
+        <v>412</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>377</v>
+        <v>414</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>412</v>
+        <v>14</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>152</v>
+        <v>331</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>355</v>
+        <v>389</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>353</v>
+        <v>419</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>278</v>
+        <v>423</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>386</v>
+        <v>425</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>385</v>
+        <v>430</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>355</v>
+        <v>433</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>65</v>
+        <v>434</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>385</v>
+        <v>439</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>434</v>
+        <v>411</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>435</v>
+        <v>331</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>438</v>
+        <v>180</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>439</v>
+        <v>411</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>441</v>
+        <v>419</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>442</v>
+        <v>157</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>444</v>
+        <v>389</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>447</v>
+        <v>387</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>40</v>
+        <v>451</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>108</v>
+        <v>300</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>452</v>
+        <v>420</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>453</v>
+        <v>389</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5984,18 +6098,18 @@
         <v>455</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>456</v>
+        <v>419</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>123</v>
+        <v>457</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>458</v>
+        <v>419</v>
       </c>
       <c r="C200" s="4" t="s">
         <v>459</v>
@@ -6006,29 +6120,29 @@
         <v>460</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>461</v>
+        <v>389</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>462</v>
+        <v>69</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C202" s="4" t="s">
         <v>463</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="C202" s="4" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>466</v>
+        <v>419</v>
       </c>
       <c r="C203" s="5" t="s">
         <v>465</v>
@@ -6036,222 +6150,222 @@
     </row>
     <row r="204" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C204" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C204" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B205" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="B205" s="3" t="s">
-        <v>353</v>
-      </c>
       <c r="C205" s="5" t="s">
-        <v>72</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>353</v>
+        <v>471</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>377</v>
+        <v>473</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>133</v>
+        <v>479</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>133</v>
+        <v>42</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C211" s="3" t="s">
-        <v>0</v>
+        <v>483</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>484</v>
+        <v>126</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>78</v>
+        <v>496</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>38</v>
+        <v>499</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C219" s="5" t="s">
-        <v>496</v>
+        <v>0</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>498</v>
+        <v>387</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>499</v>
+        <v>76</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>501</v>
+        <v>387</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>503</v>
+        <v>411</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>43</v>
+        <v>508</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6259,26 +6373,26 @@
         <v>506</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>508</v>
+        <v>138</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B225" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="B225" s="3" t="s">
-        <v>510</v>
-      </c>
       <c r="C225" s="5" t="s">
-        <v>511</v>
+        <v>138</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>0</v>
@@ -6289,35 +6403,35 @@
     </row>
     <row r="227" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B227" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="B227" s="3" t="s">
-        <v>514</v>
-      </c>
       <c r="C227" s="5" t="s">
-        <v>391</v>
+        <v>74</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>516</v>
+        <v>74</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B229" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="C229" s="5" t="s">
         <v>517</v>
-      </c>
-      <c r="C229" s="5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6336,10 +6450,10 @@
         <v>521</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>385</v>
+        <v>522</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>522</v>
+        <v>83</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6347,230 +6461,230 @@
         <v>523</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>385</v>
+        <v>524</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>178</v>
+        <v>40</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>527</v>
+        <v>387</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>194</v>
+        <v>529</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>200</v>
+        <v>532</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>105</v>
+        <v>541</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="C241" s="5" t="s">
-        <v>543</v>
+        <v>0</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>546</v>
+        <v>425</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>548</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>549</v>
+        <v>375</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>552</v>
+        <v>131</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>178</v>
+        <v>552</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>556</v>
+        <v>419</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>559</v>
+        <v>419</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>264</v>
+        <v>554</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>562</v>
+        <v>183</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>565</v>
+        <v>199</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>8</v>
+        <v>205</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6578,21 +6692,21 @@
         <v>567</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>363</v>
+        <v>117</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>573</v>
+        <v>108</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6600,109 +6714,109 @@
         <v>571</v>
       </c>
       <c r="B255" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>324</v>
+        <v>574</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="B257" s="3" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>26</v>
+        <v>574</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>258</v>
+        <v>574</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>584</v>
-      </c>
       <c r="C260" s="4" t="s">
-        <v>383</v>
+        <v>582</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="C261" s="5" t="s">
         <v>585</v>
-      </c>
-      <c r="B261" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="C261" s="5" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>116</v>
+        <v>183</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="C263" s="5" t="s">
         <v>590</v>
-      </c>
-      <c r="B263" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="C263" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>592</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>516</v>
+        <v>283</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6713,106 +6827,106 @@
         <v>594</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>378</v>
+        <v>595</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>48</v>
+        <v>598</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>599</v>
+        <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B269" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C269" s="5" t="s">
         <v>602</v>
-      </c>
-      <c r="C269" s="5" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>603</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>604</v>
+        <v>397</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>605</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>108</v>
+        <v>606</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>604</v>
+        <v>92</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>608</v>
+        <v>351</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>611</v>
+        <v>28</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6823,7 +6937,7 @@
         <v>613</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>188</v>
+        <v>277</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6839,84 +6953,84 @@
     </row>
     <row r="277" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="B277" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="B277" s="3" t="s">
-        <v>618</v>
-      </c>
       <c r="C277" s="5" t="s">
-        <v>315</v>
+        <v>417</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>619</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>620</v>
+        <v>427</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>621</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>622</v>
+        <v>479</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B280" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B280" s="1" t="s">
+      <c r="C280" s="4" t="s">
         <v>624</v>
-      </c>
-      <c r="C280" s="4" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>626</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>562</v>
+        <v>119</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>625</v>
+        <v>92</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>541</v>
+        <v>66</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>631</v>
@@ -6927,750 +7041,750 @@
     </row>
     <row r="285" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>634</v>
+        <v>412</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>474</v>
+        <v>50</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>616</v>
+        <v>639</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>625</v>
+        <v>641</v>
       </c>
     </row>
     <row r="289" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>642</v>
+        <v>111</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B290" s="1" t="s">
+      <c r="C290" s="4" t="s">
         <v>644</v>
-      </c>
-      <c r="C290" s="4" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>648</v>
+        <v>111</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>652</v>
+        <v>637</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>654</v>
+        <v>302</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>459</v>
+        <v>650</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>658</v>
+        <v>193</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>206</v>
+        <v>655</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>663</v>
+        <v>339</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>667</v>
+        <v>656</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>673</v>
+        <v>662</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>415</v>
+        <v>595</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>459</v>
+        <v>128</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>51</v>
+        <v>671</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>686</v>
+        <v>508</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>689</v>
+        <v>655</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C308" s="1" t="s">
-        <v>0</v>
+        <v>678</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>664</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C309" s="3" t="s">
-        <v>0</v>
+        <v>680</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C310" s="1" t="s">
-        <v>0</v>
+        <v>683</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>429</v>
+        <v>687</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>702</v>
+        <v>493</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>707</v>
+        <v>211</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>51</v>
+        <v>708</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C320" s="1" t="s">
-        <v>0</v>
+        <v>710</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>711</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C321" s="3" t="s">
-        <v>0</v>
+        <v>713</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>0</v>
+        <v>715</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>721</v>
+        <v>493</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C324" s="1" t="s">
-        <v>0</v>
+        <v>719</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>43</v>
+        <v>728</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="C328" s="4" t="s">
-        <v>733</v>
+        <v>0</v>
+      </c>
+      <c r="C328" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="C329" s="5" t="s">
-        <v>105</v>
+        <v>0</v>
+      </c>
+      <c r="C329" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="C330" s="4" t="s">
-        <v>738</v>
+        <v>0</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>741</v>
+        <v>463</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>741</v>
+        <v>746</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>741</v>
+        <v>53</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="C340" s="4" t="s">
-        <v>746</v>
+        <v>0</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="C341" s="5" t="s">
-        <v>741</v>
+        <v>0</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="C342" s="4" t="s">
-        <v>741</v>
+        <v>0</v>
+      </c>
+      <c r="C342" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>741</v>
+        <v>760</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="C344" s="4" t="s">
-        <v>768</v>
+        <v>0</v>
+      </c>
+      <c r="C344" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>741</v>
+        <v>767</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>741</v>
+        <v>45</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>741</v>
+        <v>772</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>778</v>
+        <v>108</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>768</v>
+        <v>777</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C351" s="5" t="s">
-        <v>741</v>
+        <v>780</v>
       </c>
     </row>
     <row r="352" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>741</v>
+        <v>780</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7678,43 +7792,43 @@
         <v>783</v>
       </c>
       <c r="B353" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="C353" s="5" t="s">
         <v>785</v>
-      </c>
-      <c r="C353" s="5" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="B354" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="B354" s="1" t="s">
-        <v>787</v>
-      </c>
       <c r="C354" s="4" t="s">
-        <v>741</v>
+        <v>785</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="B355" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="B355" s="3" t="s">
-        <v>789</v>
-      </c>
       <c r="C355" s="5" t="s">
-        <v>741</v>
+        <v>780</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B356" s="1" t="s">
         <v>790</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>746</v>
+        <v>780</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7725,7 +7839,7 @@
         <v>792</v>
       </c>
       <c r="C357" s="5" t="s">
-        <v>741</v>
+        <v>780</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7736,7 +7850,7 @@
         <v>794</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>741</v>
+        <v>780</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7747,18 +7861,18 @@
         <v>796</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>48</v>
+        <v>780</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>798</v>
+        <v>785</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7769,29 +7883,29 @@
         <v>800</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>801</v>
+        <v>780</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B362" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="B362" s="1" t="s">
-        <v>803</v>
-      </c>
       <c r="C362" s="4" t="s">
-        <v>433</v>
+        <v>780</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>804</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>433</v>
+        <v>780</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7802,18 +7916,18 @@
         <v>806</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>155</v>
+        <v>807</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="C365" s="5" t="s">
         <v>807</v>
-      </c>
-      <c r="B365" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="C365" s="5" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7824,7 +7938,7 @@
         <v>811</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>148</v>
+        <v>780</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7835,249 +7949,249 @@
         <v>813</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>814</v>
+        <v>780</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="B368" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="B368" s="1" t="s">
-        <v>816</v>
-      </c>
       <c r="C368" s="4" t="s">
-        <v>817</v>
+        <v>780</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>120</v>
+        <v>817</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>825</v>
+        <v>780</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>828</v>
+        <v>780</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>546</v>
+        <v>785</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>833</v>
+        <v>780</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>835</v>
+        <v>828</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>836</v>
+        <v>780</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>839</v>
+        <v>785</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>842</v>
+        <v>780</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>843</v>
+        <v>832</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>845</v>
+        <v>780</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>846</v>
+        <v>834</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>847</v>
+        <v>835</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>848</v>
+        <v>50</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>849</v>
+        <v>834</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C380" s="1" t="s">
-        <v>0</v>
+        <v>836</v>
+      </c>
+      <c r="C380" s="4" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C381" s="3" t="s">
-        <v>0</v>
+        <v>839</v>
+      </c>
+      <c r="C381" s="5" t="s">
+        <v>840</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C382" s="1" t="s">
-        <v>0</v>
+        <v>842</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C383" s="3" t="s">
-        <v>0</v>
+        <v>843</v>
+      </c>
+      <c r="C383" s="5" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>806</v>
+        <v>845</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>808</v>
+        <v>847</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>809</v>
+        <v>848</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>811</v>
+        <v>850</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>811</v>
+        <v>852</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>148</v>
+        <v>853</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>811</v>
+        <v>855</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>148</v>
+        <v>856</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="B389" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="B389" s="3" t="s">
-        <v>813</v>
-      </c>
       <c r="C389" s="5" t="s">
-        <v>814</v>
+        <v>123</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8085,1973 +8199,2182 @@
         <v>859</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>813</v>
+        <v>860</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>814</v>
+        <v>861</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>813</v>
+        <v>863</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>814</v>
+        <v>864</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>395</v>
+        <v>867</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>395</v>
+        <v>579</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>866</v>
+        <v>872</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>868</v>
+        <v>874</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>520</v>
+        <v>875</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>816</v>
+        <v>877</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>817</v>
+        <v>878</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>870</v>
+        <v>879</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>819</v>
+        <v>880</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>120</v>
+        <v>881</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>871</v>
+        <v>882</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>819</v>
+        <v>883</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>120</v>
+        <v>884</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>872</v>
+        <v>885</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>819</v>
+        <v>886</v>
       </c>
       <c r="C399" s="5" t="s">
-        <v>120</v>
+        <v>887</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>821</v>
+        <v>889</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>822</v>
+        <v>890</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="C401" s="5" t="s">
-        <v>876</v>
+        <v>0</v>
+      </c>
+      <c r="C401" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>877</v>
+        <v>892</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="C402" s="4" t="s">
-        <v>879</v>
+        <v>0</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>880</v>
+        <v>893</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="C403" s="5" t="s">
-        <v>825</v>
+        <v>0</v>
+      </c>
+      <c r="C403" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>881</v>
+        <v>894</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="C404" s="4" t="s">
-        <v>825</v>
+        <v>0</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>882</v>
+        <v>895</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>824</v>
+        <v>845</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>825</v>
+        <v>160</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>883</v>
+        <v>896</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>828</v>
+        <v>848</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>884</v>
+        <v>897</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>827</v>
+        <v>850</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>828</v>
+        <v>153</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>885</v>
+        <v>898</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>827</v>
+        <v>850</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>828</v>
+        <v>153</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>886</v>
+        <v>899</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>887</v>
+        <v>850</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>546</v>
+        <v>153</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>886</v>
+        <v>900</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>888</v>
+        <v>852</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>546</v>
+        <v>853</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>890</v>
+        <v>852</v>
       </c>
       <c r="C411" s="5" t="s">
-        <v>833</v>
+        <v>853</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>833</v>
+        <v>853</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>830</v>
+        <v>904</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>546</v>
+        <v>429</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>892</v>
+        <v>905</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>841</v>
+        <v>904</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>842</v>
+        <v>429</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>893</v>
+        <v>906</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>841</v>
+        <v>907</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>842</v>
+        <v>908</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>894</v>
+        <v>909</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>841</v>
+        <v>910</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>842</v>
+        <v>552</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>895</v>
+        <v>911</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>838</v>
+        <v>855</v>
       </c>
       <c r="C417" s="5" t="s">
-        <v>839</v>
+        <v>856</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
-        <v>896</v>
+        <v>912</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>839</v>
+        <v>123</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>897</v>
+        <v>913</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>839</v>
+        <v>123</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>898</v>
+        <v>914</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>899</v>
+        <v>858</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>900</v>
+        <v>123</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>901</v>
+        <v>915</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>899</v>
+        <v>860</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>900</v>
+        <v>861</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>902</v>
+        <v>916</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>835</v>
+        <v>917</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>836</v>
+        <v>918</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>903</v>
+        <v>919</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>835</v>
+        <v>920</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>836</v>
+        <v>921</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>904</v>
+        <v>922</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>835</v>
+        <v>863</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>836</v>
+        <v>864</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>905</v>
+        <v>923</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>906</v>
+        <v>863</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>907</v>
+        <v>864</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>908</v>
+        <v>924</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>906</v>
+        <v>863</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>907</v>
+        <v>864</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>909</v>
+        <v>925</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>906</v>
+        <v>866</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>907</v>
+        <v>867</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
-        <v>910</v>
+        <v>926</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>0</v>
+        <v>866</v>
+      </c>
+      <c r="C428" s="4" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>911</v>
+        <v>927</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>912</v>
+        <v>866</v>
       </c>
       <c r="C429" s="5" t="s">
-        <v>913</v>
+        <v>867</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>914</v>
+        <v>928</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>915</v>
+        <v>929</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>916</v>
+        <v>579</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>915</v>
+        <v>930</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>324</v>
+        <v>579</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>918</v>
+        <v>931</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>919</v>
+        <v>932</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>920</v>
+        <v>872</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>921</v>
+        <v>931</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>922</v>
+        <v>871</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>809</v>
+        <v>872</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>923</v>
+        <v>933</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>924</v>
+        <v>869</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>162</v>
+        <v>579</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>925</v>
+        <v>934</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>926</v>
+        <v>880</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>278</v>
+        <v>881</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>928</v>
+        <v>880</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>341</v>
+        <v>881</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="B437" s="3" t="s">
-        <v>930</v>
+        <v>880</v>
       </c>
       <c r="C437" s="5" t="s">
-        <v>557</v>
+        <v>881</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>932</v>
+        <v>877</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>933</v>
+        <v>878</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>934</v>
+        <v>877</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>935</v>
+        <v>878</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A440" s="1" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>937</v>
+        <v>877</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>935</v>
+        <v>878</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>906</v>
+        <v>874</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>907</v>
+        <v>875</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A444" s="1" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>827</v>
+        <v>874</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>828</v>
+        <v>875</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>827</v>
+        <v>874</v>
       </c>
       <c r="C445" s="5" t="s">
-        <v>828</v>
+        <v>875</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>827</v>
+        <v>948</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>828</v>
+        <v>949</v>
       </c>
     </row>
     <row r="447" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>827</v>
+        <v>948</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>828</v>
+        <v>949</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>949</v>
-      </c>
-      <c r="C449" s="5" t="s">
-        <v>947</v>
+        <v>0</v>
+      </c>
+      <c r="C449" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>949</v>
+        <v>954</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>951</v>
+        <v>956</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>947</v>
+        <v>958</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>954</v>
+        <v>351</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>955</v>
+        <v>960</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>954</v>
+        <v>848</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>953</v>
+        <v>963</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>954</v>
+        <v>167</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>954</v>
+        <v>300</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>960</v>
+        <v>375</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>959</v>
+        <v>969</v>
       </c>
       <c r="C457" s="5" t="s">
-        <v>960</v>
+        <v>590</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>959</v>
+        <v>971</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>960</v>
+        <v>972</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>959</v>
+        <v>973</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>960</v>
+        <v>974</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>964</v>
+        <v>975</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
-        <v>967</v>
+        <v>977</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>968</v>
+        <v>978</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
-        <v>969</v>
+        <v>979</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>965</v>
+        <v>948</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>966</v>
+        <v>949</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>971</v>
+        <v>866</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>972</v>
+        <v>867</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>971</v>
+        <v>866</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>972</v>
+        <v>867</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>971</v>
+        <v>866</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>972</v>
+        <v>867</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>971</v>
+        <v>866</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>972</v>
+        <v>867</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="B469" s="3" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="C469" s="5" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
-        <v>980</v>
+        <v>989</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
-        <v>981</v>
+        <v>990</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
-        <v>982</v>
+        <v>991</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>983</v>
+        <v>992</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>984</v>
+        <v>993</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
-        <v>985</v>
+        <v>994</v>
       </c>
       <c r="B473" s="3" t="s">
-        <v>983</v>
+        <v>992</v>
       </c>
       <c r="C473" s="5" t="s">
-        <v>984</v>
+        <v>993</v>
       </c>
     </row>
     <row r="474" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A474" s="1" t="s">
-        <v>986</v>
+        <v>995</v>
       </c>
       <c r="B474" s="1" t="s">
-        <v>983</v>
+        <v>992</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>984</v>
+        <v>993</v>
       </c>
     </row>
     <row r="475" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
-        <v>987</v>
+        <v>996</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>983</v>
+        <v>992</v>
       </c>
       <c r="C475" s="5" t="s">
-        <v>984</v>
+        <v>993</v>
       </c>
     </row>
     <row r="476" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A476" s="1" t="s">
-        <v>988</v>
+        <v>997</v>
       </c>
       <c r="B476" s="1" t="s">
-        <v>899</v>
+        <v>998</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>900</v>
+        <v>999</v>
       </c>
     </row>
     <row r="477" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
-        <v>989</v>
+        <v>1000</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>899</v>
+        <v>998</v>
       </c>
       <c r="C477" s="5" t="s">
-        <v>900</v>
+        <v>999</v>
       </c>
     </row>
     <row r="478" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
-        <v>990</v>
+        <v>1001</v>
       </c>
       <c r="B478" s="1" t="s">
-        <v>899</v>
+        <v>998</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>900</v>
+        <v>999</v>
       </c>
     </row>
     <row r="479" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
-        <v>991</v>
+        <v>1002</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>899</v>
+        <v>998</v>
       </c>
       <c r="C479" s="5" t="s">
-        <v>900</v>
+        <v>999</v>
       </c>
     </row>
     <row r="480" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A480" s="1" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="481" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A481" s="3" t="s">
-        <v>995</v>
+        <v>1006</v>
       </c>
       <c r="B481" s="3" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="C481" s="5" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="482" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
-        <v>996</v>
+        <v>1007</v>
       </c>
       <c r="B482" s="1" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="483" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
-        <v>997</v>
+        <v>1008</v>
       </c>
       <c r="B483" s="3" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="C483" s="5" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="484" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
       <c r="B484" s="1" t="s">
-        <v>813</v>
+        <v>1010</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>814</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="485" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
-        <v>999</v>
+        <v>1012</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>813</v>
+        <v>1010</v>
       </c>
       <c r="C485" s="5" t="s">
-        <v>814</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="486" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
-        <v>1000</v>
+        <v>1013</v>
       </c>
       <c r="B486" s="1" t="s">
-        <v>813</v>
+        <v>1010</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>814</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="487" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
-        <v>1001</v>
+        <v>1014</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>813</v>
+        <v>1010</v>
       </c>
       <c r="C487" s="5" t="s">
-        <v>814</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="488" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A488" s="1" t="s">
-        <v>1002</v>
+        <v>1015</v>
       </c>
       <c r="B488" s="1" t="s">
-        <v>862</v>
+        <v>1016</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>395</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="489" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
-        <v>1003</v>
+        <v>1018</v>
       </c>
       <c r="B489" s="3" t="s">
-        <v>862</v>
+        <v>1016</v>
       </c>
       <c r="C489" s="5" t="s">
-        <v>395</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="490" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
-        <v>1004</v>
+        <v>1019</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>862</v>
+        <v>1016</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>395</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="491" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>1005</v>
+        <v>1020</v>
       </c>
       <c r="B491" s="3" t="s">
-        <v>862</v>
+        <v>1016</v>
       </c>
       <c r="C491" s="5" t="s">
-        <v>395</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="492" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
-        <v>1006</v>
+        <v>1021</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>965</v>
+        <v>1022</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>966</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>1007</v>
+        <v>1024</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>965</v>
+        <v>1022</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>966</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>1008</v>
+        <v>1025</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>811</v>
+        <v>1022</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>148</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>1009</v>
+        <v>1026</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>811</v>
+        <v>1022</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>148</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
-        <v>1010</v>
+        <v>1027</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>811</v>
+        <v>941</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>148</v>
+        <v>942</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A497" s="3" t="s">
-        <v>1011</v>
+        <v>1028</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>811</v>
+        <v>941</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>148</v>
+        <v>942</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A498" s="1" t="s">
-        <v>1012</v>
+        <v>1029</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>1013</v>
+        <v>941</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>1014</v>
+        <v>942</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
-        <v>1015</v>
+        <v>1030</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>1013</v>
+        <v>941</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>1014</v>
+        <v>942</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
-        <v>1016</v>
+        <v>1031</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1013</v>
+        <v>1032</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>1014</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
-        <v>1017</v>
+        <v>1034</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>1013</v>
+        <v>1032</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>1014</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>1018</v>
+        <v>1035</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>959</v>
+        <v>1032</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>960</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>1019</v>
+        <v>1036</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>959</v>
+        <v>1032</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>960</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>1020</v>
+        <v>1037</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>959</v>
+        <v>852</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>960</v>
+        <v>853</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
-        <v>1021</v>
+        <v>1038</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>1022</v>
+        <v>852</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>1023</v>
+        <v>853</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>1024</v>
+        <v>1039</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>1022</v>
+        <v>852</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>1023</v>
+        <v>853</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>1025</v>
+        <v>1040</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>1022</v>
+        <v>852</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>1023</v>
+        <v>853</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>1026</v>
+        <v>1041</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>1022</v>
+        <v>904</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>1023</v>
+        <v>429</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>1027</v>
+        <v>1042</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>993</v>
+        <v>904</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>994</v>
+        <v>429</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>1028</v>
+        <v>1043</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>993</v>
+        <v>904</v>
       </c>
       <c r="C510" s="4" t="s">
-        <v>994</v>
+        <v>429</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>1029</v>
+        <v>1044</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>993</v>
+        <v>904</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>994</v>
+        <v>429</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>1030</v>
+        <v>1045</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>1031</v>
+        <v>1046</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
-        <v>1032</v>
+        <v>1047</v>
       </c>
       <c r="B514" s="1" t="s">
-        <v>993</v>
+        <v>850</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>994</v>
+        <v>153</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
-        <v>1033</v>
+        <v>1048</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>993</v>
+        <v>850</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>994</v>
+        <v>153</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A516" s="1" t="s">
-        <v>1034</v>
+        <v>1049</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>993</v>
+        <v>850</v>
       </c>
       <c r="C516" s="4" t="s">
-        <v>994</v>
+        <v>153</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
-        <v>1035</v>
+        <v>1050</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>1036</v>
+        <v>850</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>686</v>
+        <v>153</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
-        <v>1037</v>
+        <v>1051</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1036</v>
+        <v>1052</v>
       </c>
       <c r="C518" s="4" t="s">
-        <v>686</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
-        <v>1038</v>
+        <v>1054</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>377</v>
+        <v>1052</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>1039</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>1040</v>
+        <v>1055</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>915</v>
+        <v>1052</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>417</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
-        <v>1041</v>
+        <v>1056</v>
       </c>
       <c r="B521" s="3" t="s">
-        <v>959</v>
+        <v>1052</v>
       </c>
       <c r="C521" s="5" t="s">
-        <v>960</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A522" s="1" t="s">
-        <v>1042</v>
+        <v>1057</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>1043</v>
+        <v>998</v>
       </c>
       <c r="C522" s="4" t="s">
-        <v>1044</v>
+        <v>999</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A523" s="3" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C523" s="3" t="s">
-        <v>0</v>
+        <v>998</v>
+      </c>
+      <c r="C523" s="5" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A524" s="1" t="s">
-        <v>1046</v>
+        <v>1059</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C524" s="1" t="s">
-        <v>0</v>
+        <v>998</v>
+      </c>
+      <c r="C524" s="4" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>1047</v>
+        <v>1060</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>1049</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>1050</v>
+        <v>1063</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1051</v>
+        <v>1061</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>1052</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>152</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>1055</v>
+        <v>1065</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1056</v>
+        <v>1061</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>1057</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>1059</v>
+        <v>1032</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>185</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1061</v>
+        <v>1032</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>99</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>1063</v>
+        <v>1032</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>185</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
-        <v>1064</v>
+        <v>1069</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1065</v>
+        <v>1032</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>1066</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>1068</v>
+        <v>1032</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>1069</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1071</v>
+        <v>1032</v>
       </c>
       <c r="C534" s="4" t="s">
-        <v>1072</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B535" s="3" t="s">
-        <v>1073</v>
+        <v>1032</v>
       </c>
       <c r="C535" s="5" t="s">
-        <v>378</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A536" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1075</v>
+        <v>1032</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>1076</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>845</v>
+        <v>725</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="B538" s="1" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="C538" s="4" t="s">
-        <v>978</v>
+        <v>725</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>1082</v>
+        <v>411</v>
       </c>
       <c r="C539" s="5" t="s">
-        <v>573</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>1084</v>
+        <v>957</v>
       </c>
       <c r="C540" s="4" t="s">
-        <v>573</v>
+        <v>451</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>1086</v>
+        <v>998</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>1072</v>
+        <v>999</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>1091</v>
-      </c>
-      <c r="C543" s="5" t="s">
-        <v>573</v>
+        <v>0</v>
+      </c>
+      <c r="C543" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
-        <v>1092</v>
+        <v>1085</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>1093</v>
-      </c>
-      <c r="C544" s="4" t="s">
-        <v>573</v>
+        <v>0</v>
+      </c>
+      <c r="C544" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>1094</v>
+        <v>1086</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>1095</v>
+        <v>1087</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>573</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1097</v>
+        <v>1090</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>573</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>573</v>
+        <v>157</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>573</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>1104</v>
+        <v>190</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>573</v>
+        <v>102</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>573</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>573</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>465</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="554" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="C554" s="4" t="s">
-        <v>126</v>
+        <v>412</v>
       </c>
     </row>
     <row r="555" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="B555" s="3" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="C555" s="5" t="s">
-        <v>374</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="556" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="B556" s="1" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="C556" s="4" t="s">
-        <v>573</v>
+        <v>884</v>
       </c>
     </row>
     <row r="557" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="B557" s="3" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="C557" s="5" t="s">
-        <v>1121</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="558" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A558" s="1" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="B558" s="1" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="C558" s="4" t="s">
-        <v>573</v>
+        <v>606</v>
       </c>
     </row>
     <row r="559" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="B559" s="3" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="C559" s="5" t="s">
-        <v>920</v>
+        <v>606</v>
       </c>
     </row>
     <row r="560" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C560" s="4" t="s">
-        <v>920</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="561" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="B561" s="3" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="C561" s="5" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="562" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="B562" s="1" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="C562" s="4" t="s">
-        <v>1132</v>
+        <v>606</v>
       </c>
     </row>
     <row r="563" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="B563" s="3" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="C563" s="5" t="s">
-        <v>374</v>
+        <v>606</v>
       </c>
     </row>
     <row r="564" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A564" s="1" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="B564" s="1" t="s">
-        <v>337</v>
+        <v>1132</v>
       </c>
       <c r="C564" s="4" t="s">
-        <v>338</v>
+        <v>606</v>
       </c>
     </row>
     <row r="565" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="B565" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C565" s="3" t="s">
-        <v>0</v>
+        <v>1134</v>
+      </c>
+      <c r="C565" s="5" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="566" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="B566" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C566" s="1" t="s">
-        <v>0</v>
+        <v>1136</v>
+      </c>
+      <c r="C566" s="4" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="567" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B567" s="3" t="s">
         <v>1138</v>
       </c>
-      <c r="B567" s="3" t="s">
-        <v>1139</v>
-      </c>
       <c r="C567" s="5" t="s">
-        <v>465</v>
+        <v>606</v>
       </c>
     </row>
     <row r="568" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A568" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B568" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="B568" s="1" t="s">
+      <c r="C568" s="4" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A569" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B569" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C569" s="5" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A570" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C570" s="4" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A571" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B571" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A572" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C572" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A573" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B573" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C573" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A574" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C574" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A575" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B575" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C575" s="5" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A576" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B576" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C576" s="4" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A577" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B577" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C577" s="5" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A578" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B578" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C578" s="4" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A579" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B579" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C579" s="5" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A580" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B580" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C580" s="4" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A581" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B581" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C581" s="5" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A582" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B582" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C582" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A583" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B583" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C583" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A584" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B584" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C568" s="1" t="s">
+      <c r="C584" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
-    <row r="570" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
-    <row r="571" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="585" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A585" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B585" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C585" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A586" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C586" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A587" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B587" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C587" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="589" spans="1:3" ht="13.8" x14ac:dyDescent="0.3"/>
+    <row r="590" spans="1:3" ht="16.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/المواد.xlsx
+++ b/المواد.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="1173">
   <si>
     <t/>
   </si>
@@ -42,6 +42,12 @@
     <t>11/05/2025 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA  DT3VGX11</t>
+  </si>
+  <si>
+    <t>07/03/2027 12:00:00 ص</t>
+  </si>
+  <si>
     <t>EVA DT3VFX03</t>
   </si>
   <si>
@@ -171,9 +177,6 @@
     <t>EVA AAVGD58F</t>
   </si>
   <si>
-    <t>07/03/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>LH Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -234,12 +237,6 @@
     <t>TSH Kit 24T Afias Boditech</t>
   </si>
   <si>
-    <t>EVA  TSVFA91X</t>
-  </si>
-  <si>
-    <t>16/02/2027 12:00:00 ص</t>
-  </si>
-  <si>
     <t>EVA  TSVXB01X</t>
   </si>
   <si>
@@ -267,15 +264,12 @@
     <t>TNI PLUS Kit 24T Afias Boditech</t>
   </si>
   <si>
-    <t>EVA  TNVXD74X</t>
+    <t>EVA TNVXD74X</t>
   </si>
   <si>
     <t>07/05/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>EVA TNVXD74X</t>
-  </si>
-  <si>
     <t>B-HCG Kit 24T Afias Boditech</t>
   </si>
   <si>
@@ -318,9 +312,6 @@
     <t>14/01/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>EVA ACVED09E</t>
-  </si>
-  <si>
     <t>Anti-HCV Kit 25T iChroma Boditech</t>
   </si>
   <si>
@@ -357,6 +348,9 @@
     <t>11/02/2027 12:00:00 ص</t>
   </si>
   <si>
+    <t>EVA  DFSVGE05</t>
+  </si>
+  <si>
     <t>EVA DFSVFD12</t>
   </si>
   <si>
@@ -432,21 +426,18 @@
     <t>RF-IgM Kit 25T iChroma Boditech</t>
   </si>
   <si>
-    <t>EVA  RFVFH05EX</t>
+    <t>EVA  RFVHH09EX</t>
+  </si>
+  <si>
+    <t>06/04/2027 12:00:00 ص</t>
+  </si>
+  <si>
+    <t>EVA RFVFH05EX</t>
   </si>
   <si>
     <t>22/02/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>EVA  RFVHH09EX</t>
-  </si>
-  <si>
-    <t>06/04/2027 12:00:00 ص</t>
-  </si>
-  <si>
-    <t>EVA RFVFH05EX</t>
-  </si>
-  <si>
     <t>Testosterone Kit 25T iChroma Boditech</t>
   </si>
   <si>
@@ -462,9 +453,6 @@
     <t>18/02/2027 12:00:00 ص</t>
   </si>
   <si>
-    <t>EVA HCVFK12EX</t>
-  </si>
-  <si>
     <t>ASO kit 100T Agappe</t>
   </si>
   <si>
@@ -1737,9 +1725,6 @@
     <t>Vitamin D  Neo Kit 25T iChroma Boditech</t>
   </si>
   <si>
-    <t>EVA  VEVCB06E</t>
-  </si>
-  <si>
     <t>EVA  VEVDB07E</t>
   </si>
   <si>
@@ -1749,9 +1734,15 @@
     <t>EVA  VEVDB08E</t>
   </si>
   <si>
+    <t>EVA  VEVFC09E</t>
+  </si>
+  <si>
     <t>EVA VEVDB08E</t>
   </si>
   <si>
+    <t>EVA VEVFC09E</t>
+  </si>
+  <si>
     <t>C3 Kit 10T Mispa i3</t>
   </si>
   <si>
@@ -1992,15 +1983,6 @@
     <t>IGRA-TB Tube 8T iChroma Boditech</t>
   </si>
   <si>
-    <t>EVA TBTVDA40</t>
-  </si>
-  <si>
-    <t>EVA TBTVFA46</t>
-  </si>
-  <si>
-    <t>22/12/2026 12:00:00 ص</t>
-  </si>
-  <si>
     <t>EVA TBTVYA54</t>
   </si>
   <si>
@@ -2265,6 +2247,9 @@
     <t>PSA NeO Kit 25T iChroma Boditech</t>
   </si>
   <si>
+    <t>EVA  PSVGB12EX</t>
+  </si>
+  <si>
     <t>EVA PSVEB08EX</t>
   </si>
   <si>
@@ -2503,9 +2488,6 @@
   </si>
   <si>
     <t>Vitamin D  Cassette 25T hindering (WB)</t>
-  </si>
-  <si>
-    <t>EVA O00425070002</t>
   </si>
   <si>
     <t>EVA O00425100004</t>
@@ -3909,7 +3891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C590"/>
+  <dimension ref="A1:C586"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="30" customWidth="1"/>
@@ -3950,29 +3932,29 @@
     </row>
     <row r="4" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>15</v>
@@ -3983,95 +3965,95 @@
     </row>
     <row r="7" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>41</v>
@@ -4082,29 +4064,29 @@
     </row>
     <row r="16" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>49</v>
@@ -4115,178 +4097,178 @@
     </row>
     <row r="19" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="C19" s="5" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>63</v>
-      </c>
       <c r="C23" s="5" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>84</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="C33" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>87</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4297,73 +4279,73 @@
         <v>89</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4371,37 +4353,37 @@
         <v>106</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>110</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>112</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>114</v>
@@ -4412,7 +4394,7 @@
     </row>
     <row r="46" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>116</v>
@@ -4423,40 +4405,40 @@
     </row>
     <row r="47" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>120</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>125</v>
@@ -4467,18 +4449,18 @@
     </row>
     <row r="51" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>130</v>
@@ -4489,13 +4471,13 @@
     </row>
     <row r="53" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4506,12 +4488,12 @@
         <v>135</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>137</v>
@@ -4522,145 +4504,145 @@
     </row>
     <row r="56" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4668,164 +4650,164 @@
         <v>168</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>160</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>42</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>188</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>42</v>
+        <v>195</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>34</v>
+        <v>156</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -4833,626 +4815,626 @@
         <v>202</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>160</v>
+        <v>210</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>252</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>50</v>
+        <v>261</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>252</v>
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>263</v>
+        <v>0</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>265</v>
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>0</v>
+      <c r="C112" s="4" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C113" s="3" t="s">
-        <v>0</v>
+        <v>269</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>0</v>
+        <v>272</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>277</v>
+        <v>163</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>167</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>297</v>
+        <v>229</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>300</v>
+        <v>184</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>233</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>188</v>
+        <v>310</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>320</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>323</v>
+        <v>129</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>117</v>
+        <v>0</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C138" s="4" t="s">
-        <v>131</v>
+        <v>0</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>0</v>
+        <v>334</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5460,21 +5442,21 @@
         <v>333</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C141" s="3" t="s">
-        <v>0</v>
+        <v>331</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C142" s="4" t="s">
-        <v>336</v>
+        <v>0</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5485,67 +5467,67 @@
         <v>338</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>339</v>
+        <v>93</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C145" s="3" t="s">
-        <v>0</v>
+        <v>343</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>95</v>
+        <v>0</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C148" s="4" t="s">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>0</v>
@@ -5556,13 +5538,13 @@
     </row>
     <row r="150" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>351</v>
+        <v>36</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5570,340 +5552,340 @@
         <v>352</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C151" s="3" t="s">
-        <v>0</v>
+        <v>353</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C152" s="1" t="s">
-        <v>0</v>
+        <v>356</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>34</v>
+        <v>360</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>361</v>
+        <v>131</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>133</v>
+        <v>374</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>375</v>
+        <v>0</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>381</v>
+        <v>108</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>0</v>
+        <v>385</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>385</v>
+        <v>115</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>111</v>
+        <v>389</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B166" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B166" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="C166" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>117</v>
+        <v>393</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>403</v>
+        <v>67</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>408</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>66</v>
+        <v>327</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>389</v>
+        <v>418</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>331</v>
+        <v>419</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>422</v>
+        <v>383</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5911,76 +5893,76 @@
         <v>424</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>392</v>
+        <v>429</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>387</v>
+        <v>432</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>433</v>
+        <v>385</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>436</v>
+        <v>407</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>437</v>
+        <v>327</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>440</v>
+        <v>176</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -5988,7 +5970,7 @@
         <v>441</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="C189" s="5" t="s">
         <v>442</v>
@@ -5999,10 +5981,10 @@
         <v>443</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>331</v>
+        <v>153</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6010,32 +5992,32 @@
         <v>444</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>419</v>
+        <v>385</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>180</v>
+        <v>445</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>411</v>
+        <v>383</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>419</v>
+        <v>449</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>157</v>
+        <v>296</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6043,109 +6025,109 @@
         <v>448</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>450</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>449</v>
+        <v>416</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B196" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C196" s="4" t="s">
         <v>453</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>454</v>
+        <v>415</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>420</v>
+        <v>455</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>456</v>
+        <v>70</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>389</v>
+        <v>449</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>69</v>
+        <v>463</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>419</v>
+        <v>467</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6153,65 +6135,65 @@
         <v>466</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>472</v>
+        <v>44</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>476</v>
+        <v>108</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6219,98 +6201,98 @@
         <v>480</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>42</v>
+        <v>484</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>126</v>
+        <v>495</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="C216" s="4" t="s">
-        <v>496</v>
+        <v>0</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B217" s="3" t="s">
-        <v>498</v>
+        <v>383</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>499</v>
+        <v>75</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B218" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C218" s="4" t="s">
         <v>500</v>
-      </c>
-      <c r="C218" s="4" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6318,10 +6300,10 @@
         <v>501</v>
       </c>
       <c r="B219" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C219" s="3" t="s">
-        <v>0</v>
+        <v>407</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6329,65 +6311,65 @@
         <v>502</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>387</v>
+        <v>503</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>76</v>
+        <v>504</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B221" s="3" t="s">
-        <v>387</v>
+        <v>505</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>504</v>
+        <v>138</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="B222" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B222" s="1" t="s">
-        <v>411</v>
-      </c>
       <c r="C222" s="4" t="s">
-        <v>499</v>
+        <v>138</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>508</v>
+        <v>0</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>509</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="B225" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="B225" s="3" t="s">
-        <v>509</v>
-      </c>
       <c r="C225" s="5" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6395,153 +6377,153 @@
         <v>511</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>0</v>
+        <v>512</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>74</v>
+        <v>516</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>520</v>
+        <v>42</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>522</v>
+        <v>383</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>83</v>
+        <v>525</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>40</v>
+        <v>531</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>387</v>
+        <v>532</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>532</v>
+        <v>47</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="B237" s="3" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="C238" s="4" t="s">
-        <v>45</v>
+        <v>0</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>541</v>
+        <v>421</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6549,21 +6531,21 @@
         <v>542</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>544</v>
+        <v>371</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B241" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="B241" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C241" s="3" t="s">
-        <v>0</v>
+      <c r="C241" s="5" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="242" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6574,117 +6556,117 @@
         <v>547</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>425</v>
+        <v>548</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>548</v>
+        <v>415</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>375</v>
+        <v>550</v>
       </c>
     </row>
     <row r="244" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>549</v>
+        <v>415</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>131</v>
+        <v>550</v>
       </c>
     </row>
     <row r="245" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>552</v>
+        <v>179</v>
       </c>
     </row>
     <row r="246" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>419</v>
+        <v>555</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>554</v>
+        <v>195</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>419</v>
+        <v>556</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>554</v>
+        <v>201</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>183</v>
+        <v>559</v>
       </c>
     </row>
     <row r="249" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>199</v>
+        <v>562</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>205</v>
+        <v>115</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>563</v>
+        <v>105</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="253" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6692,131 +6674,131 @@
         <v>567</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>117</v>
+        <v>569</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>572</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>128</v>
+        <v>569</v>
       </c>
     </row>
     <row r="256" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>573</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>574</v>
+        <v>67</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>575</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>582</v>
+        <v>179</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>183</v>
+        <v>279</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B263" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>283</v>
+        <v>595</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -6824,257 +6806,257 @@
         <v>593</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>595</v>
+        <v>10</v>
       </c>
     </row>
     <row r="266" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="267" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B267" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C267" s="5" t="s">
         <v>599</v>
-      </c>
-      <c r="C267" s="5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B268" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B268" s="1" t="s">
-        <v>601</v>
-      </c>
       <c r="C268" s="4" t="s">
-        <v>602</v>
+        <v>393</v>
       </c>
     </row>
     <row r="269" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="270" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>397</v>
+        <v>90</v>
       </c>
     </row>
     <row r="271" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>606</v>
+        <v>347</v>
       </c>
     </row>
     <row r="272" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="273" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>351</v>
+        <v>273</v>
       </c>
     </row>
     <row r="274" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>28</v>
+        <v>613</v>
       </c>
     </row>
     <row r="275" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>277</v>
+        <v>413</v>
       </c>
     </row>
     <row r="276" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>616</v>
+        <v>423</v>
       </c>
     </row>
     <row r="277" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>417</v>
+        <v>475</v>
       </c>
     </row>
     <row r="278" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>427</v>
+        <v>621</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>479</v>
+        <v>117</v>
       </c>
     </row>
     <row r="280" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>624</v>
+        <v>90</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
     </row>
     <row r="282" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>628</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>92</v>
+        <v>629</v>
       </c>
     </row>
     <row r="283" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>66</v>
+        <v>408</v>
       </c>
     </row>
     <row r="284" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>632</v>
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B285" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>412</v>
+        <v>636</v>
       </c>
     </row>
     <row r="286" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>50</v>
+        <v>638</v>
       </c>
     </row>
     <row r="287" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>639</v>
+        <v>108</v>
       </c>
     </row>
     <row r="288" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>640</v>
@@ -7085,90 +7067,90 @@
     </row>
     <row r="289" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>642</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="290" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>643</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="291" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>111</v>
+        <v>298</v>
       </c>
     </row>
     <row r="292" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>646</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="293" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>302</v>
+        <v>189</v>
       </c>
     </row>
     <row r="294" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="295" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B295" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>193</v>
+        <v>655</v>
       </c>
     </row>
     <row r="296" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="297" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7176,10 +7158,10 @@
         <v>656</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>339</v>
+        <v>592</v>
       </c>
     </row>
     <row r="298" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7187,318 +7169,318 @@
         <v>656</v>
       </c>
       <c r="B298" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="C298" s="4" t="s">
         <v>658</v>
-      </c>
-      <c r="C298" s="4" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="299" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>661</v>
+        <v>126</v>
       </c>
     </row>
     <row r="300" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="301" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>595</v>
+        <v>667</v>
       </c>
     </row>
     <row r="302" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>664</v>
+        <v>504</v>
       </c>
     </row>
     <row r="303" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>128</v>
+        <v>652</v>
       </c>
     </row>
     <row r="304" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A304" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>508</v>
+        <v>678</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>655</v>
+        <v>681</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B309" s="3" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>684</v>
+        <v>489</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>690</v>
+        <v>207</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>493</v>
+        <v>699</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>211</v>
+        <v>705</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>702</v>
+        <v>445</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B319" s="3" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>708</v>
+        <v>489</v>
       </c>
     </row>
     <row r="320" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>711</v>
+        <v>54</v>
       </c>
     </row>
     <row r="321" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>449</v>
+        <v>716</v>
       </c>
     </row>
     <row r="322" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="323" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="B323" s="3" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>493</v>
+        <v>722</v>
       </c>
     </row>
     <row r="324" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="C324" s="4" t="s">
-        <v>53</v>
+        <v>0</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B325" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="C325" s="5" t="s">
-        <v>722</v>
+        <v>0</v>
+      </c>
+      <c r="C325" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="C326" s="4" t="s">
-        <v>725</v>
+        <v>0</v>
+      </c>
+      <c r="C326" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7509,29 +7491,29 @@
         <v>727</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>728</v>
+        <v>459</v>
       </c>
     </row>
     <row r="328" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B328" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="B328" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C328" s="1" t="s">
-        <v>0</v>
+      <c r="C328" s="4" t="s">
+        <v>730</v>
       </c>
     </row>
     <row r="329" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C329" s="3" t="s">
-        <v>0</v>
+        <v>732</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="330" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7539,120 +7521,120 @@
         <v>731</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>0</v>
+        <v>734</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>735</v>
       </c>
     </row>
     <row r="331" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>463</v>
+        <v>737</v>
       </c>
     </row>
     <row r="332" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A332" s="1" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="333" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>739</v>
+        <v>18</v>
       </c>
     </row>
     <row r="334" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="335" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="336" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A336" s="1" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>746</v>
+        <v>54</v>
       </c>
     </row>
     <row r="337" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="C337" s="5" t="s">
-        <v>749</v>
+        <v>0</v>
+      </c>
+      <c r="C337" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="C338" s="4" t="s">
-        <v>752</v>
+        <v>0</v>
+      </c>
+      <c r="C338" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="C339" s="5" t="s">
-        <v>53</v>
+        <v>0</v>
+      </c>
+      <c r="C339" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="C340" s="4" t="s">
         <v>755</v>
-      </c>
-      <c r="B340" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C340" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="341" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7671,98 +7653,98 @@
         <v>757</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C342" s="1" t="s">
-        <v>0</v>
+        <v>758</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>759</v>
       </c>
     </row>
     <row r="343" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="344" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C344" s="1" t="s">
-        <v>0</v>
+        <v>764</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="345" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="346" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>767</v>
+        <v>105</v>
       </c>
     </row>
     <row r="347" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C347" s="5" t="s">
-        <v>45</v>
+        <v>772</v>
       </c>
     </row>
     <row r="348" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="349" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C349" s="5" t="s">
-        <v>108</v>
+        <v>775</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="351" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7770,7 +7752,7 @@
         <v>778</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C351" s="5" t="s">
         <v>780</v>
@@ -7778,65 +7760,65 @@
     </row>
     <row r="352" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C353" s="5" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C355" s="5" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A356" s="1" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C357" s="5" t="s">
         <v>780</v>
@@ -7844,145 +7826,145 @@
     </row>
     <row r="358" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C359" s="5" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C361" s="5" t="s">
-        <v>780</v>
+        <v>802</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B362" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="C362" s="4" t="s">
         <v>802</v>
-      </c>
-      <c r="C362" s="4" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C363" s="5" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A364" s="1" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>807</v>
+        <v>775</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C365" s="5" t="s">
-        <v>807</v>
+        <v>775</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>811</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>780</v>
+        <v>812</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C367" s="5" t="s">
-        <v>780</v>
+        <v>802</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C369" s="5" t="s">
-        <v>817</v>
+        <v>775</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A370" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>819</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>807</v>
+        <v>780</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -7993,7 +7975,7 @@
         <v>821</v>
       </c>
       <c r="C371" s="5" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8009,299 +7991,299 @@
     </row>
     <row r="373" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C373" s="5" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A374" s="1" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C375" s="5" t="s">
-        <v>780</v>
+        <v>8</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A376" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>785</v>
+        <v>831</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C377" s="5" t="s">
-        <v>780</v>
+        <v>834</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A378" s="1" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>780</v>
+        <v>463</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C379" s="5" t="s">
-        <v>50</v>
+        <v>463</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A380" s="1" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>837</v>
+        <v>156</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C381" s="5" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A382" s="1" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>467</v>
+        <v>149</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="C383" s="5" t="s">
-        <v>467</v>
+        <v>847</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A384" s="1" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>160</v>
+        <v>850</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>847</v>
+        <v>852</v>
       </c>
       <c r="C385" s="5" t="s">
-        <v>848</v>
+        <v>121</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>153</v>
+        <v>855</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>852</v>
+        <v>857</v>
       </c>
       <c r="C387" s="5" t="s">
-        <v>853</v>
+        <v>858</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
-        <v>854</v>
+        <v>859</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>858</v>
+        <v>863</v>
       </c>
       <c r="C389" s="5" t="s">
-        <v>123</v>
+        <v>576</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
-        <v>859</v>
+        <v>864</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="C391" s="5" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>869</v>
+        <v>874</v>
       </c>
       <c r="C393" s="5" t="s">
-        <v>579</v>
+        <v>875</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
-        <v>870</v>
+        <v>876</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>871</v>
+        <v>877</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>872</v>
+        <v>878</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>873</v>
+        <v>879</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>874</v>
+        <v>880</v>
       </c>
       <c r="C395" s="5" t="s">
-        <v>875</v>
+        <v>881</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
-        <v>876</v>
+        <v>882</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>878</v>
+        <v>884</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>879</v>
+        <v>885</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="C397" s="5" t="s">
-        <v>881</v>
+        <v>0</v>
+      </c>
+      <c r="C397" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="C398" s="4" t="s">
-        <v>884</v>
+        <v>0</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="C399" s="5" t="s">
-        <v>887</v>
+        <v>0</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8309,208 +8291,208 @@
         <v>888</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>889</v>
-      </c>
-      <c r="C400" s="4" t="s">
-        <v>890</v>
+        <v>0</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C401" s="3" t="s">
-        <v>0</v>
+        <v>839</v>
+      </c>
+      <c r="C401" s="5" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A402" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C402" s="1" t="s">
-        <v>0</v>
+        <v>841</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>842</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C403" s="3" t="s">
-        <v>0</v>
+        <v>844</v>
+      </c>
+      <c r="C403" s="5" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A404" s="1" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C404" s="1" t="s">
-        <v>0</v>
+        <v>844</v>
+      </c>
+      <c r="C404" s="4" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C405" s="5" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A406" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B406" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="C406" s="4" t="s">
         <v>847</v>
-      </c>
-      <c r="C406" s="4" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="C407" s="5" t="s">
-        <v>153</v>
+        <v>847</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A408" s="1" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>153</v>
+        <v>847</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>850</v>
+        <v>898</v>
       </c>
       <c r="C409" s="5" t="s">
-        <v>153</v>
+        <v>425</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A410" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>852</v>
+        <v>898</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>853</v>
+        <v>425</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B411" s="3" t="s">
         <v>901</v>
       </c>
-      <c r="B411" s="3" t="s">
-        <v>852</v>
-      </c>
       <c r="C411" s="5" t="s">
-        <v>853</v>
+        <v>902</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>852</v>
+        <v>904</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>853</v>
+        <v>548</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>904</v>
+        <v>849</v>
       </c>
       <c r="C413" s="5" t="s">
-        <v>429</v>
+        <v>850</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A414" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>904</v>
+        <v>852</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>429</v>
+        <v>121</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>907</v>
+        <v>852</v>
       </c>
       <c r="C415" s="5" t="s">
-        <v>908</v>
+        <v>121</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A416" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>910</v>
+        <v>852</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>552</v>
+        <v>121</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="B417" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="C417" s="5" t="s">
         <v>855</v>
-      </c>
-      <c r="C417" s="5" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="C418" s="4" t="s">
         <v>912</v>
-      </c>
-      <c r="B418" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="C418" s="4" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8518,43 +8500,43 @@
         <v>913</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>858</v>
+        <v>914</v>
       </c>
       <c r="C419" s="5" t="s">
-        <v>123</v>
+        <v>915</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B420" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="C420" s="4" t="s">
         <v>858</v>
-      </c>
-      <c r="C420" s="4" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C421" s="5" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>917</v>
+        <v>857</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>918</v>
+        <v>858</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8562,87 +8544,87 @@
         <v>919</v>
       </c>
       <c r="B423" s="3" t="s">
-        <v>920</v>
+        <v>860</v>
       </c>
       <c r="C423" s="5" t="s">
-        <v>921</v>
+        <v>861</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C425" s="5" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A426" s="1" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>863</v>
+        <v>923</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>864</v>
+        <v>576</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="B427" s="3" t="s">
-        <v>866</v>
+        <v>924</v>
       </c>
       <c r="C427" s="5" t="s">
-        <v>867</v>
+        <v>576</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="B428" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="B428" s="1" t="s">
+      <c r="C428" s="4" t="s">
         <v>866</v>
-      </c>
-      <c r="C428" s="4" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B429" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="C429" s="5" t="s">
         <v>866</v>
-      </c>
-      <c r="C429" s="5" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A430" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>929</v>
+        <v>863</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8650,76 +8632,76 @@
         <v>928</v>
       </c>
       <c r="B431" s="3" t="s">
-        <v>930</v>
+        <v>874</v>
       </c>
       <c r="C431" s="5" t="s">
-        <v>579</v>
+        <v>875</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>932</v>
+        <v>874</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="433" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B433" s="3" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
     </row>
     <row r="434" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A434" s="1" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>579</v>
+        <v>872</v>
       </c>
     </row>
     <row r="435" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="C435" s="5" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
     </row>
     <row r="436" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A436" s="1" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
     </row>
     <row r="437" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="C437" s="5" t="s">
         <v>936</v>
-      </c>
-      <c r="B437" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="C437" s="5" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="438" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8727,10 +8709,10 @@
         <v>937</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>877</v>
+        <v>935</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>878</v>
+        <v>936</v>
       </c>
     </row>
     <row r="439" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8738,10 +8720,10 @@
         <v>938</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="C439" s="5" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
     </row>
     <row r="440" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8749,10 +8731,10 @@
         <v>939</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
     </row>
     <row r="441" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8760,21 +8742,21 @@
         <v>940</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>941</v>
+        <v>868</v>
       </c>
       <c r="C441" s="5" t="s">
-        <v>942</v>
+        <v>869</v>
       </c>
     </row>
     <row r="442" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="C442" s="4" t="s">
         <v>943</v>
-      </c>
-      <c r="B442" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="C442" s="4" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="443" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8782,10 +8764,10 @@
         <v>944</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>874</v>
+        <v>942</v>
       </c>
       <c r="C443" s="5" t="s">
-        <v>875</v>
+        <v>943</v>
       </c>
     </row>
     <row r="444" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8793,10 +8775,10 @@
         <v>945</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>874</v>
+        <v>942</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>875</v>
+        <v>943</v>
       </c>
     </row>
     <row r="445" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8804,10 +8786,10 @@
         <v>946</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="C445" s="5" t="s">
-        <v>875</v>
+        <v>0</v>
+      </c>
+      <c r="C445" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="446" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8826,87 +8808,87 @@
         <v>950</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="C447" s="5" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
     </row>
     <row r="448" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="B448" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="B448" s="1" t="s">
-        <v>948</v>
-      </c>
       <c r="C448" s="4" t="s">
-        <v>949</v>
+        <v>347</v>
       </c>
     </row>
     <row r="449" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C449" s="3" t="s">
-        <v>0</v>
+        <v>955</v>
+      </c>
+      <c r="C449" s="5" t="s">
+        <v>842</v>
       </c>
     </row>
     <row r="450" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A450" s="1" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>955</v>
+        <v>163</v>
       </c>
     </row>
     <row r="451" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B451" s="3" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C451" s="5" t="s">
-        <v>958</v>
+        <v>296</v>
       </c>
     </row>
     <row r="452" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
     </row>
     <row r="453" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C453" s="5" t="s">
-        <v>848</v>
+        <v>587</v>
       </c>
     </row>
     <row r="454" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A454" s="1" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>167</v>
+        <v>966</v>
       </c>
     </row>
     <row r="455" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -8914,109 +8896,109 @@
         <v>964</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C455" s="5" t="s">
-        <v>300</v>
+        <v>968</v>
       </c>
     </row>
     <row r="456" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>375</v>
+        <v>968</v>
       </c>
     </row>
     <row r="457" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="B457" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="C457" s="5" t="s">
         <v>968</v>
-      </c>
-      <c r="B457" s="3" t="s">
-        <v>969</v>
-      </c>
-      <c r="C457" s="5" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="458" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B458" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="B458" s="1" t="s">
-        <v>971</v>
-      </c>
       <c r="C458" s="4" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
     </row>
     <row r="459" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>973</v>
+        <v>942</v>
       </c>
       <c r="C459" s="5" t="s">
-        <v>974</v>
+        <v>943</v>
       </c>
     </row>
     <row r="460" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>976</v>
+        <v>860</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>974</v>
+        <v>861</v>
       </c>
     </row>
     <row r="461" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>976</v>
+        <v>860</v>
       </c>
       <c r="C461" s="5" t="s">
-        <v>974</v>
+        <v>861</v>
       </c>
     </row>
     <row r="462" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>976</v>
+        <v>860</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>974</v>
+        <v>861</v>
       </c>
     </row>
     <row r="463" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>948</v>
+        <v>860</v>
       </c>
       <c r="C463" s="5" t="s">
-        <v>949</v>
+        <v>861</v>
       </c>
     </row>
     <row r="464" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B464" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="C464" s="4" t="s">
         <v>980</v>
-      </c>
-      <c r="B464" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="C464" s="4" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="465" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9024,54 +9006,54 @@
         <v>981</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>866</v>
+        <v>982</v>
       </c>
       <c r="C465" s="5" t="s">
-        <v>867</v>
+        <v>980</v>
       </c>
     </row>
     <row r="466" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A466" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B466" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="B466" s="1" t="s">
-        <v>866</v>
-      </c>
       <c r="C466" s="4" t="s">
-        <v>867</v>
+        <v>980</v>
       </c>
     </row>
     <row r="467" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A467" s="3" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B467" s="3" t="s">
-        <v>866</v>
+        <v>982</v>
       </c>
       <c r="C467" s="5" t="s">
-        <v>867</v>
+        <v>980</v>
       </c>
     </row>
     <row r="468" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A468" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="469" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="B469" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="C469" s="5" t="s">
         <v>987</v>
-      </c>
-      <c r="B469" s="3" t="s">
-        <v>988</v>
-      </c>
-      <c r="C469" s="5" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="470" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9079,10 +9061,10 @@
         <v>989</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="471" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9090,10 +9072,10 @@
         <v>990</v>
       </c>
       <c r="B471" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="C471" s="5" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="472" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9321,54 +9303,54 @@
         <v>1021</v>
       </c>
       <c r="B492" s="1" t="s">
-        <v>1022</v>
+        <v>935</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>1023</v>
+        <v>936</v>
       </c>
     </row>
     <row r="493" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="B493" s="3" t="s">
-        <v>1022</v>
+        <v>935</v>
       </c>
       <c r="C493" s="5" t="s">
-        <v>1023</v>
+        <v>936</v>
       </c>
     </row>
     <row r="494" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B494" s="1" t="s">
-        <v>1022</v>
+        <v>935</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>1023</v>
+        <v>936</v>
       </c>
     </row>
     <row r="495" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B495" s="3" t="s">
-        <v>1022</v>
+        <v>935</v>
       </c>
       <c r="C495" s="5" t="s">
-        <v>1023</v>
+        <v>936</v>
       </c>
     </row>
     <row r="496" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B496" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C496" s="4" t="s">
         <v>1027</v>
-      </c>
-      <c r="B496" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="C496" s="4" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="497" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9376,10 +9358,10 @@
         <v>1028</v>
       </c>
       <c r="B497" s="3" t="s">
-        <v>941</v>
+        <v>1026</v>
       </c>
       <c r="C497" s="5" t="s">
-        <v>942</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="498" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9387,10 +9369,10 @@
         <v>1029</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>941</v>
+        <v>1026</v>
       </c>
       <c r="C498" s="4" t="s">
-        <v>942</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="499" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9398,10 +9380,10 @@
         <v>1030</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>941</v>
+        <v>1026</v>
       </c>
       <c r="C499" s="5" t="s">
-        <v>942</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="500" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9409,164 +9391,164 @@
         <v>1031</v>
       </c>
       <c r="B500" s="1" t="s">
-        <v>1032</v>
+        <v>846</v>
       </c>
       <c r="C500" s="4" t="s">
-        <v>1033</v>
+        <v>847</v>
       </c>
     </row>
     <row r="501" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>1032</v>
+        <v>846</v>
       </c>
       <c r="C501" s="5" t="s">
-        <v>1033</v>
+        <v>847</v>
       </c>
     </row>
     <row r="502" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A502" s="1" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B502" s="1" t="s">
-        <v>1032</v>
+        <v>846</v>
       </c>
       <c r="C502" s="4" t="s">
-        <v>1033</v>
+        <v>847</v>
       </c>
     </row>
     <row r="503" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="B503" s="3" t="s">
-        <v>1032</v>
+        <v>846</v>
       </c>
       <c r="C503" s="5" t="s">
-        <v>1033</v>
+        <v>847</v>
       </c>
     </row>
     <row r="504" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A504" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B504" s="1" t="s">
-        <v>852</v>
+        <v>898</v>
       </c>
       <c r="C504" s="4" t="s">
-        <v>853</v>
+        <v>425</v>
       </c>
     </row>
     <row r="505" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>852</v>
+        <v>898</v>
       </c>
       <c r="C505" s="5" t="s">
-        <v>853</v>
+        <v>425</v>
       </c>
     </row>
     <row r="506" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B506" s="1" t="s">
-        <v>852</v>
+        <v>898</v>
       </c>
       <c r="C506" s="4" t="s">
-        <v>853</v>
+        <v>425</v>
       </c>
     </row>
     <row r="507" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="B507" s="3" t="s">
-        <v>852</v>
+        <v>898</v>
       </c>
       <c r="C507" s="5" t="s">
-        <v>853</v>
+        <v>425</v>
       </c>
     </row>
     <row r="508" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A508" s="1" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B508" s="1" t="s">
-        <v>904</v>
+        <v>998</v>
       </c>
       <c r="C508" s="4" t="s">
-        <v>429</v>
+        <v>999</v>
       </c>
     </row>
     <row r="509" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B509" s="3" t="s">
-        <v>904</v>
+        <v>998</v>
       </c>
       <c r="C509" s="5" t="s">
-        <v>429</v>
+        <v>999</v>
       </c>
     </row>
     <row r="510" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A510" s="1" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B510" s="1" t="s">
-        <v>904</v>
+        <v>844</v>
       </c>
       <c r="C510" s="4" t="s">
-        <v>429</v>
+        <v>149</v>
       </c>
     </row>
     <row r="511" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="B511" s="3" t="s">
-        <v>904</v>
+        <v>844</v>
       </c>
       <c r="C511" s="5" t="s">
-        <v>429</v>
+        <v>149</v>
       </c>
     </row>
     <row r="512" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B512" s="1" t="s">
-        <v>1004</v>
+        <v>844</v>
       </c>
       <c r="C512" s="4" t="s">
-        <v>1005</v>
+        <v>149</v>
       </c>
     </row>
     <row r="513" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B513" s="3" t="s">
-        <v>1004</v>
+        <v>844</v>
       </c>
       <c r="C513" s="5" t="s">
-        <v>1005</v>
+        <v>149</v>
       </c>
     </row>
     <row r="514" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B514" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C514" s="4" t="s">
         <v>1047</v>
-      </c>
-      <c r="B514" s="1" t="s">
-        <v>850</v>
-      </c>
-      <c r="C514" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="515" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9574,10 +9556,10 @@
         <v>1048</v>
       </c>
       <c r="B515" s="3" t="s">
-        <v>850</v>
+        <v>1046</v>
       </c>
       <c r="C515" s="5" t="s">
-        <v>153</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="516" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9585,10 +9567,10 @@
         <v>1049</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>850</v>
+        <v>1046</v>
       </c>
       <c r="C516" s="4" t="s">
-        <v>153</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="517" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9596,10 +9578,10 @@
         <v>1050</v>
       </c>
       <c r="B517" s="3" t="s">
-        <v>850</v>
+        <v>1046</v>
       </c>
       <c r="C517" s="5" t="s">
-        <v>153</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="518" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9607,43 +9589,43 @@
         <v>1051</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>1052</v>
+        <v>992</v>
       </c>
       <c r="C518" s="4" t="s">
-        <v>1053</v>
+        <v>993</v>
       </c>
     </row>
     <row r="519" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B519" s="3" t="s">
-        <v>1052</v>
+        <v>992</v>
       </c>
       <c r="C519" s="5" t="s">
-        <v>1053</v>
+        <v>993</v>
       </c>
     </row>
     <row r="520" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A520" s="1" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B520" s="1" t="s">
-        <v>1052</v>
+        <v>992</v>
       </c>
       <c r="C520" s="4" t="s">
-        <v>1053</v>
+        <v>993</v>
       </c>
     </row>
     <row r="521" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B521" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C521" s="5" t="s">
         <v>1056</v>
-      </c>
-      <c r="B521" s="3" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C521" s="5" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="522" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9651,10 +9633,10 @@
         <v>1057</v>
       </c>
       <c r="B522" s="1" t="s">
-        <v>998</v>
+        <v>1055</v>
       </c>
       <c r="C522" s="4" t="s">
-        <v>999</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="523" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9662,10 +9644,10 @@
         <v>1058</v>
       </c>
       <c r="B523" s="3" t="s">
-        <v>998</v>
+        <v>1055</v>
       </c>
       <c r="C523" s="5" t="s">
-        <v>999</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="524" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9673,10 +9655,10 @@
         <v>1059</v>
       </c>
       <c r="B524" s="1" t="s">
-        <v>998</v>
+        <v>1055</v>
       </c>
       <c r="C524" s="4" t="s">
-        <v>999</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="525" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9684,120 +9666,120 @@
         <v>1060</v>
       </c>
       <c r="B525" s="3" t="s">
-        <v>1061</v>
+        <v>1026</v>
       </c>
       <c r="C525" s="5" t="s">
-        <v>1062</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="526" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B526" s="1" t="s">
-        <v>1061</v>
+        <v>1026</v>
       </c>
       <c r="C526" s="4" t="s">
-        <v>1062</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="527" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B527" s="3" t="s">
-        <v>1061</v>
+        <v>1026</v>
       </c>
       <c r="C527" s="5" t="s">
-        <v>1062</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="528" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B528" s="1" t="s">
-        <v>1061</v>
+        <v>1026</v>
       </c>
       <c r="C528" s="4" t="s">
-        <v>1062</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="529" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B529" s="3" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C529" s="5" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="530" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A530" s="1" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B530" s="1" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C530" s="4" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="531" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B531" s="3" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C531" s="5" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="532" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B532" s="1" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C532" s="4" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="533" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B533" s="3" t="s">
-        <v>1032</v>
+        <v>1069</v>
       </c>
       <c r="C533" s="5" t="s">
-        <v>1033</v>
+        <v>719</v>
       </c>
     </row>
     <row r="534" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B534" s="1" t="s">
-        <v>1032</v>
+        <v>1069</v>
       </c>
       <c r="C534" s="4" t="s">
-        <v>1033</v>
+        <v>719</v>
       </c>
     </row>
     <row r="535" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B535" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C535" s="5" t="s">
         <v>1072</v>
-      </c>
-      <c r="B535" s="3" t="s">
-        <v>1032</v>
-      </c>
-      <c r="C535" s="5" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="536" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9805,10 +9787,10 @@
         <v>1073</v>
       </c>
       <c r="B536" s="1" t="s">
-        <v>1032</v>
+        <v>951</v>
       </c>
       <c r="C536" s="4" t="s">
-        <v>1033</v>
+        <v>447</v>
       </c>
     </row>
     <row r="537" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9816,32 +9798,32 @@
         <v>1074</v>
       </c>
       <c r="B537" s="3" t="s">
-        <v>1075</v>
+        <v>992</v>
       </c>
       <c r="C537" s="5" t="s">
-        <v>725</v>
+        <v>993</v>
       </c>
     </row>
     <row r="538" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B538" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="B538" s="1" t="s">
-        <v>1075</v>
-      </c>
       <c r="C538" s="4" t="s">
-        <v>725</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="539" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B539" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="C539" s="5" t="s">
-        <v>1078</v>
+        <v>0</v>
+      </c>
+      <c r="C539" s="3" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="540" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9849,10 +9831,10 @@
         <v>1079</v>
       </c>
       <c r="B540" s="1" t="s">
-        <v>957</v>
-      </c>
-      <c r="C540" s="4" t="s">
-        <v>451</v>
+        <v>0</v>
+      </c>
+      <c r="C540" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="541" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
@@ -9860,521 +9842,477 @@
         <v>1080</v>
       </c>
       <c r="B541" s="3" t="s">
-        <v>998</v>
+        <v>1081</v>
       </c>
       <c r="C541" s="5" t="s">
-        <v>999</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="542" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A542" s="1" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B542" s="1" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C542" s="4" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="543" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B543" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C543" s="3" t="s">
-        <v>0</v>
+        <v>1087</v>
+      </c>
+      <c r="C543" s="5" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="544" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A544" s="1" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="B544" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C544" s="1" t="s">
-        <v>0</v>
+        <v>1089</v>
+      </c>
+      <c r="C544" s="4" t="s">
+        <v>1090</v>
       </c>
     </row>
     <row r="545" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="B545" s="3" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
       <c r="C545" s="5" t="s">
-        <v>1088</v>
+        <v>186</v>
       </c>
     </row>
     <row r="546" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A546" s="1" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="B546" s="1" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>1091</v>
+        <v>99</v>
       </c>
     </row>
     <row r="547" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="B547" s="3" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="C547" s="5" t="s">
-        <v>157</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="548" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="B548" s="1" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="C548" s="4" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="549" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="B549" s="3" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="C549" s="5" t="s">
-        <v>190</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="550" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A550" s="1" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B550" s="1" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="C550" s="4" t="s">
-        <v>102</v>
+        <v>408</v>
       </c>
     </row>
     <row r="551" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="B551" s="3" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="C551" s="5" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="552" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B552" s="1" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="C552" s="4" t="s">
-        <v>1106</v>
+        <v>878</v>
       </c>
     </row>
     <row r="553" spans="1:3" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="B553" s="3" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="C553" s="5" t="s">
-        <v>1109</v>
+        <v>1